--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -413,299 +413,236 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Bitkub</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ave. daily vol. (THB)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Binance TH</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ave. daily vol. (THB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>THB_USDT</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>354658771.72</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>USDTTHB</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>298158638.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>THB_BTC</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>69595143.01000001</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BTCTHB</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>54634259.87466</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>THB_ETH</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>14733990.67</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VELOTHB</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1566785.1844</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>THB_KUB</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8652846.640000001</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>XRPTHB</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>530097.1267</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>THB_XRP</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8554651.029999999</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ETHTHB</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>365463.454</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Exchange</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Volume (THB)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Price (THB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-08-14 16:39:06</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Binance TH</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>THB_USDT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>THB_BTC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>THB_BTC 7d-Avg</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>THB_ETH</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>THB_KUB</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>THB_XRP</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>USDTTHB</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>502390836.85</v>
-      </c>
-      <c r="F2" t="n">
-        <v>33.11</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-14 16:39:06</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Binance TH</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>BTCTHB</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>63050072.75102</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2078248</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-14 16:39:06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Binance TH</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BTCTHB 7d-Avg</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>VELOTHB</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>1963361.639</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1086</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-14 16:39:06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Binance TH</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>XRPTHB</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>734427.0186</v>
-      </c>
-      <c r="F5" t="n">
-        <v>33.22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-14 16:39:06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Binance TH</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>SOLTHB</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>375017.7144</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2506.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-14 16:39:06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bitkub</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>THB_USDT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>393600320.76</v>
-      </c>
-      <c r="F7" t="n">
-        <v>33.11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-08-14 16:39:06</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bitkub</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>THB_BTC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>139379317.8</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2078284.52</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-08-14 16:39:06</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bitkub</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>THB_ETH</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>27173995.54</v>
-      </c>
-      <c r="F9" t="n">
-        <v>62000.05</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-08-14 16:39:06</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Bitkub</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>THB_XRP</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>12035607.92</v>
-      </c>
-      <c r="F10" t="n">
-        <v>33.18</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-08-14 16:39:06</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Bitkub</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>THB_USDC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>7456966.86</v>
-      </c>
-      <c r="F11" t="n">
-        <v>33.11</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ETHTHB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2082634.88</v>
+      </c>
+      <c r="E14" t="n">
+        <v>62175.42</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="G14" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="H14" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2082026</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="L14" t="n">
+        <v>33.09</v>
+      </c>
+      <c r="M14" t="n">
+        <v>62201</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -46,8 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,16 +448,16 @@
           <t>THB_USDT</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>354658771.72</v>
+      <c r="C2" s="1" t="n">
+        <v>353708238.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>USDTTHB</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>298158638.7</v>
+      <c r="E2" s="1" t="n">
+        <v>295567718.67</v>
       </c>
     </row>
     <row r="3">
@@ -468,16 +469,16 @@
           <t>THB_BTC</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>69595143.01000001</v>
+      <c r="C3" s="1" t="n">
+        <v>69559195.08</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>BTCTHB</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>54634259.87466</v>
+      <c r="E3" s="1" t="n">
+        <v>54186128.94003</v>
       </c>
     </row>
     <row r="4">
@@ -489,16 +490,16 @@
           <t>THB_ETH</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>14733990.67</v>
+      <c r="C4" s="1" t="n">
+        <v>14751066.16</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>VELOTHB</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>1566785.1844</v>
+      <c r="E4" s="1" t="n">
+        <v>1564635.1658</v>
       </c>
     </row>
     <row r="5">
@@ -510,16 +511,16 @@
           <t>THB_KUB</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>8652846.640000001</v>
+      <c r="C5" s="1" t="n">
+        <v>8683443.720000001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>XRPTHB</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>530097.1267</v>
+      <c r="E5" s="1" t="n">
+        <v>685073.3212</v>
       </c>
     </row>
     <row r="6">
@@ -531,15 +532,15 @@
           <t>THB_XRP</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>8554651.029999999</v>
+      <c r="C6" s="1" t="n">
+        <v>8611087.689999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>ETHTHB</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="1" t="n">
         <v>365463.454</v>
       </c>
     </row>
@@ -614,34 +615,34 @@
       <c r="A14" t="n">
         <v>16</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="1" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>2082299.99</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>62181.42</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>33.06</v>
       </c>
-      <c r="C14" t="n">
-        <v>2082634.88</v>
-      </c>
-      <c r="E14" t="n">
-        <v>62175.42</v>
-      </c>
-      <c r="F14" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="H14" s="1" t="n">
         <v>33.06</v>
       </c>
-      <c r="H14" t="n">
-        <v>33.05</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2082026</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.1015</v>
-      </c>
-      <c r="L14" t="n">
-        <v>33.09</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="I14" s="1" t="n">
+        <v>2082425</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="M14" s="1" t="n">
         <v>62201</v>
       </c>
     </row>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>353708238.6</v>
+        <v>555935973.22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>295567718.67</v>
+        <v>349253017.36</v>
       </c>
     </row>
     <row r="3">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>69559195.08</v>
+        <v>83947187.86</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>54186128.94003</v>
+        <v>55147671.45308</v>
       </c>
     </row>
     <row r="4">
@@ -491,15 +491,15 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>14751066.16</v>
+        <v>33938402.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VELOTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1564635.1658</v>
+        <v>1214584.6106</v>
       </c>
     </row>
     <row r="5">
@@ -508,19 +508,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THB_KUB</t>
+          <t>THB_XRP</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>8683443.720000001</v>
+        <v>15978823.17</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>VELOTHB</t>
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>685073.3212</v>
+        <v>1133712.6956</v>
       </c>
     </row>
     <row r="6">
@@ -529,19 +529,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_XRP</t>
+          <t>THB_KUB</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>8611087.689999999</v>
+        <v>8714676.98</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>365463.454</v>
+        <v>1100220.0746</v>
       </c>
     </row>
     <row r="13">
@@ -572,14 +572,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>THB_XRP</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>THB_KUB</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>THB_XRP</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>USDTTHB</t>
@@ -597,53 +597,53 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>ETHTHB</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>VELOTHB</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>XRPTHB</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>ETHTHB</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>33.07</v>
+        <v>555935973.22</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>2082299.99</v>
+        <v>83947187.86</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>62181.42</v>
+        <v>33938402.4</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>15.61</v>
+        <v>15978823.17</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>33.06</v>
+        <v>8714676.98</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>33.06</v>
+        <v>349253017.36</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>2082425</v>
+        <v>55147671.45308</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>0.1018</v>
+        <v>1214584.6106</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>33.08</v>
+        <v>1133712.6956</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>62201</v>
+        <v>1100220.0746</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:GQ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,26 @@
           <t>Ave. daily vol. (THB)</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bitkub</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Ave. daily vol. (THB)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Binance TH</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Ave. daily vol. (THB)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,7 +469,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>555935973.22</v>
+        <v>558774049.83</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -457,7 +477,23 @@
         </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>349253017.36</v>
+        <v>349792699.51</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>THB_USDT</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>558763983.42</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>USDTTHB</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>349792699.51</v>
       </c>
     </row>
     <row r="3">
@@ -470,7 +506,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>83947187.86</v>
+        <v>84235751.65000001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -478,7 +514,23 @@
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>55147671.45308</v>
+        <v>55889180.66205</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>THB_BTC</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>84235751.65000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BTCTHB</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>55889180.66205</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +543,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>33938402.4</v>
+        <v>33819519.53</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -499,7 +551,23 @@
         </is>
       </c>
       <c r="E4" s="1" t="n">
-        <v>1214584.6106</v>
+        <v>1234378.8297</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>THB_ETH</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>33822631.66</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ETHTHB</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1234378.8297</v>
       </c>
     </row>
     <row r="5">
@@ -512,7 +580,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>15978823.17</v>
+        <v>16206221.05</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -520,7 +588,23 @@
         </is>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1133712.6956</v>
+        <v>1125889.5078</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>THB_XRP</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>16206221.05</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>VELOTHB</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>1125889.5078</v>
       </c>
     </row>
     <row r="6">
@@ -533,7 +617,7 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>8714676.98</v>
+        <v>8641198.48</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -541,7 +625,23 @@
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1100220.0746</v>
+        <v>1093867.338</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>THB_KUB</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>8641198.48</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>XRPTHB</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>1093867.338</v>
       </c>
     </row>
     <row r="13">
@@ -580,32 +680,32 @@
           <t>THB_KUB</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>USDTTHB</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>BTCTHB</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>BTCTHB 7d-Avg</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>ETHTHB</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>VELOTHB</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>XRPTHB</t>
         </is>
@@ -616,34 +716,69 @@
         <v>17</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>555935973.22</v>
+        <v>558763983.42</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>83947187.86</v>
+        <v>84235751.65000001</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>33938402.4</v>
+        <v>33822631.66</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>15978823.17</v>
+        <v>16206221.05</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>8714676.98</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>349253017.36</v>
+        <v>8641198.48</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>55147671.45308</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>1214584.6106</v>
+        <v>349792699.51</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>55889180.66205</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1133712.6956</v>
+        <v>1234378.8297</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>1100220.0746</v>
+        <v>1125889.5078</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>1093867.338</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>558774049.83</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>84235751.65000001</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>33819519.53</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>16206221.05</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>8641198.48</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>349792699.51</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>55889180.66205</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>1234378.8297</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>1125889.5078</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>1093867.338</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GQ15"/>
+  <dimension ref="A1:BXW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,37 +425,37 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Ave. daily vol. (THB)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+          <t>Ave. daily vol.</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Binance TH</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Ave. daily vol. (THB)</t>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Ave. daily vol.</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Bitkub</t>
+          <t>Orbix</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Ave. daily vol. (THB)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Binance TH</t>
+          <t>Ave. daily vol.</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Ave. daily vol. (THB)</t>
+          <t>InnovestX</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Ave. daily vol.</t>
         </is>
       </c>
     </row>
@@ -469,31 +469,23 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>558774049.83</v>
-      </c>
-      <c r="D2" t="inlineStr">
+        <v>551045348.6900001</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>USDTTHB</t>
         </is>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>349792699.51</v>
+      <c r="F2" s="1" t="n">
+        <v>509829468.19</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>THB_USDT</t>
+          <t>ETH_THB</t>
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>558763983.42</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>USDTTHB</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>349792699.51</v>
+        <v>10983319.22900662</v>
       </c>
     </row>
     <row r="3">
@@ -506,31 +498,23 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>84235751.65000001</v>
-      </c>
-      <c r="D3" t="inlineStr">
+        <v>220476615.52</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>BTCTHB</t>
         </is>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>55889180.66205</v>
+      <c r="F3" s="1" t="n">
+        <v>64769141.71668</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>THB_BTC</t>
+          <t>BTC_THB</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>84235751.65000001</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>BTCTHB</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>55889180.66205</v>
+        <v>6432562.173783358</v>
       </c>
     </row>
     <row r="4">
@@ -539,35 +523,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THB_ETH</t>
+          <t>THB_XRP</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>33819519.53</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ETHTHB</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>1234378.8297</v>
+        <v>93178984.48</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>XRPTHB</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>10480182.4452</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>THB_ETH</t>
+          <t>USDT_THB</t>
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>33822631.66</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ETHTHB</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>1234378.8297</v>
+        <v>2870747.687850092</v>
       </c>
     </row>
     <row r="5">
@@ -576,35 +552,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THB_XRP</t>
+          <t>THB_ETH</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>16206221.05</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VELOTHB</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>1125889.5078</v>
+        <v>90275120.17</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ETHTHB</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>6117432.4433</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>THB_XRP</t>
+          <t>SOL_THB</t>
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>16206221.05</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>VELOTHB</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>1125889.5078</v>
+        <v>415382.6845121348</v>
       </c>
     </row>
     <row r="6">
@@ -613,35 +581,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_KUB</t>
+          <t>THB_DOGE</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>8641198.48</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>XRPTHB</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>1093867.338</v>
+        <v>44989755.94</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SOLTHB</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1970255.447</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>THB_KUB</t>
+          <t>XRP_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>8641198.48</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>XRPTHB</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>1093867.338</v>
+        <v>386869.6463569931</v>
       </c>
     </row>
     <row r="13">
@@ -667,118 +627,4464 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>THB_XRP</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>THB_ETH</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>THB_XRP</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>THB_DOGE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>THB_SOL</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>THB_XLM</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>THB_LUNA</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>THB_ADA</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>THB_NEAR</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>THB_USDC</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>THB_XAUT</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>THB_KUB</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>THB_BSB</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>THB_LM</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>THB_AGI</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>THB_BICO</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>THB_CRV</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>THB_BNB</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>THB_GALA</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>THB_CATI</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>THB_BONK</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>THB_SYND</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>THB_WLD</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>THB_OP</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>THB_MOVR</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>THB_TRUMP</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>THB_LIT</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>THB_HYPE</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>THB_PORTAL</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>THB_SIX</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>THB_PENGU</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>THB_SCRT</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>THB_EPIC</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>THB_PUMP</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>THB_ENA</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>THB_BMT</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>THB_HBAR</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>THB_ASTER</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>THB_JFIN</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>THB_MKR</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>THB_SUI</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>THB_PEPE</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>THB_VELO</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>THB_STO</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>THB_POL</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>THB_SQD</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>THB_UNI</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>THB_TAO</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>THB_CHIP</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>THB_SPX</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>THB_MAVIA</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>THB_LINK</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>THB_AVL</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>THB_BCH</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>THB_TRX</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>THB_G</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>THB_CTXC</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>THB_ZEREBRO</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>THB_NOM</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>THB_JASMY</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>THB_ONDO</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>THB_SWELL</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>THB_RNDR</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>THB_ALCH</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>THB_DOT</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>THB_IOST</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>THB_ZIL</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>THB_EIGEN</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>THB_TON</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>THB_GPS</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>THB_PLN</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>THB_OBT</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>THB_BLU</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>THB_MBX</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>THB_SD</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>THB_BR</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>THB_HEMI</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>THB_FHE</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>THB_VVV</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>THB_BEAM</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>THB_PUFFR</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>THB_GRASS</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>THB_SHIB</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>THB_MPLX</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>THB_TRIA</t>
+        </is>
+      </c>
+      <c r="CK13" t="inlineStr">
+        <is>
+          <t>THB_STG</t>
+        </is>
+      </c>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>THB_AVAX</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>THB_ZAMA</t>
+        </is>
+      </c>
+      <c r="CN13" t="inlineStr">
+        <is>
+          <t>THB_ZRC</t>
+        </is>
+      </c>
+      <c r="CO13" t="inlineStr">
+        <is>
+          <t>THB_ORDER</t>
+        </is>
+      </c>
+      <c r="CP13" t="inlineStr">
+        <is>
+          <t>THB_HFT</t>
+        </is>
+      </c>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>THB_DMC</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>THB_ARB</t>
+        </is>
+      </c>
+      <c r="CS13" t="inlineStr">
+        <is>
+          <t>THB_AAVE</t>
+        </is>
+      </c>
+      <c r="CT13" t="inlineStr">
+        <is>
+          <t>THB_ALPHA</t>
+        </is>
+      </c>
+      <c r="CU13" t="inlineStr">
+        <is>
+          <t>THB_HUMA</t>
+        </is>
+      </c>
+      <c r="CV13" t="inlineStr">
+        <is>
+          <t>THB_RESOLV</t>
+        </is>
+      </c>
+      <c r="CW13" t="inlineStr">
+        <is>
+          <t>THB_EDEN</t>
+        </is>
+      </c>
+      <c r="CX13" t="inlineStr">
+        <is>
+          <t>THB_TA</t>
+        </is>
+      </c>
+      <c r="CY13" t="inlineStr">
+        <is>
+          <t>THB_IMX</t>
+        </is>
+      </c>
+      <c r="CZ13" t="inlineStr">
+        <is>
+          <t>THB_SAPIEN</t>
+        </is>
+      </c>
+      <c r="DA13" t="inlineStr">
+        <is>
+          <t>THB_FLOKI</t>
+        </is>
+      </c>
+      <c r="DB13" t="inlineStr">
+        <is>
+          <t>THB_AUSD</t>
+        </is>
+      </c>
+      <c r="DC13" t="inlineStr">
+        <is>
+          <t>THB_SPEC</t>
+        </is>
+      </c>
+      <c r="DD13" t="inlineStr">
+        <is>
+          <t>THB_ZBT</t>
+        </is>
+      </c>
+      <c r="DE13" t="inlineStr">
+        <is>
+          <t>THB_IMU</t>
+        </is>
+      </c>
+      <c r="DF13" t="inlineStr">
+        <is>
+          <t>THB_BAND</t>
+        </is>
+      </c>
+      <c r="DG13" t="inlineStr">
+        <is>
+          <t>THB_DYDX</t>
+        </is>
+      </c>
+      <c r="DH13" t="inlineStr">
+        <is>
+          <t>THB_LDO</t>
+        </is>
+      </c>
+      <c r="DI13" t="inlineStr">
+        <is>
+          <t>THB_BLAST</t>
+        </is>
+      </c>
+      <c r="DJ13" t="inlineStr">
+        <is>
+          <t>THB_FORT</t>
+        </is>
+      </c>
+      <c r="DK13" t="inlineStr">
+        <is>
+          <t>THB_PEOPLE</t>
+        </is>
+      </c>
+      <c r="DL13" t="inlineStr">
+        <is>
+          <t>THB_ETHFI</t>
+        </is>
+      </c>
+      <c r="DM13" t="inlineStr">
+        <is>
+          <t>THB_IOTX</t>
+        </is>
+      </c>
+      <c r="DN13" t="inlineStr">
+        <is>
+          <t>THB_FIDA</t>
+        </is>
+      </c>
+      <c r="DO13" t="inlineStr">
+        <is>
+          <t>THB_ZENT</t>
+        </is>
+      </c>
+      <c r="DP13" t="inlineStr">
+        <is>
+          <t>THB_HNT</t>
+        </is>
+      </c>
+      <c r="DQ13" t="inlineStr">
+        <is>
+          <t>THB_YB</t>
+        </is>
+      </c>
+      <c r="DR13" t="inlineStr">
+        <is>
+          <t>THB_EDGE</t>
+        </is>
+      </c>
+      <c r="DS13" t="inlineStr">
+        <is>
+          <t>THB_BASED</t>
+        </is>
+      </c>
+      <c r="DT13" t="inlineStr">
+        <is>
+          <t>THB_BIRB</t>
+        </is>
+      </c>
+      <c r="DU13" t="inlineStr">
+        <is>
+          <t>THB_NXPC</t>
+        </is>
+      </c>
+      <c r="DV13" t="inlineStr">
+        <is>
+          <t>THB_CPOOL</t>
+        </is>
+      </c>
+      <c r="DW13" t="inlineStr">
+        <is>
+          <t>THB_CLEAR</t>
+        </is>
+      </c>
+      <c r="DX13" t="inlineStr">
+        <is>
+          <t>THB_FLOW</t>
+        </is>
+      </c>
+      <c r="DY13" t="inlineStr">
+        <is>
+          <t>THB_MORPHO</t>
+        </is>
+      </c>
+      <c r="DZ13" t="inlineStr">
+        <is>
+          <t>THB_ATOM</t>
+        </is>
+      </c>
+      <c r="EA13" t="inlineStr">
+        <is>
+          <t>THB_GRT</t>
+        </is>
+      </c>
+      <c r="EB13" t="inlineStr">
+        <is>
+          <t>THB_FET</t>
+        </is>
+      </c>
+      <c r="EC13" t="inlineStr">
+        <is>
+          <t>THB_ABT</t>
+        </is>
+      </c>
+      <c r="ED13" t="inlineStr">
+        <is>
+          <t>THB_KSM</t>
+        </is>
+      </c>
+      <c r="EE13" t="inlineStr">
+        <is>
+          <t>THB_PYTH</t>
+        </is>
+      </c>
+      <c r="EF13" t="inlineStr">
+        <is>
+          <t>THB_AZTEC</t>
+        </is>
+      </c>
+      <c r="EG13" t="inlineStr">
+        <is>
+          <t>THB_KITE</t>
+        </is>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
+          <t>THB_FF</t>
+        </is>
+      </c>
+      <c r="EI13" t="inlineStr">
+        <is>
+          <t>THB_PAXG</t>
+        </is>
+      </c>
+      <c r="EJ13" t="inlineStr">
+        <is>
+          <t>THB_XMN</t>
+        </is>
+      </c>
+      <c r="EK13" t="inlineStr">
+        <is>
+          <t>THB_ID</t>
+        </is>
+      </c>
+      <c r="EL13" t="inlineStr">
+        <is>
+          <t>THB_ZETA</t>
+        </is>
+      </c>
+      <c r="EM13" t="inlineStr">
+        <is>
+          <t>THB_BABYDOGE</t>
+        </is>
+      </c>
+      <c r="EN13" t="inlineStr">
+        <is>
+          <t>THB_SUN</t>
+        </is>
+      </c>
+      <c r="EO13" t="inlineStr">
+        <is>
+          <t>THB_PERP</t>
+        </is>
+      </c>
+      <c r="EP13" t="inlineStr">
+        <is>
+          <t>THB_APEX</t>
+        </is>
+      </c>
+      <c r="EQ13" t="inlineStr">
+        <is>
+          <t>THB_AERO</t>
+        </is>
+      </c>
+      <c r="ER13" t="inlineStr">
+        <is>
+          <t>THB_CHZ</t>
+        </is>
+      </c>
+      <c r="ES13" t="inlineStr">
+        <is>
+          <t>THB_ROBO</t>
+        </is>
+      </c>
+      <c r="ET13" t="inlineStr">
+        <is>
+          <t>THB_1INCH</t>
+        </is>
+      </c>
+      <c r="EU13" t="inlineStr">
+        <is>
+          <t>THB_PRCL</t>
+        </is>
+      </c>
+      <c r="EV13" t="inlineStr">
+        <is>
+          <t>THB_SNT</t>
+        </is>
+      </c>
+      <c r="EW13" t="inlineStr">
+        <is>
+          <t>THB_KAITO</t>
+        </is>
+      </c>
+      <c r="EX13" t="inlineStr">
+        <is>
+          <t>THB_XPL</t>
+        </is>
+      </c>
+      <c r="EY13" t="inlineStr">
+        <is>
+          <t>THB_MNT</t>
+        </is>
+      </c>
+      <c r="EZ13" t="inlineStr">
+        <is>
+          <t>THB_PEAQ</t>
+        </is>
+      </c>
+      <c r="FA13" t="inlineStr">
+        <is>
+          <t>THB_REALX</t>
+        </is>
+      </c>
+      <c r="FB13" t="inlineStr">
+        <is>
+          <t>THB_QNT</t>
+        </is>
+      </c>
+      <c r="FC13" t="inlineStr">
+        <is>
+          <t>THB_SHELL</t>
+        </is>
+      </c>
+      <c r="FD13" t="inlineStr">
+        <is>
+          <t>THB_ES</t>
+        </is>
+      </c>
+      <c r="FE13" t="inlineStr">
+        <is>
+          <t>THB_VIRTUAL</t>
+        </is>
+      </c>
+      <c r="FF13" t="inlineStr">
+        <is>
+          <t>THB_TOSHI</t>
+        </is>
+      </c>
+      <c r="FG13" t="inlineStr">
+        <is>
+          <t>THB_HYPER</t>
+        </is>
+      </c>
+      <c r="FH13" t="inlineStr">
+        <is>
+          <t>THB_RDNT</t>
+        </is>
+      </c>
+      <c r="FI13" t="inlineStr">
+        <is>
+          <t>THB_LQTY</t>
+        </is>
+      </c>
+      <c r="FJ13" t="inlineStr">
+        <is>
+          <t>THB_HOLO</t>
+        </is>
+      </c>
+      <c r="FK13" t="inlineStr">
+        <is>
+          <t>THB_KAIA</t>
+        </is>
+      </c>
+      <c r="FL13" t="inlineStr">
+        <is>
+          <t>THB_LA</t>
+        </is>
+      </c>
+      <c r="FM13" t="inlineStr">
+        <is>
+          <t>THB_OMNI</t>
+        </is>
+      </c>
+      <c r="FN13" t="inlineStr">
+        <is>
+          <t>THB_STABLE</t>
+        </is>
+      </c>
+      <c r="FO13" t="inlineStr">
+        <is>
+          <t>THB_SOON</t>
+        </is>
+      </c>
+      <c r="FP13" t="inlineStr">
+        <is>
+          <t>THB_TNSR</t>
+        </is>
+      </c>
+      <c r="FQ13" t="inlineStr">
+        <is>
+          <t>THB_NEIRO</t>
+        </is>
+      </c>
+      <c r="FR13" t="inlineStr">
+        <is>
+          <t>THB_IO</t>
+        </is>
+      </c>
+      <c r="FS13" t="inlineStr">
+        <is>
+          <t>THB_SKR</t>
+        </is>
+      </c>
+      <c r="FT13" t="inlineStr">
+        <is>
+          <t>THB_JTO</t>
+        </is>
+      </c>
+      <c r="FU13" t="inlineStr">
+        <is>
+          <t>THB_GLMR</t>
+        </is>
+      </c>
+      <c r="FV13" t="inlineStr">
+        <is>
+          <t>THB_REZ</t>
+        </is>
+      </c>
+      <c r="FW13" t="inlineStr">
+        <is>
+          <t>THB_APE</t>
+        </is>
+      </c>
+      <c r="FX13" t="inlineStr">
+        <is>
+          <t>THB_GLM</t>
+        </is>
+      </c>
+      <c r="FY13" t="inlineStr">
+        <is>
+          <t>THB_EL</t>
+        </is>
+      </c>
+      <c r="FZ13" t="inlineStr">
+        <is>
+          <t>THB_CVC</t>
+        </is>
+      </c>
+      <c r="GA13" t="inlineStr">
+        <is>
+          <t>THB_SXT</t>
+        </is>
+      </c>
+      <c r="GB13" t="inlineStr">
+        <is>
+          <t>THB_JUP</t>
+        </is>
+      </c>
+      <c r="GC13" t="inlineStr">
+        <is>
+          <t>THB_WIN</t>
+        </is>
+      </c>
+      <c r="GD13" t="inlineStr">
+        <is>
+          <t>THB_IQ</t>
+        </is>
+      </c>
+      <c r="GE13" t="inlineStr">
+        <is>
+          <t>THB_CORE</t>
+        </is>
+      </c>
+      <c r="GF13" t="inlineStr">
+        <is>
+          <t>THB_FLUID</t>
+        </is>
+      </c>
+      <c r="GG13" t="inlineStr">
+        <is>
+          <t>THB_SPK</t>
+        </is>
+      </c>
+      <c r="GH13" t="inlineStr">
+        <is>
+          <t>THB_S</t>
+        </is>
+      </c>
+      <c r="GI13" t="inlineStr">
+        <is>
+          <t>THB_ALGO</t>
+        </is>
+      </c>
+      <c r="GJ13" t="inlineStr">
+        <is>
+          <t>THB_PARTI</t>
+        </is>
+      </c>
+      <c r="GK13" t="inlineStr">
+        <is>
+          <t>THB_PENDLE</t>
+        </is>
+      </c>
+      <c r="GL13" t="inlineStr">
+        <is>
+          <t>THB_ACH</t>
+        </is>
+      </c>
+      <c r="GM13" t="inlineStr">
+        <is>
+          <t>THB_POW</t>
+        </is>
+      </c>
+      <c r="GN13" t="inlineStr">
+        <is>
+          <t>THB_ELIZAOS</t>
+        </is>
+      </c>
+      <c r="GO13" t="inlineStr">
+        <is>
+          <t>THB_BAT</t>
+        </is>
+      </c>
+      <c r="GP13" t="inlineStr">
+        <is>
+          <t>THB_ORCA</t>
+        </is>
+      </c>
+      <c r="GQ13" t="inlineStr">
+        <is>
+          <t>THB_ALT</t>
+        </is>
+      </c>
+      <c r="GR13" t="inlineStr">
+        <is>
+          <t>THB_KNC</t>
+        </is>
+      </c>
+      <c r="GS13" t="inlineStr">
+        <is>
+          <t>THB_WLFI</t>
+        </is>
+      </c>
+      <c r="GT13" t="inlineStr">
+        <is>
+          <t>THB_COMP</t>
+        </is>
+      </c>
+      <c r="GU13" t="inlineStr">
+        <is>
+          <t>THB_HOME</t>
+        </is>
+      </c>
+      <c r="GV13" t="inlineStr">
+        <is>
+          <t>THB_FLUX</t>
+        </is>
+      </c>
+      <c r="GW13" t="inlineStr">
+        <is>
+          <t>THB_PYBOBO</t>
+        </is>
+      </c>
+      <c r="GX13" t="inlineStr">
+        <is>
+          <t>THB_WIF</t>
+        </is>
+      </c>
+      <c r="GY13" t="inlineStr">
+        <is>
+          <t>THB_RON</t>
+        </is>
+      </c>
+      <c r="GZ13" t="inlineStr">
+        <is>
+          <t>THB_JOE</t>
+        </is>
+      </c>
+      <c r="HA13" t="inlineStr">
+        <is>
+          <t>THB_L3</t>
+        </is>
+      </c>
+      <c r="HB13" t="inlineStr">
+        <is>
+          <t>THB_API3</t>
+        </is>
+      </c>
+      <c r="HC13" t="inlineStr">
+        <is>
+          <t>THB_MEME</t>
+        </is>
+      </c>
+      <c r="HD13" t="inlineStr">
+        <is>
+          <t>THB_B3</t>
+        </is>
+      </c>
+      <c r="HE13" t="inlineStr">
+        <is>
+          <t>THB_TREE</t>
+        </is>
+      </c>
+      <c r="HF13" t="inlineStr">
+        <is>
+          <t>THB_PNUT</t>
+        </is>
+      </c>
+      <c r="HG13" t="inlineStr">
+        <is>
+          <t>THB_GRAM</t>
+        </is>
+      </c>
+      <c r="HH13" t="inlineStr">
+        <is>
+          <t>THB_VIC</t>
+        </is>
+      </c>
+      <c r="HI13" t="inlineStr">
+        <is>
+          <t>THB_W</t>
+        </is>
+      </c>
+      <c r="HJ13" t="inlineStr">
+        <is>
+          <t>THB_SUSHI</t>
+        </is>
+      </c>
+      <c r="HK13" t="inlineStr">
+        <is>
+          <t>THB_POPCAT</t>
+        </is>
+      </c>
+      <c r="HL13" t="inlineStr">
+        <is>
+          <t>THB_ICNT</t>
+        </is>
+      </c>
+      <c r="HM13" t="inlineStr">
+        <is>
+          <t>THB_WEMIX</t>
+        </is>
+      </c>
+      <c r="HN13" t="inlineStr">
+        <is>
+          <t>THB_ATH</t>
+        </is>
+      </c>
+      <c r="HO13" t="inlineStr">
+        <is>
+          <t>THB_MITO</t>
+        </is>
+      </c>
+      <c r="HP13" t="inlineStr">
+        <is>
+          <t>THB_MEW</t>
+        </is>
+      </c>
+      <c r="HQ13" t="inlineStr">
+        <is>
+          <t>THB_ZIG</t>
+        </is>
+      </c>
+      <c r="HR13" t="inlineStr">
+        <is>
+          <t>THB_PLUME</t>
+        </is>
+      </c>
+      <c r="HS13" t="inlineStr">
+        <is>
+          <t>THB_PIEVERSE</t>
+        </is>
+      </c>
+      <c r="HT13" t="inlineStr">
+        <is>
+          <t>THB_SAND</t>
+        </is>
+      </c>
+      <c r="HU13" t="inlineStr">
+        <is>
+          <t>THB_HAEDAL</t>
+        </is>
+      </c>
+      <c r="HV13" t="inlineStr">
+        <is>
+          <t>THB_OPG</t>
+        </is>
+      </c>
+      <c r="HW13" t="inlineStr">
+        <is>
+          <t>THB_SAHARA</t>
+        </is>
+      </c>
+      <c r="HX13" t="inlineStr">
+        <is>
+          <t>THB_SIGN</t>
+        </is>
+      </c>
+      <c r="HY13" t="inlineStr">
+        <is>
+          <t>THB_TAIKO</t>
+        </is>
+      </c>
+      <c r="HZ13" t="inlineStr">
+        <is>
+          <t>THB_SONIC</t>
+        </is>
+      </c>
+      <c r="IA13" t="inlineStr">
+        <is>
+          <t>THB_LINEA</t>
+        </is>
+      </c>
+      <c r="IB13" t="inlineStr">
+        <is>
+          <t>THB_ZRO</t>
+        </is>
+      </c>
+      <c r="IC13" t="inlineStr">
+        <is>
+          <t>THB_APT</t>
+        </is>
+      </c>
+      <c r="ID13" t="inlineStr">
+        <is>
+          <t>THB_LAYER</t>
+        </is>
+      </c>
+      <c r="IE13" t="inlineStr">
+        <is>
+          <t>THB_BOME</t>
+        </is>
+      </c>
+      <c r="IF13" t="inlineStr">
+        <is>
+          <t>THB_ZRX</t>
+        </is>
+      </c>
+      <c r="IG13" t="inlineStr">
+        <is>
+          <t>THB_FLOCK</t>
+        </is>
+      </c>
+      <c r="IH13" t="inlineStr">
+        <is>
+          <t>THB_LRC</t>
+        </is>
+      </c>
+      <c r="II13" t="inlineStr">
+        <is>
+          <t>THB_XDC</t>
+        </is>
+      </c>
+      <c r="IJ13" t="inlineStr">
+        <is>
+          <t>THB_RAY</t>
+        </is>
+      </c>
+      <c r="IK13" t="inlineStr">
+        <is>
+          <t>THB_ELSA</t>
+        </is>
+      </c>
+      <c r="IL13" t="inlineStr">
+        <is>
+          <t>THB_SNX</t>
+        </is>
+      </c>
+      <c r="IM13" t="inlineStr">
+        <is>
+          <t>THB_ENJ</t>
+        </is>
+      </c>
+      <c r="IN13" t="inlineStr">
+        <is>
+          <t>THB_CAKE</t>
+        </is>
+      </c>
+      <c r="IO13" t="inlineStr">
+        <is>
+          <t>THB_C</t>
+        </is>
+      </c>
+      <c r="IP13" t="inlineStr">
+        <is>
+          <t>THB_ZORA</t>
+        </is>
+      </c>
+      <c r="IQ13" t="inlineStr">
+        <is>
+          <t>THB_CHILLGUY</t>
+        </is>
+      </c>
+      <c r="IR13" t="inlineStr">
+        <is>
+          <t>THB_SCR</t>
+        </is>
+      </c>
+      <c r="IS13" t="inlineStr">
+        <is>
+          <t>THB_VOOI</t>
+        </is>
+      </c>
+      <c r="IT13" t="inlineStr">
+        <is>
+          <t>THB_KMNO</t>
+        </is>
+      </c>
+      <c r="IU13" t="inlineStr">
+        <is>
+          <t>THB_SKY</t>
+        </is>
+      </c>
+      <c r="IV13" t="inlineStr">
+        <is>
+          <t>THB_RSR</t>
+        </is>
+      </c>
+      <c r="IW13" t="inlineStr">
+        <is>
+          <t>THB_MET</t>
+        </is>
+      </c>
+      <c r="IX13" t="inlineStr">
+        <is>
+          <t>THB_MOG</t>
+        </is>
+      </c>
+      <c r="IY13" t="inlineStr">
+        <is>
+          <t>THB_F</t>
+        </is>
+      </c>
+      <c r="IZ13" t="inlineStr">
+        <is>
+          <t>THB_ICP</t>
+        </is>
+      </c>
+      <c r="JA13" t="inlineStr">
+        <is>
+          <t>THB_FXS</t>
+        </is>
+      </c>
+      <c r="JB13" t="inlineStr">
+        <is>
+          <t>THB_CORN</t>
+        </is>
+      </c>
+      <c r="JC13" t="inlineStr">
+        <is>
+          <t>THB_BLEND</t>
+        </is>
+      </c>
+      <c r="JD13" t="inlineStr">
+        <is>
+          <t>THB_RED</t>
+        </is>
+      </c>
+      <c r="JE13" t="inlineStr">
+        <is>
+          <t>THB_LYX</t>
+        </is>
+      </c>
+      <c r="JF13" t="inlineStr">
+        <is>
+          <t>THB_WET</t>
+        </is>
+      </c>
+      <c r="JG13" t="inlineStr">
+        <is>
+          <t>THB_DEGEN</t>
+        </is>
+      </c>
+      <c r="JH13" t="inlineStr">
+        <is>
+          <t>THB_PRIME</t>
+        </is>
+      </c>
+      <c r="JI13" t="inlineStr">
+        <is>
+          <t>THB_ZK</t>
+        </is>
+      </c>
+      <c r="JJ13" t="inlineStr">
+        <is>
+          <t>THB_DBR</t>
+        </is>
+      </c>
+      <c r="JK13" t="inlineStr">
+        <is>
+          <t>THB_PONKE</t>
+        </is>
+      </c>
+      <c r="JL13" t="inlineStr">
+        <is>
+          <t>THB_YFI</t>
+        </is>
+      </c>
+      <c r="JM13" t="inlineStr">
+        <is>
+          <t>THB_ACX</t>
+        </is>
+      </c>
+      <c r="JN13" t="inlineStr">
+        <is>
+          <t>THB_INJ</t>
+        </is>
+      </c>
+      <c r="JO13" t="inlineStr">
+        <is>
+          <t>THB_GOAT</t>
+        </is>
+      </c>
+      <c r="JP13" t="inlineStr">
+        <is>
+          <t>THB_BTT</t>
+        </is>
+      </c>
+      <c r="JQ13" t="inlineStr">
+        <is>
+          <t>THB_AXS</t>
+        </is>
+      </c>
+      <c r="JR13" t="inlineStr">
+        <is>
+          <t>THB_ILV</t>
+        </is>
+      </c>
+      <c r="JS13" t="inlineStr">
+        <is>
+          <t>THB_XTZ</t>
+        </is>
+      </c>
+      <c r="JT13" t="inlineStr">
+        <is>
+          <t>THB_GT</t>
+        </is>
+      </c>
+      <c r="JU13" t="inlineStr">
+        <is>
+          <t>THB_ERA</t>
+        </is>
+      </c>
+      <c r="JV13" t="inlineStr">
+        <is>
+          <t>THB_CFG</t>
+        </is>
+      </c>
+      <c r="JW13" t="inlineStr">
+        <is>
+          <t>THB_AIXBT</t>
+        </is>
+      </c>
+      <c r="JX13" t="inlineStr">
+        <is>
+          <t>THB_ASP</t>
+        </is>
+      </c>
+      <c r="JY13" t="inlineStr">
+        <is>
+          <t>THB_BAN</t>
+        </is>
+      </c>
+      <c r="JZ13" t="inlineStr">
+        <is>
+          <t>THB_TIA</t>
+        </is>
+      </c>
+      <c r="KA13" t="inlineStr">
+        <is>
+          <t>THB_USD1</t>
+        </is>
+      </c>
+      <c r="KB13" t="inlineStr">
+        <is>
+          <t>THB_ANIME</t>
+        </is>
+      </c>
+      <c r="KC13" t="inlineStr">
+        <is>
+          <t>THB_COOKIE</t>
+        </is>
+      </c>
+      <c r="KD13" t="inlineStr">
+        <is>
+          <t>THB_MANA</t>
+        </is>
+      </c>
+      <c r="KE13" t="inlineStr">
+        <is>
+          <t>THB_MON</t>
+        </is>
+      </c>
+      <c r="KF13" t="inlineStr">
+        <is>
+          <t>THB_IP</t>
+        </is>
+      </c>
+      <c r="KG13" t="inlineStr">
+        <is>
+          <t>THB_ENS</t>
+        </is>
+      </c>
+      <c r="KH13" t="inlineStr">
+        <is>
+          <t>THB_SKL</t>
+        </is>
+      </c>
+      <c r="KI13" t="inlineStr">
+        <is>
+          <t>THB_STRK</t>
+        </is>
+      </c>
+      <c r="KJ13" t="inlineStr">
+        <is>
+          <t>THB_FIL</t>
+        </is>
+      </c>
+      <c r="KK13" t="inlineStr">
+        <is>
+          <t>THB_JST</t>
+        </is>
+      </c>
+      <c r="KL13" t="inlineStr">
+        <is>
+          <t>THB_RLUSD</t>
+        </is>
+      </c>
+      <c r="KM13" t="inlineStr">
+        <is>
+          <t>THB_CFX</t>
+        </is>
+      </c>
+      <c r="KN13" t="inlineStr">
+        <is>
+          <t>THB_CETUS</t>
+        </is>
+      </c>
+      <c r="KO13" t="inlineStr">
+        <is>
+          <t>THB_KERNEL</t>
+        </is>
+      </c>
+      <c r="KP13" t="inlineStr">
+        <is>
+          <t>THB_PROMPT</t>
+        </is>
+      </c>
+      <c r="KQ13" t="inlineStr">
+        <is>
+          <t>THB_OPEN</t>
+        </is>
+      </c>
+      <c r="KR13" t="inlineStr">
+        <is>
+          <t>THB_PYUSD</t>
+        </is>
+      </c>
+      <c r="KS13" t="inlineStr">
+        <is>
+          <t>THB_ANKR</t>
+        </is>
+      </c>
+      <c r="KT13" t="inlineStr">
+        <is>
+          <t>THB_BABY</t>
+        </is>
+      </c>
+      <c r="KU13" t="inlineStr">
+        <is>
+          <t>THB_SFP</t>
+        </is>
+      </c>
+      <c r="KV13" t="inlineStr">
+        <is>
+          <t>THB_AGLD</t>
+        </is>
+      </c>
+      <c r="KW13" t="inlineStr">
+        <is>
+          <t>THB_CARV</t>
+        </is>
+      </c>
+      <c r="KX13" t="inlineStr">
+        <is>
+          <t>THB_DAI</t>
+        </is>
+      </c>
+      <c r="KY13" t="inlineStr">
+        <is>
+          <t>THB_SUMX</t>
+        </is>
+      </c>
+      <c r="KZ13" t="inlineStr">
+        <is>
+          <t>THB_DOOD</t>
+        </is>
+      </c>
+      <c r="LA13" t="inlineStr">
+        <is>
+          <t>THB_CGPT</t>
+        </is>
+      </c>
+      <c r="LB13" t="inlineStr">
+        <is>
+          <t>THB_OSMO</t>
+        </is>
+      </c>
+      <c r="LC13" t="inlineStr">
+        <is>
+          <t>THB_CELO</t>
+        </is>
+      </c>
+      <c r="LD13" t="inlineStr">
+        <is>
+          <t>THB_BRETT</t>
+        </is>
+      </c>
+      <c r="LE13" t="inlineStr">
+        <is>
+          <t>THB_USAT</t>
+        </is>
+      </c>
+      <c r="LF13" t="inlineStr">
+        <is>
+          <t>THB_DATA</t>
+        </is>
+      </c>
+      <c r="LG13" t="inlineStr">
+        <is>
+          <t>THB_TOKEN</t>
+        </is>
+      </c>
+      <c r="LH13" t="inlineStr">
+        <is>
+          <t>THB_BAL</t>
+        </is>
+      </c>
+      <c r="LI13" t="inlineStr">
+        <is>
+          <t>THB_SPELL</t>
+        </is>
+      </c>
+      <c r="LJ13" t="inlineStr">
+        <is>
+          <t>THB_MOCA</t>
+        </is>
+      </c>
+      <c r="LK13" t="inlineStr">
+        <is>
+          <t>THB_SSV</t>
+        </is>
+      </c>
+      <c r="LL13" t="inlineStr">
+        <is>
+          <t>THB_ZKP</t>
+        </is>
+      </c>
+      <c r="LM13" t="inlineStr">
+        <is>
+          <t>THB_BREV</t>
+        </is>
+      </c>
+      <c r="LN13" t="inlineStr">
+        <is>
+          <t>THB_XAN</t>
+        </is>
+      </c>
+      <c r="LO13" t="inlineStr">
+        <is>
+          <t>THB_SOMI</t>
+        </is>
+      </c>
+      <c r="LP13" t="inlineStr">
+        <is>
+          <t>THB_TOWNS</t>
+        </is>
+      </c>
+      <c r="LQ13" t="inlineStr">
+        <is>
+          <t>THB_TWT</t>
+        </is>
+      </c>
+      <c r="LR13" t="inlineStr">
+        <is>
+          <t>THB_UMA</t>
+        </is>
+      </c>
+      <c r="LS13" t="inlineStr">
+        <is>
+          <t>THB_0G</t>
+        </is>
+      </c>
+      <c r="LT13" t="inlineStr">
+        <is>
+          <t>THB_AEVO</t>
+        </is>
+      </c>
+      <c r="LU13" t="inlineStr">
+        <is>
+          <t>THB_SCA</t>
+        </is>
+      </c>
+      <c r="LV13" t="inlineStr">
+        <is>
+          <t>THB_BLUR</t>
+        </is>
+      </c>
+      <c r="LW13" t="inlineStr">
+        <is>
+          <t>THB_GMX</t>
+        </is>
+      </c>
+      <c r="LX13" t="inlineStr">
+        <is>
+          <t>THB_GMT</t>
+        </is>
+      </c>
+      <c r="LY13" t="inlineStr">
+        <is>
+          <t>THB_XAI</t>
+        </is>
+      </c>
+      <c r="LZ13" t="inlineStr">
+        <is>
+          <t>THB_MAGIC</t>
+        </is>
+      </c>
+      <c r="MA13" t="inlineStr">
+        <is>
+          <t>THB_RPL</t>
+        </is>
+      </c>
+      <c r="MB13" t="inlineStr">
+        <is>
+          <t>THB_AVA</t>
+        </is>
+      </c>
+      <c r="MC13" t="inlineStr">
+        <is>
+          <t>THB_SOSO</t>
+        </is>
+      </c>
+      <c r="MD13" t="inlineStr">
+        <is>
+          <t>THB_MASK</t>
+        </is>
+      </c>
+      <c r="ME13" t="inlineStr">
+        <is>
+          <t>THB_NEXO</t>
+        </is>
+      </c>
+      <c r="MF13" t="inlineStr">
+        <is>
+          <t>THB_FRAX</t>
+        </is>
+      </c>
+      <c r="MG13" t="inlineStr">
+        <is>
+          <t>THB_ME</t>
+        </is>
+      </c>
+      <c r="MH13" t="inlineStr">
+        <is>
+          <t>THB_2Z</t>
+        </is>
+      </c>
+      <c r="MI13" t="inlineStr">
+        <is>
+          <t>THB_TRB</t>
+        </is>
+      </c>
+      <c r="MJ13" t="inlineStr">
+        <is>
+          <t>THB_AXL</t>
+        </is>
+      </c>
+      <c r="MK13" t="inlineStr">
+        <is>
+          <t>THB_PROVE</t>
+        </is>
+      </c>
+      <c r="ML13" t="inlineStr">
+        <is>
+          <t>THB_TURTLE</t>
+        </is>
+      </c>
+      <c r="MM13" t="inlineStr">
+        <is>
+          <t>THB_WCT</t>
+        </is>
+      </c>
+      <c r="MN13" t="inlineStr">
+        <is>
+          <t>THB_RECALL</t>
+        </is>
+      </c>
+      <c r="MO13" t="inlineStr">
+        <is>
+          <t>THB_CELR</t>
+        </is>
+      </c>
+      <c r="MP13" t="inlineStr">
+        <is>
+          <t>THB_SAFE</t>
+        </is>
+      </c>
+      <c r="MQ13" t="inlineStr">
+        <is>
+          <t>THB_SEI</t>
+        </is>
+      </c>
+      <c r="MR13" t="inlineStr">
+        <is>
+          <t>THB_BARD</t>
+        </is>
+      </c>
+      <c r="MS13" t="inlineStr">
+        <is>
+          <t>THB_CYBER</t>
+        </is>
+      </c>
+      <c r="MT13" t="inlineStr">
+        <is>
+          <t>THB_TRAC</t>
+        </is>
+      </c>
+      <c r="MU13" t="inlineStr">
+        <is>
+          <t>THB_NEWT</t>
+        </is>
+      </c>
+      <c r="MV13" t="inlineStr">
+        <is>
+          <t>THB_AVNT</t>
+        </is>
+      </c>
+      <c r="MW13" t="inlineStr">
+        <is>
+          <t>THB_MANTA</t>
+        </is>
+      </c>
+      <c r="MX13" t="inlineStr">
+        <is>
+          <t>THB_SYRUP</t>
+        </is>
+      </c>
+      <c r="MY13" t="inlineStr">
+        <is>
+          <t>THB_ZKC</t>
+        </is>
+      </c>
+      <c r="MZ13" t="inlineStr">
+        <is>
+          <t>THB_LPT</t>
+        </is>
+      </c>
+      <c r="NA13" t="inlineStr">
+        <is>
+          <t>THB_GNO</t>
+        </is>
+      </c>
+      <c r="NB13" t="inlineStr">
+        <is>
+          <t>THB_C98</t>
+        </is>
+      </c>
+      <c r="NC13" t="inlineStr">
+        <is>
+          <t>THB_WOO</t>
+        </is>
+      </c>
+      <c r="ND13" t="inlineStr">
+        <is>
+          <t>THB_ARKM</t>
+        </is>
+      </c>
+      <c r="NE13" t="inlineStr">
+        <is>
+          <t>THB_SOPH</t>
+        </is>
+      </c>
+      <c r="NF13" t="inlineStr">
+        <is>
+          <t>THB_ALPACA</t>
+        </is>
+      </c>
+      <c r="NG13" t="inlineStr">
+        <is>
+          <t>THB_ANT</t>
+        </is>
+      </c>
+      <c r="NH13" t="inlineStr">
+        <is>
+          <t>THB_ASI</t>
+        </is>
+      </c>
+      <c r="NI13" t="inlineStr">
+        <is>
+          <t>THB_AST</t>
+        </is>
+      </c>
+      <c r="NJ13" t="inlineStr">
+        <is>
+          <t>THB_ASTR</t>
+        </is>
+      </c>
+      <c r="NK13" t="inlineStr">
+        <is>
+          <t>THB_BEAR</t>
+        </is>
+      </c>
+      <c r="NL13" t="inlineStr">
+        <is>
+          <t>THB_BLUE</t>
+        </is>
+      </c>
+      <c r="NM13" t="inlineStr">
+        <is>
+          <t>THB_BNT</t>
+        </is>
+      </c>
+      <c r="NN13" t="inlineStr">
+        <is>
+          <t>THB_BOBA</t>
+        </is>
+      </c>
+      <c r="NO13" t="inlineStr">
+        <is>
+          <t>THB_BSV</t>
+        </is>
+      </c>
+      <c r="NP13" t="inlineStr">
+        <is>
+          <t>THB_BTG</t>
+        </is>
+      </c>
+      <c r="NQ13" t="inlineStr">
+        <is>
+          <t>THB_BULL</t>
+        </is>
+      </c>
+      <c r="NR13" t="inlineStr">
+        <is>
+          <t>THB_BUSD</t>
+        </is>
+      </c>
+      <c r="NS13" t="inlineStr">
+        <is>
+          <t>THB_CRO</t>
+        </is>
+      </c>
+      <c r="NT13" t="inlineStr">
+        <is>
+          <t>THB_CVX</t>
+        </is>
+      </c>
+      <c r="NU13" t="inlineStr">
+        <is>
+          <t>THB_DASH</t>
+        </is>
+      </c>
+      <c r="NV13" t="inlineStr">
+        <is>
+          <t>THB_DENT</t>
+        </is>
+      </c>
+      <c r="NW13" t="inlineStr">
+        <is>
+          <t>THB_DGD</t>
+        </is>
+      </c>
+      <c r="NX13" t="inlineStr">
+        <is>
+          <t>THB_DGX</t>
+        </is>
+      </c>
+      <c r="NY13" t="inlineStr">
+        <is>
+          <t>THB_DOLO</t>
+        </is>
+      </c>
+      <c r="NZ13" t="inlineStr">
+        <is>
+          <t>THB_DON</t>
+        </is>
+      </c>
+      <c r="OA13" t="inlineStr">
+        <is>
+          <t>THB_ENG</t>
+        </is>
+      </c>
+      <c r="OB13" t="inlineStr">
+        <is>
+          <t>THB_ENSO</t>
+        </is>
+      </c>
+      <c r="OC13" t="inlineStr">
+        <is>
+          <t>THB_EOS</t>
+        </is>
+      </c>
+      <c r="OD13" t="inlineStr">
+        <is>
+          <t>THB_ETC</t>
+        </is>
+      </c>
+      <c r="OE13" t="inlineStr">
+        <is>
+          <t>THB_EVX</t>
+        </is>
+      </c>
+      <c r="OF13" t="inlineStr">
+        <is>
+          <t>THB_EXFI</t>
+        </is>
+      </c>
+      <c r="OG13" t="inlineStr">
+        <is>
+          <t>THB_FLR</t>
+        </is>
+      </c>
+      <c r="OH13" t="inlineStr">
+        <is>
+          <t>THB_FTM</t>
+        </is>
+      </c>
+      <c r="OI13" t="inlineStr">
+        <is>
+          <t>THB_FTT</t>
+        </is>
+      </c>
+      <c r="OJ13" t="inlineStr">
+        <is>
+          <t>THB_GAL</t>
+        </is>
+      </c>
+      <c r="OK13" t="inlineStr">
+        <is>
+          <t>THB_GALA1</t>
+        </is>
+      </c>
+      <c r="OL13" t="inlineStr">
+        <is>
+          <t>THB_GF</t>
+        </is>
+      </c>
+      <c r="OM13" t="inlineStr">
+        <is>
+          <t>THB_GHST</t>
+        </is>
+      </c>
+      <c r="ON13" t="inlineStr">
+        <is>
+          <t>THB_GNT</t>
+        </is>
+      </c>
+      <c r="OO13" t="inlineStr">
+        <is>
+          <t>THB_GODS</t>
+        </is>
+      </c>
+      <c r="OP13" t="inlineStr">
+        <is>
+          <t>THB_GUSD</t>
+        </is>
+      </c>
+      <c r="OQ13" t="inlineStr">
+        <is>
+          <t>THB_INF</t>
+        </is>
+      </c>
+      <c r="OR13" t="inlineStr">
+        <is>
+          <t>THB_KAVA</t>
+        </is>
+      </c>
+      <c r="OS13" t="inlineStr">
+        <is>
+          <t>THB_KEY</t>
+        </is>
+      </c>
+      <c r="OT13" t="inlineStr">
+        <is>
+          <t>THB_KLAY</t>
+        </is>
+      </c>
+      <c r="OU13" t="inlineStr">
+        <is>
+          <t>THB_LINA</t>
+        </is>
+      </c>
+      <c r="OV13" t="inlineStr">
+        <is>
+          <t>THB_LTC</t>
+        </is>
+      </c>
+      <c r="OW13" t="inlineStr">
+        <is>
+          <t>THB_LUMI</t>
+        </is>
+      </c>
+      <c r="OX13" t="inlineStr">
+        <is>
+          <t>THB_LUNA2</t>
+        </is>
+      </c>
+      <c r="OY13" t="inlineStr">
+        <is>
+          <t>THB_LYXE</t>
+        </is>
+      </c>
+      <c r="OZ13" t="inlineStr">
+        <is>
+          <t>THB_MATIC</t>
+        </is>
+      </c>
+      <c r="PA13" t="inlineStr">
+        <is>
+          <t>THB_MIR</t>
+        </is>
+      </c>
+      <c r="PB13" t="inlineStr">
+        <is>
+          <t>THB_MIRA</t>
+        </is>
+      </c>
+      <c r="PC13" t="inlineStr">
+        <is>
+          <t>THB_MODE</t>
+        </is>
+      </c>
+      <c r="PD13" t="inlineStr">
+        <is>
+          <t>THB_NEXT</t>
+        </is>
+      </c>
+      <c r="PE13" t="inlineStr">
+        <is>
+          <t>THB_OCEAN</t>
+        </is>
+      </c>
+      <c r="PF13" t="inlineStr">
+        <is>
+          <t>THB_OM</t>
+        </is>
+      </c>
+      <c r="PG13" t="inlineStr">
+        <is>
+          <t>THB_OMG</t>
+        </is>
+      </c>
+      <c r="PH13" t="inlineStr">
+        <is>
+          <t>THB_PAX</t>
+        </is>
+      </c>
+      <c r="PI13" t="inlineStr">
+        <is>
+          <t>THB_POLY</t>
+        </is>
+      </c>
+      <c r="PJ13" t="inlineStr">
+        <is>
+          <t>THB_POP</t>
+        </is>
+      </c>
+      <c r="PK13" t="inlineStr">
+        <is>
+          <t>THB_QI</t>
+        </is>
+      </c>
+      <c r="PL13" t="inlineStr">
+        <is>
+          <t>THB_RDN</t>
+        </is>
+      </c>
+      <c r="PM13" t="inlineStr">
+        <is>
+          <t>THB_REP</t>
+        </is>
+      </c>
+      <c r="PN13" t="inlineStr">
+        <is>
+          <t>THB_SGB</t>
+        </is>
+      </c>
+      <c r="PO13" t="inlineStr">
+        <is>
+          <t>THB_SLP</t>
+        </is>
+      </c>
+      <c r="PP13" t="inlineStr">
+        <is>
+          <t>THB_SOLO</t>
+        </is>
+      </c>
+      <c r="PQ13" t="inlineStr">
+        <is>
+          <t>THB_STAKE</t>
+        </is>
+      </c>
+      <c r="PR13" t="inlineStr">
+        <is>
+          <t>THB_STORJ</t>
+        </is>
+      </c>
+      <c r="PS13" t="inlineStr">
+        <is>
+          <t>THB_SZO</t>
+        </is>
+      </c>
+      <c r="PT13" t="inlineStr">
+        <is>
+          <t>THB_TNT</t>
+        </is>
+      </c>
+      <c r="PU13" t="inlineStr">
+        <is>
+          <t>THB_TUSD</t>
+        </is>
+      </c>
+      <c r="PV13" t="inlineStr">
+        <is>
+          <t>THB_USDS</t>
+        </is>
+      </c>
+      <c r="PW13" t="inlineStr">
+        <is>
+          <t>THB_WABI</t>
+        </is>
+      </c>
+      <c r="PX13" t="inlineStr">
+        <is>
+          <t>THB_WAN</t>
+        </is>
+      </c>
+      <c r="PY13" t="inlineStr">
+        <is>
+          <t>THB_WNXM</t>
+        </is>
+      </c>
+      <c r="PZ13" t="inlineStr">
+        <is>
+          <t>THB_XMR</t>
+        </is>
+      </c>
+      <c r="QA13" t="inlineStr">
+        <is>
+          <t>THB_YGG</t>
+        </is>
+      </c>
+      <c r="QB13" t="inlineStr">
+        <is>
+          <t>THB_ZEC</t>
+        </is>
+      </c>
+      <c r="QC13" t="inlineStr">
         <is>
           <t>USDTTHB</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="QD13" t="inlineStr">
         <is>
           <t>BTCTHB</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="QE13" t="inlineStr">
         <is>
           <t>BTCTHB 7d-Avg</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="QF13" t="inlineStr">
+        <is>
+          <t>XRPTHB</t>
+        </is>
+      </c>
+      <c r="QG13" t="inlineStr">
         <is>
           <t>ETHTHB</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="QH13" t="inlineStr">
+        <is>
+          <t>SOLTHB</t>
+        </is>
+      </c>
+      <c r="QI13" t="inlineStr">
+        <is>
+          <t>BNBTHB</t>
+        </is>
+      </c>
+      <c r="QJ13" t="inlineStr">
         <is>
           <t>VELOTHB</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>XRPTHB</t>
+      <c r="QK13" t="inlineStr">
+        <is>
+          <t>ASTERTHB</t>
+        </is>
+      </c>
+      <c r="QL13" t="inlineStr">
+        <is>
+          <t>ZENTTHB</t>
+        </is>
+      </c>
+      <c r="QM13" t="inlineStr">
+        <is>
+          <t>PLUMETHB</t>
+        </is>
+      </c>
+      <c r="QN13" t="inlineStr">
+        <is>
+          <t>ATHTHB</t>
+        </is>
+      </c>
+      <c r="QO13" t="inlineStr">
+        <is>
+          <t>ETH_THB</t>
+        </is>
+      </c>
+      <c r="QP13" t="inlineStr">
+        <is>
+          <t>BTC_THB</t>
+        </is>
+      </c>
+      <c r="QQ13" t="inlineStr">
+        <is>
+          <t>BTC_THB 7d-Avg</t>
+        </is>
+      </c>
+      <c r="QR13" t="inlineStr">
+        <is>
+          <t>USDT_THB</t>
+        </is>
+      </c>
+      <c r="QS13" t="inlineStr">
+        <is>
+          <t>SOL_THB</t>
+        </is>
+      </c>
+      <c r="QT13" t="inlineStr">
+        <is>
+          <t>XRP_THB</t>
+        </is>
+      </c>
+      <c r="QU13" t="inlineStr">
+        <is>
+          <t>DOGE_THB</t>
+        </is>
+      </c>
+      <c r="QV13" t="inlineStr">
+        <is>
+          <t>BNB_THB</t>
+        </is>
+      </c>
+      <c r="QW13" t="inlineStr">
+        <is>
+          <t>TRX_THB</t>
+        </is>
+      </c>
+      <c r="QX13" t="inlineStr">
+        <is>
+          <t>LINK_THB</t>
+        </is>
+      </c>
+      <c r="QY13" t="inlineStr">
+        <is>
+          <t>XLM_THB</t>
+        </is>
+      </c>
+      <c r="QZ13" t="inlineStr">
+        <is>
+          <t>GALA_THB</t>
+        </is>
+      </c>
+      <c r="RA13" t="inlineStr">
+        <is>
+          <t>VET_THB</t>
+        </is>
+      </c>
+      <c r="RB13" t="inlineStr">
+        <is>
+          <t>ADA_THB</t>
+        </is>
+      </c>
+      <c r="RC13" t="inlineStr">
+        <is>
+          <t>USDC_THB</t>
+        </is>
+      </c>
+      <c r="RD13" t="inlineStr">
+        <is>
+          <t>ETC_THB</t>
+        </is>
+      </c>
+      <c r="RE13" t="inlineStr">
+        <is>
+          <t>XAUT_THB</t>
+        </is>
+      </c>
+      <c r="RF13" t="inlineStr">
+        <is>
+          <t>EOS_THB</t>
+        </is>
+      </c>
+      <c r="RG13" t="inlineStr">
+        <is>
+          <t>ICP_THB</t>
+        </is>
+      </c>
+      <c r="RH13" t="inlineStr">
+        <is>
+          <t>AVAX_THB</t>
+        </is>
+      </c>
+      <c r="RI13" t="inlineStr">
+        <is>
+          <t>NEAR_THB</t>
+        </is>
+      </c>
+      <c r="RJ13" t="inlineStr">
+        <is>
+          <t>FIL_THB</t>
+        </is>
+      </c>
+      <c r="RK13" t="inlineStr">
+        <is>
+          <t>STRK_THB</t>
+        </is>
+      </c>
+      <c r="RL13" t="inlineStr">
+        <is>
+          <t>KITE_THB</t>
+        </is>
+      </c>
+      <c r="RM13" t="inlineStr">
+        <is>
+          <t>W_THB</t>
+        </is>
+      </c>
+      <c r="RN13" t="inlineStr">
+        <is>
+          <t>CFG_THB</t>
+        </is>
+      </c>
+      <c r="RO13" t="inlineStr">
+        <is>
+          <t>NEXO_THB</t>
+        </is>
+      </c>
+      <c r="RP13" t="inlineStr">
+        <is>
+          <t>SENT_THB</t>
+        </is>
+      </c>
+      <c r="RQ13" t="inlineStr">
+        <is>
+          <t>ASTER_THB</t>
+        </is>
+      </c>
+      <c r="RR13" t="inlineStr">
+        <is>
+          <t>FLOW_THB</t>
+        </is>
+      </c>
+      <c r="RS13" t="inlineStr">
+        <is>
+          <t>WLFI_THB</t>
+        </is>
+      </c>
+      <c r="RT13" t="inlineStr">
+        <is>
+          <t>FET_THB</t>
+        </is>
+      </c>
+      <c r="RU13" t="inlineStr">
+        <is>
+          <t>SNX_THB</t>
+        </is>
+      </c>
+      <c r="RV13" t="inlineStr">
+        <is>
+          <t>AAVE_THB</t>
+        </is>
+      </c>
+      <c r="RW13" t="inlineStr">
+        <is>
+          <t>ENJ_THB</t>
+        </is>
+      </c>
+      <c r="RX13" t="inlineStr">
+        <is>
+          <t>WLD_THB</t>
+        </is>
+      </c>
+      <c r="RY13" t="inlineStr">
+        <is>
+          <t>SKY_THB</t>
+        </is>
+      </c>
+      <c r="RZ13" t="inlineStr">
+        <is>
+          <t>TON_THB</t>
+        </is>
+      </c>
+      <c r="SA13" t="inlineStr">
+        <is>
+          <t>PYTH_THB</t>
+        </is>
+      </c>
+      <c r="SB13" t="inlineStr">
+        <is>
+          <t>KAITO_THB</t>
+        </is>
+      </c>
+      <c r="SC13" t="inlineStr">
+        <is>
+          <t>STG_THB</t>
+        </is>
+      </c>
+      <c r="SD13" t="inlineStr">
+        <is>
+          <t>APE_THB</t>
+        </is>
+      </c>
+      <c r="SE13" t="inlineStr">
+        <is>
+          <t>ENS_THB</t>
+        </is>
+      </c>
+      <c r="SF13" t="inlineStr">
+        <is>
+          <t>LIT_THB</t>
+        </is>
+      </c>
+      <c r="SG13" t="inlineStr">
+        <is>
+          <t>CAKE_THB</t>
+        </is>
+      </c>
+      <c r="SH13" t="inlineStr">
+        <is>
+          <t>DEXE_THB</t>
+        </is>
+      </c>
+      <c r="SI13" t="inlineStr">
+        <is>
+          <t>JUP_THB</t>
+        </is>
+      </c>
+      <c r="SJ13" t="inlineStr">
+        <is>
+          <t>ZENT_THB</t>
+        </is>
+      </c>
+      <c r="SK13" t="inlineStr">
+        <is>
+          <t>0G_THB</t>
+        </is>
+      </c>
+      <c r="SL13" t="inlineStr">
+        <is>
+          <t>AXS_THB</t>
+        </is>
+      </c>
+      <c r="SM13" t="inlineStr">
+        <is>
+          <t>SAHARA_THB</t>
+        </is>
+      </c>
+      <c r="SN13" t="inlineStr">
+        <is>
+          <t>CVX_THB</t>
+        </is>
+      </c>
+      <c r="SO13" t="inlineStr">
+        <is>
+          <t>JFIN_THB</t>
+        </is>
+      </c>
+      <c r="SP13" t="inlineStr">
+        <is>
+          <t>TWT_THB</t>
+        </is>
+      </c>
+      <c r="SQ13" t="inlineStr">
+        <is>
+          <t>SUN_THB</t>
+        </is>
+      </c>
+      <c r="SR13" t="inlineStr">
+        <is>
+          <t>MATIC_THB</t>
+        </is>
+      </c>
+      <c r="SS13" t="inlineStr">
+        <is>
+          <t>AVNT_THB</t>
+        </is>
+      </c>
+      <c r="ST13" t="inlineStr">
+        <is>
+          <t>GRASS_THB</t>
+        </is>
+      </c>
+      <c r="SU13" t="inlineStr">
+        <is>
+          <t>ALGO_THB</t>
+        </is>
+      </c>
+      <c r="SV13" t="inlineStr">
+        <is>
+          <t>GNO_THB</t>
+        </is>
+      </c>
+      <c r="SW13" t="inlineStr">
+        <is>
+          <t>HNT_THB</t>
+        </is>
+      </c>
+      <c r="SX13" t="inlineStr">
+        <is>
+          <t>DOT_THB</t>
+        </is>
+      </c>
+      <c r="SY13" t="inlineStr">
+        <is>
+          <t>TUSD_THB</t>
+        </is>
+      </c>
+      <c r="SZ13" t="inlineStr">
+        <is>
+          <t>GRT_THB</t>
+        </is>
+      </c>
+      <c r="TA13" t="inlineStr">
+        <is>
+          <t>AERO_THB</t>
+        </is>
+      </c>
+      <c r="TB13" t="inlineStr">
+        <is>
+          <t>YFI_THB</t>
+        </is>
+      </c>
+      <c r="TC13" t="inlineStr">
+        <is>
+          <t>MANA_THB</t>
+        </is>
+      </c>
+      <c r="TD13" t="inlineStr">
+        <is>
+          <t>QNT_THB</t>
+        </is>
+      </c>
+      <c r="TE13" t="inlineStr">
+        <is>
+          <t>COMP_THB</t>
+        </is>
+      </c>
+      <c r="TF13" t="inlineStr">
+        <is>
+          <t>CRV_THB</t>
+        </is>
+      </c>
+      <c r="TG13" t="inlineStr">
+        <is>
+          <t>KMNO_THB</t>
+        </is>
+      </c>
+      <c r="TH13" t="inlineStr">
+        <is>
+          <t>ARB_THB</t>
+        </is>
+      </c>
+      <c r="TI13" t="inlineStr">
+        <is>
+          <t>JST_THB</t>
+        </is>
+      </c>
+      <c r="TJ13" t="inlineStr">
+        <is>
+          <t>UNI_THB</t>
+        </is>
+      </c>
+      <c r="TK13" t="inlineStr">
+        <is>
+          <t>VIRTUAL_THB</t>
+        </is>
+      </c>
+      <c r="TL13" t="inlineStr">
+        <is>
+          <t>ENA_THB</t>
+        </is>
+      </c>
+      <c r="TM13" t="inlineStr">
+        <is>
+          <t>ZRX_THB</t>
+        </is>
+      </c>
+      <c r="TN13" t="inlineStr">
+        <is>
+          <t>ATH_THB</t>
+        </is>
+      </c>
+      <c r="TO13" t="inlineStr">
+        <is>
+          <t>VVV_THB</t>
+        </is>
+      </c>
+      <c r="TP13" t="inlineStr">
+        <is>
+          <t>PENDLE_THB</t>
+        </is>
+      </c>
+      <c r="TQ13" t="inlineStr">
+        <is>
+          <t>IMX_THB</t>
+        </is>
+      </c>
+      <c r="TR13" t="inlineStr">
+        <is>
+          <t>1INCH_THB</t>
+        </is>
+      </c>
+      <c r="TS13" t="inlineStr">
+        <is>
+          <t>RAY_THB</t>
+        </is>
+      </c>
+      <c r="TT13" t="inlineStr">
+        <is>
+          <t>MORPHO_THB</t>
+        </is>
+      </c>
+      <c r="TU13" t="inlineStr">
+        <is>
+          <t>PAXG_THB</t>
+        </is>
+      </c>
+      <c r="TV13" t="inlineStr">
+        <is>
+          <t>USD1_THB</t>
+        </is>
+      </c>
+      <c r="TW13" t="inlineStr">
+        <is>
+          <t>RENDER_THB</t>
+        </is>
+      </c>
+      <c r="TX13" t="inlineStr">
+        <is>
+          <t>JTO_THB</t>
+        </is>
+      </c>
+      <c r="TY13" t="inlineStr">
+        <is>
+          <t>SAND_THB</t>
+        </is>
+      </c>
+      <c r="TZ13" t="inlineStr">
+        <is>
+          <t>RSR_THB</t>
+        </is>
+      </c>
+      <c r="UA13" t="inlineStr">
+        <is>
+          <t>ZRO_THB</t>
+        </is>
+      </c>
+      <c r="UB13" t="inlineStr">
+        <is>
+          <t>LPT_THB</t>
+        </is>
+      </c>
+      <c r="UC13" t="inlineStr">
+        <is>
+          <t>BAT_THB</t>
+        </is>
+      </c>
+      <c r="UD13" t="inlineStr">
+        <is>
+          <t>NXPC_THB</t>
+        </is>
+      </c>
+      <c r="UE13" t="inlineStr">
+        <is>
+          <t>EIGEN_THB</t>
+        </is>
+      </c>
+      <c r="UF13" t="inlineStr">
+        <is>
+          <t>BAND_THB</t>
+        </is>
+      </c>
+      <c r="UG13" t="inlineStr">
+        <is>
+          <t>LDO_THB</t>
+        </is>
+      </c>
+      <c r="UH13" t="inlineStr">
+        <is>
+          <t>XPL_THB</t>
+        </is>
+      </c>
+      <c r="UI13" t="inlineStr">
+        <is>
+          <t>ONDO_THB</t>
+        </is>
+      </c>
+      <c r="UJ13" t="inlineStr">
+        <is>
+          <t>OP_THB</t>
+        </is>
+      </c>
+      <c r="UK13" t="inlineStr">
+        <is>
+          <t>ATOM_THB</t>
+        </is>
+      </c>
+      <c r="UL13" t="inlineStr">
+        <is>
+          <t>XTZ_THB</t>
+        </is>
+      </c>
+      <c r="UM13" t="inlineStr">
+        <is>
+          <t>ORCA_THB</t>
+        </is>
+      </c>
+      <c r="UN13" t="inlineStr">
+        <is>
+          <t>BCH_THB</t>
+        </is>
+      </c>
+      <c r="UO13" t="inlineStr">
+        <is>
+          <t>BETA_THB</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>558763983.42</v>
+        <v>551045348.6900001</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>84235751.65000001</v>
+        <v>220476615.52</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>33822631.66</v>
+        <v>93178984.48</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>16206221.05</v>
+        <v>90275120.17</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>8641198.48</v>
+        <v>44989755.94</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>26278632.55</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>349792699.51</v>
+        <v>13335243.7</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>55889180.66205</v>
+        <v>10099228.43</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>9437128.48</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>1234378.8297</v>
+        <v>8535555.85</v>
       </c>
       <c r="M14" s="1" t="n">
-        <v>1125889.5078</v>
+        <v>7416404.98</v>
       </c>
       <c r="N14" s="1" t="n">
-        <v>1093867.338</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>17</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>558774049.83</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>84235751.65000001</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>33819519.53</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>16206221.05</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>8641198.48</v>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>349792699.51</v>
-      </c>
-      <c r="J15" s="1" t="n">
-        <v>55889180.66205</v>
-      </c>
-      <c r="L15" s="1" t="n">
-        <v>1234378.8297</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>1125889.5078</v>
-      </c>
-      <c r="N15" s="1" t="n">
-        <v>1093867.338</v>
+        <v>7133349.27</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>6267456.57</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>5494513.19</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>4735275.25</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>4429958.82</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>4422071.5</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>4391644.61</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>4382967.2</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>4284604.03</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>4227227.21</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>4167827.42</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>4077416.43</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>3994272.02</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>3438591.1</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>2991090.99</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>2773846.88</v>
+      </c>
+      <c r="AD14" s="1" t="n">
+        <v>2751353.2</v>
+      </c>
+      <c r="AE14" s="1" t="n">
+        <v>2416640.08</v>
+      </c>
+      <c r="AF14" s="1" t="n">
+        <v>2392320.44</v>
+      </c>
+      <c r="AG14" s="1" t="n">
+        <v>2368739.96</v>
+      </c>
+      <c r="AH14" s="1" t="n">
+        <v>2315694.22</v>
+      </c>
+      <c r="AI14" s="1" t="n">
+        <v>2019163.94</v>
+      </c>
+      <c r="AJ14" s="1" t="n">
+        <v>1900190.83</v>
+      </c>
+      <c r="AK14" s="1" t="n">
+        <v>1878865.13</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>1864882.94</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>1775582.11</v>
+      </c>
+      <c r="AN14" s="1" t="n">
+        <v>1726714.84</v>
+      </c>
+      <c r="AO14" s="1" t="n">
+        <v>1707768.09</v>
+      </c>
+      <c r="AP14" s="1" t="n">
+        <v>1640885.13</v>
+      </c>
+      <c r="AQ14" s="1" t="n">
+        <v>1587235.59</v>
+      </c>
+      <c r="AR14" s="1" t="n">
+        <v>1542377.54</v>
+      </c>
+      <c r="AS14" s="1" t="n">
+        <v>1511880.67</v>
+      </c>
+      <c r="AT14" s="1" t="n">
+        <v>1466811.86</v>
+      </c>
+      <c r="AU14" s="1" t="n">
+        <v>1289350.65</v>
+      </c>
+      <c r="AV14" s="1" t="n">
+        <v>1282075.72</v>
+      </c>
+      <c r="AW14" s="1" t="n">
+        <v>1137834.56</v>
+      </c>
+      <c r="AX14" s="1" t="n">
+        <v>1116462.58</v>
+      </c>
+      <c r="AY14" s="1" t="n">
+        <v>1076872.16</v>
+      </c>
+      <c r="AZ14" s="1" t="n">
+        <v>1007930.29</v>
+      </c>
+      <c r="BA14" s="1" t="n">
+        <v>1005829.97</v>
+      </c>
+      <c r="BB14" s="1" t="n">
+        <v>998676.75</v>
+      </c>
+      <c r="BC14" s="1" t="n">
+        <v>991616.86</v>
+      </c>
+      <c r="BD14" s="1" t="n">
+        <v>928916.53</v>
+      </c>
+      <c r="BE14" s="1" t="n">
+        <v>903301.92</v>
+      </c>
+      <c r="BF14" s="1" t="n">
+        <v>880883.55</v>
+      </c>
+      <c r="BG14" s="1" t="n">
+        <v>877166.76</v>
+      </c>
+      <c r="BH14" s="1" t="n">
+        <v>862014.58</v>
+      </c>
+      <c r="BI14" s="1" t="n">
+        <v>848368.67</v>
+      </c>
+      <c r="BJ14" s="1" t="n">
+        <v>815950.35</v>
+      </c>
+      <c r="BK14" s="1" t="n">
+        <v>799499.36</v>
+      </c>
+      <c r="BL14" s="1" t="n">
+        <v>783991.2</v>
+      </c>
+      <c r="BM14" s="1" t="n">
+        <v>725123.72</v>
+      </c>
+      <c r="BN14" s="1" t="n">
+        <v>712773.98</v>
+      </c>
+      <c r="BO14" s="1" t="n">
+        <v>691293.52</v>
+      </c>
+      <c r="BP14" s="1" t="n">
+        <v>669685.15</v>
+      </c>
+      <c r="BQ14" s="1" t="n">
+        <v>658575.38</v>
+      </c>
+      <c r="BR14" s="1" t="n">
+        <v>613615.9300000001</v>
+      </c>
+      <c r="BS14" s="1" t="n">
+        <v>612209.14</v>
+      </c>
+      <c r="BT14" s="1" t="n">
+        <v>606043.35</v>
+      </c>
+      <c r="BU14" s="1" t="n">
+        <v>566528.22</v>
+      </c>
+      <c r="BV14" s="1" t="n">
+        <v>544055.21</v>
+      </c>
+      <c r="BW14" s="1" t="n">
+        <v>506257.37</v>
+      </c>
+      <c r="BX14" s="1" t="n">
+        <v>494419.97</v>
+      </c>
+      <c r="BY14" s="1" t="n">
+        <v>426535.81</v>
+      </c>
+      <c r="BZ14" s="1" t="n">
+        <v>417269.18</v>
+      </c>
+      <c r="CA14" s="1" t="n">
+        <v>416214.11</v>
+      </c>
+      <c r="CB14" s="1" t="n">
+        <v>410892.66</v>
+      </c>
+      <c r="CC14" s="1" t="n">
+        <v>405059.54</v>
+      </c>
+      <c r="CD14" s="1" t="n">
+        <v>374057.17</v>
+      </c>
+      <c r="CE14" s="1" t="n">
+        <v>361856.83</v>
+      </c>
+      <c r="CF14" s="1" t="n">
+        <v>337233.98</v>
+      </c>
+      <c r="CG14" s="1" t="n">
+        <v>328609.74</v>
+      </c>
+      <c r="CH14" s="1" t="n">
+        <v>324925.09</v>
+      </c>
+      <c r="CI14" s="1" t="n">
+        <v>321236.64</v>
+      </c>
+      <c r="CJ14" s="1" t="n">
+        <v>317982.47</v>
+      </c>
+      <c r="CK14" s="1" t="n">
+        <v>314653.83</v>
+      </c>
+      <c r="CL14" s="1" t="n">
+        <v>312641.95</v>
+      </c>
+      <c r="CM14" s="1" t="n">
+        <v>306827.74</v>
+      </c>
+      <c r="CN14" s="1" t="n">
+        <v>299169.93</v>
+      </c>
+      <c r="CO14" s="1" t="n">
+        <v>296858.35</v>
+      </c>
+      <c r="CP14" s="1" t="n">
+        <v>294090.6</v>
+      </c>
+      <c r="CQ14" s="1" t="n">
+        <v>271350.19</v>
+      </c>
+      <c r="CR14" s="1" t="n">
+        <v>254504.23</v>
+      </c>
+      <c r="CS14" s="1" t="n">
+        <v>251337.19</v>
+      </c>
+      <c r="CT14" s="1" t="n">
+        <v>246667.8</v>
+      </c>
+      <c r="CU14" s="1" t="n">
+        <v>239140.38</v>
+      </c>
+      <c r="CV14" s="1" t="n">
+        <v>236812.1</v>
+      </c>
+      <c r="CW14" s="1" t="n">
+        <v>236186.81</v>
+      </c>
+      <c r="CX14" s="1" t="n">
+        <v>236054.04</v>
+      </c>
+      <c r="CY14" s="1" t="n">
+        <v>227441.07</v>
+      </c>
+      <c r="CZ14" s="1" t="n">
+        <v>218959.8</v>
+      </c>
+      <c r="DA14" s="1" t="n">
+        <v>214912.01</v>
+      </c>
+      <c r="DB14" s="1" t="n">
+        <v>208648.19</v>
+      </c>
+      <c r="DC14" s="1" t="n">
+        <v>206152.62</v>
+      </c>
+      <c r="DD14" s="1" t="n">
+        <v>197620.01</v>
+      </c>
+      <c r="DE14" s="1" t="n">
+        <v>196756.47</v>
+      </c>
+      <c r="DF14" s="1" t="n">
+        <v>194923</v>
+      </c>
+      <c r="DG14" s="1" t="n">
+        <v>193516.03</v>
+      </c>
+      <c r="DH14" s="1" t="n">
+        <v>189577.94</v>
+      </c>
+      <c r="DI14" s="1" t="n">
+        <v>186300.69</v>
+      </c>
+      <c r="DJ14" s="1" t="n">
+        <v>186057.51</v>
+      </c>
+      <c r="DK14" s="1" t="n">
+        <v>170654.29</v>
+      </c>
+      <c r="DL14" s="1" t="n">
+        <v>170447.8</v>
+      </c>
+      <c r="DM14" s="1" t="n">
+        <v>164837.35</v>
+      </c>
+      <c r="DN14" s="1" t="n">
+        <v>163871.54</v>
+      </c>
+      <c r="DO14" s="1" t="n">
+        <v>158187.67</v>
+      </c>
+      <c r="DP14" s="1" t="n">
+        <v>156315.62</v>
+      </c>
+      <c r="DQ14" s="1" t="n">
+        <v>153334.24</v>
+      </c>
+      <c r="DR14" s="1" t="n">
+        <v>152065.49</v>
+      </c>
+      <c r="DS14" s="1" t="n">
+        <v>149788.23</v>
+      </c>
+      <c r="DT14" s="1" t="n">
+        <v>148544.24</v>
+      </c>
+      <c r="DU14" s="1" t="n">
+        <v>140768.14</v>
+      </c>
+      <c r="DV14" s="1" t="n">
+        <v>140469.43</v>
+      </c>
+      <c r="DW14" s="1" t="n">
+        <v>135243.2</v>
+      </c>
+      <c r="DX14" s="1" t="n">
+        <v>132435.48</v>
+      </c>
+      <c r="DY14" s="1" t="n">
+        <v>131969.53</v>
+      </c>
+      <c r="DZ14" s="1" t="n">
+        <v>130030.6</v>
+      </c>
+      <c r="EA14" s="1" t="n">
+        <v>127589.76</v>
+      </c>
+      <c r="EB14" s="1" t="n">
+        <v>125680.96</v>
+      </c>
+      <c r="EC14" s="1" t="n">
+        <v>124847.87</v>
+      </c>
+      <c r="ED14" s="1" t="n">
+        <v>124154.52</v>
+      </c>
+      <c r="EE14" s="1" t="n">
+        <v>117354.31</v>
+      </c>
+      <c r="EF14" s="1" t="n">
+        <v>115178.53</v>
+      </c>
+      <c r="EG14" s="1" t="n">
+        <v>115052.19</v>
+      </c>
+      <c r="EH14" s="1" t="n">
+        <v>114086.72</v>
+      </c>
+      <c r="EI14" s="1" t="n">
+        <v>113143.47</v>
+      </c>
+      <c r="EJ14" s="1" t="n">
+        <v>102804.19</v>
+      </c>
+      <c r="EK14" s="1" t="n">
+        <v>102166.98</v>
+      </c>
+      <c r="EL14" s="1" t="n">
+        <v>98080.77</v>
+      </c>
+      <c r="EM14" s="1" t="n">
+        <v>97540.22</v>
+      </c>
+      <c r="EN14" s="1" t="n">
+        <v>97497.53</v>
+      </c>
+      <c r="EO14" s="1" t="n">
+        <v>93014.25</v>
+      </c>
+      <c r="EP14" s="1" t="n">
+        <v>88793.35000000001</v>
+      </c>
+      <c r="EQ14" s="1" t="n">
+        <v>87988.47</v>
+      </c>
+      <c r="ER14" s="1" t="n">
+        <v>87062.16</v>
+      </c>
+      <c r="ES14" s="1" t="n">
+        <v>86620.41</v>
+      </c>
+      <c r="ET14" s="1" t="n">
+        <v>83600.14999999999</v>
+      </c>
+      <c r="EU14" s="1" t="n">
+        <v>81902.35000000001</v>
+      </c>
+      <c r="EV14" s="1" t="n">
+        <v>81484.5</v>
+      </c>
+      <c r="EW14" s="1" t="n">
+        <v>77459.72</v>
+      </c>
+      <c r="EX14" s="1" t="n">
+        <v>73209.32000000001</v>
+      </c>
+      <c r="EY14" s="1" t="n">
+        <v>71841.47</v>
+      </c>
+      <c r="EZ14" s="1" t="n">
+        <v>71613.27</v>
+      </c>
+      <c r="FA14" s="1" t="n">
+        <v>70884</v>
+      </c>
+      <c r="FB14" s="1" t="n">
+        <v>70583.37</v>
+      </c>
+      <c r="FC14" s="1" t="n">
+        <v>70268.81</v>
+      </c>
+      <c r="FD14" s="1" t="n">
+        <v>69656.67</v>
+      </c>
+      <c r="FE14" s="1" t="n">
+        <v>67355.99000000001</v>
+      </c>
+      <c r="FF14" s="1" t="n">
+        <v>66641.42</v>
+      </c>
+      <c r="FG14" s="1" t="n">
+        <v>66440.89999999999</v>
+      </c>
+      <c r="FH14" s="1" t="n">
+        <v>66407.73</v>
+      </c>
+      <c r="FI14" s="1" t="n">
+        <v>65624.87</v>
+      </c>
+      <c r="FJ14" s="1" t="n">
+        <v>65282.99</v>
+      </c>
+      <c r="FK14" s="1" t="n">
+        <v>64885.44</v>
+      </c>
+      <c r="FL14" s="1" t="n">
+        <v>61892.37</v>
+      </c>
+      <c r="FM14" s="1" t="n">
+        <v>61598.86</v>
+      </c>
+      <c r="FN14" s="1" t="n">
+        <v>60499.98</v>
+      </c>
+      <c r="FO14" s="1" t="n">
+        <v>60364.33</v>
+      </c>
+      <c r="FP14" s="1" t="n">
+        <v>59446.99</v>
+      </c>
+      <c r="FQ14" s="1" t="n">
+        <v>58316.4</v>
+      </c>
+      <c r="FR14" s="1" t="n">
+        <v>58103.13</v>
+      </c>
+      <c r="FS14" s="1" t="n">
+        <v>55809.34</v>
+      </c>
+      <c r="FT14" s="1" t="n">
+        <v>53851.11</v>
+      </c>
+      <c r="FU14" s="1" t="n">
+        <v>52625.96</v>
+      </c>
+      <c r="FV14" s="1" t="n">
+        <v>52096</v>
+      </c>
+      <c r="FW14" s="1" t="n">
+        <v>49681.41</v>
+      </c>
+      <c r="FX14" s="1" t="n">
+        <v>49147.34</v>
+      </c>
+      <c r="FY14" s="1" t="n">
+        <v>48729.06</v>
+      </c>
+      <c r="FZ14" s="1" t="n">
+        <v>47369.74</v>
+      </c>
+      <c r="GA14" s="1" t="n">
+        <v>45591.51</v>
+      </c>
+      <c r="GB14" s="1" t="n">
+        <v>45172.21</v>
+      </c>
+      <c r="GC14" s="1" t="n">
+        <v>44754.93</v>
+      </c>
+      <c r="GD14" s="1" t="n">
+        <v>43927.97</v>
+      </c>
+      <c r="GE14" s="1" t="n">
+        <v>42266.15</v>
+      </c>
+      <c r="GF14" s="1" t="n">
+        <v>42093.86</v>
+      </c>
+      <c r="GG14" s="1" t="n">
+        <v>41190.07</v>
+      </c>
+      <c r="GH14" s="1" t="n">
+        <v>40992.87</v>
+      </c>
+      <c r="GI14" s="1" t="n">
+        <v>40904.4</v>
+      </c>
+      <c r="GJ14" s="1" t="n">
+        <v>40123.28</v>
+      </c>
+      <c r="GK14" s="1" t="n">
+        <v>39022.98</v>
+      </c>
+      <c r="GL14" s="1" t="n">
+        <v>37911.35</v>
+      </c>
+      <c r="GM14" s="1" t="n">
+        <v>37769.43</v>
+      </c>
+      <c r="GN14" s="1" t="n">
+        <v>36869.97</v>
+      </c>
+      <c r="GO14" s="1" t="n">
+        <v>35235.17</v>
+      </c>
+      <c r="GP14" s="1" t="n">
+        <v>35004.75</v>
+      </c>
+      <c r="GQ14" s="1" t="n">
+        <v>34313.76</v>
+      </c>
+      <c r="GR14" s="1" t="n">
+        <v>34246.99</v>
+      </c>
+      <c r="GS14" s="1" t="n">
+        <v>33991.57</v>
+      </c>
+      <c r="GT14" s="1" t="n">
+        <v>33756.95</v>
+      </c>
+      <c r="GU14" s="1" t="n">
+        <v>33113.92</v>
+      </c>
+      <c r="GV14" s="1" t="n">
+        <v>32317.41</v>
+      </c>
+      <c r="GW14" s="1" t="n">
+        <v>31798.75</v>
+      </c>
+      <c r="GX14" s="1" t="n">
+        <v>31789.85</v>
+      </c>
+      <c r="GY14" s="1" t="n">
+        <v>31786.5</v>
+      </c>
+      <c r="GZ14" s="1" t="n">
+        <v>29666.9</v>
+      </c>
+      <c r="HA14" s="1" t="n">
+        <v>28479.01</v>
+      </c>
+      <c r="HB14" s="1" t="n">
+        <v>28474.18</v>
+      </c>
+      <c r="HC14" s="1" t="n">
+        <v>28284.74</v>
+      </c>
+      <c r="HD14" s="1" t="n">
+        <v>28143.68</v>
+      </c>
+      <c r="HE14" s="1" t="n">
+        <v>26429.6</v>
+      </c>
+      <c r="HF14" s="1" t="n">
+        <v>25788.69</v>
+      </c>
+      <c r="HG14" s="1" t="n">
+        <v>24432.49</v>
+      </c>
+      <c r="HH14" s="1" t="n">
+        <v>23768.32</v>
+      </c>
+      <c r="HI14" s="1" t="n">
+        <v>23296.08</v>
+      </c>
+      <c r="HJ14" s="1" t="n">
+        <v>22507.23</v>
+      </c>
+      <c r="HK14" s="1" t="n">
+        <v>21613.59</v>
+      </c>
+      <c r="HL14" s="1" t="n">
+        <v>21411.87</v>
+      </c>
+      <c r="HM14" s="1" t="n">
+        <v>21264.1</v>
+      </c>
+      <c r="HN14" s="1" t="n">
+        <v>21079.95</v>
+      </c>
+      <c r="HO14" s="1" t="n">
+        <v>20892.93</v>
+      </c>
+      <c r="HP14" s="1" t="n">
+        <v>20227.42</v>
+      </c>
+      <c r="HQ14" s="1" t="n">
+        <v>20080.69</v>
+      </c>
+      <c r="HR14" s="1" t="n">
+        <v>19732.8</v>
+      </c>
+      <c r="HS14" s="1" t="n">
+        <v>18332.36</v>
+      </c>
+      <c r="HT14" s="1" t="n">
+        <v>18186.47</v>
+      </c>
+      <c r="HU14" s="1" t="n">
+        <v>18080.82</v>
+      </c>
+      <c r="HV14" s="1" t="n">
+        <v>17890.08</v>
+      </c>
+      <c r="HW14" s="1" t="n">
+        <v>17366.49</v>
+      </c>
+      <c r="HX14" s="1" t="n">
+        <v>17156.02</v>
+      </c>
+      <c r="HY14" s="1" t="n">
+        <v>16423.79</v>
+      </c>
+      <c r="HZ14" s="1" t="n">
+        <v>15432.78</v>
+      </c>
+      <c r="IA14" s="1" t="n">
+        <v>15359.03</v>
+      </c>
+      <c r="IB14" s="1" t="n">
+        <v>15012.44</v>
+      </c>
+      <c r="IC14" s="1" t="n">
+        <v>14902.64</v>
+      </c>
+      <c r="ID14" s="1" t="n">
+        <v>14831.45</v>
+      </c>
+      <c r="IE14" s="1" t="n">
+        <v>14275.85</v>
+      </c>
+      <c r="IF14" s="1" t="n">
+        <v>13097.69</v>
+      </c>
+      <c r="IG14" s="1" t="n">
+        <v>13046</v>
+      </c>
+      <c r="IH14" s="1" t="n">
+        <v>11668.78</v>
+      </c>
+      <c r="II14" s="1" t="n">
+        <v>11217.72</v>
+      </c>
+      <c r="IJ14" s="1" t="n">
+        <v>11007.18</v>
+      </c>
+      <c r="IK14" s="1" t="n">
+        <v>9974.91</v>
+      </c>
+      <c r="IL14" s="1" t="n">
+        <v>9574.049999999999</v>
+      </c>
+      <c r="IM14" s="1" t="n">
+        <v>9567.16</v>
+      </c>
+      <c r="IN14" s="1" t="n">
+        <v>9180.469999999999</v>
+      </c>
+      <c r="IO14" s="1" t="n">
+        <v>8672.4</v>
+      </c>
+      <c r="IP14" s="1" t="n">
+        <v>8265.66</v>
+      </c>
+      <c r="IQ14" s="1" t="n">
+        <v>7659.74</v>
+      </c>
+      <c r="IR14" s="1" t="n">
+        <v>7089.37</v>
+      </c>
+      <c r="IS14" s="1" t="n">
+        <v>6772.89</v>
+      </c>
+      <c r="IT14" s="1" t="n">
+        <v>6399.17</v>
+      </c>
+      <c r="IU14" s="1" t="n">
+        <v>6359.69</v>
+      </c>
+      <c r="IV14" s="1" t="n">
+        <v>5946.13</v>
+      </c>
+      <c r="IW14" s="1" t="n">
+        <v>5740</v>
+      </c>
+      <c r="IX14" s="1" t="n">
+        <v>5281.4</v>
+      </c>
+      <c r="IY14" s="1" t="n">
+        <v>5154.27</v>
+      </c>
+      <c r="IZ14" s="1" t="n">
+        <v>5083.47</v>
+      </c>
+      <c r="JA14" s="1" t="n">
+        <v>5043.86</v>
+      </c>
+      <c r="JB14" s="1" t="n">
+        <v>4949.16</v>
+      </c>
+      <c r="JC14" s="1" t="n">
+        <v>4863.59</v>
+      </c>
+      <c r="JD14" s="1" t="n">
+        <v>4785.82</v>
+      </c>
+      <c r="JE14" s="1" t="n">
+        <v>4774.94</v>
+      </c>
+      <c r="JF14" s="1" t="n">
+        <v>4771.78</v>
+      </c>
+      <c r="JG14" s="1" t="n">
+        <v>4465.41</v>
+      </c>
+      <c r="JH14" s="1" t="n">
+        <v>4353.95</v>
+      </c>
+      <c r="JI14" s="1" t="n">
+        <v>4289.84</v>
+      </c>
+      <c r="JJ14" s="1" t="n">
+        <v>3811.39</v>
+      </c>
+      <c r="JK14" s="1" t="n">
+        <v>3714.62</v>
+      </c>
+      <c r="JL14" s="1" t="n">
+        <v>3637.52</v>
+      </c>
+      <c r="JM14" s="1" t="n">
+        <v>3516.97</v>
+      </c>
+      <c r="JN14" s="1" t="n">
+        <v>3490.38</v>
+      </c>
+      <c r="JO14" s="1" t="n">
+        <v>2990.88</v>
+      </c>
+      <c r="JP14" s="1" t="n">
+        <v>2987.32</v>
+      </c>
+      <c r="JQ14" s="1" t="n">
+        <v>2942.64</v>
+      </c>
+      <c r="JR14" s="1" t="n">
+        <v>2902.42</v>
+      </c>
+      <c r="JS14" s="1" t="n">
+        <v>2825.94</v>
+      </c>
+      <c r="JT14" s="1" t="n">
+        <v>2813.65</v>
+      </c>
+      <c r="JU14" s="1" t="n">
+        <v>2723.48</v>
+      </c>
+      <c r="JV14" s="1" t="n">
+        <v>2629.41</v>
+      </c>
+      <c r="JW14" s="1" t="n">
+        <v>2600.84</v>
+      </c>
+      <c r="JX14" s="1" t="n">
+        <v>2241.08</v>
+      </c>
+      <c r="JY14" s="1" t="n">
+        <v>2140.63</v>
+      </c>
+      <c r="JZ14" s="1" t="n">
+        <v>2110.22</v>
+      </c>
+      <c r="KA14" s="1" t="n">
+        <v>1971.66</v>
+      </c>
+      <c r="KB14" s="1" t="n">
+        <v>1968.05</v>
+      </c>
+      <c r="KC14" s="1" t="n">
+        <v>1894.02</v>
+      </c>
+      <c r="KD14" s="1" t="n">
+        <v>1843.25</v>
+      </c>
+      <c r="KE14" s="1" t="n">
+        <v>1833.64</v>
+      </c>
+      <c r="KF14" s="1" t="n">
+        <v>1791.2</v>
+      </c>
+      <c r="KG14" s="1" t="n">
+        <v>1698.14</v>
+      </c>
+      <c r="KH14" s="1" t="n">
+        <v>1623.34</v>
+      </c>
+      <c r="KI14" s="1" t="n">
+        <v>1594.89</v>
+      </c>
+      <c r="KJ14" s="1" t="n">
+        <v>1583.98</v>
+      </c>
+      <c r="KK14" s="1" t="n">
+        <v>1454.51</v>
+      </c>
+      <c r="KL14" s="1" t="n">
+        <v>1393.82</v>
+      </c>
+      <c r="KM14" s="1" t="n">
+        <v>1330.47</v>
+      </c>
+      <c r="KN14" s="1" t="n">
+        <v>1313.3</v>
+      </c>
+      <c r="KO14" s="1" t="n">
+        <v>1209.14</v>
+      </c>
+      <c r="KP14" s="1" t="n">
+        <v>1168.02</v>
+      </c>
+      <c r="KQ14" s="1" t="n">
+        <v>1132.97</v>
+      </c>
+      <c r="KR14" s="1" t="n">
+        <v>1119.87</v>
+      </c>
+      <c r="KS14" s="1" t="n">
+        <v>1111.06</v>
+      </c>
+      <c r="KT14" s="1" t="n">
+        <v>1094.15</v>
+      </c>
+      <c r="KU14" s="1" t="n">
+        <v>995.96</v>
+      </c>
+      <c r="KV14" s="1" t="n">
+        <v>893.9400000000001</v>
+      </c>
+      <c r="KW14" s="1" t="n">
+        <v>856.76</v>
+      </c>
+      <c r="KX14" s="1" t="n">
+        <v>850.1799999999999</v>
+      </c>
+      <c r="KY14" s="1" t="n">
+        <v>804.01</v>
+      </c>
+      <c r="KZ14" s="1" t="n">
+        <v>788.62</v>
+      </c>
+      <c r="LA14" s="1" t="n">
+        <v>759.1</v>
+      </c>
+      <c r="LB14" s="1" t="n">
+        <v>742.12</v>
+      </c>
+      <c r="LC14" s="1" t="n">
+        <v>730.87</v>
+      </c>
+      <c r="LD14" s="1" t="n">
+        <v>685.38</v>
+      </c>
+      <c r="LE14" s="1" t="n">
+        <v>614.91</v>
+      </c>
+      <c r="LF14" s="1" t="n">
+        <v>572.55</v>
+      </c>
+      <c r="LG14" s="1" t="n">
+        <v>559.92</v>
+      </c>
+      <c r="LH14" s="1" t="n">
+        <v>501.26</v>
+      </c>
+      <c r="LI14" s="1" t="n">
+        <v>451.31</v>
+      </c>
+      <c r="LJ14" s="1" t="n">
+        <v>449.6</v>
+      </c>
+      <c r="LK14" s="1" t="n">
+        <v>403.38</v>
+      </c>
+      <c r="LL14" s="1" t="n">
+        <v>398.52</v>
+      </c>
+      <c r="LM14" s="1" t="n">
+        <v>398.41</v>
+      </c>
+      <c r="LN14" s="1" t="n">
+        <v>333.45</v>
+      </c>
+      <c r="LO14" s="1" t="n">
+        <v>311.62</v>
+      </c>
+      <c r="LP14" s="1" t="n">
+        <v>300.44</v>
+      </c>
+      <c r="LQ14" s="1" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="LR14" s="1" t="n">
+        <v>258.23</v>
+      </c>
+      <c r="LS14" s="1" t="n">
+        <v>248.89</v>
+      </c>
+      <c r="LT14" s="1" t="n">
+        <v>245.45</v>
+      </c>
+      <c r="LU14" s="1" t="n">
+        <v>228.63</v>
+      </c>
+      <c r="LV14" s="1" t="n">
+        <v>222.74</v>
+      </c>
+      <c r="LW14" s="1" t="n">
+        <v>216.66</v>
+      </c>
+      <c r="LX14" s="1" t="n">
+        <v>211.35</v>
+      </c>
+      <c r="LY14" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="LZ14" s="1" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="MA14" s="1" t="n">
+        <v>199.48</v>
+      </c>
+      <c r="MB14" s="1" t="n">
+        <v>199.47</v>
+      </c>
+      <c r="MC14" s="1" t="n">
+        <v>199.47</v>
+      </c>
+      <c r="MD14" s="1" t="n">
+        <v>199.31</v>
+      </c>
+      <c r="ME14" s="1" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="MF14" s="1" t="n">
+        <v>195.4</v>
+      </c>
+      <c r="MG14" s="1" t="n">
+        <v>194.98</v>
+      </c>
+      <c r="MH14" s="1" t="n">
+        <v>191.87</v>
+      </c>
+      <c r="MI14" s="1" t="n">
+        <v>186.93</v>
+      </c>
+      <c r="MJ14" s="1" t="n">
+        <v>129.65</v>
+      </c>
+      <c r="MK14" s="1" t="n">
+        <v>113.44</v>
+      </c>
+      <c r="ML14" s="1" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="MM14" s="1" t="n">
+        <v>107.07</v>
+      </c>
+      <c r="MN14" s="1" t="n">
+        <v>106.03</v>
+      </c>
+      <c r="MO14" s="1" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="MP14" s="1" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="MQ14" s="1" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="MR14" s="1" t="n">
+        <v>92.54000000000001</v>
+      </c>
+      <c r="MS14" s="1" t="n">
+        <v>87.95</v>
+      </c>
+      <c r="MT14" s="1" t="n">
+        <v>80.08</v>
+      </c>
+      <c r="MU14" s="1" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="MV14" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="MW14" s="1" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="MX14" s="1" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="MY14" s="1" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="MZ14" s="1" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="NA14" s="1" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="NB14" s="1" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="NC14" s="1" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="ND14" s="1" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="NE14" s="1" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="NF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NG14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NH14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NI14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NK14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NL14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NM14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NN14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NO14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NP14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NQ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NR14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NS14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NT14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NU14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NW14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NX14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NY14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NZ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OC14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OD14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OG14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OH14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OI14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OK14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OL14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OM14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ON14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OO14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OP14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OQ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OR14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OS14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OT14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OU14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OW14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OX14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OY14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OZ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PC14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PD14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PG14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PH14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PI14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PK14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PL14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PM14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PN14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PO14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PP14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PQ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PR14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PS14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PT14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PU14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PW14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PX14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PY14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PZ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QC14" s="1" t="n">
+        <v>509829468.19</v>
+      </c>
+      <c r="QD14" s="1" t="n">
+        <v>64769141.71668</v>
+      </c>
+      <c r="QF14" s="1" t="n">
+        <v>10480182.4452</v>
+      </c>
+      <c r="QG14" s="1" t="n">
+        <v>6117432.4433</v>
+      </c>
+      <c r="QH14" s="1" t="n">
+        <v>1970255.447</v>
+      </c>
+      <c r="QI14" s="1" t="n">
+        <v>1781970.7054</v>
+      </c>
+      <c r="QJ14" s="1" t="n">
+        <v>939451.5763</v>
+      </c>
+      <c r="QK14" s="1" t="n">
+        <v>175565.0978</v>
+      </c>
+      <c r="QL14" s="1" t="n">
+        <v>10962.4476</v>
+      </c>
+      <c r="QM14" s="1" t="n">
+        <v>8360.57674</v>
+      </c>
+      <c r="QN14" s="1" t="n">
+        <v>903.806649</v>
+      </c>
+      <c r="QO14" s="1" t="n">
+        <v>10983319.22900662</v>
+      </c>
+      <c r="QP14" s="1" t="n">
+        <v>6432562.173783358</v>
+      </c>
+      <c r="QR14" s="1" t="n">
+        <v>2870747.687850092</v>
+      </c>
+      <c r="QS14" s="1" t="n">
+        <v>415382.6845121348</v>
+      </c>
+      <c r="QT14" s="1" t="n">
+        <v>386869.6463569931</v>
+      </c>
+      <c r="QU14" s="1" t="n">
+        <v>294342.4275569342</v>
+      </c>
+      <c r="QV14" s="1" t="n">
+        <v>77244.63564496679</v>
+      </c>
+      <c r="QW14" s="1" t="n">
+        <v>21324.5965294527</v>
+      </c>
+      <c r="QX14" s="1" t="n">
+        <v>14958.4171</v>
+      </c>
+      <c r="QY14" s="1" t="n">
+        <v>10986.88</v>
+      </c>
+      <c r="QZ14" s="1" t="n">
+        <v>6751.0955619394</v>
+      </c>
+      <c r="RA14" s="1" t="n">
+        <v>4666.4838</v>
+      </c>
+      <c r="RB14" s="1" t="n">
+        <v>3222.490167433</v>
+      </c>
+      <c r="RC14" s="1" t="n">
+        <v>1190.3075</v>
+      </c>
+      <c r="RD14" s="1" t="n">
+        <v>498.666066</v>
+      </c>
+      <c r="RE14" s="1" t="n">
+        <v>453.7844069122</v>
+      </c>
+      <c r="RF14" s="1" t="n">
+        <v>398.9328546</v>
+      </c>
+      <c r="RG14" s="1" t="n">
+        <v>398.9328540683</v>
+      </c>
+      <c r="RH14" s="1" t="n">
+        <v>244.56531</v>
+      </c>
+      <c r="RI14" s="1" t="n">
+        <v>63.363064</v>
+      </c>
+      <c r="RJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RK14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RL14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RM14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RN14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RO14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RP14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RQ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RR14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RS14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RT14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RU14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RW14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RX14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RY14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="RZ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SC14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SD14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SG14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SH14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SI14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SK14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SL14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SM14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SN14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SO14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SP14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SQ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SR14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SS14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ST14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SU14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SW14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SX14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SY14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="SZ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TC14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TD14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TG14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TH14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TI14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TK14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TL14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TM14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TN14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TO14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TP14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TQ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TR14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TS14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TT14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TU14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TW14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TX14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TY14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="TZ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UC14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UD14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UG14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UH14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UI14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UK14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UL14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UM14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UN14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="UO14" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>574690297.36</v>
+        <v>568660713.29</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>467330717.69</v>
+        <v>477159198.56</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -489,7 +489,15 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>11418675.23511377</v>
+        <v>11362893.17644277</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BTCTHB</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>22777811.28</v>
       </c>
     </row>
     <row r="3">
@@ -502,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>226027491.92</v>
+        <v>230172684.85</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -510,7 +518,7 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>56626600.72849</v>
+        <v>59431221.008</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -518,7 +526,15 @@
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>5915900.034764385</v>
+        <v>5798165.383009525</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>XRPTHB</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>3656214.5</v>
       </c>
     </row>
     <row r="4">
@@ -531,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>110109964.92</v>
+        <v>111501034.51</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -539,7 +555,7 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>13094292.6231</v>
+        <v>12347424.0953</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -547,7 +563,15 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>3556224.796734105</v>
+        <v>3595761.256052385</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ETHTHB</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>1295063.04</v>
       </c>
     </row>
     <row r="5">
@@ -560,7 +584,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>74029329.95</v>
+        <v>72974131.79000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -568,7 +592,7 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>8661351.4428</v>
+        <v>8972833.5349</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -577,6 +601,14 @@
       </c>
       <c r="I5" s="1" t="n">
         <v>759551.87093175</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SOLTHB</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>1113927.77</v>
       </c>
     </row>
     <row r="6">
@@ -589,7 +621,7 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>37196128.88</v>
+        <v>38907350.08</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -597,7 +629,7 @@
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>3115484.7788</v>
+        <v>3269370.7132</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -605,7 +637,15 @@
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>714843.6512889932</v>
+        <v>576305.3392889932</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>BCHTHB</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>465985.55</v>
       </c>
     </row>
     <row r="7"/>
@@ -622,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW2"/>
+  <dimension ref="A1:BXW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4175,6 +4215,1337 @@
         <v>0</v>
       </c>
       <c r="QB2" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>568660713.29</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>230172684.85</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>111501034.51</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>72974131.79000001</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>38907350.08</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>33144379.36</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>11977123.27</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>11580035.25</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>10071884.83</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>8682439.02</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>10799962.4</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>8177609.11</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>7156639.01</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>7406149.72</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>6596483.82</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>6145877.72</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>6131176.94</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>5775203.51</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>5190318.49</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>4065809.69</v>
+      </c>
+      <c r="W3" s="1" t="n">
+        <v>3332110.98</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>4077416.43</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>4029103.77</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>3560406.86</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>3341772.76</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>3404112.36</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>3692783.24</v>
+      </c>
+      <c r="AD3" s="1" t="n">
+        <v>3163337.51</v>
+      </c>
+      <c r="AE3" s="1" t="n">
+        <v>2950372.97</v>
+      </c>
+      <c r="AF3" s="1" t="n">
+        <v>2763123.05</v>
+      </c>
+      <c r="AG3" s="1" t="n">
+        <v>2204654.73</v>
+      </c>
+      <c r="AH3" s="1" t="n">
+        <v>2369395.92</v>
+      </c>
+      <c r="AI3" s="1" t="n">
+        <v>2125534.84</v>
+      </c>
+      <c r="AJ3" s="1" t="n">
+        <v>1939655.56</v>
+      </c>
+      <c r="AK3" s="1" t="n">
+        <v>1686357.36</v>
+      </c>
+      <c r="AL3" s="1" t="n">
+        <v>1973409.27</v>
+      </c>
+      <c r="AM3" s="1" t="n">
+        <v>1587235.59</v>
+      </c>
+      <c r="AN3" s="1" t="n">
+        <v>894982.11</v>
+      </c>
+      <c r="AO3" s="1" t="n">
+        <v>1517274.92</v>
+      </c>
+      <c r="AP3" s="1" t="n">
+        <v>1711067.44</v>
+      </c>
+      <c r="AQ3" s="1" t="n">
+        <v>1503267.29</v>
+      </c>
+      <c r="AR3" s="1" t="n">
+        <v>1512573.4</v>
+      </c>
+      <c r="AS3" s="1" t="n">
+        <v>1434386.8</v>
+      </c>
+      <c r="AT3" s="1" t="n">
+        <v>1301323.68</v>
+      </c>
+      <c r="AU3" s="1" t="n">
+        <v>1369240.07</v>
+      </c>
+      <c r="AV3" s="1" t="n">
+        <v>1375458.9</v>
+      </c>
+      <c r="AW3" s="1" t="n">
+        <v>1513007</v>
+      </c>
+      <c r="AX3" s="1" t="n">
+        <v>1351206.18</v>
+      </c>
+      <c r="AY3" s="1" t="n">
+        <v>1090368.94</v>
+      </c>
+      <c r="AZ3" s="1" t="n">
+        <v>1096439.97</v>
+      </c>
+      <c r="BA3" s="1" t="n">
+        <v>1064297.97</v>
+      </c>
+      <c r="BB3" s="1" t="n">
+        <v>1143562.45</v>
+      </c>
+      <c r="BC3" s="1" t="n">
+        <v>1238748.59</v>
+      </c>
+      <c r="BD3" s="1" t="n">
+        <v>1033588.43</v>
+      </c>
+      <c r="BE3" s="1" t="n">
+        <v>928864.66</v>
+      </c>
+      <c r="BF3" s="1" t="n">
+        <v>879680.92</v>
+      </c>
+      <c r="BG3" s="1" t="n">
+        <v>867824.39</v>
+      </c>
+      <c r="BH3" s="1" t="n">
+        <v>862014.58</v>
+      </c>
+      <c r="BI3" s="1" t="n">
+        <v>863504.4300000001</v>
+      </c>
+      <c r="BJ3" s="1" t="n">
+        <v>806717.8</v>
+      </c>
+      <c r="BK3" s="1" t="n">
+        <v>893236.64</v>
+      </c>
+      <c r="BL3" s="1" t="n">
+        <v>998049.47</v>
+      </c>
+      <c r="BM3" s="1" t="n">
+        <v>804382.71</v>
+      </c>
+      <c r="BN3" s="1" t="n">
+        <v>716464.6899999999</v>
+      </c>
+      <c r="BO3" s="1" t="n">
+        <v>718904.38</v>
+      </c>
+      <c r="BP3" s="1" t="n">
+        <v>639033.9399999999</v>
+      </c>
+      <c r="BQ3" s="1" t="n">
+        <v>640818.52</v>
+      </c>
+      <c r="BR3" s="1" t="n">
+        <v>606043.35</v>
+      </c>
+      <c r="BS3" s="1" t="n">
+        <v>545075.72</v>
+      </c>
+      <c r="BT3" s="1" t="n">
+        <v>693630.13</v>
+      </c>
+      <c r="BU3" s="1" t="n">
+        <v>564758.71</v>
+      </c>
+      <c r="BV3" s="1" t="n">
+        <v>608929.02</v>
+      </c>
+      <c r="BW3" s="1" t="n">
+        <v>538879.3100000001</v>
+      </c>
+      <c r="BX3" s="1" t="n">
+        <v>573376.49</v>
+      </c>
+      <c r="BY3" s="1" t="n">
+        <v>513730.95</v>
+      </c>
+      <c r="BZ3" s="1" t="n">
+        <v>432453.18</v>
+      </c>
+      <c r="CA3" s="1" t="n">
+        <v>427907.93</v>
+      </c>
+      <c r="CB3" s="1" t="n">
+        <v>421370.68</v>
+      </c>
+      <c r="CC3" s="1" t="n">
+        <v>483106.95</v>
+      </c>
+      <c r="CD3" s="1" t="n">
+        <v>407036.04</v>
+      </c>
+      <c r="CE3" s="1" t="n">
+        <v>378119.94</v>
+      </c>
+      <c r="CF3" s="1" t="n">
+        <v>371827.31</v>
+      </c>
+      <c r="CG3" s="1" t="n">
+        <v>1113419.11</v>
+      </c>
+      <c r="CH3" s="1" t="n">
+        <v>362350.43</v>
+      </c>
+      <c r="CI3" s="1" t="n">
+        <v>363948.84</v>
+      </c>
+      <c r="CJ3" s="1" t="n">
+        <v>363905.89</v>
+      </c>
+      <c r="CK3" s="1" t="n">
+        <v>340285.71</v>
+      </c>
+      <c r="CL3" s="1" t="n">
+        <v>332264.97</v>
+      </c>
+      <c r="CM3" s="1" t="n">
+        <v>305083.15</v>
+      </c>
+      <c r="CN3" s="1" t="n">
+        <v>273464.17</v>
+      </c>
+      <c r="CO3" s="1" t="n">
+        <v>781362.66</v>
+      </c>
+      <c r="CP3" s="1" t="n">
+        <v>194527.17</v>
+      </c>
+      <c r="CQ3" s="1" t="n">
+        <v>286267.5</v>
+      </c>
+      <c r="CR3" s="1" t="n">
+        <v>237564.35</v>
+      </c>
+      <c r="CS3" s="1" t="n">
+        <v>266224.24</v>
+      </c>
+      <c r="CT3" s="1" t="n">
+        <v>261778.9</v>
+      </c>
+      <c r="CU3" s="1" t="n">
+        <v>246667.8</v>
+      </c>
+      <c r="CV3" s="1" t="n">
+        <v>296079.68</v>
+      </c>
+      <c r="CW3" s="1" t="n">
+        <v>243211.78</v>
+      </c>
+      <c r="CX3" s="1" t="n">
+        <v>238788.96</v>
+      </c>
+      <c r="CY3" s="1" t="n">
+        <v>236054.04</v>
+      </c>
+      <c r="CZ3" s="1" t="n">
+        <v>232357.6</v>
+      </c>
+      <c r="DA3" s="1" t="n">
+        <v>223955.74</v>
+      </c>
+      <c r="DB3" s="1" t="n">
+        <v>215864.86</v>
+      </c>
+      <c r="DC3" s="1" t="n">
+        <v>210972.48</v>
+      </c>
+      <c r="DD3" s="1" t="n">
+        <v>210647.2</v>
+      </c>
+      <c r="DE3" s="1" t="n">
+        <v>204713.72</v>
+      </c>
+      <c r="DF3" s="1" t="n">
+        <v>196756.47</v>
+      </c>
+      <c r="DG3" s="1" t="n">
+        <v>125216.39</v>
+      </c>
+      <c r="DH3" s="1" t="n">
+        <v>187286.64</v>
+      </c>
+      <c r="DI3" s="1" t="n">
+        <v>183098.03</v>
+      </c>
+      <c r="DJ3" s="1" t="n">
+        <v>207774.83</v>
+      </c>
+      <c r="DK3" s="1" t="n">
+        <v>165952.53</v>
+      </c>
+      <c r="DL3" s="1" t="n">
+        <v>163871.54</v>
+      </c>
+      <c r="DM3" s="1" t="n">
+        <v>166433.16</v>
+      </c>
+      <c r="DN3" s="1" t="n">
+        <v>215715.14</v>
+      </c>
+      <c r="DO3" s="1" t="n">
+        <v>146580.59</v>
+      </c>
+      <c r="DP3" s="1" t="n">
+        <v>153334.24</v>
+      </c>
+      <c r="DQ3" s="1" t="n">
+        <v>150055.85</v>
+      </c>
+      <c r="DR3" s="1" t="n">
+        <v>148333.96</v>
+      </c>
+      <c r="DS3" s="1" t="n">
+        <v>144183.72</v>
+      </c>
+      <c r="DT3" s="1" t="n">
+        <v>290587.99</v>
+      </c>
+      <c r="DU3" s="1" t="n">
+        <v>135243.2</v>
+      </c>
+      <c r="DV3" s="1" t="n">
+        <v>128842.15</v>
+      </c>
+      <c r="DW3" s="1" t="n">
+        <v>156516.8</v>
+      </c>
+      <c r="DX3" s="1" t="n">
+        <v>137876.66</v>
+      </c>
+      <c r="DY3" s="1" t="n">
+        <v>125985.42</v>
+      </c>
+      <c r="DZ3" s="1" t="n">
+        <v>118854.8</v>
+      </c>
+      <c r="EA3" s="1" t="n">
+        <v>138669.02</v>
+      </c>
+      <c r="EB3" s="1" t="n">
+        <v>115816.67</v>
+      </c>
+      <c r="EC3" s="1" t="n">
+        <v>107811.02</v>
+      </c>
+      <c r="ED3" s="1" t="n">
+        <v>107950.9</v>
+      </c>
+      <c r="EE3" s="1" t="n">
+        <v>106573.26</v>
+      </c>
+      <c r="EF3" s="1" t="n">
+        <v>104382.5</v>
+      </c>
+      <c r="EG3" s="1" t="n">
+        <v>102315.68</v>
+      </c>
+      <c r="EH3" s="1" t="n">
+        <v>103215.28</v>
+      </c>
+      <c r="EI3" s="1" t="n">
+        <v>21036.29</v>
+      </c>
+      <c r="EJ3" s="1" t="n">
+        <v>82848.03</v>
+      </c>
+      <c r="EK3" s="1" t="n">
+        <v>145671.33</v>
+      </c>
+      <c r="EL3" s="1" t="n">
+        <v>97497.53</v>
+      </c>
+      <c r="EM3" s="1" t="n">
+        <v>102231.33</v>
+      </c>
+      <c r="EN3" s="1" t="n">
+        <v>92954.91</v>
+      </c>
+      <c r="EO3" s="1" t="n">
+        <v>87769.41</v>
+      </c>
+      <c r="EP3" s="1" t="n">
+        <v>126988.33</v>
+      </c>
+      <c r="EQ3" s="1" t="n">
+        <v>83717.39999999999</v>
+      </c>
+      <c r="ER3" s="1" t="n">
+        <v>91828.47</v>
+      </c>
+      <c r="ES3" s="1" t="n">
+        <v>96509.25999999999</v>
+      </c>
+      <c r="ET3" s="1" t="n">
+        <v>77953.46000000001</v>
+      </c>
+      <c r="EU3" s="1" t="n">
+        <v>75420.2</v>
+      </c>
+      <c r="EV3" s="1" t="n">
+        <v>55275.78</v>
+      </c>
+      <c r="EW3" s="1" t="n">
+        <v>32885.7</v>
+      </c>
+      <c r="EX3" s="1" t="n">
+        <v>76072.67</v>
+      </c>
+      <c r="EY3" s="1" t="n">
+        <v>69787.16</v>
+      </c>
+      <c r="EZ3" s="1" t="n">
+        <v>67759.47</v>
+      </c>
+      <c r="FA3" s="1" t="n">
+        <v>66407.73</v>
+      </c>
+      <c r="FB3" s="1" t="n">
+        <v>66124.87</v>
+      </c>
+      <c r="FC3" s="1" t="n">
+        <v>65676.05</v>
+      </c>
+      <c r="FD3" s="1" t="n">
+        <v>65539.53</v>
+      </c>
+      <c r="FE3" s="1" t="n">
+        <v>65190.88</v>
+      </c>
+      <c r="FF3" s="1" t="n">
+        <v>65548.62</v>
+      </c>
+      <c r="FG3" s="1" t="n">
+        <v>67113.61</v>
+      </c>
+      <c r="FH3" s="1" t="n">
+        <v>63512.76</v>
+      </c>
+      <c r="FI3" s="1" t="n">
+        <v>62357.75</v>
+      </c>
+      <c r="FJ3" s="1" t="n">
+        <v>61598.86</v>
+      </c>
+      <c r="FK3" s="1" t="n">
+        <v>41580.04</v>
+      </c>
+      <c r="FL3" s="1" t="n">
+        <v>58877.91</v>
+      </c>
+      <c r="FM3" s="1" t="n">
+        <v>60758.91</v>
+      </c>
+      <c r="FN3" s="1" t="n">
+        <v>60093.12</v>
+      </c>
+      <c r="FO3" s="1" t="n">
+        <v>496.99</v>
+      </c>
+      <c r="FP3" s="1" t="n">
+        <v>59065</v>
+      </c>
+      <c r="FQ3" s="1" t="n">
+        <v>81321.53999999999</v>
+      </c>
+      <c r="FR3" s="1" t="n">
+        <v>56209.17</v>
+      </c>
+      <c r="FS3" s="1" t="n">
+        <v>68464.27</v>
+      </c>
+      <c r="FT3" s="1" t="n">
+        <v>55803.1</v>
+      </c>
+      <c r="FU3" s="1" t="n">
+        <v>54822.34</v>
+      </c>
+      <c r="FV3" s="1" t="n">
+        <v>33556.27</v>
+      </c>
+      <c r="FW3" s="1" t="n">
+        <v>50625.14</v>
+      </c>
+      <c r="FX3" s="1" t="n">
+        <v>61289.23</v>
+      </c>
+      <c r="FY3" s="1" t="n">
+        <v>52681.62</v>
+      </c>
+      <c r="FZ3" s="1" t="n">
+        <v>51529.01</v>
+      </c>
+      <c r="GA3" s="1" t="n">
+        <v>49106.02</v>
+      </c>
+      <c r="GB3" s="1" t="n">
+        <v>48557.65</v>
+      </c>
+      <c r="GC3" s="1" t="n">
+        <v>48549.24</v>
+      </c>
+      <c r="GD3" s="1" t="n">
+        <v>47945.12</v>
+      </c>
+      <c r="GE3" s="1" t="n">
+        <v>48806.15</v>
+      </c>
+      <c r="GF3" s="1" t="n">
+        <v>47658.44</v>
+      </c>
+      <c r="GG3" s="1" t="n">
+        <v>46083.73</v>
+      </c>
+      <c r="GH3" s="1" t="n">
+        <v>45235.28</v>
+      </c>
+      <c r="GI3" s="1" t="n">
+        <v>45057.51</v>
+      </c>
+      <c r="GJ3" s="1" t="n">
+        <v>43539.13</v>
+      </c>
+      <c r="GK3" s="1" t="n">
+        <v>42842.24</v>
+      </c>
+      <c r="GL3" s="1" t="n">
+        <v>42266.15</v>
+      </c>
+      <c r="GM3" s="1" t="n">
+        <v>41818.55</v>
+      </c>
+      <c r="GN3" s="1" t="n">
+        <v>40923.3</v>
+      </c>
+      <c r="GO3" s="1" t="n">
+        <v>40616.23</v>
+      </c>
+      <c r="GP3" s="1" t="n">
+        <v>38922.98</v>
+      </c>
+      <c r="GQ3" s="1" t="n">
+        <v>38992.08</v>
+      </c>
+      <c r="GR3" s="1" t="n">
+        <v>38766.35</v>
+      </c>
+      <c r="GS3" s="1" t="n">
+        <v>37911.35</v>
+      </c>
+      <c r="GT3" s="1" t="n">
+        <v>38443.95</v>
+      </c>
+      <c r="GU3" s="1" t="n">
+        <v>37680.31</v>
+      </c>
+      <c r="GV3" s="1" t="n">
+        <v>37119.24</v>
+      </c>
+      <c r="GW3" s="1" t="n">
+        <v>36869.97</v>
+      </c>
+      <c r="GX3" s="1" t="n">
+        <v>36764.69</v>
+      </c>
+      <c r="GY3" s="1" t="n">
+        <v>35073.23</v>
+      </c>
+      <c r="GZ3" s="1" t="n">
+        <v>27346.51</v>
+      </c>
+      <c r="HA3" s="1" t="n">
+        <v>31393.39</v>
+      </c>
+      <c r="HB3" s="1" t="n">
+        <v>29981.32</v>
+      </c>
+      <c r="HC3" s="1" t="n">
+        <v>29903.53</v>
+      </c>
+      <c r="HD3" s="1" t="n">
+        <v>29211.3</v>
+      </c>
+      <c r="HE3" s="1" t="n">
+        <v>28174.75</v>
+      </c>
+      <c r="HF3" s="1" t="n">
+        <v>27713.32</v>
+      </c>
+      <c r="HG3" s="1" t="n">
+        <v>27191.75</v>
+      </c>
+      <c r="HH3" s="1" t="n">
+        <v>26529.35</v>
+      </c>
+      <c r="HI3" s="1" t="n">
+        <v>24256.95</v>
+      </c>
+      <c r="HJ3" s="1" t="n">
+        <v>26349.41</v>
+      </c>
+      <c r="HK3" s="1" t="n">
+        <v>22970.36</v>
+      </c>
+      <c r="HL3" s="1" t="n">
+        <v>22787.51</v>
+      </c>
+      <c r="HM3" s="1" t="n">
+        <v>22708.68</v>
+      </c>
+      <c r="HN3" s="1" t="n">
+        <v>22671.24</v>
+      </c>
+      <c r="HO3" s="1" t="n">
+        <v>20753.51</v>
+      </c>
+      <c r="HP3" s="1" t="n">
+        <v>20763.74</v>
+      </c>
+      <c r="HQ3" s="1" t="n">
+        <v>20227.42</v>
+      </c>
+      <c r="HR3" s="1" t="n">
+        <v>19699.1</v>
+      </c>
+      <c r="HS3" s="1" t="n">
+        <v>47989.24</v>
+      </c>
+      <c r="HT3" s="1" t="n">
+        <v>18519.68</v>
+      </c>
+      <c r="HU3" s="1" t="n">
+        <v>18080.94</v>
+      </c>
+      <c r="HV3" s="1" t="n">
+        <v>31444.98</v>
+      </c>
+      <c r="HW3" s="1" t="n">
+        <v>17156.02</v>
+      </c>
+      <c r="HX3" s="1" t="n">
+        <v>15894.78</v>
+      </c>
+      <c r="HY3" s="1" t="n">
+        <v>15411.03</v>
+      </c>
+      <c r="HZ3" s="1" t="n">
+        <v>15129.67</v>
+      </c>
+      <c r="IA3" s="1" t="n">
+        <v>14788.35</v>
+      </c>
+      <c r="IB3" s="1" t="n">
+        <v>14512.21</v>
+      </c>
+      <c r="IC3" s="1" t="n">
+        <v>14373</v>
+      </c>
+      <c r="ID3" s="1" t="n">
+        <v>12831.05</v>
+      </c>
+      <c r="IE3" s="1" t="n">
+        <v>144672.02</v>
+      </c>
+      <c r="IF3" s="1" t="n">
+        <v>12113.11</v>
+      </c>
+      <c r="IG3" s="1" t="n">
+        <v>11894.77</v>
+      </c>
+      <c r="IH3" s="1" t="n">
+        <v>4340.71</v>
+      </c>
+      <c r="II3" s="1" t="n">
+        <v>17297</v>
+      </c>
+      <c r="IJ3" s="1" t="n">
+        <v>11296.95</v>
+      </c>
+      <c r="IK3" s="1" t="n">
+        <v>11172.42</v>
+      </c>
+      <c r="IL3" s="1" t="n">
+        <v>10949.69</v>
+      </c>
+      <c r="IM3" s="1" t="n">
+        <v>10817.18</v>
+      </c>
+      <c r="IN3" s="1" t="n">
+        <v>10751.53</v>
+      </c>
+      <c r="IO3" s="1" t="n">
+        <v>10255.96</v>
+      </c>
+      <c r="IP3" s="1" t="n">
+        <v>10252.8</v>
+      </c>
+      <c r="IQ3" s="1" t="n">
+        <v>10051.48</v>
+      </c>
+      <c r="IR3" s="1" t="n">
+        <v>9974.91</v>
+      </c>
+      <c r="IS3" s="1" t="n">
+        <v>9747.620000000001</v>
+      </c>
+      <c r="IT3" s="1" t="n">
+        <v>9074.6</v>
+      </c>
+      <c r="IU3" s="1" t="n">
+        <v>8578.940000000001</v>
+      </c>
+      <c r="IV3" s="1" t="n">
+        <v>9706.77</v>
+      </c>
+      <c r="IW3" s="1" t="n">
+        <v>7659.74</v>
+      </c>
+      <c r="IX3" s="1" t="n">
+        <v>25453.52</v>
+      </c>
+      <c r="IY3" s="1" t="n">
+        <v>7130.52</v>
+      </c>
+      <c r="IZ3" s="1" t="n">
+        <v>6887.64</v>
+      </c>
+      <c r="JA3" s="1" t="n">
+        <v>6772.89</v>
+      </c>
+      <c r="JB3" s="1" t="n">
+        <v>6294.66</v>
+      </c>
+      <c r="JC3" s="1" t="n">
+        <v>4472.81</v>
+      </c>
+      <c r="JD3" s="1" t="n">
+        <v>11172.92</v>
+      </c>
+      <c r="JE3" s="1" t="n">
+        <v>5478.54</v>
+      </c>
+      <c r="JF3" s="1" t="n">
+        <v>5281.4</v>
+      </c>
+      <c r="JG3" s="1" t="n">
+        <v>6996.43</v>
+      </c>
+      <c r="JH3" s="1" t="n">
+        <v>5154.27</v>
+      </c>
+      <c r="JI3" s="1" t="n">
+        <v>304353.91</v>
+      </c>
+      <c r="JJ3" s="1" t="n">
+        <v>5084.1</v>
+      </c>
+      <c r="JK3" s="1" t="n">
+        <v>5087.28</v>
+      </c>
+      <c r="JL3" s="1" t="n">
+        <v>5043.86</v>
+      </c>
+      <c r="JM3" s="1" t="n">
+        <v>4970.31</v>
+      </c>
+      <c r="JN3" s="1" t="n">
+        <v>8639.049999999999</v>
+      </c>
+      <c r="JO3" s="1" t="n">
+        <v>4863.59</v>
+      </c>
+      <c r="JP3" s="1" t="n">
+        <v>4774.94</v>
+      </c>
+      <c r="JQ3" s="1" t="n">
+        <v>4771.78</v>
+      </c>
+      <c r="JR3" s="1" t="n">
+        <v>3182.07</v>
+      </c>
+      <c r="JS3" s="1" t="n">
+        <v>4539.76</v>
+      </c>
+      <c r="JT3" s="1" t="n">
+        <v>4353.95</v>
+      </c>
+      <c r="JU3" s="1" t="n">
+        <v>5197.21</v>
+      </c>
+      <c r="JV3" s="1" t="n">
+        <v>3755.76</v>
+      </c>
+      <c r="JW3" s="1" t="n">
+        <v>3714.62</v>
+      </c>
+      <c r="JX3" s="1" t="n">
+        <v>8517.790000000001</v>
+      </c>
+      <c r="JY3" s="1" t="n">
+        <v>3281.13</v>
+      </c>
+      <c r="JZ3" s="1" t="n">
+        <v>3275.23</v>
+      </c>
+      <c r="KA3" s="1" t="n">
+        <v>3201.45</v>
+      </c>
+      <c r="KB3" s="1" t="n">
+        <v>3935.03</v>
+      </c>
+      <c r="KC3" s="1" t="n">
+        <v>3052.85</v>
+      </c>
+      <c r="KD3" s="1" t="n">
+        <v>2990.88</v>
+      </c>
+      <c r="KE3" s="1" t="n">
+        <v>2569.11</v>
+      </c>
+      <c r="KF3" s="1" t="n">
+        <v>2600.84</v>
+      </c>
+      <c r="KG3" s="1" t="n">
+        <v>2566.16</v>
+      </c>
+      <c r="KH3" s="1" t="n">
+        <v>2420.87</v>
+      </c>
+      <c r="KI3" s="1" t="n">
+        <v>2133.16</v>
+      </c>
+      <c r="KJ3" s="1" t="n">
+        <v>1968.05</v>
+      </c>
+      <c r="KK3" s="1" t="n">
+        <v>1936.71</v>
+      </c>
+      <c r="KL3" s="1" t="n">
+        <v>1791.2</v>
+      </c>
+      <c r="KM3" s="1" t="n">
+        <v>1696.51</v>
+      </c>
+      <c r="KN3" s="1" t="n">
+        <v>11650.73</v>
+      </c>
+      <c r="KO3" s="1" t="n">
+        <v>1594.89</v>
+      </c>
+      <c r="KP3" s="1" t="n">
+        <v>1400.01</v>
+      </c>
+      <c r="KQ3" s="1" t="n">
+        <v>1454.51</v>
+      </c>
+      <c r="KR3" s="1" t="n">
+        <v>3051.3</v>
+      </c>
+      <c r="KS3" s="1" t="n">
+        <v>1429.58</v>
+      </c>
+      <c r="KT3" s="1" t="n">
+        <v>1417.84</v>
+      </c>
+      <c r="KU3" s="1" t="n">
+        <v>5831.54</v>
+      </c>
+      <c r="KV3" s="1" t="n">
+        <v>1304.22</v>
+      </c>
+      <c r="KW3" s="1" t="n">
+        <v>26702.16</v>
+      </c>
+      <c r="KX3" s="1" t="n">
+        <v>381.99</v>
+      </c>
+      <c r="KY3" s="1" t="n">
+        <v>1020.83</v>
+      </c>
+      <c r="KZ3" s="1" t="n">
+        <v>1190.1</v>
+      </c>
+      <c r="LA3" s="1" t="n">
+        <v>275.41</v>
+      </c>
+      <c r="LB3" s="1" t="n">
+        <v>1122.94</v>
+      </c>
+      <c r="LC3" s="1" t="n">
+        <v>1119.87</v>
+      </c>
+      <c r="LD3" s="1" t="n">
+        <v>997.5</v>
+      </c>
+      <c r="LE3" s="1" t="n">
+        <v>861.3</v>
+      </c>
+      <c r="LF3" s="1" t="n">
+        <v>893.9400000000001</v>
+      </c>
+      <c r="LG3" s="1" t="n">
+        <v>793.73</v>
+      </c>
+      <c r="LH3" s="1" t="n">
+        <v>850.1799999999999</v>
+      </c>
+      <c r="LI3" s="1" t="n">
+        <v>733.98</v>
+      </c>
+      <c r="LJ3" s="1" t="n">
+        <v>759.1</v>
+      </c>
+      <c r="LK3" s="1" t="n">
+        <v>685.38</v>
+      </c>
+      <c r="LL3" s="1" t="n">
+        <v>614.91</v>
+      </c>
+      <c r="LM3" s="1" t="n">
+        <v>559.92</v>
+      </c>
+      <c r="LN3" s="1" t="n">
+        <v>451.31</v>
+      </c>
+      <c r="LO3" s="1" t="n">
+        <v>449.6</v>
+      </c>
+      <c r="LP3" s="1" t="n">
+        <v>435</v>
+      </c>
+      <c r="LQ3" s="1" t="n">
+        <v>417.78</v>
+      </c>
+      <c r="LR3" s="1" t="n">
+        <v>411.37</v>
+      </c>
+      <c r="LS3" s="1" t="n">
+        <v>408.96</v>
+      </c>
+      <c r="LT3" s="1" t="n">
+        <v>398.52</v>
+      </c>
+      <c r="LU3" s="1" t="n">
+        <v>398.41</v>
+      </c>
+      <c r="LV3" s="1" t="n">
+        <v>301.61</v>
+      </c>
+      <c r="LW3" s="1" t="n">
+        <v>387.88</v>
+      </c>
+      <c r="LX3" s="1" t="n">
+        <v>244.11</v>
+      </c>
+      <c r="LY3" s="1" t="n">
+        <v>199.7</v>
+      </c>
+      <c r="LZ3" s="1" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="MA3" s="1" t="n">
+        <v>433.2</v>
+      </c>
+      <c r="MB3" s="1" t="n">
+        <v>1297.12</v>
+      </c>
+      <c r="MC3" s="1" t="n">
+        <v>305.53</v>
+      </c>
+      <c r="MD3" s="1" t="n">
+        <v>303.08</v>
+      </c>
+      <c r="ME3" s="1" t="n">
+        <v>156.2</v>
+      </c>
+      <c r="MF3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MG3" s="1" t="n">
+        <v>74591.28999999999</v>
+      </c>
+      <c r="MH3" s="1" t="n">
+        <v>248.89</v>
+      </c>
+      <c r="MI3" s="1" t="n">
+        <v>132.85</v>
+      </c>
+      <c r="MJ3" s="1" t="n">
+        <v>216.66</v>
+      </c>
+      <c r="MK3" s="1" t="n">
+        <v>211.35</v>
+      </c>
+      <c r="ML3" s="1" t="n">
+        <v>252.18</v>
+      </c>
+      <c r="MM3" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="MN3" s="1" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="MO3" s="1" t="n">
+        <v>199.47</v>
+      </c>
+      <c r="MP3" s="1" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="MQ3" s="1" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="MR3" s="1" t="n">
+        <v>195.4</v>
+      </c>
+      <c r="MS3" s="1" t="n">
+        <v>144.29</v>
+      </c>
+      <c r="MT3" s="1" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="MU3" s="1" t="n">
+        <v>20077.65</v>
+      </c>
+      <c r="MV3" s="1" t="n">
+        <v>113.44</v>
+      </c>
+      <c r="MW3" s="1" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="MX3" s="1" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="MY3" s="1" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="MZ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NA3" s="1" t="n">
+        <v>92.54000000000001</v>
+      </c>
+      <c r="NB3" s="1" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="NC3" s="1" t="n">
+        <v>51.15</v>
+      </c>
+      <c r="ND3" s="1" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="NE3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NF3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NG3" s="1" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="NH3" s="1" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="NI3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NJ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NK3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NL3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NM3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NN3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NO3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NP3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NQ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NR3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NS3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NT3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NU3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NV3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NW3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NX3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NY3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NZ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OA3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OB3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OC3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OD3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OE3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OF3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OG3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OH3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OI3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OJ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OK3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OL3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OM3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ON3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OO3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OP3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OQ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OR3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OS3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OT3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OU3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OV3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OW3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OX3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OY3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OZ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PA3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PB3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PC3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PD3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PE3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PF3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PG3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PH3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PI3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PJ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PK3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PL3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PM3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PN3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PO3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PP3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PQ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PR3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PS3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PT3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PU3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PV3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PW3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PX3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PY3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PZ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QA3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QB3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4189,7 +5560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW2"/>
+  <dimension ref="A1:BXW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4295,6 +5666,44 @@
       </c>
       <c r="M2" s="1" t="n">
         <v>903.806649</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>477159198.56</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>59431221.008</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>12347424.0953</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>8972833.5349</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>3269370.7132</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>1724129.839</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>1051692.3268</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>176784.5229</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>12742.0037</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>8360.57674</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>3930.337943</v>
       </c>
     </row>
   </sheetData>
@@ -4308,7 +5717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW2"/>
+  <dimension ref="A1:BXW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +6566,323 @@
         <v>0</v>
       </c>
       <c r="DB2" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>11362893.17644277</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>5798165.383009525</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>3595761.256052385</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>759551.87093175</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>576305.3392889932</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>442902.6259438318</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>325820.2597201968</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>44146.2197843141</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>38492.0139759845</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>20735.115</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>15062.4116</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>13031.35616</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>731.097615</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>3943.0207694116</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>1190.3075</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>453.7844069122</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>249.9888</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>99.73321319999999</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>63.363064</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="W3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB3" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5171,7 +6897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW2"/>
+  <dimension ref="A1:BXW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5180,10 +6906,316 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>BTCTHB</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>BTCTHB 7d-Avg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>XRPTHB</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ETHTHB</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>SOLTHB</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>BCHTHB</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>USDTTHB</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>XLMTHB</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ADATHB</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>POLTHB</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ARBTHB</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>CRVTHB</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>AAVETHB</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>LINKTHB</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>LDOTHB</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>YFITHB</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>CHZTHB</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>BNBTHB</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>SNXTHB</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>SUSHITHB</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>REALXTHB</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>NEARTHB</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>AVAXTHB</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>SANDTHB</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>XAUTTHB</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ZRXTHB</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>SUMXTHB</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>COMPTHB</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ASTERTHB</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>AXSTHB</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>BLUTHB</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>DYDXTHB</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>KNCTHB</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>PENDLETHB</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>TIATHB</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>UNITHB</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>USDCTHB</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>WLDTHB</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>22777811.28</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>3656214.5</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>1295063.04</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1113927.77</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>465985.55</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>434891.77</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>330647.95</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>209131.23</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>51937.42</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>42860.59</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>39721.12</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>29533.06</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>27117.95</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>19829.11</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>17356.64</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>15713.17</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>12101.49</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>10009.93</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>8754.68</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>6779.62</v>
+      </c>
+      <c r="W3" s="1" t="n">
+        <v>6038.24</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>4999.99</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>4658.21</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>4141.6</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>1616.55</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>560.4400000000001</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AD3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>568660713.29</v>
+        <v>619529776.17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,15 +481,15 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>477159198.56</v>
+        <v>716383579.21</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ETH_THB</t>
+          <t>BTC_THB</t>
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>11362893.17644277</v>
+        <v>4953546.256993227</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>22777811.28</v>
+        <v>36245644.96</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>230172684.85</v>
+        <v>248098256.84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,23 +518,23 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>59431221.008</v>
+        <v>75393355.71813001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BTC_THB</t>
+          <t>ETH_THB</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>5798165.383009525</v>
+        <v>4859159.536246131</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>USDTTHB</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>3656214.5</v>
+        <v>10941725.57</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>111501034.51</v>
+        <v>78658560.29000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>12347424.0953</v>
+        <v>20514427.1186</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -563,15 +563,15 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>3595761.256052385</v>
+        <v>4130046.350622243</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1295063.04</v>
+        <v>2598733.24</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>72974131.79000001</v>
+        <v>33834050.91</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>8972833.5349</v>
+        <v>12551433.4178</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,15 +600,15 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>759551.87093175</v>
+        <v>450768.0417339354</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SOLTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>1113927.77</v>
+        <v>849950.76</v>
       </c>
     </row>
     <row r="6">
@@ -617,11 +617,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_SOL</t>
+          <t>THB_DOGE</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>38907350.08</v>
+        <v>25172538.44</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,15 +629,15 @@
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>3269370.7132</v>
+        <v>4815890.0662</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>XRP_THB</t>
+          <t>SOL_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>576305.3392889932</v>
+        <v>412110.0657793726</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>465985.55</v>
+        <v>701599.66</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW3"/>
+  <dimension ref="A1:BXW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5546,6 +5546,1337 @@
         <v>0</v>
       </c>
       <c r="QB3" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>619529776.17</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>248098256.84</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>78658560.29000001</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>33834050.91</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>23912925.23</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>25172538.44</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>6119358.24</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>9784362.279999999</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>8176272.66</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>15356737.17</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>21877821.42</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>10538237.89</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>6624532.08</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>1315993.58</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>7057016.7</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>3070715.41</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>3475737.64</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>3017606.95</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>2741348.49</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>562929.96</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>6074476.7</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>4077416.43</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>1469917.34</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>823293.15</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>1665241.17</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>3376338.17</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>2765472.62</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>506099.5</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>853843.76</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>3212951.12</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>1532129.16</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>2536420.06</v>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>1869921.6</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>2184495.13</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>977416.65</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>1625931.94</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>1587235.59</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>59892.11</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>443401.46</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>1825559.7</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>3506265.72</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>727323.92</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>255608.8</v>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>1433132.06</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>1638828.95</v>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>3986319.85</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>1177849.94</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>1392402.44</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>178007.5</v>
+      </c>
+      <c r="AZ4" s="1" t="n">
+        <v>450098.43</v>
+      </c>
+      <c r="BA4" s="1" t="n">
+        <v>326843.97</v>
+      </c>
+      <c r="BB4" s="1" t="n">
+        <v>1283865.4</v>
+      </c>
+      <c r="BC4" s="1" t="n">
+        <v>853761.55</v>
+      </c>
+      <c r="BD4" s="1" t="n">
+        <v>693061.41</v>
+      </c>
+      <c r="BE4" s="1" t="n">
+        <v>608846.75</v>
+      </c>
+      <c r="BF4" s="1" t="n">
+        <v>1043126.62</v>
+      </c>
+      <c r="BG4" s="1" t="n">
+        <v>127556.6</v>
+      </c>
+      <c r="BH4" s="1" t="n">
+        <v>862014.58</v>
+      </c>
+      <c r="BI4" s="1" t="n">
+        <v>273599.83</v>
+      </c>
+      <c r="BJ4" s="1" t="n">
+        <v>598807.97</v>
+      </c>
+      <c r="BK4" s="1" t="n">
+        <v>515499.66</v>
+      </c>
+      <c r="BL4" s="1" t="n">
+        <v>997383.77</v>
+      </c>
+      <c r="BM4" s="1" t="n">
+        <v>165124.52</v>
+      </c>
+      <c r="BN4" s="1" t="n">
+        <v>342677.7</v>
+      </c>
+      <c r="BO4" s="1" t="n">
+        <v>122327.07</v>
+      </c>
+      <c r="BP4" s="1" t="n">
+        <v>137811.89</v>
+      </c>
+      <c r="BQ4" s="1" t="n">
+        <v>313476.61</v>
+      </c>
+      <c r="BR4" s="1" t="n">
+        <v>606043.35</v>
+      </c>
+      <c r="BS4" s="1" t="n">
+        <v>1628867.41</v>
+      </c>
+      <c r="BT4" s="1" t="n">
+        <v>73056.78999999999</v>
+      </c>
+      <c r="BU4" s="1" t="n">
+        <v>1682401.51</v>
+      </c>
+      <c r="BV4" s="1" t="n">
+        <v>1614766.74</v>
+      </c>
+      <c r="BW4" s="1" t="n">
+        <v>11927.56</v>
+      </c>
+      <c r="BX4" s="1" t="n">
+        <v>38531.51</v>
+      </c>
+      <c r="BY4" s="1" t="n">
+        <v>337578.06</v>
+      </c>
+      <c r="BZ4" s="1" t="n">
+        <v>54049.06</v>
+      </c>
+      <c r="CA4" s="1" t="n">
+        <v>231099.71</v>
+      </c>
+      <c r="CB4" s="1" t="n">
+        <v>1165408.26</v>
+      </c>
+      <c r="CC4" s="1" t="n">
+        <v>1658482.54</v>
+      </c>
+      <c r="CD4" s="1" t="n">
+        <v>720145.29</v>
+      </c>
+      <c r="CE4" s="1" t="n">
+        <v>93701.37</v>
+      </c>
+      <c r="CF4" s="1" t="n">
+        <v>100835.82</v>
+      </c>
+      <c r="CG4" s="1" t="n">
+        <v>849823.28</v>
+      </c>
+      <c r="CH4" s="1" t="n">
+        <v>6372.18</v>
+      </c>
+      <c r="CI4" s="1" t="n">
+        <v>78816.67999999999</v>
+      </c>
+      <c r="CJ4" s="1" t="n">
+        <v>1646939.48</v>
+      </c>
+      <c r="CK4" s="1" t="n">
+        <v>445561.41</v>
+      </c>
+      <c r="CL4" s="1" t="n">
+        <v>194303.95</v>
+      </c>
+      <c r="CM4" s="1" t="n">
+        <v>31587.24</v>
+      </c>
+      <c r="CN4" s="1" t="n">
+        <v>311438.01</v>
+      </c>
+      <c r="CO4" s="1" t="n">
+        <v>1008213.67</v>
+      </c>
+      <c r="CP4" s="1" t="n">
+        <v>147757.7</v>
+      </c>
+      <c r="CQ4" s="1" t="n">
+        <v>864202.85</v>
+      </c>
+      <c r="CR4" s="1" t="n">
+        <v>207180.09</v>
+      </c>
+      <c r="CS4" s="1" t="n">
+        <v>43296.32</v>
+      </c>
+      <c r="CT4" s="1" t="n">
+        <v>19529.7</v>
+      </c>
+      <c r="CU4" s="1" t="n">
+        <v>246667.8</v>
+      </c>
+      <c r="CV4" s="1" t="n">
+        <v>264491.18</v>
+      </c>
+      <c r="CW4" s="1" t="n">
+        <v>600281.98</v>
+      </c>
+      <c r="CX4" s="1" t="n">
+        <v>225881.9</v>
+      </c>
+      <c r="CY4" s="1" t="n">
+        <v>3864</v>
+      </c>
+      <c r="CZ4" s="1" t="n">
+        <v>271226.07</v>
+      </c>
+      <c r="DA4" s="1" t="n">
+        <v>7587.43</v>
+      </c>
+      <c r="DB4" s="1" t="n">
+        <v>148836.52</v>
+      </c>
+      <c r="DC4" s="1" t="n">
+        <v>23870.69</v>
+      </c>
+      <c r="DD4" s="1" t="n">
+        <v>276884.7</v>
+      </c>
+      <c r="DE4" s="1" t="n">
+        <v>154739.74</v>
+      </c>
+      <c r="DF4" s="1" t="n">
+        <v>196756.47</v>
+      </c>
+      <c r="DG4" s="1" t="n">
+        <v>658728.48</v>
+      </c>
+      <c r="DH4" s="1" t="n">
+        <v>489340.66</v>
+      </c>
+      <c r="DI4" s="1" t="n">
+        <v>86131.63</v>
+      </c>
+      <c r="DJ4" s="1" t="n">
+        <v>43125.59</v>
+      </c>
+      <c r="DK4" s="1" t="n">
+        <v>360299.35</v>
+      </c>
+      <c r="DL4" s="1" t="n">
+        <v>85385.24000000001</v>
+      </c>
+      <c r="DM4" s="1" t="n">
+        <v>260027.89</v>
+      </c>
+      <c r="DN4" s="1" t="n">
+        <v>108155.38</v>
+      </c>
+      <c r="DO4" s="1" t="n">
+        <v>362523.76</v>
+      </c>
+      <c r="DP4" s="1" t="n">
+        <v>20031.91</v>
+      </c>
+      <c r="DQ4" s="1" t="n">
+        <v>28533.06</v>
+      </c>
+      <c r="DR4" s="1" t="n">
+        <v>229101.22</v>
+      </c>
+      <c r="DS4" s="1" t="n">
+        <v>29353.73</v>
+      </c>
+      <c r="DT4" s="1" t="n">
+        <v>192697.44</v>
+      </c>
+      <c r="DU4" s="1" t="n">
+        <v>135243.2</v>
+      </c>
+      <c r="DV4" s="1" t="n">
+        <v>216063.76</v>
+      </c>
+      <c r="DW4" s="1" t="n">
+        <v>2124.15</v>
+      </c>
+      <c r="DX4" s="1" t="n">
+        <v>413377.05</v>
+      </c>
+      <c r="DY4" s="1" t="n">
+        <v>6339.34</v>
+      </c>
+      <c r="DZ4" s="1" t="n">
+        <v>86196.39999999999</v>
+      </c>
+      <c r="EA4" s="1" t="n">
+        <v>15693.39</v>
+      </c>
+      <c r="EB4" s="1" t="n">
+        <v>2312.59</v>
+      </c>
+      <c r="EC4" s="1" t="n">
+        <v>22743.61</v>
+      </c>
+      <c r="ED4" s="1" t="n">
+        <v>402277.02</v>
+      </c>
+      <c r="EE4" s="1" t="n">
+        <v>96475.47</v>
+      </c>
+      <c r="EF4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" s="1" t="n">
+        <v>26849.53</v>
+      </c>
+      <c r="EH4" s="1" t="n">
+        <v>598.6799999999999</v>
+      </c>
+      <c r="EI4" s="1" t="n">
+        <v>105390.61</v>
+      </c>
+      <c r="EJ4" s="1" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="EK4" s="1" t="n">
+        <v>205170.53</v>
+      </c>
+      <c r="EL4" s="1" t="n">
+        <v>99465.34</v>
+      </c>
+      <c r="EM4" s="1" t="n">
+        <v>102428.18</v>
+      </c>
+      <c r="EN4" s="1" t="n">
+        <v>19256.18</v>
+      </c>
+      <c r="EO4" s="1" t="n">
+        <v>138874.69</v>
+      </c>
+      <c r="EP4" s="1" t="n">
+        <v>45908.27</v>
+      </c>
+      <c r="EQ4" s="1" t="n">
+        <v>662.3200000000001</v>
+      </c>
+      <c r="ER4" s="1" t="n">
+        <v>22007.76</v>
+      </c>
+      <c r="ES4" s="1" t="n">
+        <v>5468.67</v>
+      </c>
+      <c r="ET4" s="1" t="n">
+        <v>89880.89999999999</v>
+      </c>
+      <c r="EU4" s="1" t="n">
+        <v>45636.98</v>
+      </c>
+      <c r="EV4" s="1" t="n">
+        <v>26814.17</v>
+      </c>
+      <c r="EW4" s="1" t="n">
+        <v>101453.48</v>
+      </c>
+      <c r="EX4" s="1" t="n">
+        <v>309009.11</v>
+      </c>
+      <c r="EY4" s="1" t="n">
+        <v>25705.42</v>
+      </c>
+      <c r="EZ4" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="FA4" s="1" t="n">
+        <v>66407.73</v>
+      </c>
+      <c r="FB4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC4" s="1" t="n">
+        <v>229508.18</v>
+      </c>
+      <c r="FD4" s="1" t="n">
+        <v>1657560.14</v>
+      </c>
+      <c r="FE4" s="1" t="n">
+        <v>941605.99</v>
+      </c>
+      <c r="FF4" s="1" t="n">
+        <v>48879.86</v>
+      </c>
+      <c r="FG4" s="1" t="n">
+        <v>165409.36</v>
+      </c>
+      <c r="FH4" s="1" t="n">
+        <v>29289.71</v>
+      </c>
+      <c r="FI4" s="1" t="n">
+        <v>61319.82</v>
+      </c>
+      <c r="FJ4" s="1" t="n">
+        <v>61598.86</v>
+      </c>
+      <c r="FK4" s="1" t="n">
+        <v>70642.11</v>
+      </c>
+      <c r="FL4" s="1" t="n">
+        <v>77898.60000000001</v>
+      </c>
+      <c r="FM4" s="1" t="n">
+        <v>64856.01</v>
+      </c>
+      <c r="FN4" s="1" t="n">
+        <v>123727.27</v>
+      </c>
+      <c r="FO4" s="1" t="n">
+        <v>1234.4</v>
+      </c>
+      <c r="FP4" s="1" t="n">
+        <v>2209.86</v>
+      </c>
+      <c r="FQ4" s="1" t="n">
+        <v>532587.58</v>
+      </c>
+      <c r="FR4" s="1" t="n">
+        <v>18939.1</v>
+      </c>
+      <c r="FS4" s="1" t="n">
+        <v>834210.05</v>
+      </c>
+      <c r="FT4" s="1" t="n">
+        <v>135.25</v>
+      </c>
+      <c r="FU4" s="1" t="n">
+        <v>35867.93</v>
+      </c>
+      <c r="FV4" s="1" t="n">
+        <v>88352.22</v>
+      </c>
+      <c r="FW4" s="1" t="n">
+        <v>16073.5</v>
+      </c>
+      <c r="FX4" s="1" t="n">
+        <v>122643.4</v>
+      </c>
+      <c r="FY4" s="1" t="n">
+        <v>143122.91</v>
+      </c>
+      <c r="FZ4" s="1" t="n">
+        <v>1735.18</v>
+      </c>
+      <c r="GA4" s="1" t="n">
+        <v>73872.25</v>
+      </c>
+      <c r="GB4" s="1" t="n">
+        <v>637.63</v>
+      </c>
+      <c r="GC4" s="1" t="n">
+        <v>5101.84</v>
+      </c>
+      <c r="GD4" s="1" t="n">
+        <v>1878.05</v>
+      </c>
+      <c r="GE4" s="1" t="n">
+        <v>105103.64</v>
+      </c>
+      <c r="GF4" s="1" t="n">
+        <v>27044.54</v>
+      </c>
+      <c r="GG4" s="1" t="n">
+        <v>104488.28</v>
+      </c>
+      <c r="GH4" s="1" t="n">
+        <v>178341.25</v>
+      </c>
+      <c r="GI4" s="1" t="n">
+        <v>36368.86</v>
+      </c>
+      <c r="GJ4" s="1" t="n">
+        <v>4150.94</v>
+      </c>
+      <c r="GK4" s="1" t="n">
+        <v>519862.31</v>
+      </c>
+      <c r="GL4" s="1" t="n">
+        <v>22852.63</v>
+      </c>
+      <c r="GM4" s="1" t="n">
+        <v>78997.87</v>
+      </c>
+      <c r="GN4" s="1" t="n">
+        <v>22530.45</v>
+      </c>
+      <c r="GO4" s="1" t="n">
+        <v>379816.5</v>
+      </c>
+      <c r="GP4" s="1" t="n">
+        <v>53424.86</v>
+      </c>
+      <c r="GQ4" s="1" t="n">
+        <v>41599.55</v>
+      </c>
+      <c r="GR4" s="1" t="n">
+        <v>2817.02</v>
+      </c>
+      <c r="GS4" s="1" t="n">
+        <v>34143.13</v>
+      </c>
+      <c r="GT4" s="1" t="n">
+        <v>342522.57</v>
+      </c>
+      <c r="GU4" s="1" t="n">
+        <v>27534.95</v>
+      </c>
+      <c r="GV4" s="1" t="n">
+        <v>328255.32</v>
+      </c>
+      <c r="GW4" s="1" t="n">
+        <v>36869.97</v>
+      </c>
+      <c r="GX4" s="1" t="n">
+        <v>45556.46</v>
+      </c>
+      <c r="GY4" s="1" t="n">
+        <v>278100.44</v>
+      </c>
+      <c r="GZ4" s="1" t="n">
+        <v>942.25</v>
+      </c>
+      <c r="HA4" s="1" t="n">
+        <v>73835.96000000001</v>
+      </c>
+      <c r="HB4" s="1" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="HC4" s="1" t="n">
+        <v>44517.49</v>
+      </c>
+      <c r="HD4" s="1" t="n">
+        <v>19901.72</v>
+      </c>
+      <c r="HE4" s="1" t="n">
+        <v>15116.59</v>
+      </c>
+      <c r="HF4" s="1" t="n">
+        <v>4387.77</v>
+      </c>
+      <c r="HG4" s="1" t="n">
+        <v>16950.36</v>
+      </c>
+      <c r="HH4" s="1" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="HI4" s="1" t="n">
+        <v>36378.06</v>
+      </c>
+      <c r="HJ4" s="1" t="n">
+        <v>22134.33</v>
+      </c>
+      <c r="HK4" s="1" t="n">
+        <v>76728.41</v>
+      </c>
+      <c r="HL4" s="1" t="n">
+        <v>167725.97</v>
+      </c>
+      <c r="HM4" s="1" t="n">
+        <v>2695.75</v>
+      </c>
+      <c r="HN4" s="1" t="n">
+        <v>241214.65</v>
+      </c>
+      <c r="HO4" s="1" t="n">
+        <v>25608.29</v>
+      </c>
+      <c r="HP4" s="1" t="n">
+        <v>147152.48</v>
+      </c>
+      <c r="HQ4" s="1" t="n">
+        <v>16061.68</v>
+      </c>
+      <c r="HR4" s="1" t="n">
+        <v>12648.94</v>
+      </c>
+      <c r="HS4" s="1" t="n">
+        <v>176644.87</v>
+      </c>
+      <c r="HT4" s="1" t="n">
+        <v>52397.2</v>
+      </c>
+      <c r="HU4" s="1" t="n">
+        <v>693.8099999999999</v>
+      </c>
+      <c r="HV4" s="1" t="n">
+        <v>250594.66</v>
+      </c>
+      <c r="HW4" s="1" t="n">
+        <v>1360.57</v>
+      </c>
+      <c r="HX4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY4" s="1" t="n">
+        <v>38794.93</v>
+      </c>
+      <c r="HZ4" s="1" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="IA4" s="1" t="n">
+        <v>1951.28</v>
+      </c>
+      <c r="IB4" s="1" t="n">
+        <v>3009.52</v>
+      </c>
+      <c r="IC4" s="1" t="n">
+        <v>4931.65</v>
+      </c>
+      <c r="ID4" s="1" t="n">
+        <v>29795.35</v>
+      </c>
+      <c r="IE4" s="1" t="n">
+        <v>55348.16</v>
+      </c>
+      <c r="IF4" s="1" t="n">
+        <v>8080.83</v>
+      </c>
+      <c r="IG4" s="1" t="n">
+        <v>112246.81</v>
+      </c>
+      <c r="IH4" s="1" t="n">
+        <v>1437.42</v>
+      </c>
+      <c r="II4" s="1" t="n">
+        <v>93490.67999999999</v>
+      </c>
+      <c r="IJ4" s="1" t="n">
+        <v>22275.84</v>
+      </c>
+      <c r="IK4" s="1" t="n">
+        <v>25980.84</v>
+      </c>
+      <c r="IL4" s="1" t="n">
+        <v>4473</v>
+      </c>
+      <c r="IM4" s="1" t="n">
+        <v>30924</v>
+      </c>
+      <c r="IN4" s="1" t="n">
+        <v>2204.47</v>
+      </c>
+      <c r="IO4" s="1" t="n">
+        <v>144851.12</v>
+      </c>
+      <c r="IP4" s="1" t="n">
+        <v>1348.69</v>
+      </c>
+      <c r="IQ4" s="1" t="n">
+        <v>3859</v>
+      </c>
+      <c r="IR4" s="1" t="n">
+        <v>9974.91</v>
+      </c>
+      <c r="IS4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT4" s="1" t="n">
+        <v>8796.02</v>
+      </c>
+      <c r="IU4" s="1" t="n">
+        <v>12793.17</v>
+      </c>
+      <c r="IV4" s="1" t="n">
+        <v>17198.86</v>
+      </c>
+      <c r="IW4" s="1" t="n">
+        <v>304174.5</v>
+      </c>
+      <c r="IX4" s="1" t="n">
+        <v>28865.33</v>
+      </c>
+      <c r="IY4" s="1" t="n">
+        <v>7133.07</v>
+      </c>
+      <c r="IZ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA4" s="1" t="n">
+        <v>1513.61</v>
+      </c>
+      <c r="JB4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC4" s="1" t="n">
+        <v>12218.31</v>
+      </c>
+      <c r="JD4" s="1" t="n">
+        <v>8204.290000000001</v>
+      </c>
+      <c r="JE4" s="1" t="n">
+        <v>39220.44</v>
+      </c>
+      <c r="JF4" s="1" t="n">
+        <v>8187.33</v>
+      </c>
+      <c r="JG4" s="1" t="n">
+        <v>15648</v>
+      </c>
+      <c r="JH4" s="1" t="n">
+        <v>5154.27</v>
+      </c>
+      <c r="JI4" s="1" t="n">
+        <v>71142.39</v>
+      </c>
+      <c r="JJ4" s="1" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="JK4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JL4" s="1" t="n">
+        <v>5043.86</v>
+      </c>
+      <c r="JM4" s="1" t="n">
+        <v>3160.03</v>
+      </c>
+      <c r="JN4" s="1" t="n">
+        <v>10221.77</v>
+      </c>
+      <c r="JO4" s="1" t="n">
+        <v>4863.59</v>
+      </c>
+      <c r="JP4" s="1" t="n">
+        <v>1028.47</v>
+      </c>
+      <c r="JQ4" s="1" t="n">
+        <v>199.31</v>
+      </c>
+      <c r="JR4" s="1" t="n">
+        <v>3706.13</v>
+      </c>
+      <c r="JS4" s="1" t="n">
+        <v>60285.37</v>
+      </c>
+      <c r="JT4" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="JU4" s="1" t="n">
+        <v>15581.6</v>
+      </c>
+      <c r="JV4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JW4" s="1" t="n">
+        <v>3714.62</v>
+      </c>
+      <c r="JX4" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="JY4" s="1" t="n">
+        <v>22299.37</v>
+      </c>
+      <c r="JZ4" s="1" t="n">
+        <v>6135.33</v>
+      </c>
+      <c r="KA4" s="1" t="n">
+        <v>193118.87</v>
+      </c>
+      <c r="KB4" s="1" t="n">
+        <v>13434.1</v>
+      </c>
+      <c r="KC4" s="1" t="n">
+        <v>9159.379999999999</v>
+      </c>
+      <c r="KD4" s="1" t="n">
+        <v>398.34</v>
+      </c>
+      <c r="KE4" s="1" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="KF4" s="1" t="n">
+        <v>401.82</v>
+      </c>
+      <c r="KG4" s="1" t="n">
+        <v>33547.68</v>
+      </c>
+      <c r="KH4" s="1" t="n">
+        <v>57840.96</v>
+      </c>
+      <c r="KI4" s="1" t="n">
+        <v>40320.31</v>
+      </c>
+      <c r="KJ4" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="KK4" s="1" t="n">
+        <v>198.61</v>
+      </c>
+      <c r="KL4" s="1" t="n">
+        <v>1791.2</v>
+      </c>
+      <c r="KM4" s="1" t="n">
+        <v>29745.39</v>
+      </c>
+      <c r="KN4" s="1" t="n">
+        <v>43109.78</v>
+      </c>
+      <c r="KO4" s="1" t="n">
+        <v>56518.99</v>
+      </c>
+      <c r="KP4" s="1" t="n">
+        <v>1022.04</v>
+      </c>
+      <c r="KQ4" s="1" t="n">
+        <v>8289.67</v>
+      </c>
+      <c r="KR4" s="1" t="n">
+        <v>76.20999999999999</v>
+      </c>
+      <c r="KS4" s="1" t="n">
+        <v>688009.0600000001</v>
+      </c>
+      <c r="KT4" s="1" t="n">
+        <v>100873.61</v>
+      </c>
+      <c r="KU4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KV4" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="KW4" s="1" t="n">
+        <v>466.21</v>
+      </c>
+      <c r="KX4" s="1" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="KY4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KZ4" s="1" t="n">
+        <v>20362.5</v>
+      </c>
+      <c r="LA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LB4" s="1" t="n">
+        <v>815179.04</v>
+      </c>
+      <c r="LC4" s="1" t="n">
+        <v>584.72</v>
+      </c>
+      <c r="LD4" s="1" t="n">
+        <v>135562.43</v>
+      </c>
+      <c r="LE4" s="1" t="n">
+        <v>19145.99</v>
+      </c>
+      <c r="LF4" s="1" t="n">
+        <v>199.46</v>
+      </c>
+      <c r="LG4" s="1" t="n">
+        <v>2166.8</v>
+      </c>
+      <c r="LH4" s="1" t="n">
+        <v>850.1799999999999</v>
+      </c>
+      <c r="LI4" s="1" t="n">
+        <v>13114.72</v>
+      </c>
+      <c r="LJ4" s="1" t="n">
+        <v>1771.64</v>
+      </c>
+      <c r="LK4" s="1" t="n">
+        <v>629.6900000000001</v>
+      </c>
+      <c r="LL4" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LM4" s="1" t="n">
+        <v>559.92</v>
+      </c>
+      <c r="LN4" s="1" t="n">
+        <v>451.31</v>
+      </c>
+      <c r="LO4" s="1" t="n">
+        <v>449.6</v>
+      </c>
+      <c r="LP4" s="1" t="n">
+        <v>10337.43</v>
+      </c>
+      <c r="LQ4" s="1" t="n">
+        <v>110.83</v>
+      </c>
+      <c r="LR4" s="1" t="n">
+        <v>3217.77</v>
+      </c>
+      <c r="LS4" s="1" t="n">
+        <v>185.79</v>
+      </c>
+      <c r="LT4" s="1" t="n">
+        <v>997.38</v>
+      </c>
+      <c r="LU4" s="1" t="n">
+        <v>398.41</v>
+      </c>
+      <c r="LV4" s="1" t="n">
+        <v>1569.29</v>
+      </c>
+      <c r="LW4" s="1" t="n">
+        <v>44830.93</v>
+      </c>
+      <c r="LX4" s="1" t="n">
+        <v>929.67</v>
+      </c>
+      <c r="LY4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LZ4" s="1" t="n">
+        <v>10086.22</v>
+      </c>
+      <c r="MA4" s="1" t="n">
+        <v>253.88</v>
+      </c>
+      <c r="MB4" s="1" t="n">
+        <v>2780.11</v>
+      </c>
+      <c r="MC4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MD4" s="1" t="n">
+        <v>31450.04</v>
+      </c>
+      <c r="ME4" s="1" t="n">
+        <v>487.83</v>
+      </c>
+      <c r="MF4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MG4" s="1" t="n">
+        <v>223184.58</v>
+      </c>
+      <c r="MH4" s="1" t="n">
+        <v>5064.07</v>
+      </c>
+      <c r="MI4" s="1" t="n">
+        <v>8544.66</v>
+      </c>
+      <c r="MJ4" s="1" t="n">
+        <v>7423.97</v>
+      </c>
+      <c r="MK4" s="1" t="n">
+        <v>1187.34</v>
+      </c>
+      <c r="ML4" s="1" t="n">
+        <v>362.16</v>
+      </c>
+      <c r="MM4" s="1" t="n">
+        <v>200.33</v>
+      </c>
+      <c r="MN4" s="1" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="MO4" s="1" t="n">
+        <v>199.47</v>
+      </c>
+      <c r="MP4" s="1" t="n">
+        <v>17049.92</v>
+      </c>
+      <c r="MQ4" s="1" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="MR4" s="1" t="n">
+        <v>18229.31</v>
+      </c>
+      <c r="MS4" s="1" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="MT4" s="1" t="n">
+        <v>10695.41</v>
+      </c>
+      <c r="MU4" s="1" t="n">
+        <v>84085.89999999999</v>
+      </c>
+      <c r="MV4" s="1" t="n">
+        <v>4987.52</v>
+      </c>
+      <c r="MW4" s="1" t="n">
+        <v>5087.26</v>
+      </c>
+      <c r="MX4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MY4" s="1" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="MZ4" s="1" t="n">
+        <v>12764.38</v>
+      </c>
+      <c r="NA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NB4" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="NC4" s="1" t="n">
+        <v>9142.620000000001</v>
+      </c>
+      <c r="ND4" s="1" t="n">
+        <v>169392.28</v>
+      </c>
+      <c r="NE4" s="1" t="n">
+        <v>1646.62</v>
+      </c>
+      <c r="NF4" s="1" t="n">
+        <v>549.75</v>
+      </c>
+      <c r="NG4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="NH4" s="1" t="n">
+        <v>21909.38</v>
+      </c>
+      <c r="NI4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NJ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NK4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NL4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NM4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NN4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NO4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NP4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NQ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NR4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NS4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NT4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NU4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NV4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NW4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NX4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NY4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NZ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OB4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OC4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OD4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OE4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OF4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OG4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OH4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OI4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OJ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OK4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OL4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OM4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ON4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OO4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OP4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OQ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OR4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OS4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OT4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OU4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OV4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OW4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OX4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OY4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OZ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PB4" s="1" t="n">
+        <v>498.74</v>
+      </c>
+      <c r="PC4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PD4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PE4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PF4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PG4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PH4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PI4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PJ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PK4" s="1" t="n">
+        <v>9859.5</v>
+      </c>
+      <c r="PL4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PM4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PN4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PO4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PP4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PQ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PR4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PS4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PT4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PU4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PV4" s="1" t="n">
+        <v>713.37</v>
+      </c>
+      <c r="PW4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PX4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PY4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PZ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QB4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5560,7 +6891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW3"/>
+  <dimension ref="A1:BXW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5704,6 +7035,44 @@
       </c>
       <c r="M3" s="1" t="n">
         <v>3930.337943</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>716383579.21</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>75393355.71813001</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>20514427.1186</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>12551433.4178</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>4815890.0662</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>3202469.9998</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>3717558.3548</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>17727.1743</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>34306.2575</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>2406.2268</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>21670.594923</v>
       </c>
     </row>
   </sheetData>
@@ -5717,7 +7086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW3"/>
+  <dimension ref="A1:BXW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6883,6 +8252,323 @@
         <v>0</v>
       </c>
       <c r="DB3" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>4859159.536246131</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>4953546.256993227</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>4130046.350622243</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>450768.0417339354</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>153110.837</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>412110.0657793726</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>102482.6571023</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>28119.22</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>65188.8275766628</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>6.1055</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>202.09</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>99.00360000000001</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>8385.18833635</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>3982.065004</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>181.4858</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>49.725</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>167.02335</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="1" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BJ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX4" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="CY4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6897,7 +8583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW3"/>
+  <dimension ref="A1:BXW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7216,6 +8902,122 @@
       </c>
       <c r="AM3" s="1" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>36245644.96</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>2598733.24</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>849950.76</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>335367.25</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>701599.66</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>10941725.57</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>251047.86</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>302812.17</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1296.22</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>68988.31</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>19601.58</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>507</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>3568.93</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>3734.4</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>18624.65</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>48523.7</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>14679.77</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>3130</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>509581.38</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>253467.65</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>501.5</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>3930.68</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>42819.57</v>
+      </c>
+      <c r="AI4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>101601.13</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>33559.37</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>5000.76</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>619529776.17</v>
+        <v>285979797.87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>716383579.21</v>
+        <v>261410758.19</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>4953546.256993227</v>
+        <v>3979710.360752966</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>36245644.96</v>
+        <v>5631460.13</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>248098256.84</v>
+        <v>134381485.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,23 +518,23 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>75393355.71813001</v>
+        <v>48491748.89671</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ETH_THB</t>
+          <t>USDT_THB</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>4859159.536246131</v>
+        <v>2702582.529013106</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>USDTTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>10941725.57</v>
+        <v>384768.28</v>
       </c>
     </row>
     <row r="4">
@@ -547,31 +547,31 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>78658560.29000001</v>
+        <v>48448514.94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>VELOTHB</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>3432271.8459</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ETH_THB</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>462719.9286716436</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>XRPTHB</t>
         </is>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>20514427.1186</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>USDT_THB</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>4130046.350622243</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>XRPTHB</t>
-        </is>
-      </c>
       <c r="L4" s="1" t="n">
-        <v>2598733.24</v>
+        <v>355884.26</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>33834050.91</v>
+        <v>17015404.99</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -592,23 +592,23 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>12551433.4178</v>
+        <v>2642830.7577</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ADA_THB</t>
+          <t>DOGE_THB</t>
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>450768.0417339354</v>
+        <v>103794.8951224</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>SOLTHB</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>849950.76</v>
+        <v>261960.65</v>
       </c>
     </row>
     <row r="6">
@@ -617,35 +617,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_DOGE</t>
+          <t>THB_TRUMP</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>25172538.44</v>
+        <v>13531302.87</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SOLTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>4815890.0662</v>
+        <v>1139423.6635</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SOL_THB</t>
+          <t>BNB_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>412110.0657793726</v>
+        <v>76936.77997432501</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>BCHTHB</t>
+          <t>USDTTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>701599.66</v>
+        <v>194119.38</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW4"/>
+  <dimension ref="A1:BXW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6877,6 +6877,1337 @@
         <v>0</v>
       </c>
       <c r="QB4" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>285979797.87</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>134381485.9</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>48448514.94</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>17015404.99</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>9943789.130000001</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>6560060.82</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>3428097.4</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>3886675.32</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>5998577.77</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>4212083.78</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>13531302.87</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>6576119.97</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>3096928.19</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1543756.47</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>3259539.45</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>2551699.18</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>2022992.03</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>1879958.42</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>2761207.45</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>1179213.4</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>3252394.5</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>4077416.43</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>976324.89</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>885564.3100000001</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>2734056.25</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>3351546.34</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>2897746.23</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>986555.85</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>896459.55</v>
+      </c>
+      <c r="AF5" s="1" t="n">
+        <v>5594951.03</v>
+      </c>
+      <c r="AG5" s="1" t="n">
+        <v>534613.77</v>
+      </c>
+      <c r="AH5" s="1" t="n">
+        <v>618596.05</v>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>2262645.52</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>1068572.55</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>717429.15</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>359317.12</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>1587235.59</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>3116.47</v>
+      </c>
+      <c r="AO5" s="1" t="n">
+        <v>825844.04</v>
+      </c>
+      <c r="AP5" s="1" t="n">
+        <v>291172.7</v>
+      </c>
+      <c r="AQ5" s="1" t="n">
+        <v>1182459.98</v>
+      </c>
+      <c r="AR5" s="1" t="n">
+        <v>154071.98</v>
+      </c>
+      <c r="AS5" s="1" t="n">
+        <v>45820.48</v>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>443203.22</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>780303.29</v>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>1849775.58</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>688153.45</v>
+      </c>
+      <c r="AX5" s="1" t="n">
+        <v>835931.72</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>181166.65</v>
+      </c>
+      <c r="AZ5" s="1" t="n">
+        <v>114088.73</v>
+      </c>
+      <c r="BA5" s="1" t="n">
+        <v>95536.19</v>
+      </c>
+      <c r="BB5" s="1" t="n">
+        <v>536037.39</v>
+      </c>
+      <c r="BC5" s="1" t="n">
+        <v>1549692.8</v>
+      </c>
+      <c r="BD5" s="1" t="n">
+        <v>248006.67</v>
+      </c>
+      <c r="BE5" s="1" t="n">
+        <v>691333.1</v>
+      </c>
+      <c r="BF5" s="1" t="n">
+        <v>336323.66</v>
+      </c>
+      <c r="BG5" s="1" t="n">
+        <v>37921.92</v>
+      </c>
+      <c r="BH5" s="1" t="n">
+        <v>862014.58</v>
+      </c>
+      <c r="BI5" s="1" t="n">
+        <v>416945.68</v>
+      </c>
+      <c r="BJ5" s="1" t="n">
+        <v>26355.77</v>
+      </c>
+      <c r="BK5" s="1" t="n">
+        <v>67579.16</v>
+      </c>
+      <c r="BL5" s="1" t="n">
+        <v>1474.24</v>
+      </c>
+      <c r="BM5" s="1" t="n">
+        <v>46695.29</v>
+      </c>
+      <c r="BN5" s="1" t="n">
+        <v>160071.27</v>
+      </c>
+      <c r="BO5" s="1" t="n">
+        <v>53543.77</v>
+      </c>
+      <c r="BP5" s="1" t="n">
+        <v>183335.67</v>
+      </c>
+      <c r="BQ5" s="1" t="n">
+        <v>93960.99000000001</v>
+      </c>
+      <c r="BR5" s="1" t="n">
+        <v>606043.35</v>
+      </c>
+      <c r="BS5" s="1" t="n">
+        <v>123098.29</v>
+      </c>
+      <c r="BT5" s="1" t="n">
+        <v>658520.3</v>
+      </c>
+      <c r="BU5" s="1" t="n">
+        <v>741854.1800000001</v>
+      </c>
+      <c r="BV5" s="1" t="n">
+        <v>497220.34</v>
+      </c>
+      <c r="BW5" s="1" t="n">
+        <v>23083.11</v>
+      </c>
+      <c r="BX5" s="1" t="n">
+        <v>28310.66</v>
+      </c>
+      <c r="BY5" s="1" t="n">
+        <v>216836.13</v>
+      </c>
+      <c r="BZ5" s="1" t="n">
+        <v>38768.69</v>
+      </c>
+      <c r="CA5" s="1" t="n">
+        <v>73419.94</v>
+      </c>
+      <c r="CB5" s="1" t="n">
+        <v>550350.3100000001</v>
+      </c>
+      <c r="CC5" s="1" t="n">
+        <v>234024.64</v>
+      </c>
+      <c r="CD5" s="1" t="n">
+        <v>110655</v>
+      </c>
+      <c r="CE5" s="1" t="n">
+        <v>1752.18</v>
+      </c>
+      <c r="CF5" s="1" t="n">
+        <v>80883.89</v>
+      </c>
+      <c r="CG5" s="1" t="n">
+        <v>549967.88</v>
+      </c>
+      <c r="CH5" s="1" t="n">
+        <v>34210.28</v>
+      </c>
+      <c r="CI5" s="1" t="n">
+        <v>69027.75</v>
+      </c>
+      <c r="CJ5" s="1" t="n">
+        <v>790220.24</v>
+      </c>
+      <c r="CK5" s="1" t="n">
+        <v>205598.6</v>
+      </c>
+      <c r="CL5" s="1" t="n">
+        <v>60600.26</v>
+      </c>
+      <c r="CM5" s="1" t="n">
+        <v>12608.03</v>
+      </c>
+      <c r="CN5" s="1" t="n">
+        <v>99261.38</v>
+      </c>
+      <c r="CO5" s="1" t="n">
+        <v>600019.96</v>
+      </c>
+      <c r="CP5" s="1" t="n">
+        <v>184305.61</v>
+      </c>
+      <c r="CQ5" s="1" t="n">
+        <v>398901.11</v>
+      </c>
+      <c r="CR5" s="1" t="n">
+        <v>338068.26</v>
+      </c>
+      <c r="CS5" s="1" t="n">
+        <v>28909.83</v>
+      </c>
+      <c r="CT5" s="1" t="n">
+        <v>37538.21</v>
+      </c>
+      <c r="CU5" s="1" t="n">
+        <v>246667.8</v>
+      </c>
+      <c r="CV5" s="1" t="n">
+        <v>254749.02</v>
+      </c>
+      <c r="CW5" s="1" t="n">
+        <v>274514.22</v>
+      </c>
+      <c r="CX5" s="1" t="n">
+        <v>32538.95</v>
+      </c>
+      <c r="CY5" s="1" t="n">
+        <v>4481.98</v>
+      </c>
+      <c r="CZ5" s="1" t="n">
+        <v>89214.39999999999</v>
+      </c>
+      <c r="DA5" s="1" t="n">
+        <v>2493.76</v>
+      </c>
+      <c r="DB5" s="1" t="n">
+        <v>42985.94</v>
+      </c>
+      <c r="DC5" s="1" t="n">
+        <v>3473.18</v>
+      </c>
+      <c r="DD5" s="1" t="n">
+        <v>102827.93</v>
+      </c>
+      <c r="DE5" s="1" t="n">
+        <v>76983.63</v>
+      </c>
+      <c r="DF5" s="1" t="n">
+        <v>196756.47</v>
+      </c>
+      <c r="DG5" s="1" t="n">
+        <v>4397280.2</v>
+      </c>
+      <c r="DH5" s="1" t="n">
+        <v>94126.85000000001</v>
+      </c>
+      <c r="DI5" s="1" t="n">
+        <v>227091.46</v>
+      </c>
+      <c r="DJ5" s="1" t="n">
+        <v>31202.77</v>
+      </c>
+      <c r="DK5" s="1" t="n">
+        <v>88018.99000000001</v>
+      </c>
+      <c r="DL5" s="1" t="n">
+        <v>7226.72</v>
+      </c>
+      <c r="DM5" s="1" t="n">
+        <v>101213.24</v>
+      </c>
+      <c r="DN5" s="1" t="n">
+        <v>38925.47</v>
+      </c>
+      <c r="DO5" s="1" t="n">
+        <v>83321.75999999999</v>
+      </c>
+      <c r="DP5" s="1" t="n">
+        <v>125832.9</v>
+      </c>
+      <c r="DQ5" s="1" t="n">
+        <v>61475.2</v>
+      </c>
+      <c r="DR5" s="1" t="n">
+        <v>25736.53</v>
+      </c>
+      <c r="DS5" s="1" t="n">
+        <v>17833.87</v>
+      </c>
+      <c r="DT5" s="1" t="n">
+        <v>60936.47</v>
+      </c>
+      <c r="DU5" s="1" t="n">
+        <v>135243.2</v>
+      </c>
+      <c r="DV5" s="1" t="n">
+        <v>38720.73</v>
+      </c>
+      <c r="DW5" s="1" t="n">
+        <v>26232.29</v>
+      </c>
+      <c r="DX5" s="1" t="n">
+        <v>260304.78</v>
+      </c>
+      <c r="DY5" s="1" t="n">
+        <v>84701.67999999999</v>
+      </c>
+      <c r="DZ5" s="1" t="n">
+        <v>10319.56</v>
+      </c>
+      <c r="EA5" s="1" t="n">
+        <v>59296.53</v>
+      </c>
+      <c r="EB5" s="1" t="n">
+        <v>5559.6</v>
+      </c>
+      <c r="EC5" s="1" t="n">
+        <v>20143.45</v>
+      </c>
+      <c r="ED5" s="1" t="n">
+        <v>10465.77</v>
+      </c>
+      <c r="EE5" s="1" t="n">
+        <v>68342.16</v>
+      </c>
+      <c r="EF5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" s="1" t="n">
+        <v>16436.8</v>
+      </c>
+      <c r="EH5" s="1" t="n">
+        <v>862.03</v>
+      </c>
+      <c r="EI5" s="1" t="n">
+        <v>52523.59</v>
+      </c>
+      <c r="EJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK5" s="1" t="n">
+        <v>152127.16</v>
+      </c>
+      <c r="EL5" s="1" t="n">
+        <v>1546.37</v>
+      </c>
+      <c r="EM5" s="1" t="n">
+        <v>38870.48</v>
+      </c>
+      <c r="EN5" s="1" t="n">
+        <v>55340.84</v>
+      </c>
+      <c r="EO5" s="1" t="n">
+        <v>4704871.61</v>
+      </c>
+      <c r="EP5" s="1" t="n">
+        <v>154694.84</v>
+      </c>
+      <c r="EQ5" s="1" t="n">
+        <v>348.66</v>
+      </c>
+      <c r="ER5" s="1" t="n">
+        <v>7631.61</v>
+      </c>
+      <c r="ES5" s="1" t="n">
+        <v>24661.22</v>
+      </c>
+      <c r="ET5" s="1" t="n">
+        <v>14078.84</v>
+      </c>
+      <c r="EU5" s="1" t="n">
+        <v>30259.4</v>
+      </c>
+      <c r="EV5" s="1" t="n">
+        <v>6899.02</v>
+      </c>
+      <c r="EW5" s="1" t="n">
+        <v>98399.97</v>
+      </c>
+      <c r="EX5" s="1" t="n">
+        <v>43154.73</v>
+      </c>
+      <c r="EY5" s="1" t="n">
+        <v>11196.42</v>
+      </c>
+      <c r="EZ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" s="1" t="n">
+        <v>66407.73</v>
+      </c>
+      <c r="FB5" s="1" t="n">
+        <v>22090.18</v>
+      </c>
+      <c r="FC5" s="1" t="n">
+        <v>70703.67</v>
+      </c>
+      <c r="FD5" s="1" t="n">
+        <v>1191.27</v>
+      </c>
+      <c r="FE5" s="1" t="n">
+        <v>1311349.83</v>
+      </c>
+      <c r="FF5" s="1" t="n">
+        <v>15898.38</v>
+      </c>
+      <c r="FG5" s="1" t="n">
+        <v>52104.91</v>
+      </c>
+      <c r="FH5" s="1" t="n">
+        <v>151129.1</v>
+      </c>
+      <c r="FI5" s="1" t="n">
+        <v>18606.37</v>
+      </c>
+      <c r="FJ5" s="1" t="n">
+        <v>61598.86</v>
+      </c>
+      <c r="FK5" s="1" t="n">
+        <v>72117.39999999999</v>
+      </c>
+      <c r="FL5" s="1" t="n">
+        <v>27473.48</v>
+      </c>
+      <c r="FM5" s="1" t="n">
+        <v>8752.459999999999</v>
+      </c>
+      <c r="FN5" s="1" t="n">
+        <v>36260.14</v>
+      </c>
+      <c r="FO5" s="1" t="n">
+        <v>13892.69</v>
+      </c>
+      <c r="FP5" s="1" t="n">
+        <v>7291.28</v>
+      </c>
+      <c r="FQ5" s="1" t="n">
+        <v>302736.06</v>
+      </c>
+      <c r="FR5" s="1" t="n">
+        <v>10184.53</v>
+      </c>
+      <c r="FS5" s="1" t="n">
+        <v>2490547.68</v>
+      </c>
+      <c r="FT5" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="FU5" s="1" t="n">
+        <v>31803.01</v>
+      </c>
+      <c r="FV5" s="1" t="n">
+        <v>391591.29</v>
+      </c>
+      <c r="FW5" s="1" t="n">
+        <v>8380.709999999999</v>
+      </c>
+      <c r="FX5" s="1" t="n">
+        <v>40048.99</v>
+      </c>
+      <c r="FY5" s="1" t="n">
+        <v>70519.22</v>
+      </c>
+      <c r="FZ5" s="1" t="n">
+        <v>613.9</v>
+      </c>
+      <c r="GA5" s="1" t="n">
+        <v>61830.43</v>
+      </c>
+      <c r="GB5" s="1" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="GC5" s="1" t="n">
+        <v>62384.37</v>
+      </c>
+      <c r="GD5" s="1" t="n">
+        <v>34444.94</v>
+      </c>
+      <c r="GE5" s="1" t="n">
+        <v>99839.41</v>
+      </c>
+      <c r="GF5" s="1" t="n">
+        <v>10084.76</v>
+      </c>
+      <c r="GG5" s="1" t="n">
+        <v>104257.87</v>
+      </c>
+      <c r="GH5" s="1" t="n">
+        <v>169597.74</v>
+      </c>
+      <c r="GI5" s="1" t="n">
+        <v>29489.75</v>
+      </c>
+      <c r="GJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK5" s="1" t="n">
+        <v>189912.04</v>
+      </c>
+      <c r="GL5" s="1" t="n">
+        <v>29488.64</v>
+      </c>
+      <c r="GM5" s="1" t="n">
+        <v>27669.78</v>
+      </c>
+      <c r="GN5" s="1" t="n">
+        <v>2146.01</v>
+      </c>
+      <c r="GO5" s="1" t="n">
+        <v>36582.17</v>
+      </c>
+      <c r="GP5" s="1" t="n">
+        <v>134.04</v>
+      </c>
+      <c r="GQ5" s="1" t="n">
+        <v>28318.02</v>
+      </c>
+      <c r="GR5" s="1" t="n">
+        <v>990.62</v>
+      </c>
+      <c r="GS5" s="1" t="n">
+        <v>63676.17</v>
+      </c>
+      <c r="GT5" s="1" t="n">
+        <v>360094.34</v>
+      </c>
+      <c r="GU5" s="1" t="n">
+        <v>5561.96</v>
+      </c>
+      <c r="GV5" s="1" t="n">
+        <v>114774.64</v>
+      </c>
+      <c r="GW5" s="1" t="n">
+        <v>36869.97</v>
+      </c>
+      <c r="GX5" s="1" t="n">
+        <v>453.68</v>
+      </c>
+      <c r="GY5" s="1" t="n">
+        <v>428955.94</v>
+      </c>
+      <c r="GZ5" s="1" t="n">
+        <v>22161.91</v>
+      </c>
+      <c r="HA5" s="1" t="n">
+        <v>73835.96000000001</v>
+      </c>
+      <c r="HB5" s="1" t="n">
+        <v>3006.3</v>
+      </c>
+      <c r="HC5" s="1" t="n">
+        <v>13566.47</v>
+      </c>
+      <c r="HD5" s="1" t="n">
+        <v>495.76</v>
+      </c>
+      <c r="HE5" s="1" t="n">
+        <v>2310.71</v>
+      </c>
+      <c r="HF5" s="1" t="n">
+        <v>7279.73</v>
+      </c>
+      <c r="HG5" s="1" t="n">
+        <v>14192.74</v>
+      </c>
+      <c r="HH5" s="1" t="n">
+        <v>1422.34</v>
+      </c>
+      <c r="HI5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HJ5" s="1" t="n">
+        <v>29616.13</v>
+      </c>
+      <c r="HK5" s="1" t="n">
+        <v>101701.27</v>
+      </c>
+      <c r="HL5" s="1" t="n">
+        <v>5399.26</v>
+      </c>
+      <c r="HM5" s="1" t="n">
+        <v>17648.94</v>
+      </c>
+      <c r="HN5" s="1" t="n">
+        <v>526427.77</v>
+      </c>
+      <c r="HO5" s="1" t="n">
+        <v>34755.44</v>
+      </c>
+      <c r="HP5" s="1" t="n">
+        <v>53486.1</v>
+      </c>
+      <c r="HQ5" s="1" t="n">
+        <v>16999.11</v>
+      </c>
+      <c r="HR5" s="1" t="n">
+        <v>997.49</v>
+      </c>
+      <c r="HS5" s="1" t="n">
+        <v>86776.58</v>
+      </c>
+      <c r="HT5" s="1" t="n">
+        <v>74844.09</v>
+      </c>
+      <c r="HU5" s="1" t="n">
+        <v>1155.18</v>
+      </c>
+      <c r="HV5" s="1" t="n">
+        <v>529.5</v>
+      </c>
+      <c r="HW5" s="1" t="n">
+        <v>16423.36</v>
+      </c>
+      <c r="HX5" s="1" t="n">
+        <v>541.86</v>
+      </c>
+      <c r="HY5" s="1" t="n">
+        <v>4360.68</v>
+      </c>
+      <c r="HZ5" s="1" t="n">
+        <v>25493.69</v>
+      </c>
+      <c r="IA5" s="1" t="n">
+        <v>2172.83</v>
+      </c>
+      <c r="IB5" s="1" t="n">
+        <v>3237.24</v>
+      </c>
+      <c r="IC5" s="1" t="n">
+        <v>43863.6</v>
+      </c>
+      <c r="ID5" s="1" t="n">
+        <v>29795.35</v>
+      </c>
+      <c r="IE5" s="1" t="n">
+        <v>376793.33</v>
+      </c>
+      <c r="IF5" s="1" t="n">
+        <v>3273.46</v>
+      </c>
+      <c r="IG5" s="1" t="n">
+        <v>22516.68</v>
+      </c>
+      <c r="IH5" s="1" t="n">
+        <v>115.74</v>
+      </c>
+      <c r="II5" s="1" t="n">
+        <v>61366.72</v>
+      </c>
+      <c r="IJ5" s="1" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="IK5" s="1" t="n">
+        <v>335.41</v>
+      </c>
+      <c r="IL5" s="1" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="IM5" s="1" t="n">
+        <v>6063.08</v>
+      </c>
+      <c r="IN5" s="1" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="IO5" s="1" t="n">
+        <v>1441.36</v>
+      </c>
+      <c r="IP5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IQ5" s="1" t="n">
+        <v>185.26</v>
+      </c>
+      <c r="IR5" s="1" t="n">
+        <v>1198.73</v>
+      </c>
+      <c r="IS5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT5" s="1" t="n">
+        <v>7064.82</v>
+      </c>
+      <c r="IU5" s="1" t="n">
+        <v>50659.75</v>
+      </c>
+      <c r="IV5" s="1" t="n">
+        <v>11219.57</v>
+      </c>
+      <c r="IW5" s="1" t="n">
+        <v>17079.99</v>
+      </c>
+      <c r="IX5" s="1" t="n">
+        <v>997.5</v>
+      </c>
+      <c r="IY5" s="1" t="n">
+        <v>1984.78</v>
+      </c>
+      <c r="IZ5" s="1" t="n">
+        <v>56330.34</v>
+      </c>
+      <c r="JA5" s="1" t="n">
+        <v>3864.89</v>
+      </c>
+      <c r="JB5" s="1" t="n">
+        <v>3603.69</v>
+      </c>
+      <c r="JC5" s="1" t="n">
+        <v>9074.530000000001</v>
+      </c>
+      <c r="JD5" s="1" t="n">
+        <v>13383.87</v>
+      </c>
+      <c r="JE5" s="1" t="n">
+        <v>95026.53999999999</v>
+      </c>
+      <c r="JF5" s="1" t="n">
+        <v>1352.93</v>
+      </c>
+      <c r="JG5" s="1" t="n">
+        <v>17951.59</v>
+      </c>
+      <c r="JH5" s="1" t="n">
+        <v>5154.27</v>
+      </c>
+      <c r="JI5" s="1" t="n">
+        <v>71142.39</v>
+      </c>
+      <c r="JJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK5" s="1" t="n">
+        <v>137589.12</v>
+      </c>
+      <c r="JL5" s="1" t="n">
+        <v>5043.86</v>
+      </c>
+      <c r="JM5" s="1" t="n">
+        <v>3160.03</v>
+      </c>
+      <c r="JN5" s="1" t="n">
+        <v>9588.52</v>
+      </c>
+      <c r="JO5" s="1" t="n">
+        <v>4863.59</v>
+      </c>
+      <c r="JP5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JQ5" s="1" t="n">
+        <v>1317.39</v>
+      </c>
+      <c r="JR5" s="1" t="n">
+        <v>122699.53</v>
+      </c>
+      <c r="JS5" s="1" t="n">
+        <v>9265.889999999999</v>
+      </c>
+      <c r="JT5" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="JU5" s="1" t="n">
+        <v>2919.88</v>
+      </c>
+      <c r="JV5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JW5" s="1" t="n">
+        <v>3714.62</v>
+      </c>
+      <c r="JX5" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="JY5" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="JZ5" s="1" t="n">
+        <v>6135.33</v>
+      </c>
+      <c r="KA5" s="1" t="n">
+        <v>32589.77</v>
+      </c>
+      <c r="KB5" s="1" t="n">
+        <v>9183.469999999999</v>
+      </c>
+      <c r="KC5" s="1" t="n">
+        <v>799.15</v>
+      </c>
+      <c r="KD5" s="1" t="n">
+        <v>398.34</v>
+      </c>
+      <c r="KE5" s="1" t="n">
+        <v>219.45</v>
+      </c>
+      <c r="KF5" s="1" t="n">
+        <v>2292.55</v>
+      </c>
+      <c r="KG5" s="1" t="n">
+        <v>501.72</v>
+      </c>
+      <c r="KH5" s="1" t="n">
+        <v>6698.35</v>
+      </c>
+      <c r="KI5" s="1" t="n">
+        <v>14431.4</v>
+      </c>
+      <c r="KJ5" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="KK5" s="1" t="n">
+        <v>840.05</v>
+      </c>
+      <c r="KL5" s="1" t="n">
+        <v>1791.2</v>
+      </c>
+      <c r="KM5" s="1" t="n">
+        <v>1995</v>
+      </c>
+      <c r="KN5" s="1" t="n">
+        <v>10716.16</v>
+      </c>
+      <c r="KO5" s="1" t="n">
+        <v>10241.87</v>
+      </c>
+      <c r="KP5" s="1" t="n">
+        <v>56026.19</v>
+      </c>
+      <c r="KQ5" s="1" t="n">
+        <v>8289.67</v>
+      </c>
+      <c r="KR5" s="1" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="KS5" s="1" t="n">
+        <v>58968.68</v>
+      </c>
+      <c r="KT5" s="1" t="n">
+        <v>100747.16</v>
+      </c>
+      <c r="KU5" s="1" t="n">
+        <v>6290.09</v>
+      </c>
+      <c r="KV5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KW5" s="1" t="n">
+        <v>343450.79</v>
+      </c>
+      <c r="KX5" s="1" t="n">
+        <v>7512.72</v>
+      </c>
+      <c r="KY5" s="1" t="n">
+        <v>117.51</v>
+      </c>
+      <c r="KZ5" s="1" t="n">
+        <v>4388.89</v>
+      </c>
+      <c r="LA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LB5" s="1" t="n">
+        <v>51518.7</v>
+      </c>
+      <c r="LC5" s="1" t="n">
+        <v>584.72</v>
+      </c>
+      <c r="LD5" s="1" t="n">
+        <v>11540.87</v>
+      </c>
+      <c r="LE5" s="1" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="LF5" s="1" t="n">
+        <v>199.46</v>
+      </c>
+      <c r="LG5" s="1" t="n">
+        <v>52591.41</v>
+      </c>
+      <c r="LH5" s="1" t="n">
+        <v>850.1799999999999</v>
+      </c>
+      <c r="LI5" s="1" t="n">
+        <v>1510.37</v>
+      </c>
+      <c r="LJ5" s="1" t="n">
+        <v>1771.64</v>
+      </c>
+      <c r="LK5" s="1" t="n">
+        <v>1276.12</v>
+      </c>
+      <c r="LL5" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LM5" s="1" t="n">
+        <v>559.92</v>
+      </c>
+      <c r="LN5" s="1" t="n">
+        <v>451.31</v>
+      </c>
+      <c r="LO5" s="1" t="n">
+        <v>152337.21</v>
+      </c>
+      <c r="LP5" s="1" t="n">
+        <v>1133.73</v>
+      </c>
+      <c r="LQ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LR5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LS5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LT5" s="1" t="n">
+        <v>892531.83</v>
+      </c>
+      <c r="LU5" s="1" t="n">
+        <v>398.41</v>
+      </c>
+      <c r="LV5" s="1" t="n">
+        <v>61.93</v>
+      </c>
+      <c r="LW5" s="1" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="LX5" s="1" t="n">
+        <v>4322.55</v>
+      </c>
+      <c r="LY5" s="1" t="n">
+        <v>159.07</v>
+      </c>
+      <c r="LZ5" s="1" t="n">
+        <v>321787.2</v>
+      </c>
+      <c r="MA5" s="1" t="n">
+        <v>11001.9</v>
+      </c>
+      <c r="MB5" s="1" t="n">
+        <v>212.38</v>
+      </c>
+      <c r="MC5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MD5" s="1" t="n">
+        <v>994.42</v>
+      </c>
+      <c r="ME5" s="1" t="n">
+        <v>12190.15</v>
+      </c>
+      <c r="MF5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MG5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MH5" s="1" t="n">
+        <v>1298.79</v>
+      </c>
+      <c r="MI5" s="1" t="n">
+        <v>759.33</v>
+      </c>
+      <c r="MJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MK5" s="1" t="n">
+        <v>123419.77</v>
+      </c>
+      <c r="ML5" s="1" t="n">
+        <v>7193.37</v>
+      </c>
+      <c r="MM5" s="1" t="n">
+        <v>200.33</v>
+      </c>
+      <c r="MN5" s="1" t="n">
+        <v>3166.24</v>
+      </c>
+      <c r="MO5" s="1" t="n">
+        <v>648.2</v>
+      </c>
+      <c r="MP5" s="1" t="n">
+        <v>17049.92</v>
+      </c>
+      <c r="MQ5" s="1" t="n">
+        <v>674.1900000000001</v>
+      </c>
+      <c r="MR5" s="1" t="n">
+        <v>114.71</v>
+      </c>
+      <c r="MS5" s="1" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="MT5" s="1" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="MU5" s="1" t="n">
+        <v>1119.04</v>
+      </c>
+      <c r="MV5" s="1" t="n">
+        <v>126.78</v>
+      </c>
+      <c r="MW5" s="1" t="n">
+        <v>4730.57</v>
+      </c>
+      <c r="MX5" s="1" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="MY5" s="1" t="n">
+        <v>24714.99</v>
+      </c>
+      <c r="MZ5" s="1" t="n">
+        <v>36586</v>
+      </c>
+      <c r="NA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NB5" s="1" t="n">
+        <v>2230.58</v>
+      </c>
+      <c r="NC5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ND5" s="1" t="n">
+        <v>177020.67</v>
+      </c>
+      <c r="NE5" s="1" t="n">
+        <v>6450.34</v>
+      </c>
+      <c r="NF5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NG5" s="1" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="NH5" s="1" t="n">
+        <v>12908.56</v>
+      </c>
+      <c r="NI5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NK5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NL5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NM5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NN5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NO5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NP5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NQ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NR5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NS5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NT5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NU5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NV5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NW5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NX5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NY5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NZ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OB5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OC5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OD5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OE5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OF5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OG5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OH5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OI5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OK5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OL5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OM5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ON5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OO5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OP5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OQ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OR5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OS5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OT5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OU5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OV5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OW5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OX5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OY5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OZ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PB5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PC5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PD5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PE5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PF5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PG5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PH5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PI5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PK5" s="1" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="PL5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PM5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PN5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PO5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PP5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PQ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PR5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PS5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PT5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PU5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PV5" s="1" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="PW5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PX5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PY5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PZ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QB5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6891,7 +8222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW4"/>
+  <dimension ref="A1:BXW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7073,6 +8404,44 @@
       </c>
       <c r="M4" s="1" t="n">
         <v>21670.594923</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>261410758.19</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>48491748.89671</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>1139423.6635</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>2642830.7577</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>692382.0906</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>232432.2371</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>3432271.8459</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>1732.8444</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>27831.2915</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>2406.2268</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>18211.777897</v>
       </c>
     </row>
   </sheetData>
@@ -7086,7 +8455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW4"/>
+  <dimension ref="A1:BXW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8569,6 +9938,323 @@
         <v>0</v>
       </c>
       <c r="DB4" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>462719.9286716436</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>3979710.360752966</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>2702582.529013106</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>47314.2777</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>57145.386479251</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>2864.4658696224</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>103794.8951224</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>7980.21</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>76936.77997432501</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>887.10456</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>10480.6164</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>1002.6208328068</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>666.28112</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" s="1" t="n">
+        <v>468.74610396</v>
+      </c>
+      <c r="BN5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" s="1" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="BS5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8583,7 +10269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW4"/>
+  <dimension ref="A1:BXW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +10704,122 @@
       </c>
       <c r="AM4" s="1" t="n">
         <v>5000.76</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>5631460.13</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>355884.26</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>384768.28</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>261960.65</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>23155.07</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>194119.38</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>65797.67</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>970.04</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>11043.86</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>38854.79</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>7233.03</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>12021.47</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>5024.35</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1494.74</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>2999.99</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>15342.23</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>10455</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>15600</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>937.96</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>19239.81</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>1062.42</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>520.62</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="1" t="n">
+        <v>3933.2</v>
+      </c>
+      <c r="AH5" s="1" t="n">
+        <v>1505.84</v>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>76418.82000000001</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>5099.67</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>285979797.87</v>
+        <v>443871296.48</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>261410758.19</v>
+        <v>392741491.24</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>3979710.360752966</v>
+        <v>11660804.79300562</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>5631460.13</v>
+        <v>10617444.77</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>134381485.9</v>
+        <v>184543799.25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,15 +518,15 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>48491748.89671</v>
+        <v>65195196.59569</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>USDT_THB</t>
+          <t>ETH_THB</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2702582.529013106</v>
+        <v>4277752.634009851</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>384768.28</v>
+        <v>2052548.64</v>
       </c>
     </row>
     <row r="4">
@@ -547,23 +547,23 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>48448514.94</v>
+        <v>91071180.15000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VELOTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>3432271.8459</v>
+        <v>9415381.5888</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ETH_THB</t>
+          <t>USDT_THB</t>
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>462719.9286716436</v>
+        <v>2296484.907633151</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>355884.26</v>
+        <v>1335528.34</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>17015404.99</v>
+        <v>34604363.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -592,23 +592,23 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2642830.7577</v>
+        <v>6646997.9254</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DOGE_THB</t>
+          <t>XRP_THB</t>
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>103794.8951224</v>
+        <v>282808.312</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SOLTHB</t>
+          <t>USDTTHB</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>261960.65</v>
+        <v>665252.58</v>
       </c>
     </row>
     <row r="6">
@@ -617,35 +617,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_TRUMP</t>
+          <t>THB_SKR</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>13531302.87</v>
+        <v>27375240.74</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>VELOTHB</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1139423.6635</v>
+        <v>5884670.745</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BNB_THB</t>
+          <t>SOL_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>76936.77997432501</v>
+        <v>238610.4375296088</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>USDTTHB</t>
+          <t>NEARTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>194119.38</v>
+        <v>475244.58</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW5"/>
+  <dimension ref="A1:BXW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8208,6 +8208,1337 @@
         <v>0</v>
       </c>
       <c r="QB5" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>443871296.48</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>184543799.25</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>91071180.15000001</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>34604363.36</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>18122990.49</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>24476305.27</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>7786155.32</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>11014979.05</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>7501792.54</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>8608309.67</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>7384696.46</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>15556712.45</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>7113904.42</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>2068655.57</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>5247769.23</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>2279604.86</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>2626950.16</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>3006219.59</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>2646102.48</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>622074.02</v>
+      </c>
+      <c r="W6" s="1" t="n">
+        <v>3690120.87</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>4077416.43</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>944340.21</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>556178.21</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>3710831.37</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>4075501.31</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>2657823.77</v>
+      </c>
+      <c r="AD6" s="1" t="n">
+        <v>1617648.8</v>
+      </c>
+      <c r="AE6" s="1" t="n">
+        <v>1827276.61</v>
+      </c>
+      <c r="AF6" s="1" t="n">
+        <v>3324428.01</v>
+      </c>
+      <c r="AG6" s="1" t="n">
+        <v>757144.55</v>
+      </c>
+      <c r="AH6" s="1" t="n">
+        <v>775847.38</v>
+      </c>
+      <c r="AI6" s="1" t="n">
+        <v>5343204</v>
+      </c>
+      <c r="AJ6" s="1" t="n">
+        <v>663909.03</v>
+      </c>
+      <c r="AK6" s="1" t="n">
+        <v>336893.89</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>1201765.61</v>
+      </c>
+      <c r="AM6" s="1" t="n">
+        <v>1587235.59</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>52729.83</v>
+      </c>
+      <c r="AO6" s="1" t="n">
+        <v>558175.38</v>
+      </c>
+      <c r="AP6" s="1" t="n">
+        <v>592729.02</v>
+      </c>
+      <c r="AQ6" s="1" t="n">
+        <v>1126946.75</v>
+      </c>
+      <c r="AR6" s="1" t="n">
+        <v>4107245.6</v>
+      </c>
+      <c r="AS6" s="1" t="n">
+        <v>343556.5</v>
+      </c>
+      <c r="AT6" s="1" t="n">
+        <v>1716239.47</v>
+      </c>
+      <c r="AU6" s="1" t="n">
+        <v>1595636.23</v>
+      </c>
+      <c r="AV6" s="1" t="n">
+        <v>3022386.01</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>954453.71</v>
+      </c>
+      <c r="AX6" s="1" t="n">
+        <v>653409.29</v>
+      </c>
+      <c r="AY6" s="1" t="n">
+        <v>1175990.96</v>
+      </c>
+      <c r="AZ6" s="1" t="n">
+        <v>358407.03</v>
+      </c>
+      <c r="BA6" s="1" t="n">
+        <v>215774.9</v>
+      </c>
+      <c r="BB6" s="1" t="n">
+        <v>457167.04</v>
+      </c>
+      <c r="BC6" s="1" t="n">
+        <v>1483137.59</v>
+      </c>
+      <c r="BD6" s="1" t="n">
+        <v>344725.9</v>
+      </c>
+      <c r="BE6" s="1" t="n">
+        <v>348844.02</v>
+      </c>
+      <c r="BF6" s="1" t="n">
+        <v>692345.1899999999</v>
+      </c>
+      <c r="BG6" s="1" t="n">
+        <v>16938.66</v>
+      </c>
+      <c r="BH6" s="1" t="n">
+        <v>862014.58</v>
+      </c>
+      <c r="BI6" s="1" t="n">
+        <v>130663.76</v>
+      </c>
+      <c r="BJ6" s="1" t="n">
+        <v>1251961.77</v>
+      </c>
+      <c r="BK6" s="1" t="n">
+        <v>114315.05</v>
+      </c>
+      <c r="BL6" s="1" t="n">
+        <v>50474.37</v>
+      </c>
+      <c r="BM6" s="1" t="n">
+        <v>677373.5</v>
+      </c>
+      <c r="BN6" s="1" t="n">
+        <v>756069.66</v>
+      </c>
+      <c r="BO6" s="1" t="n">
+        <v>74374.19</v>
+      </c>
+      <c r="BP6" s="1" t="n">
+        <v>205549.64</v>
+      </c>
+      <c r="BQ6" s="1" t="n">
+        <v>310992.07</v>
+      </c>
+      <c r="BR6" s="1" t="n">
+        <v>606043.35</v>
+      </c>
+      <c r="BS6" s="1" t="n">
+        <v>502544.06</v>
+      </c>
+      <c r="BT6" s="1" t="n">
+        <v>380604.62</v>
+      </c>
+      <c r="BU6" s="1" t="n">
+        <v>1180970.46</v>
+      </c>
+      <c r="BV6" s="1" t="n">
+        <v>1271292.72</v>
+      </c>
+      <c r="BW6" s="1" t="n">
+        <v>6247.44</v>
+      </c>
+      <c r="BX6" s="1" t="n">
+        <v>349.12</v>
+      </c>
+      <c r="BY6" s="1" t="n">
+        <v>210322.72</v>
+      </c>
+      <c r="BZ6" s="1" t="n">
+        <v>78271.78999999999</v>
+      </c>
+      <c r="CA6" s="1" t="n">
+        <v>323810.95</v>
+      </c>
+      <c r="CB6" s="1" t="n">
+        <v>84900.73</v>
+      </c>
+      <c r="CC6" s="1" t="n">
+        <v>355163.47</v>
+      </c>
+      <c r="CD6" s="1" t="n">
+        <v>121996.84</v>
+      </c>
+      <c r="CE6" s="1" t="n">
+        <v>162278.54</v>
+      </c>
+      <c r="CF6" s="1" t="n">
+        <v>85911.27</v>
+      </c>
+      <c r="CG6" s="1" t="n">
+        <v>1211298.46</v>
+      </c>
+      <c r="CH6" s="1" t="n">
+        <v>40284.31</v>
+      </c>
+      <c r="CI6" s="1" t="n">
+        <v>19731.57</v>
+      </c>
+      <c r="CJ6" s="1" t="n">
+        <v>744425.28</v>
+      </c>
+      <c r="CK6" s="1" t="n">
+        <v>25526.42</v>
+      </c>
+      <c r="CL6" s="1" t="n">
+        <v>144292</v>
+      </c>
+      <c r="CM6" s="1" t="n">
+        <v>5754.75</v>
+      </c>
+      <c r="CN6" s="1" t="n">
+        <v>39680.5</v>
+      </c>
+      <c r="CO6" s="1" t="n">
+        <v>775331.5600000001</v>
+      </c>
+      <c r="CP6" s="1" t="n">
+        <v>46342.75</v>
+      </c>
+      <c r="CQ6" s="1" t="n">
+        <v>96161.96000000001</v>
+      </c>
+      <c r="CR6" s="1" t="n">
+        <v>482623.9</v>
+      </c>
+      <c r="CS6" s="1" t="n">
+        <v>17564.27</v>
+      </c>
+      <c r="CT6" s="1" t="n">
+        <v>192287.62</v>
+      </c>
+      <c r="CU6" s="1" t="n">
+        <v>246667.8</v>
+      </c>
+      <c r="CV6" s="1" t="n">
+        <v>524472.3199999999</v>
+      </c>
+      <c r="CW6" s="1" t="n">
+        <v>100803.07</v>
+      </c>
+      <c r="CX6" s="1" t="n">
+        <v>67077</v>
+      </c>
+      <c r="CY6" s="1" t="n">
+        <v>9151.540000000001</v>
+      </c>
+      <c r="CZ6" s="1" t="n">
+        <v>441190.81</v>
+      </c>
+      <c r="DA6" s="1" t="n">
+        <v>2593.39</v>
+      </c>
+      <c r="DB6" s="1" t="n">
+        <v>277375.65</v>
+      </c>
+      <c r="DC6" s="1" t="n">
+        <v>38120.2</v>
+      </c>
+      <c r="DD6" s="1" t="n">
+        <v>33108.26</v>
+      </c>
+      <c r="DE6" s="1" t="n">
+        <v>33165.12</v>
+      </c>
+      <c r="DF6" s="1" t="n">
+        <v>196756.47</v>
+      </c>
+      <c r="DG6" s="1" t="n">
+        <v>13036309.58</v>
+      </c>
+      <c r="DH6" s="1" t="n">
+        <v>144837.97</v>
+      </c>
+      <c r="DI6" s="1" t="n">
+        <v>97293.39999999999</v>
+      </c>
+      <c r="DJ6" s="1" t="n">
+        <v>101298.59</v>
+      </c>
+      <c r="DK6" s="1" t="n">
+        <v>252679.55</v>
+      </c>
+      <c r="DL6" s="1" t="n">
+        <v>42647.23</v>
+      </c>
+      <c r="DM6" s="1" t="n">
+        <v>165795.28</v>
+      </c>
+      <c r="DN6" s="1" t="n">
+        <v>57430.97</v>
+      </c>
+      <c r="DO6" s="1" t="n">
+        <v>218870.19</v>
+      </c>
+      <c r="DP6" s="1" t="n">
+        <v>405.61</v>
+      </c>
+      <c r="DQ6" s="1" t="n">
+        <v>61141.49</v>
+      </c>
+      <c r="DR6" s="1" t="n">
+        <v>57453.76</v>
+      </c>
+      <c r="DS6" s="1" t="n">
+        <v>200251.48</v>
+      </c>
+      <c r="DT6" s="1" t="n">
+        <v>826359.42</v>
+      </c>
+      <c r="DU6" s="1" t="n">
+        <v>135243.2</v>
+      </c>
+      <c r="DV6" s="1" t="n">
+        <v>180604.52</v>
+      </c>
+      <c r="DW6" s="1" t="n">
+        <v>28351.63</v>
+      </c>
+      <c r="DX6" s="1" t="n">
+        <v>188209.07</v>
+      </c>
+      <c r="DY6" s="1" t="n">
+        <v>42921.24</v>
+      </c>
+      <c r="DZ6" s="1" t="n">
+        <v>215202.72</v>
+      </c>
+      <c r="EA6" s="1" t="n">
+        <v>65798.53999999999</v>
+      </c>
+      <c r="EB6" s="1" t="n">
+        <v>3556.39</v>
+      </c>
+      <c r="EC6" s="1" t="n">
+        <v>21670.2</v>
+      </c>
+      <c r="ED6" s="1" t="n">
+        <v>27332.37</v>
+      </c>
+      <c r="EE6" s="1" t="n">
+        <v>125990.72</v>
+      </c>
+      <c r="EF6" s="1" t="n">
+        <v>721.7</v>
+      </c>
+      <c r="EG6" s="1" t="n">
+        <v>40743.9</v>
+      </c>
+      <c r="EH6" s="1" t="n">
+        <v>861.13</v>
+      </c>
+      <c r="EI6" s="1" t="n">
+        <v>38619.33</v>
+      </c>
+      <c r="EJ6" s="1" t="n">
+        <v>7181.06</v>
+      </c>
+      <c r="EK6" s="1" t="n">
+        <v>58093.63</v>
+      </c>
+      <c r="EL6" s="1" t="n">
+        <v>1546.37</v>
+      </c>
+      <c r="EM6" s="1" t="n">
+        <v>798</v>
+      </c>
+      <c r="EN6" s="1" t="n">
+        <v>56207.89</v>
+      </c>
+      <c r="EO6" s="1" t="n">
+        <v>5801569.46</v>
+      </c>
+      <c r="EP6" s="1" t="n">
+        <v>546475.28</v>
+      </c>
+      <c r="EQ6" s="1" t="n">
+        <v>277.27</v>
+      </c>
+      <c r="ER6" s="1" t="n">
+        <v>25307.81</v>
+      </c>
+      <c r="ES6" s="1" t="n">
+        <v>142005.83</v>
+      </c>
+      <c r="ET6" s="1" t="n">
+        <v>23747.65</v>
+      </c>
+      <c r="EU6" s="1" t="n">
+        <v>71949.38</v>
+      </c>
+      <c r="EV6" s="1" t="n">
+        <v>68486.8</v>
+      </c>
+      <c r="EW6" s="1" t="n">
+        <v>56857.96</v>
+      </c>
+      <c r="EX6" s="1" t="n">
+        <v>134579.17</v>
+      </c>
+      <c r="EY6" s="1" t="n">
+        <v>9301.6</v>
+      </c>
+      <c r="EZ6" s="1" t="n">
+        <v>202304.17</v>
+      </c>
+      <c r="FA6" s="1" t="n">
+        <v>66407.73</v>
+      </c>
+      <c r="FB6" s="1" t="n">
+        <v>203313.49</v>
+      </c>
+      <c r="FC6" s="1" t="n">
+        <v>192204.45</v>
+      </c>
+      <c r="FD6" s="1" t="n">
+        <v>8737.440000000001</v>
+      </c>
+      <c r="FE6" s="1" t="n">
+        <v>618116.08</v>
+      </c>
+      <c r="FF6" s="1" t="n">
+        <v>7362.59</v>
+      </c>
+      <c r="FG6" s="1" t="n">
+        <v>83540.27</v>
+      </c>
+      <c r="FH6" s="1" t="n">
+        <v>58642.07</v>
+      </c>
+      <c r="FI6" s="1" t="n">
+        <v>147393.54</v>
+      </c>
+      <c r="FJ6" s="1" t="n">
+        <v>61598.86</v>
+      </c>
+      <c r="FK6" s="1" t="n">
+        <v>83113.97</v>
+      </c>
+      <c r="FL6" s="1" t="n">
+        <v>78557.3</v>
+      </c>
+      <c r="FM6" s="1" t="n">
+        <v>14773.78</v>
+      </c>
+      <c r="FN6" s="1" t="n">
+        <v>103787.17</v>
+      </c>
+      <c r="FO6" s="1" t="n">
+        <v>10264.94</v>
+      </c>
+      <c r="FP6" s="1" t="n">
+        <v>28293.59</v>
+      </c>
+      <c r="FQ6" s="1" t="n">
+        <v>105464.8</v>
+      </c>
+      <c r="FR6" s="1" t="n">
+        <v>33032.66</v>
+      </c>
+      <c r="FS6" s="1" t="n">
+        <v>27375240.74</v>
+      </c>
+      <c r="FT6" s="1" t="n">
+        <v>76944.27</v>
+      </c>
+      <c r="FU6" s="1" t="n">
+        <v>55889.59</v>
+      </c>
+      <c r="FV6" s="1" t="n">
+        <v>143501.04</v>
+      </c>
+      <c r="FW6" s="1" t="n">
+        <v>286.99</v>
+      </c>
+      <c r="FX6" s="1" t="n">
+        <v>2935.11</v>
+      </c>
+      <c r="FY6" s="1" t="n">
+        <v>67717.23</v>
+      </c>
+      <c r="FZ6" s="1" t="n">
+        <v>490.66</v>
+      </c>
+      <c r="GA6" s="1" t="n">
+        <v>130047.13</v>
+      </c>
+      <c r="GB6" s="1" t="n">
+        <v>3333.85</v>
+      </c>
+      <c r="GC6" s="1" t="n">
+        <v>111432.4</v>
+      </c>
+      <c r="GD6" s="1" t="n">
+        <v>8706.139999999999</v>
+      </c>
+      <c r="GE6" s="1" t="n">
+        <v>256973.09</v>
+      </c>
+      <c r="GF6" s="1" t="n">
+        <v>44159.84</v>
+      </c>
+      <c r="GG6" s="1" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="GH6" s="1" t="n">
+        <v>251010.47</v>
+      </c>
+      <c r="GI6" s="1" t="n">
+        <v>49373.22</v>
+      </c>
+      <c r="GJ6" s="1" t="n">
+        <v>1644.76</v>
+      </c>
+      <c r="GK6" s="1" t="n">
+        <v>116856.65</v>
+      </c>
+      <c r="GL6" s="1" t="n">
+        <v>1661.05</v>
+      </c>
+      <c r="GM6" s="1" t="n">
+        <v>307526.03</v>
+      </c>
+      <c r="GN6" s="1" t="n">
+        <v>16714.05</v>
+      </c>
+      <c r="GO6" s="1" t="n">
+        <v>86691.37</v>
+      </c>
+      <c r="GP6" s="1" t="n">
+        <v>1116.56</v>
+      </c>
+      <c r="GQ6" s="1" t="n">
+        <v>23614.17</v>
+      </c>
+      <c r="GR6" s="1" t="n">
+        <v>224.59</v>
+      </c>
+      <c r="GS6" s="1" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="GT6" s="1" t="n">
+        <v>268353.69</v>
+      </c>
+      <c r="GU6" s="1" t="n">
+        <v>93944.58</v>
+      </c>
+      <c r="GV6" s="1" t="n">
+        <v>74947.41</v>
+      </c>
+      <c r="GW6" s="1" t="n">
+        <v>36869.97</v>
+      </c>
+      <c r="GX6" s="1" t="n">
+        <v>2027.01</v>
+      </c>
+      <c r="GY6" s="1" t="n">
+        <v>68848.77</v>
+      </c>
+      <c r="GZ6" s="1" t="n">
+        <v>221858.53</v>
+      </c>
+      <c r="HA6" s="1" t="n">
+        <v>249.32</v>
+      </c>
+      <c r="HB6" s="1" t="n">
+        <v>5963.14</v>
+      </c>
+      <c r="HC6" s="1" t="n">
+        <v>71924.86</v>
+      </c>
+      <c r="HD6" s="1" t="n">
+        <v>661.08</v>
+      </c>
+      <c r="HE6" s="1" t="n">
+        <v>149309.15</v>
+      </c>
+      <c r="HF6" s="1" t="n">
+        <v>9244.860000000001</v>
+      </c>
+      <c r="HG6" s="1" t="n">
+        <v>75633.87</v>
+      </c>
+      <c r="HH6" s="1" t="n">
+        <v>54838.11</v>
+      </c>
+      <c r="HI6" s="1" t="n">
+        <v>41445.57</v>
+      </c>
+      <c r="HJ6" s="1" t="n">
+        <v>11570.62</v>
+      </c>
+      <c r="HK6" s="1" t="n">
+        <v>29023.09</v>
+      </c>
+      <c r="HL6" s="1" t="n">
+        <v>150113.69</v>
+      </c>
+      <c r="HM6" s="1" t="n">
+        <v>103824.72</v>
+      </c>
+      <c r="HN6" s="1" t="n">
+        <v>267512.73</v>
+      </c>
+      <c r="HO6" s="1" t="n">
+        <v>15311.66</v>
+      </c>
+      <c r="HP6" s="1" t="n">
+        <v>17886.08</v>
+      </c>
+      <c r="HQ6" s="1" t="n">
+        <v>11645.19</v>
+      </c>
+      <c r="HR6" s="1" t="n">
+        <v>25356.83</v>
+      </c>
+      <c r="HS6" s="1" t="n">
+        <v>122531.26</v>
+      </c>
+      <c r="HT6" s="1" t="n">
+        <v>60991.43</v>
+      </c>
+      <c r="HU6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV6" s="1" t="n">
+        <v>6964.01</v>
+      </c>
+      <c r="HW6" s="1" t="n">
+        <v>97541.21000000001</v>
+      </c>
+      <c r="HX6" s="1" t="n">
+        <v>35951.32</v>
+      </c>
+      <c r="HY6" s="1" t="n">
+        <v>115242.03</v>
+      </c>
+      <c r="HZ6" s="1" t="n">
+        <v>104879.51</v>
+      </c>
+      <c r="IA6" s="1" t="n">
+        <v>10436.33</v>
+      </c>
+      <c r="IB6" s="1" t="n">
+        <v>264040.93</v>
+      </c>
+      <c r="IC6" s="1" t="n">
+        <v>8130.26</v>
+      </c>
+      <c r="ID6" s="1" t="n">
+        <v>6244.41</v>
+      </c>
+      <c r="IE6" s="1" t="n">
+        <v>115887.6</v>
+      </c>
+      <c r="IF6" s="1" t="n">
+        <v>881.13</v>
+      </c>
+      <c r="IG6" s="1" t="n">
+        <v>5081392.37</v>
+      </c>
+      <c r="IH6" s="1" t="n">
+        <v>197692.07</v>
+      </c>
+      <c r="II6" s="1" t="n">
+        <v>245868.41</v>
+      </c>
+      <c r="IJ6" s="1" t="n">
+        <v>63410.96</v>
+      </c>
+      <c r="IK6" s="1" t="n">
+        <v>35579.45</v>
+      </c>
+      <c r="IL6" s="1" t="n">
+        <v>91.93000000000001</v>
+      </c>
+      <c r="IM6" s="1" t="n">
+        <v>449.38</v>
+      </c>
+      <c r="IN6" s="1" t="n">
+        <v>251.39</v>
+      </c>
+      <c r="IO6" s="1" t="n">
+        <v>24486.39</v>
+      </c>
+      <c r="IP6" s="1" t="n">
+        <v>9666.57</v>
+      </c>
+      <c r="IQ6" s="1" t="n">
+        <v>10901.65</v>
+      </c>
+      <c r="IR6" s="1" t="n">
+        <v>4398.73</v>
+      </c>
+      <c r="IS6" s="1" t="n">
+        <v>222.57</v>
+      </c>
+      <c r="IT6" s="1" t="n">
+        <v>45142.29</v>
+      </c>
+      <c r="IU6" s="1" t="n">
+        <v>28354.67</v>
+      </c>
+      <c r="IV6" s="1" t="n">
+        <v>5834.59</v>
+      </c>
+      <c r="IW6" s="1" t="n">
+        <v>381628.92</v>
+      </c>
+      <c r="IX6" s="1" t="n">
+        <v>39749.88</v>
+      </c>
+      <c r="IY6" s="1" t="n">
+        <v>8787.16</v>
+      </c>
+      <c r="IZ6" s="1" t="n">
+        <v>153945.55</v>
+      </c>
+      <c r="JA6" s="1" t="n">
+        <v>62355</v>
+      </c>
+      <c r="JB6" s="1" t="n">
+        <v>26810.47</v>
+      </c>
+      <c r="JC6" s="1" t="n">
+        <v>50301.88</v>
+      </c>
+      <c r="JD6" s="1" t="n">
+        <v>55223.71</v>
+      </c>
+      <c r="JE6" s="1" t="n">
+        <v>95026.53999999999</v>
+      </c>
+      <c r="JF6" s="1" t="n">
+        <v>6216.27</v>
+      </c>
+      <c r="JG6" s="1" t="n">
+        <v>41517.33</v>
+      </c>
+      <c r="JH6" s="1" t="n">
+        <v>5154.27</v>
+      </c>
+      <c r="JI6" s="1" t="n">
+        <v>55978.89</v>
+      </c>
+      <c r="JJ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK6" s="1" t="n">
+        <v>37740.91</v>
+      </c>
+      <c r="JL6" s="1" t="n">
+        <v>5043.86</v>
+      </c>
+      <c r="JM6" s="1" t="n">
+        <v>1152.67</v>
+      </c>
+      <c r="JN6" s="1" t="n">
+        <v>42911.75</v>
+      </c>
+      <c r="JO6" s="1" t="n">
+        <v>195022.64</v>
+      </c>
+      <c r="JP6" s="1" t="n">
+        <v>5206.46</v>
+      </c>
+      <c r="JQ6" s="1" t="n">
+        <v>598.67</v>
+      </c>
+      <c r="JR6" s="1" t="n">
+        <v>998.77</v>
+      </c>
+      <c r="JS6" s="1" t="n">
+        <v>3674480.83</v>
+      </c>
+      <c r="JT6" s="1" t="n">
+        <v>3045.06</v>
+      </c>
+      <c r="JU6" s="1" t="n">
+        <v>94739.17999999999</v>
+      </c>
+      <c r="JV6" s="1" t="n">
+        <v>219.81</v>
+      </c>
+      <c r="JW6" s="1" t="n">
+        <v>3714.62</v>
+      </c>
+      <c r="JX6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JY6" s="1" t="n">
+        <v>19532.7</v>
+      </c>
+      <c r="JZ6" s="1" t="n">
+        <v>1673701.77</v>
+      </c>
+      <c r="KA6" s="1" t="n">
+        <v>100962.89</v>
+      </c>
+      <c r="KB6" s="1" t="n">
+        <v>59238.96</v>
+      </c>
+      <c r="KC6" s="1" t="n">
+        <v>64739.41</v>
+      </c>
+      <c r="KD6" s="1" t="n">
+        <v>2783.1</v>
+      </c>
+      <c r="KE6" s="1" t="n">
+        <v>465.5</v>
+      </c>
+      <c r="KF6" s="1" t="n">
+        <v>28482.81</v>
+      </c>
+      <c r="KG6" s="1" t="n">
+        <v>12664.39</v>
+      </c>
+      <c r="KH6" s="1" t="n">
+        <v>4585.19</v>
+      </c>
+      <c r="KI6" s="1" t="n">
+        <v>585.9400000000001</v>
+      </c>
+      <c r="KJ6" s="1" t="n">
+        <v>458160.31</v>
+      </c>
+      <c r="KK6" s="1" t="n">
+        <v>198.89</v>
+      </c>
+      <c r="KL6" s="1" t="n">
+        <v>1791.2</v>
+      </c>
+      <c r="KM6" s="1" t="n">
+        <v>114155.85</v>
+      </c>
+      <c r="KN6" s="1" t="n">
+        <v>126334.56</v>
+      </c>
+      <c r="KO6" s="1" t="n">
+        <v>45063.84</v>
+      </c>
+      <c r="KP6" s="1" t="n">
+        <v>16306.75</v>
+      </c>
+      <c r="KQ6" s="1" t="n">
+        <v>398.97</v>
+      </c>
+      <c r="KR6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS6" s="1" t="n">
+        <v>392851.94</v>
+      </c>
+      <c r="KT6" s="1" t="n">
+        <v>100747.16</v>
+      </c>
+      <c r="KU6" s="1" t="n">
+        <v>32291.36</v>
+      </c>
+      <c r="KV6" s="1" t="n">
+        <v>12678.64</v>
+      </c>
+      <c r="KW6" s="1" t="n">
+        <v>68566.66</v>
+      </c>
+      <c r="KX6" s="1" t="n">
+        <v>312.58</v>
+      </c>
+      <c r="KY6" s="1" t="n">
+        <v>17447.61</v>
+      </c>
+      <c r="KZ6" s="1" t="n">
+        <v>3047.71</v>
+      </c>
+      <c r="LA6" s="1" t="n">
+        <v>20709.79</v>
+      </c>
+      <c r="LB6" s="1" t="n">
+        <v>533888.51</v>
+      </c>
+      <c r="LC6" s="1" t="n">
+        <v>684.59</v>
+      </c>
+      <c r="LD6" s="1" t="n">
+        <v>404132.64</v>
+      </c>
+      <c r="LE6" s="1" t="n">
+        <v>66.01000000000001</v>
+      </c>
+      <c r="LF6" s="1" t="n">
+        <v>797.96</v>
+      </c>
+      <c r="LG6" s="1" t="n">
+        <v>200724.63</v>
+      </c>
+      <c r="LH6" s="1" t="n">
+        <v>850.1799999999999</v>
+      </c>
+      <c r="LI6" s="1" t="n">
+        <v>1276.93</v>
+      </c>
+      <c r="LJ6" s="1" t="n">
+        <v>1925.57</v>
+      </c>
+      <c r="LK6" s="1" t="n">
+        <v>2093.11</v>
+      </c>
+      <c r="LL6" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LM6" s="1" t="n">
+        <v>559.92</v>
+      </c>
+      <c r="LN6" s="1" t="n">
+        <v>451.31</v>
+      </c>
+      <c r="LO6" s="1" t="n">
+        <v>152337.21</v>
+      </c>
+      <c r="LP6" s="1" t="n">
+        <v>16553.49</v>
+      </c>
+      <c r="LQ6" s="1" t="n">
+        <v>442.6</v>
+      </c>
+      <c r="LR6" s="1" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="LS6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LT6" s="1" t="n">
+        <v>584470.72</v>
+      </c>
+      <c r="LU6" s="1" t="n">
+        <v>4114.96</v>
+      </c>
+      <c r="LV6" s="1" t="n">
+        <v>616.76</v>
+      </c>
+      <c r="LW6" s="1" t="n">
+        <v>12251.98</v>
+      </c>
+      <c r="LX6" s="1" t="n">
+        <v>898.08</v>
+      </c>
+      <c r="LY6" s="1" t="n">
+        <v>216338.94</v>
+      </c>
+      <c r="LZ6" s="1" t="n">
+        <v>358421.42</v>
+      </c>
+      <c r="MA6" s="1" t="n">
+        <v>15354.59</v>
+      </c>
+      <c r="MB6" s="1" t="n">
+        <v>15151.14</v>
+      </c>
+      <c r="MC6" s="1" t="n">
+        <v>306.19</v>
+      </c>
+      <c r="MD6" s="1" t="n">
+        <v>10047.63</v>
+      </c>
+      <c r="ME6" s="1" t="n">
+        <v>313.55</v>
+      </c>
+      <c r="MF6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MG6" s="1" t="n">
+        <v>1251.31</v>
+      </c>
+      <c r="MH6" s="1" t="n">
+        <v>31603.39</v>
+      </c>
+      <c r="MI6" s="1" t="n">
+        <v>16807.9</v>
+      </c>
+      <c r="MJ6" s="1" t="n">
+        <v>385.7</v>
+      </c>
+      <c r="MK6" s="1" t="n">
+        <v>10663.54</v>
+      </c>
+      <c r="ML6" s="1" t="n">
+        <v>1506.28</v>
+      </c>
+      <c r="MM6" s="1" t="n">
+        <v>18977.78</v>
+      </c>
+      <c r="MN6" s="1" t="n">
+        <v>453378.08</v>
+      </c>
+      <c r="MO6" s="1" t="n">
+        <v>200.98</v>
+      </c>
+      <c r="MP6" s="1" t="n">
+        <v>17049.92</v>
+      </c>
+      <c r="MQ6" s="1" t="n">
+        <v>674.1900000000001</v>
+      </c>
+      <c r="MR6" s="1" t="n">
+        <v>3192.26</v>
+      </c>
+      <c r="MS6" s="1" t="n">
+        <v>224745.58</v>
+      </c>
+      <c r="MT6" s="1" t="n">
+        <v>91607</v>
+      </c>
+      <c r="MU6" s="1" t="n">
+        <v>15172.33</v>
+      </c>
+      <c r="MV6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MW6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MX6" s="1" t="n">
+        <v>1180.25</v>
+      </c>
+      <c r="MY6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MZ6" s="1" t="n">
+        <v>69194.77</v>
+      </c>
+      <c r="NA6" s="1" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="NB6" s="1" t="n">
+        <v>2081.15</v>
+      </c>
+      <c r="NC6" s="1" t="n">
+        <v>174.55</v>
+      </c>
+      <c r="ND6" s="1" t="n">
+        <v>432577.21</v>
+      </c>
+      <c r="NE6" s="1" t="n">
+        <v>5300.8</v>
+      </c>
+      <c r="NF6" s="1" t="n">
+        <v>864.28</v>
+      </c>
+      <c r="NG6" s="1" t="n">
+        <v>212344.54</v>
+      </c>
+      <c r="NH6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NI6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NJ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NK6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NL6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NM6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NN6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NO6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NP6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NQ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NR6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NS6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NT6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NU6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NV6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NW6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NX6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NY6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NZ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OA6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OB6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OC6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OD6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OE6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OF6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OG6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OH6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OI6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OJ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OK6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OL6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OM6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ON6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OO6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OP6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OQ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OR6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OS6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OT6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OU6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OV6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OW6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OX6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OY6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OZ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PA6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PB6" s="1" t="n">
+        <v>3432.96</v>
+      </c>
+      <c r="PC6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PD6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PE6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PF6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PG6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PH6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PI6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PJ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PK6" s="1" t="n">
+        <v>2007.75</v>
+      </c>
+      <c r="PL6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PM6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PN6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PO6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PP6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PQ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PR6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PS6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PT6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PU6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PV6" s="1" t="n">
+        <v>321.74</v>
+      </c>
+      <c r="PW6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PX6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PY6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PZ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QA6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QB6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8222,7 +9553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW5"/>
+  <dimension ref="A1:BXW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8442,6 +9773,44 @@
       </c>
       <c r="M5" s="1" t="n">
         <v>18211.777897</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>392741491.24</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>65195196.59569</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>9415381.5888</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>6646997.9254</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>4684499.3946</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>2810106.3008</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>5884670.745</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>207981.7887</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>3803.5443</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>2406.2268</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>8353.971426</v>
       </c>
     </row>
   </sheetData>
@@ -8455,7 +9824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW5"/>
+  <dimension ref="A1:BXW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10255,6 +11624,323 @@
         <v>0</v>
       </c>
       <c r="DB5" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>4277752.634009851</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>11660804.79300562</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>2296484.907633151</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>7098.3877</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>282808.312</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>238610.4375296088</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>119762.1541260108</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>10172.02</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>2687.4562366903</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>2000.5142730324</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>317.22117</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>13.9212</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>3823.98087305</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>5755.5172369968</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="1" t="n">
+        <v>137.4294</v>
+      </c>
+      <c r="BD6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CE6" s="1" t="n">
+        <v>38.0282731822</v>
+      </c>
+      <c r="CF6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10269,7 +11955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW5"/>
+  <dimension ref="A1:BXW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10819,6 +12505,122 @@
         <v>5099.67</v>
       </c>
       <c r="AM5" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>10617444.77</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>1335528.34</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>2052548.64</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>150294.18</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>9045.83</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>665252.58</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>248491.57</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>17618.95</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>33947.55</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>137438.71</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>1261.25</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>6298.83</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>54222.44</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>1004.17</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>53180.05</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>6500.82</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1" t="n">
+        <v>475244.58</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>29854.75</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>4478.24</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>500.5</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>4628.52</v>
+      </c>
+      <c r="AD6" s="1" t="n">
+        <v>2514.87</v>
+      </c>
+      <c r="AE6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="1" t="n">
+        <v>5360.07</v>
+      </c>
+      <c r="AH6" s="1" t="n">
+        <v>509.91</v>
+      </c>
+      <c r="AI6" s="1" t="n">
+        <v>183.73</v>
+      </c>
+      <c r="AJ6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="1" t="n">
+        <v>83540.81</v>
+      </c>
+      <c r="AL6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>443871296.48</v>
+        <v>636253556.98</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,15 +481,15 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>392741491.24</v>
+        <v>581708257.35</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>BTC_THB</t>
+          <t>ETH_THB</t>
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>11660804.79300562</v>
+        <v>9912121.759959191</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>10617444.77</v>
+        <v>7397723.44</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>184543799.25</v>
+        <v>147936014.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,23 +518,23 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>65195196.59569</v>
+        <v>48804439.41577</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ETH_THB</t>
+          <t>USDT_THB</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>4277752.634009851</v>
+        <v>4290140.761853345</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>USDTTHB</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>2052548.64</v>
+        <v>1810833.35</v>
       </c>
     </row>
     <row r="4">
@@ -547,31 +547,31 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>91071180.15000001</v>
+        <v>52653716.13</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>VELOTHB</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>9415381.5888</v>
+        <v>3749855.9863</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>USDT_THB</t>
+          <t>BTC_THB</t>
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>2296484.907633151</v>
+        <v>3141085.601054557</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>SOLTHB</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1335528.34</v>
+        <v>807689.66</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>34604363.36</v>
+        <v>24232499.76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>XRPTHB</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>3565104.2812</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>XRP_THB</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>163279.8326533492</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>ETHTHB</t>
         </is>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>6646997.9254</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>XRP_THB</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>282808.312</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>USDTTHB</t>
-        </is>
-      </c>
       <c r="L5" s="1" t="n">
-        <v>665252.58</v>
+        <v>698241.9</v>
       </c>
     </row>
     <row r="6">
@@ -621,15 +621,15 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>27375240.74</v>
+        <v>19190322.06</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VELOTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>5884670.745</v>
+        <v>3495473.5744</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -637,15 +637,15 @@
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>238610.4375296088</v>
+        <v>95784.8865180244</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>NEARTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>475244.58</v>
+        <v>691593.8100000001</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW6"/>
+  <dimension ref="A1:BXW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9539,6 +9539,1337 @@
         <v>0</v>
       </c>
       <c r="QB6" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>636253556.98</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>147936014.55</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>52653716.13</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>24232499.76</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>14107151.24</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>11866488.96</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>5121988.67</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>6175715.81</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>2792003.73</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>13014596.48</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>3862489.98</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>14302643.38</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>5671416.63</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>506041.76</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>5970447.26</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>2450429.43</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>2073733.75</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>2446759.18</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>14337916.24</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>798279.99</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>3675386.45</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>4077416.43</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>378834.55</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>176237.21</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>1203486.16</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>7533657.32</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>1029094.09</v>
+      </c>
+      <c r="AD7" s="1" t="n">
+        <v>4087455.39</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>477763.57</v>
+      </c>
+      <c r="AF7" s="1" t="n">
+        <v>2332465.25</v>
+      </c>
+      <c r="AG7" s="1" t="n">
+        <v>658885.64</v>
+      </c>
+      <c r="AH7" s="1" t="n">
+        <v>176983.07</v>
+      </c>
+      <c r="AI7" s="1" t="n">
+        <v>1381977.78</v>
+      </c>
+      <c r="AJ7" s="1" t="n">
+        <v>207280.45</v>
+      </c>
+      <c r="AK7" s="1" t="n">
+        <v>355744.75</v>
+      </c>
+      <c r="AL7" s="1" t="n">
+        <v>834724.54</v>
+      </c>
+      <c r="AM7" s="1" t="n">
+        <v>1587235.59</v>
+      </c>
+      <c r="AN7" s="1" t="n">
+        <v>113004.79</v>
+      </c>
+      <c r="AO7" s="1" t="n">
+        <v>679901.6800000001</v>
+      </c>
+      <c r="AP7" s="1" t="n">
+        <v>1347650.94</v>
+      </c>
+      <c r="AQ7" s="1" t="n">
+        <v>7083013.6</v>
+      </c>
+      <c r="AR7" s="1" t="n">
+        <v>1253278.2</v>
+      </c>
+      <c r="AS7" s="1" t="n">
+        <v>46578.57</v>
+      </c>
+      <c r="AT7" s="1" t="n">
+        <v>916887.85</v>
+      </c>
+      <c r="AU7" s="1" t="n">
+        <v>1450989.97</v>
+      </c>
+      <c r="AV7" s="1" t="n">
+        <v>882474.02</v>
+      </c>
+      <c r="AW7" s="1" t="n">
+        <v>655862.8100000001</v>
+      </c>
+      <c r="AX7" s="1" t="n">
+        <v>640657.33</v>
+      </c>
+      <c r="AY7" s="1" t="n">
+        <v>429665.55</v>
+      </c>
+      <c r="AZ7" s="1" t="n">
+        <v>300177.73</v>
+      </c>
+      <c r="BA7" s="1" t="n">
+        <v>189791.82</v>
+      </c>
+      <c r="BB7" s="1" t="n">
+        <v>726329.74</v>
+      </c>
+      <c r="BC7" s="1" t="n">
+        <v>1557200.78</v>
+      </c>
+      <c r="BD7" s="1" t="n">
+        <v>247092.45</v>
+      </c>
+      <c r="BE7" s="1" t="n">
+        <v>461460.49</v>
+      </c>
+      <c r="BF7" s="1" t="n">
+        <v>303439.15</v>
+      </c>
+      <c r="BG7" s="1" t="n">
+        <v>15071.62</v>
+      </c>
+      <c r="BH7" s="1" t="n">
+        <v>862014.58</v>
+      </c>
+      <c r="BI7" s="1" t="n">
+        <v>69015.86</v>
+      </c>
+      <c r="BJ7" s="1" t="n">
+        <v>336859.65</v>
+      </c>
+      <c r="BK7" s="1" t="n">
+        <v>463630.36</v>
+      </c>
+      <c r="BL7" s="1" t="n">
+        <v>50469.53</v>
+      </c>
+      <c r="BM7" s="1" t="n">
+        <v>98900.84</v>
+      </c>
+      <c r="BN7" s="1" t="n">
+        <v>661477.96</v>
+      </c>
+      <c r="BO7" s="1" t="n">
+        <v>33765.98</v>
+      </c>
+      <c r="BP7" s="1" t="n">
+        <v>194037.96</v>
+      </c>
+      <c r="BQ7" s="1" t="n">
+        <v>51025.63</v>
+      </c>
+      <c r="BR7" s="1" t="n">
+        <v>606043.35</v>
+      </c>
+      <c r="BS7" s="1" t="n">
+        <v>627110.67</v>
+      </c>
+      <c r="BT7" s="1" t="n">
+        <v>64862.62</v>
+      </c>
+      <c r="BU7" s="1" t="n">
+        <v>1164663.71</v>
+      </c>
+      <c r="BV7" s="1" t="n">
+        <v>537096.71</v>
+      </c>
+      <c r="BW7" s="1" t="n">
+        <v>77297.03999999999</v>
+      </c>
+      <c r="BX7" s="1" t="n">
+        <v>755.2</v>
+      </c>
+      <c r="BY7" s="1" t="n">
+        <v>481100.95</v>
+      </c>
+      <c r="BZ7" s="1" t="n">
+        <v>155718.44</v>
+      </c>
+      <c r="CA7" s="1" t="n">
+        <v>143156.64</v>
+      </c>
+      <c r="CB7" s="1" t="n">
+        <v>57222.5</v>
+      </c>
+      <c r="CC7" s="1" t="n">
+        <v>220624.15</v>
+      </c>
+      <c r="CD7" s="1" t="n">
+        <v>220265.02</v>
+      </c>
+      <c r="CE7" s="1" t="n">
+        <v>68650.81</v>
+      </c>
+      <c r="CF7" s="1" t="n">
+        <v>63793.85</v>
+      </c>
+      <c r="CG7" s="1" t="n">
+        <v>218835.71</v>
+      </c>
+      <c r="CH7" s="1" t="n">
+        <v>54075.17</v>
+      </c>
+      <c r="CI7" s="1" t="n">
+        <v>24572.1</v>
+      </c>
+      <c r="CJ7" s="1" t="n">
+        <v>1058603.74</v>
+      </c>
+      <c r="CK7" s="1" t="n">
+        <v>28850.62</v>
+      </c>
+      <c r="CL7" s="1" t="n">
+        <v>64658.78</v>
+      </c>
+      <c r="CM7" s="1" t="n">
+        <v>1271.36</v>
+      </c>
+      <c r="CN7" s="1" t="n">
+        <v>47028.91</v>
+      </c>
+      <c r="CO7" s="1" t="n">
+        <v>1514098.3</v>
+      </c>
+      <c r="CP7" s="1" t="n">
+        <v>20928.66</v>
+      </c>
+      <c r="CQ7" s="1" t="n">
+        <v>61150.62</v>
+      </c>
+      <c r="CR7" s="1" t="n">
+        <v>393458.01</v>
+      </c>
+      <c r="CS7" s="1" t="n">
+        <v>76211.84</v>
+      </c>
+      <c r="CT7" s="1" t="n">
+        <v>85350.63</v>
+      </c>
+      <c r="CU7" s="1" t="n">
+        <v>246667.8</v>
+      </c>
+      <c r="CV7" s="1" t="n">
+        <v>157836.95</v>
+      </c>
+      <c r="CW7" s="1" t="n">
+        <v>37119.38</v>
+      </c>
+      <c r="CX7" s="1" t="n">
+        <v>74564.87</v>
+      </c>
+      <c r="CY7" s="1" t="n">
+        <v>7857.04</v>
+      </c>
+      <c r="CZ7" s="1" t="n">
+        <v>203642.73</v>
+      </c>
+      <c r="DA7" s="1" t="n">
+        <v>120426.67</v>
+      </c>
+      <c r="DB7" s="1" t="n">
+        <v>150959.96</v>
+      </c>
+      <c r="DC7" s="1" t="n">
+        <v>9881.360000000001</v>
+      </c>
+      <c r="DD7" s="1" t="n">
+        <v>21779.26</v>
+      </c>
+      <c r="DE7" s="1" t="n">
+        <v>60232.53</v>
+      </c>
+      <c r="DF7" s="1" t="n">
+        <v>196756.47</v>
+      </c>
+      <c r="DG7" s="1" t="n">
+        <v>2346025.55</v>
+      </c>
+      <c r="DH7" s="1" t="n">
+        <v>515793.25</v>
+      </c>
+      <c r="DI7" s="1" t="n">
+        <v>185974.43</v>
+      </c>
+      <c r="DJ7" s="1" t="n">
+        <v>38334.71</v>
+      </c>
+      <c r="DK7" s="1" t="n">
+        <v>228449.31</v>
+      </c>
+      <c r="DL7" s="1" t="n">
+        <v>816.79</v>
+      </c>
+      <c r="DM7" s="1" t="n">
+        <v>535974.73</v>
+      </c>
+      <c r="DN7" s="1" t="n">
+        <v>43690.63</v>
+      </c>
+      <c r="DO7" s="1" t="n">
+        <v>48724.11</v>
+      </c>
+      <c r="DP7" s="1" t="n">
+        <v>12099.38</v>
+      </c>
+      <c r="DQ7" s="1" t="n">
+        <v>1624303.78</v>
+      </c>
+      <c r="DR7" s="1" t="n">
+        <v>143719.11</v>
+      </c>
+      <c r="DS7" s="1" t="n">
+        <v>146731.36</v>
+      </c>
+      <c r="DT7" s="1" t="n">
+        <v>237475.6</v>
+      </c>
+      <c r="DU7" s="1" t="n">
+        <v>135243.2</v>
+      </c>
+      <c r="DV7" s="1" t="n">
+        <v>631080.27</v>
+      </c>
+      <c r="DW7" s="1" t="n">
+        <v>59915.44</v>
+      </c>
+      <c r="DX7" s="1" t="n">
+        <v>407790.08</v>
+      </c>
+      <c r="DY7" s="1" t="n">
+        <v>59481.83</v>
+      </c>
+      <c r="DZ7" s="1" t="n">
+        <v>177351.4</v>
+      </c>
+      <c r="EA7" s="1" t="n">
+        <v>119661.56</v>
+      </c>
+      <c r="EB7" s="1" t="n">
+        <v>539.64</v>
+      </c>
+      <c r="EC7" s="1" t="n">
+        <v>49947.93</v>
+      </c>
+      <c r="ED7" s="1" t="n">
+        <v>79083.57000000001</v>
+      </c>
+      <c r="EE7" s="1" t="n">
+        <v>28857.01</v>
+      </c>
+      <c r="EF7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG7" s="1" t="n">
+        <v>42689.77</v>
+      </c>
+      <c r="EH7" s="1" t="n">
+        <v>861.13</v>
+      </c>
+      <c r="EI7" s="1" t="n">
+        <v>18704.38</v>
+      </c>
+      <c r="EJ7" s="1" t="n">
+        <v>2305.16</v>
+      </c>
+      <c r="EK7" s="1" t="n">
+        <v>175628.23</v>
+      </c>
+      <c r="EL7" s="1" t="n">
+        <v>553.61</v>
+      </c>
+      <c r="EM7" s="1" t="n">
+        <v>1333.24</v>
+      </c>
+      <c r="EN7" s="1" t="n">
+        <v>15656.05</v>
+      </c>
+      <c r="EO7" s="1" t="n">
+        <v>2296276.06</v>
+      </c>
+      <c r="EP7" s="1" t="n">
+        <v>3185783.07</v>
+      </c>
+      <c r="EQ7" s="1" t="n">
+        <v>15565.94</v>
+      </c>
+      <c r="ER7" s="1" t="n">
+        <v>25130.22</v>
+      </c>
+      <c r="ES7" s="1" t="n">
+        <v>25821.13</v>
+      </c>
+      <c r="ET7" s="1" t="n">
+        <v>83439.48</v>
+      </c>
+      <c r="EU7" s="1" t="n">
+        <v>23388.89</v>
+      </c>
+      <c r="EV7" s="1" t="n">
+        <v>17233.75</v>
+      </c>
+      <c r="EW7" s="1" t="n">
+        <v>238482.69</v>
+      </c>
+      <c r="EX7" s="1" t="n">
+        <v>136374.05</v>
+      </c>
+      <c r="EY7" s="1" t="n">
+        <v>682.5</v>
+      </c>
+      <c r="EZ7" s="1" t="n">
+        <v>40693.89</v>
+      </c>
+      <c r="FA7" s="1" t="n">
+        <v>66407.73</v>
+      </c>
+      <c r="FB7" s="1" t="n">
+        <v>185075.48</v>
+      </c>
+      <c r="FC7" s="1" t="n">
+        <v>38705.5</v>
+      </c>
+      <c r="FD7" s="1" t="n">
+        <v>397748.89</v>
+      </c>
+      <c r="FE7" s="1" t="n">
+        <v>378396.22</v>
+      </c>
+      <c r="FF7" s="1" t="n">
+        <v>2509.91</v>
+      </c>
+      <c r="FG7" s="1" t="n">
+        <v>59025.25</v>
+      </c>
+      <c r="FH7" s="1" t="n">
+        <v>421744.49</v>
+      </c>
+      <c r="FI7" s="1" t="n">
+        <v>30117.56</v>
+      </c>
+      <c r="FJ7" s="1" t="n">
+        <v>61598.86</v>
+      </c>
+      <c r="FK7" s="1" t="n">
+        <v>249282.74</v>
+      </c>
+      <c r="FL7" s="1" t="n">
+        <v>114485.69</v>
+      </c>
+      <c r="FM7" s="1" t="n">
+        <v>127183.57</v>
+      </c>
+      <c r="FN7" s="1" t="n">
+        <v>50701.15</v>
+      </c>
+      <c r="FO7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" s="1" t="n">
+        <v>74040.77</v>
+      </c>
+      <c r="FQ7" s="1" t="n">
+        <v>14213.69</v>
+      </c>
+      <c r="FR7" s="1" t="n">
+        <v>23367.24</v>
+      </c>
+      <c r="FS7" s="1" t="n">
+        <v>19190322.06</v>
+      </c>
+      <c r="FT7" s="1" t="n">
+        <v>73614.27</v>
+      </c>
+      <c r="FU7" s="1" t="n">
+        <v>69260.53</v>
+      </c>
+      <c r="FV7" s="1" t="n">
+        <v>66060.78</v>
+      </c>
+      <c r="FW7" s="1" t="n">
+        <v>36612.41</v>
+      </c>
+      <c r="FX7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" s="1" t="n">
+        <v>49353.14</v>
+      </c>
+      <c r="FZ7" s="1" t="n">
+        <v>86.45</v>
+      </c>
+      <c r="GA7" s="1" t="n">
+        <v>65188.19</v>
+      </c>
+      <c r="GB7" s="1" t="n">
+        <v>1216.94</v>
+      </c>
+      <c r="GC7" s="1" t="n">
+        <v>45371.71</v>
+      </c>
+      <c r="GD7" s="1" t="n">
+        <v>15003.07</v>
+      </c>
+      <c r="GE7" s="1" t="n">
+        <v>175459.09</v>
+      </c>
+      <c r="GF7" s="1" t="n">
+        <v>41290.35</v>
+      </c>
+      <c r="GG7" s="1" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="GH7" s="1" t="n">
+        <v>142230.4</v>
+      </c>
+      <c r="GI7" s="1" t="n">
+        <v>64609.58</v>
+      </c>
+      <c r="GJ7" s="1" t="n">
+        <v>15422.53</v>
+      </c>
+      <c r="GK7" s="1" t="n">
+        <v>88724.60000000001</v>
+      </c>
+      <c r="GL7" s="1" t="n">
+        <v>31979.78</v>
+      </c>
+      <c r="GM7" s="1" t="n">
+        <v>1259.01</v>
+      </c>
+      <c r="GN7" s="1" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="GO7" s="1" t="n">
+        <v>202373.64</v>
+      </c>
+      <c r="GP7" s="1" t="n">
+        <v>100941.61</v>
+      </c>
+      <c r="GQ7" s="1" t="n">
+        <v>17791.92</v>
+      </c>
+      <c r="GR7" s="1" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="GS7" s="1" t="n">
+        <v>4238.96</v>
+      </c>
+      <c r="GT7" s="1" t="n">
+        <v>27780.27</v>
+      </c>
+      <c r="GU7" s="1" t="n">
+        <v>198538.75</v>
+      </c>
+      <c r="GV7" s="1" t="n">
+        <v>55160.69</v>
+      </c>
+      <c r="GW7" s="1" t="n">
+        <v>36869.97</v>
+      </c>
+      <c r="GX7" s="1" t="n">
+        <v>643.04</v>
+      </c>
+      <c r="GY7" s="1" t="n">
+        <v>9887.98</v>
+      </c>
+      <c r="GZ7" s="1" t="n">
+        <v>25037.37</v>
+      </c>
+      <c r="HA7" s="1" t="n">
+        <v>448.64</v>
+      </c>
+      <c r="HB7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC7" s="1" t="n">
+        <v>19667.26</v>
+      </c>
+      <c r="HD7" s="1" t="n">
+        <v>2677.58</v>
+      </c>
+      <c r="HE7" s="1" t="n">
+        <v>27025.48</v>
+      </c>
+      <c r="HF7" s="1" t="n">
+        <v>26721.57</v>
+      </c>
+      <c r="HG7" s="1" t="n">
+        <v>180594.73</v>
+      </c>
+      <c r="HH7" s="1" t="n">
+        <v>6731.16</v>
+      </c>
+      <c r="HI7" s="1" t="n">
+        <v>14678.39</v>
+      </c>
+      <c r="HJ7" s="1" t="n">
+        <v>6531.24</v>
+      </c>
+      <c r="HK7" s="1" t="n">
+        <v>14535.47</v>
+      </c>
+      <c r="HL7" s="1" t="n">
+        <v>41523.9</v>
+      </c>
+      <c r="HM7" s="1" t="n">
+        <v>63488.39</v>
+      </c>
+      <c r="HN7" s="1" t="n">
+        <v>87355.92</v>
+      </c>
+      <c r="HO7" s="1" t="n">
+        <v>17346.3</v>
+      </c>
+      <c r="HP7" s="1" t="n">
+        <v>30951.08</v>
+      </c>
+      <c r="HQ7" s="1" t="n">
+        <v>19521.35</v>
+      </c>
+      <c r="HR7" s="1" t="n">
+        <v>249.35</v>
+      </c>
+      <c r="HS7" s="1" t="n">
+        <v>3763.7</v>
+      </c>
+      <c r="HT7" s="1" t="n">
+        <v>35663.33</v>
+      </c>
+      <c r="HU7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV7" s="1" t="n">
+        <v>19329.6</v>
+      </c>
+      <c r="HW7" s="1" t="n">
+        <v>52182.13</v>
+      </c>
+      <c r="HX7" s="1" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="HY7" s="1" t="n">
+        <v>53541.01</v>
+      </c>
+      <c r="HZ7" s="1" t="n">
+        <v>51406.95</v>
+      </c>
+      <c r="IA7" s="1" t="n">
+        <v>23241.28</v>
+      </c>
+      <c r="IB7" s="1" t="n">
+        <v>113922.2</v>
+      </c>
+      <c r="IC7" s="1" t="n">
+        <v>2493.4</v>
+      </c>
+      <c r="ID7" s="1" t="n">
+        <v>5145.45</v>
+      </c>
+      <c r="IE7" s="1" t="n">
+        <v>27182.73</v>
+      </c>
+      <c r="IF7" s="1" t="n">
+        <v>1908.74</v>
+      </c>
+      <c r="IG7" s="1" t="n">
+        <v>7476059</v>
+      </c>
+      <c r="IH7" s="1" t="n">
+        <v>585545.5</v>
+      </c>
+      <c r="II7" s="1" t="n">
+        <v>190119.01</v>
+      </c>
+      <c r="IJ7" s="1" t="n">
+        <v>66817.96000000001</v>
+      </c>
+      <c r="IK7" s="1" t="n">
+        <v>53375.19</v>
+      </c>
+      <c r="IL7" s="1" t="n">
+        <v>124.68</v>
+      </c>
+      <c r="IM7" s="1" t="n">
+        <v>85.54000000000001</v>
+      </c>
+      <c r="IN7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IO7" s="1" t="n">
+        <v>22486.22</v>
+      </c>
+      <c r="IP7" s="1" t="n">
+        <v>1831.96</v>
+      </c>
+      <c r="IQ7" s="1" t="n">
+        <v>6087</v>
+      </c>
+      <c r="IR7" s="1" t="n">
+        <v>284.16</v>
+      </c>
+      <c r="IS7" s="1" t="n">
+        <v>83.79000000000001</v>
+      </c>
+      <c r="IT7" s="1" t="n">
+        <v>49425.81</v>
+      </c>
+      <c r="IU7" s="1" t="n">
+        <v>14057.23</v>
+      </c>
+      <c r="IV7" s="1" t="n">
+        <v>4650.45</v>
+      </c>
+      <c r="IW7" s="1" t="n">
+        <v>150945.83</v>
+      </c>
+      <c r="IX7" s="1" t="n">
+        <v>7424.99</v>
+      </c>
+      <c r="IY7" s="1" t="n">
+        <v>1010.23</v>
+      </c>
+      <c r="IZ7" s="1" t="n">
+        <v>97145.11</v>
+      </c>
+      <c r="JA7" s="1" t="n">
+        <v>88251.41</v>
+      </c>
+      <c r="JB7" s="1" t="n">
+        <v>1037.69</v>
+      </c>
+      <c r="JC7" s="1" t="n">
+        <v>3440.28</v>
+      </c>
+      <c r="JD7" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="JE7" s="1" t="n">
+        <v>698.04</v>
+      </c>
+      <c r="JF7" s="1" t="n">
+        <v>9173.02</v>
+      </c>
+      <c r="JG7" s="1" t="n">
+        <v>68195.62</v>
+      </c>
+      <c r="JH7" s="1" t="n">
+        <v>74201.34</v>
+      </c>
+      <c r="JI7" s="1" t="n">
+        <v>55978.89</v>
+      </c>
+      <c r="JJ7" s="1" t="n">
+        <v>14934.09</v>
+      </c>
+      <c r="JK7" s="1" t="n">
+        <v>17915.55</v>
+      </c>
+      <c r="JL7" s="1" t="n">
+        <v>5043.86</v>
+      </c>
+      <c r="JM7" s="1" t="n">
+        <v>1350.5</v>
+      </c>
+      <c r="JN7" s="1" t="n">
+        <v>44906.75</v>
+      </c>
+      <c r="JO7" s="1" t="n">
+        <v>198073.25</v>
+      </c>
+      <c r="JP7" s="1" t="n">
+        <v>6936.47</v>
+      </c>
+      <c r="JQ7" s="1" t="n">
+        <v>598.67</v>
+      </c>
+      <c r="JR7" s="1" t="n">
+        <v>9153.74</v>
+      </c>
+      <c r="JS7" s="1" t="n">
+        <v>672464.39</v>
+      </c>
+      <c r="JT7" s="1" t="n">
+        <v>3045.06</v>
+      </c>
+      <c r="JU7" s="1" t="n">
+        <v>15488</v>
+      </c>
+      <c r="JV7" s="1" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="JW7" s="1" t="n">
+        <v>3714.62</v>
+      </c>
+      <c r="JX7" s="1" t="n">
+        <v>2385.62</v>
+      </c>
+      <c r="JY7" s="1" t="n">
+        <v>2994.89</v>
+      </c>
+      <c r="JZ7" s="1" t="n">
+        <v>6228182.83</v>
+      </c>
+      <c r="KA7" s="1" t="n">
+        <v>292.38</v>
+      </c>
+      <c r="KB7" s="1" t="n">
+        <v>1352.79</v>
+      </c>
+      <c r="KC7" s="1" t="n">
+        <v>2535.33</v>
+      </c>
+      <c r="KD7" s="1" t="n">
+        <v>2783.1</v>
+      </c>
+      <c r="KE7" s="1" t="n">
+        <v>485.46</v>
+      </c>
+      <c r="KF7" s="1" t="n">
+        <v>11995.01</v>
+      </c>
+      <c r="KG7" s="1" t="n">
+        <v>91721.72</v>
+      </c>
+      <c r="KH7" s="1" t="n">
+        <v>2805.62</v>
+      </c>
+      <c r="KI7" s="1" t="n">
+        <v>642.05</v>
+      </c>
+      <c r="KJ7" s="1" t="n">
+        <v>865229.33</v>
+      </c>
+      <c r="KK7" s="1" t="n">
+        <v>397.48</v>
+      </c>
+      <c r="KL7" s="1" t="n">
+        <v>1791.2</v>
+      </c>
+      <c r="KM7" s="1" t="n">
+        <v>82569.53</v>
+      </c>
+      <c r="KN7" s="1" t="n">
+        <v>126205.64</v>
+      </c>
+      <c r="KO7" s="1" t="n">
+        <v>95916.86</v>
+      </c>
+      <c r="KP7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KQ7" s="1" t="n">
+        <v>398.97</v>
+      </c>
+      <c r="KR7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS7" s="1" t="n">
+        <v>21184.95</v>
+      </c>
+      <c r="KT7" s="1" t="n">
+        <v>74960.60000000001</v>
+      </c>
+      <c r="KU7" s="1" t="n">
+        <v>492.43</v>
+      </c>
+      <c r="KV7" s="1" t="n">
+        <v>1081.29</v>
+      </c>
+      <c r="KW7" s="1" t="n">
+        <v>108178.1</v>
+      </c>
+      <c r="KX7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KY7" s="1" t="n">
+        <v>41624.05</v>
+      </c>
+      <c r="KZ7" s="1" t="n">
+        <v>3467.83</v>
+      </c>
+      <c r="LA7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LB7" s="1" t="n">
+        <v>480518.93</v>
+      </c>
+      <c r="LC7" s="1" t="n">
+        <v>593.62</v>
+      </c>
+      <c r="LD7" s="1" t="n">
+        <v>47004.71</v>
+      </c>
+      <c r="LE7" s="1" t="n">
+        <v>2486.76</v>
+      </c>
+      <c r="LF7" s="1" t="n">
+        <v>797.96</v>
+      </c>
+      <c r="LG7" s="1" t="n">
+        <v>16871.97</v>
+      </c>
+      <c r="LH7" s="1" t="n">
+        <v>850.1799999999999</v>
+      </c>
+      <c r="LI7" s="1" t="n">
+        <v>33892.38</v>
+      </c>
+      <c r="LJ7" s="1" t="n">
+        <v>918.5</v>
+      </c>
+      <c r="LK7" s="1" t="n">
+        <v>8278.780000000001</v>
+      </c>
+      <c r="LL7" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LM7" s="1" t="n">
+        <v>559.92</v>
+      </c>
+      <c r="LN7" s="1" t="n">
+        <v>451.31</v>
+      </c>
+      <c r="LO7" s="1" t="n">
+        <v>274.22</v>
+      </c>
+      <c r="LP7" s="1" t="n">
+        <v>4916.3</v>
+      </c>
+      <c r="LQ7" s="1" t="n">
+        <v>291.09</v>
+      </c>
+      <c r="LR7" s="1" t="n">
+        <v>133527.9</v>
+      </c>
+      <c r="LS7" s="1" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="LT7" s="1" t="n">
+        <v>72120.06</v>
+      </c>
+      <c r="LU7" s="1" t="n">
+        <v>4114.96</v>
+      </c>
+      <c r="LV7" s="1" t="n">
+        <v>5511.44</v>
+      </c>
+      <c r="LW7" s="1" t="n">
+        <v>91569.63</v>
+      </c>
+      <c r="LX7" s="1" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="LY7" s="1" t="n">
+        <v>93549.22</v>
+      </c>
+      <c r="LZ7" s="1" t="n">
+        <v>18249.1</v>
+      </c>
+      <c r="MA7" s="1" t="n">
+        <v>3037.95</v>
+      </c>
+      <c r="MB7" s="1" t="n">
+        <v>38861.19</v>
+      </c>
+      <c r="MC7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MD7" s="1" t="n">
+        <v>11648.35</v>
+      </c>
+      <c r="ME7" s="1" t="n">
+        <v>311.72</v>
+      </c>
+      <c r="MF7" s="1" t="n">
+        <v>576.8</v>
+      </c>
+      <c r="MG7" s="1" t="n">
+        <v>225407.35</v>
+      </c>
+      <c r="MH7" s="1" t="n">
+        <v>966981.27</v>
+      </c>
+      <c r="MI7" s="1" t="n">
+        <v>864.3200000000001</v>
+      </c>
+      <c r="MJ7" s="1" t="n">
+        <v>7294.66</v>
+      </c>
+      <c r="MK7" s="1" t="n">
+        <v>112875.75</v>
+      </c>
+      <c r="ML7" s="1" t="n">
+        <v>48655.05</v>
+      </c>
+      <c r="MM7" s="1" t="n">
+        <v>17521.83</v>
+      </c>
+      <c r="MN7" s="1" t="n">
+        <v>104251.84</v>
+      </c>
+      <c r="MO7" s="1" t="n">
+        <v>200.98</v>
+      </c>
+      <c r="MP7" s="1" t="n">
+        <v>4531.98</v>
+      </c>
+      <c r="MQ7" s="1" t="n">
+        <v>674.1900000000001</v>
+      </c>
+      <c r="MR7" s="1" t="n">
+        <v>2148.27</v>
+      </c>
+      <c r="MS7" s="1" t="n">
+        <v>20210.55</v>
+      </c>
+      <c r="MT7" s="1" t="n">
+        <v>141186.24</v>
+      </c>
+      <c r="MU7" s="1" t="n">
+        <v>281.53</v>
+      </c>
+      <c r="MV7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MW7" s="1" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="MX7" s="1" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="MY7" s="1" t="n">
+        <v>20944.64</v>
+      </c>
+      <c r="MZ7" s="1" t="n">
+        <v>34566.47</v>
+      </c>
+      <c r="NA7" s="1" t="n">
+        <v>11308.44</v>
+      </c>
+      <c r="NB7" s="1" t="n">
+        <v>272.26</v>
+      </c>
+      <c r="NC7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ND7" s="1" t="n">
+        <v>233235.84</v>
+      </c>
+      <c r="NE7" s="1" t="n">
+        <v>3648.07</v>
+      </c>
+      <c r="NF7" s="1" t="n">
+        <v>595.54</v>
+      </c>
+      <c r="NG7" s="1" t="n">
+        <v>199.48</v>
+      </c>
+      <c r="NH7" s="1" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="NI7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NJ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NK7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NL7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NM7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NN7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NO7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NP7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NQ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NR7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NS7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NT7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NU7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NV7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NW7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NX7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NY7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NZ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OA7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OB7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OC7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OD7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OE7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OF7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OG7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OH7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OI7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OJ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OK7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OL7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OM7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ON7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OO7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OP7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OQ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OR7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OS7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OT7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OU7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OV7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OW7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OX7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OY7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="OZ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PA7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PB7" s="1" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="PC7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PD7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PE7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PF7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PG7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PH7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PI7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PJ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PK7" s="1" t="n">
+        <v>389.02</v>
+      </c>
+      <c r="PL7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PM7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PN7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PO7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PP7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PQ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PR7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PS7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PT7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PU7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PV7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PW7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PX7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PY7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PZ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QA7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="QB7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9553,7 +10884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW6"/>
+  <dimension ref="A1:BXW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9811,6 +11142,44 @@
       </c>
       <c r="M6" s="1" t="n">
         <v>8353.971426</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>581708257.35</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>48804439.41577</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>3565104.2812</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>3495473.5744</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1657625.3544</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>1807613.6919</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>3749855.9863</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>6789.3039</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>112382.8108</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>2406.2268</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>1307.177864</v>
       </c>
     </row>
   </sheetData>
@@ -9824,7 +11193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW6"/>
+  <dimension ref="A1:BXW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11941,6 +13310,323 @@
         <v>0</v>
       </c>
       <c r="DB6" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>9912121.759959191</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>3141085.601054557</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>4290140.761853345</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>58591.8420878144</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>163279.8326533492</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>95784.8865180244</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>58541.95753621111</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>40540.9222136425</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>34281.9972467293</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>11006.2935638066</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>940.34304</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>19.94664273</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>1587.7288</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>403.9174761432</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="1" t="n">
+        <v>872.45408976</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11955,7 +13641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW6"/>
+  <dimension ref="A1:BXW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12622,6 +14308,122 @@
       </c>
       <c r="AM6" s="1" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>7397723.44</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>691593.8100000001</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>698241.9</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>807689.66</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>1810833.35</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>99482.2</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>273423.88</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>65030.67</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>148113.09</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>593329.99</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>7680.81</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>50145.91</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>19094.15</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>999.3</v>
+      </c>
+      <c r="T7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>10324.43</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1" t="n">
+        <v>419690.63</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>19696.64</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>52784.94</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>539.37</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>7871.27</v>
+      </c>
+      <c r="AD7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>400680.25</v>
+      </c>
+      <c r="AF7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="1" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="AH7" s="1" t="n">
+        <v>2000.15</v>
+      </c>
+      <c r="AI7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="1" t="n">
+        <v>856.66</v>
+      </c>
+      <c r="AL7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="1" t="n">
+        <v>36091.97</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>636253556.98</v>
+        <v>713693516.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,15 +481,15 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>581708257.35</v>
+        <v>663898092.9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ETH_THB</t>
+          <t>USDT_THB</t>
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>9912121.759959191</v>
+        <v>5914672.159152444</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>7397723.44</v>
+        <v>43493302.82</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>147936014.55</v>
+        <v>211392989.47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,15 +518,15 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>48804439.41577</v>
+        <v>90768932.19856</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>USDT_THB</t>
+          <t>BTC_THB</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>4290140.761853345</v>
+        <v>5661176.57772499</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>1810833.35</v>
+        <v>27684810.1</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>52653716.13</v>
+        <v>60369541.99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,23 +555,23 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>3749855.9863</v>
+        <v>6106177.1453</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BTC_THB</t>
+          <t>ETH_THB</t>
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>3141085.601054557</v>
+        <v>2516027.21619388</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SOLTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>807689.66</v>
+        <v>2437495.28</v>
       </c>
     </row>
     <row r="5">
@@ -584,15 +584,15 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>24232499.76</v>
+        <v>30768388.56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>3565104.2812</v>
+        <v>5744680.597</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>163279.8326533492</v>
+        <v>144186.3810903071</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>698241.9</v>
+        <v>1880993.27</v>
       </c>
     </row>
     <row r="6">
@@ -617,35 +617,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_SKR</t>
+          <t>THB_NEAR</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>19190322.06</v>
+        <v>27847477.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>SOLTHB</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>3495473.5744</v>
+        <v>1828824.6069</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SOL_THB</t>
+          <t>DOGE_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>95784.8865180244</v>
+        <v>93009.91077186359</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>XAUTTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>691593.8100000001</v>
+        <v>983889.95</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW7"/>
+  <dimension ref="A1:BXW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10871,6 +10871,1086 @@
       </c>
       <c r="QB7" s="1" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>713693516.2</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>211392989.47</v>
+      </c>
+      <c r="D8" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>60369541.99</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>30768388.56</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>21426297.81</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>21927185.81</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>6081972.77</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>4792573.94</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>12724602.83</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>12983862.85</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>4566345.75</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>27847477.2</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>5500529.14</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>2664262.6</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>4463348.52</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1827201.88</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>2548915.04</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>3130922.84</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>20905576.18</v>
+      </c>
+      <c r="V8" s="1" t="n">
+        <v>2321081.84</v>
+      </c>
+      <c r="W8" s="1" t="n">
+        <v>3229485.19</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>99771.77</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <v>311110.45</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>1215714.35</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>8644585.630000001</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>1951623.96</v>
+      </c>
+      <c r="AD8" s="1" t="n">
+        <v>3574980.13</v>
+      </c>
+      <c r="AE8" s="1" t="n">
+        <v>1220415.16</v>
+      </c>
+      <c r="AF8" s="1" t="n">
+        <v>1289384.96</v>
+      </c>
+      <c r="AG8" s="1" t="n">
+        <v>1670298.63</v>
+      </c>
+      <c r="AH8" s="1" t="n">
+        <v>1773700.26</v>
+      </c>
+      <c r="AI8" s="1" t="n">
+        <v>8050554.85</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>541346.39</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <v>461033.16</v>
+      </c>
+      <c r="AL8" s="1" t="n">
+        <v>709983.15</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>71373.02</v>
+      </c>
+      <c r="AO8" s="1" t="n">
+        <v>423255.76</v>
+      </c>
+      <c r="AP8" s="1" t="n">
+        <v>598130.78</v>
+      </c>
+      <c r="AQ8" s="1" t="n">
+        <v>5435226.01</v>
+      </c>
+      <c r="AR8" s="1" t="n">
+        <v>1320433.09</v>
+      </c>
+      <c r="AS8" s="1" t="n">
+        <v>90475.64999999999</v>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>1036828.33</v>
+      </c>
+      <c r="AU8" s="1" t="n">
+        <v>774778.83</v>
+      </c>
+      <c r="AV8" s="1" t="n">
+        <v>784926.53</v>
+      </c>
+      <c r="AW8" s="1" t="n">
+        <v>1551257.71</v>
+      </c>
+      <c r="AX8" s="1" t="n">
+        <v>943727.27</v>
+      </c>
+      <c r="AY8" s="1" t="n">
+        <v>245310.38</v>
+      </c>
+      <c r="AZ8" s="1" t="n">
+        <v>170390.94</v>
+      </c>
+      <c r="BA8" s="1" t="n">
+        <v>338053.66</v>
+      </c>
+      <c r="BB8" s="1" t="n">
+        <v>132225.24</v>
+      </c>
+      <c r="BC8" s="1" t="n">
+        <v>2495336.34</v>
+      </c>
+      <c r="BD8" s="1" t="n">
+        <v>135482.84</v>
+      </c>
+      <c r="BE8" s="1" t="n">
+        <v>412322.32</v>
+      </c>
+      <c r="BF8" s="1" t="n">
+        <v>615527.42</v>
+      </c>
+      <c r="BG8" s="1" t="n">
+        <v>25114.61</v>
+      </c>
+      <c r="BI8" s="1" t="n">
+        <v>53763.9</v>
+      </c>
+      <c r="BJ8" s="1" t="n">
+        <v>92950.49000000001</v>
+      </c>
+      <c r="BK8" s="1" t="n">
+        <v>866189.0600000001</v>
+      </c>
+      <c r="BL8" s="1" t="n">
+        <v>450.07</v>
+      </c>
+      <c r="BM8" s="1" t="n">
+        <v>1019466.74</v>
+      </c>
+      <c r="BN8" s="1" t="n">
+        <v>1688549.56</v>
+      </c>
+      <c r="BO8" s="1" t="n">
+        <v>4045.85</v>
+      </c>
+      <c r="BP8" s="1" t="n">
+        <v>885903.73</v>
+      </c>
+      <c r="BQ8" s="1" t="n">
+        <v>15639.82</v>
+      </c>
+      <c r="BS8" s="1" t="n">
+        <v>382724.08</v>
+      </c>
+      <c r="BT8" s="1" t="n">
+        <v>256017.58</v>
+      </c>
+      <c r="BU8" s="1" t="n">
+        <v>1636779.99</v>
+      </c>
+      <c r="BV8" s="1" t="n">
+        <v>564943.29</v>
+      </c>
+      <c r="BW8" s="1" t="n">
+        <v>29314.42</v>
+      </c>
+      <c r="BX8" s="1" t="n">
+        <v>755.2</v>
+      </c>
+      <c r="BY8" s="1" t="n">
+        <v>60948.92</v>
+      </c>
+      <c r="BZ8" s="1" t="n">
+        <v>162228.11</v>
+      </c>
+      <c r="CA8" s="1" t="n">
+        <v>92691.71000000001</v>
+      </c>
+      <c r="CB8" s="1" t="n">
+        <v>27557.48</v>
+      </c>
+      <c r="CC8" s="1" t="n">
+        <v>43361.72</v>
+      </c>
+      <c r="CD8" s="1" t="n">
+        <v>241956.32</v>
+      </c>
+      <c r="CE8" s="1" t="n">
+        <v>56030.4</v>
+      </c>
+      <c r="CF8" s="1" t="n">
+        <v>110570.19</v>
+      </c>
+      <c r="CG8" s="1" t="n">
+        <v>1100943.22</v>
+      </c>
+      <c r="CH8" s="1" t="n">
+        <v>39716.67</v>
+      </c>
+      <c r="CI8" s="1" t="n">
+        <v>7741.33</v>
+      </c>
+      <c r="CJ8" s="1" t="n">
+        <v>2239879.87</v>
+      </c>
+      <c r="CK8" s="1" t="n">
+        <v>11516.78</v>
+      </c>
+      <c r="CL8" s="1" t="n">
+        <v>495274.68</v>
+      </c>
+      <c r="CM8" s="1" t="n">
+        <v>125388.67</v>
+      </c>
+      <c r="CN8" s="1" t="n">
+        <v>101827.22</v>
+      </c>
+      <c r="CO8" s="1" t="n">
+        <v>816342.16</v>
+      </c>
+      <c r="CP8" s="1" t="n">
+        <v>10795.48</v>
+      </c>
+      <c r="CQ8" s="1" t="n">
+        <v>235690.92</v>
+      </c>
+      <c r="CR8" s="1" t="n">
+        <v>10708.87</v>
+      </c>
+      <c r="CS8" s="1" t="n">
+        <v>11557.59</v>
+      </c>
+      <c r="CT8" s="1" t="n">
+        <v>7029.1</v>
+      </c>
+      <c r="CV8" s="1" t="n">
+        <v>464789.3</v>
+      </c>
+      <c r="CW8" s="1" t="n">
+        <v>400169.57</v>
+      </c>
+      <c r="CX8" s="1" t="n">
+        <v>103082.61</v>
+      </c>
+      <c r="CY8" s="1" t="n">
+        <v>3128.01</v>
+      </c>
+      <c r="CZ8" s="1" t="n">
+        <v>120064.92</v>
+      </c>
+      <c r="DA8" s="1" t="n">
+        <v>34635.48</v>
+      </c>
+      <c r="DB8" s="1" t="n">
+        <v>102127.29</v>
+      </c>
+      <c r="DC8" s="1" t="n">
+        <v>114770.07</v>
+      </c>
+      <c r="DD8" s="1" t="n">
+        <v>109671.07</v>
+      </c>
+      <c r="DE8" s="1" t="n">
+        <v>58671.72</v>
+      </c>
+      <c r="DG8" s="1" t="n">
+        <v>689382.75</v>
+      </c>
+      <c r="DH8" s="1" t="n">
+        <v>259405.17</v>
+      </c>
+      <c r="DI8" s="1" t="n">
+        <v>37157.72</v>
+      </c>
+      <c r="DJ8" s="1" t="n">
+        <v>101855.45</v>
+      </c>
+      <c r="DK8" s="1" t="n">
+        <v>83465.64</v>
+      </c>
+      <c r="DL8" s="1" t="n">
+        <v>37150.39</v>
+      </c>
+      <c r="DM8" s="1" t="n">
+        <v>28935.61</v>
+      </c>
+      <c r="DN8" s="1" t="n">
+        <v>4657.44</v>
+      </c>
+      <c r="DO8" s="1" t="n">
+        <v>87140.25999999999</v>
+      </c>
+      <c r="DP8" s="1" t="n">
+        <v>199.48</v>
+      </c>
+      <c r="DQ8" s="1" t="n">
+        <v>1411551.13</v>
+      </c>
+      <c r="DR8" s="1" t="n">
+        <v>148594.67</v>
+      </c>
+      <c r="DS8" s="1" t="n">
+        <v>227944.44</v>
+      </c>
+      <c r="DT8" s="1" t="n">
+        <v>130570.11</v>
+      </c>
+      <c r="DV8" s="1" t="n">
+        <v>230810.42</v>
+      </c>
+      <c r="DW8" s="1" t="n">
+        <v>59364.12</v>
+      </c>
+      <c r="DX8" s="1" t="n">
+        <v>25297.66</v>
+      </c>
+      <c r="DY8" s="1" t="n">
+        <v>75123.22</v>
+      </c>
+      <c r="DZ8" s="1" t="n">
+        <v>143136.34</v>
+      </c>
+      <c r="EA8" s="1" t="n">
+        <v>3966.3</v>
+      </c>
+      <c r="EB8" s="1" t="n">
+        <v>2283.95</v>
+      </c>
+      <c r="EC8" s="1" t="n">
+        <v>147509.43</v>
+      </c>
+      <c r="ED8" s="1" t="n">
+        <v>3966.53</v>
+      </c>
+      <c r="EE8" s="1" t="n">
+        <v>21085.62</v>
+      </c>
+      <c r="EF8" s="1" t="n">
+        <v>1553.29</v>
+      </c>
+      <c r="EG8" s="1" t="n">
+        <v>12406.8</v>
+      </c>
+      <c r="EH8" s="1" t="n">
+        <v>5168.56</v>
+      </c>
+      <c r="EI8" s="1" t="n">
+        <v>22435.98</v>
+      </c>
+      <c r="EJ8" s="1" t="n">
+        <v>3346.62</v>
+      </c>
+      <c r="EK8" s="1" t="n">
+        <v>65036.27</v>
+      </c>
+      <c r="EL8" s="1" t="n">
+        <v>1488.53</v>
+      </c>
+      <c r="EM8" s="1" t="n">
+        <v>1333.24</v>
+      </c>
+      <c r="EN8" s="1" t="n">
+        <v>23154.84</v>
+      </c>
+      <c r="EO8" s="1" t="n">
+        <v>1374805.85</v>
+      </c>
+      <c r="EP8" s="1" t="n">
+        <v>2205009.23</v>
+      </c>
+      <c r="EQ8" s="1" t="n">
+        <v>33848.1</v>
+      </c>
+      <c r="ER8" s="1" t="n">
+        <v>36583.8</v>
+      </c>
+      <c r="ES8" s="1" t="n">
+        <v>15466.58</v>
+      </c>
+      <c r="ET8" s="1" t="n">
+        <v>76893.5</v>
+      </c>
+      <c r="EU8" s="1" t="n">
+        <v>82143.05</v>
+      </c>
+      <c r="EV8" s="1" t="n">
+        <v>46108.97</v>
+      </c>
+      <c r="EW8" s="1" t="n">
+        <v>736464.83</v>
+      </c>
+      <c r="EX8" s="1" t="n">
+        <v>77113.22</v>
+      </c>
+      <c r="EY8" s="1" t="n">
+        <v>5008.59</v>
+      </c>
+      <c r="EZ8" s="1" t="n">
+        <v>51501.31</v>
+      </c>
+      <c r="FB8" s="1" t="n">
+        <v>10955.46</v>
+      </c>
+      <c r="FC8" s="1" t="n">
+        <v>123972.74</v>
+      </c>
+      <c r="FD8" s="1" t="n">
+        <v>511525.88</v>
+      </c>
+      <c r="FE8" s="1" t="n">
+        <v>440731.07</v>
+      </c>
+      <c r="FF8" s="1" t="n">
+        <v>3343.67</v>
+      </c>
+      <c r="FG8" s="1" t="n">
+        <v>446715.07</v>
+      </c>
+      <c r="FH8" s="1" t="n">
+        <v>13279.11</v>
+      </c>
+      <c r="FI8" s="1" t="n">
+        <v>68543.57000000001</v>
+      </c>
+      <c r="FK8" s="1" t="n">
+        <v>975914.77</v>
+      </c>
+      <c r="FL8" s="1" t="n">
+        <v>43218.79</v>
+      </c>
+      <c r="FM8" s="1" t="n">
+        <v>34078.54</v>
+      </c>
+      <c r="FN8" s="1" t="n">
+        <v>53859.25</v>
+      </c>
+      <c r="FO8" s="1" t="n">
+        <v>266.05</v>
+      </c>
+      <c r="FP8" s="1" t="n">
+        <v>141756.39</v>
+      </c>
+      <c r="FQ8" s="1" t="n">
+        <v>29446.27</v>
+      </c>
+      <c r="FR8" s="1" t="n">
+        <v>3590.96</v>
+      </c>
+      <c r="FS8" s="1" t="n">
+        <v>9442683.300000001</v>
+      </c>
+      <c r="FT8" s="1" t="n">
+        <v>80178.53999999999</v>
+      </c>
+      <c r="FU8" s="1" t="n">
+        <v>21032.05</v>
+      </c>
+      <c r="FV8" s="1" t="n">
+        <v>99616.75</v>
+      </c>
+      <c r="FW8" s="1" t="n">
+        <v>10178.24</v>
+      </c>
+      <c r="FX8" s="1" t="n">
+        <v>102.21</v>
+      </c>
+      <c r="FY8" s="1" t="n">
+        <v>7738.93</v>
+      </c>
+      <c r="FZ8" s="1" t="n">
+        <v>261516.52</v>
+      </c>
+      <c r="GA8" s="1" t="n">
+        <v>31315.51</v>
+      </c>
+      <c r="GB8" s="1" t="n">
+        <v>9078.059999999999</v>
+      </c>
+      <c r="GC8" s="1" t="n">
+        <v>212298.61</v>
+      </c>
+      <c r="GD8" s="1" t="n">
+        <v>3197.86</v>
+      </c>
+      <c r="GE8" s="1" t="n">
+        <v>117006.4</v>
+      </c>
+      <c r="GF8" s="1" t="n">
+        <v>35156.03</v>
+      </c>
+      <c r="GG8" s="1" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="GH8" s="1" t="n">
+        <v>10304.17</v>
+      </c>
+      <c r="GI8" s="1" t="n">
+        <v>176410.04</v>
+      </c>
+      <c r="GJ8" s="1" t="n">
+        <v>374277.47</v>
+      </c>
+      <c r="GK8" s="1" t="n">
+        <v>491288.59</v>
+      </c>
+      <c r="GL8" s="1" t="n">
+        <v>464.44</v>
+      </c>
+      <c r="GM8" s="1" t="n">
+        <v>13672.79</v>
+      </c>
+      <c r="GN8" s="1" t="n">
+        <v>20623.26</v>
+      </c>
+      <c r="GO8" s="1" t="n">
+        <v>62394.44</v>
+      </c>
+      <c r="GP8" s="1" t="n">
+        <v>31982.63</v>
+      </c>
+      <c r="GQ8" s="1" t="n">
+        <v>55619.15</v>
+      </c>
+      <c r="GR8" s="1" t="n">
+        <v>50923.26</v>
+      </c>
+      <c r="GS8" s="1" t="n">
+        <v>911.42</v>
+      </c>
+      <c r="GT8" s="1" t="n">
+        <v>347943.49</v>
+      </c>
+      <c r="GU8" s="1" t="n">
+        <v>8179.22</v>
+      </c>
+      <c r="GV8" s="1" t="n">
+        <v>63195.3</v>
+      </c>
+      <c r="GX8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY8" s="1" t="n">
+        <v>8818.139999999999</v>
+      </c>
+      <c r="GZ8" s="1" t="n">
+        <v>20544.76</v>
+      </c>
+      <c r="HA8" s="1" t="n">
+        <v>267.1</v>
+      </c>
+      <c r="HB8" s="1" t="n">
+        <v>241.84</v>
+      </c>
+      <c r="HC8" s="1" t="n">
+        <v>47181.85</v>
+      </c>
+      <c r="HD8" s="1" t="n">
+        <v>22795.39</v>
+      </c>
+      <c r="HE8" s="1" t="n">
+        <v>55262.61</v>
+      </c>
+      <c r="HF8" s="1" t="n">
+        <v>4212.1</v>
+      </c>
+      <c r="HG8" s="1" t="n">
+        <v>42660.97</v>
+      </c>
+      <c r="HH8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI8" s="1" t="n">
+        <v>15425.99</v>
+      </c>
+      <c r="HJ8" s="1" t="n">
+        <v>55599.02</v>
+      </c>
+      <c r="HK8" s="1" t="n">
+        <v>152915.02</v>
+      </c>
+      <c r="HL8" s="1" t="n">
+        <v>85888.74000000001</v>
+      </c>
+      <c r="HM8" s="1" t="n">
+        <v>6558.39</v>
+      </c>
+      <c r="HN8" s="1" t="n">
+        <v>24682.83</v>
+      </c>
+      <c r="HO8" s="1" t="n">
+        <v>23073.23</v>
+      </c>
+      <c r="HP8" s="1" t="n">
+        <v>21362.37</v>
+      </c>
+      <c r="HQ8" s="1" t="n">
+        <v>8907.959999999999</v>
+      </c>
+      <c r="HR8" s="1" t="n">
+        <v>1114340.26</v>
+      </c>
+      <c r="HS8" s="1" t="n">
+        <v>130142.35</v>
+      </c>
+      <c r="HT8" s="1" t="n">
+        <v>50979.05</v>
+      </c>
+      <c r="HU8" s="1" t="n">
+        <v>299.24</v>
+      </c>
+      <c r="HV8" s="1" t="n">
+        <v>8228.5</v>
+      </c>
+      <c r="HW8" s="1" t="n">
+        <v>2546.73</v>
+      </c>
+      <c r="HX8" s="1" t="n">
+        <v>343.59</v>
+      </c>
+      <c r="HY8" s="1" t="n">
+        <v>142908.2</v>
+      </c>
+      <c r="HZ8" s="1" t="n">
+        <v>190446.03</v>
+      </c>
+      <c r="IA8" s="1" t="n">
+        <v>106508.62</v>
+      </c>
+      <c r="IB8" s="1" t="n">
+        <v>17320.1</v>
+      </c>
+      <c r="IC8" s="1" t="n">
+        <v>4869.02</v>
+      </c>
+      <c r="ID8" s="1" t="n">
+        <v>10552.06</v>
+      </c>
+      <c r="IE8" s="1" t="n">
+        <v>96063.12</v>
+      </c>
+      <c r="IF8" s="1" t="n">
+        <v>2487.2</v>
+      </c>
+      <c r="IG8" s="1" t="n">
+        <v>2262333.33</v>
+      </c>
+      <c r="IH8" s="1" t="n">
+        <v>396186.87</v>
+      </c>
+      <c r="II8" s="1" t="n">
+        <v>92632.86</v>
+      </c>
+      <c r="IJ8" s="1" t="n">
+        <v>157234.68</v>
+      </c>
+      <c r="IK8" s="1" t="n">
+        <v>2139.44</v>
+      </c>
+      <c r="IL8" s="1" t="n">
+        <v>917.6900000000001</v>
+      </c>
+      <c r="IM8" s="1" t="n">
+        <v>692.41</v>
+      </c>
+      <c r="IN8" s="1" t="n">
+        <v>3569.3</v>
+      </c>
+      <c r="IO8" s="1" t="n">
+        <v>1673.62</v>
+      </c>
+      <c r="IP8" s="1" t="n">
+        <v>388.91</v>
+      </c>
+      <c r="IQ8" s="1" t="n">
+        <v>208.41</v>
+      </c>
+      <c r="IR8" s="1" t="n">
+        <v>1304.7</v>
+      </c>
+      <c r="IS8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT8" s="1" t="n">
+        <v>96515.67999999999</v>
+      </c>
+      <c r="IU8" s="1" t="n">
+        <v>372.6</v>
+      </c>
+      <c r="IV8" s="1" t="n">
+        <v>32101.24</v>
+      </c>
+      <c r="IW8" s="1" t="n">
+        <v>212753.8</v>
+      </c>
+      <c r="IX8" s="1" t="n">
+        <v>11026.56</v>
+      </c>
+      <c r="IY8" s="1" t="n">
+        <v>2642.6</v>
+      </c>
+      <c r="IZ8" s="1" t="n">
+        <v>984.6799999999999</v>
+      </c>
+      <c r="JA8" s="1" t="n">
+        <v>27414.16</v>
+      </c>
+      <c r="JB8" s="1" t="n">
+        <v>35460.87</v>
+      </c>
+      <c r="JC8" s="1" t="n">
+        <v>452418.46</v>
+      </c>
+      <c r="JD8" s="1" t="n">
+        <v>1628.55</v>
+      </c>
+      <c r="JE8" s="1" t="n">
+        <v>698.04</v>
+      </c>
+      <c r="JF8" s="1" t="n">
+        <v>14930.7</v>
+      </c>
+      <c r="JG8" s="1" t="n">
+        <v>23551.28</v>
+      </c>
+      <c r="JH8" s="1" t="n">
+        <v>74201.34</v>
+      </c>
+      <c r="JI8" s="1" t="n">
+        <v>61927.58</v>
+      </c>
+      <c r="JJ8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK8" s="1" t="n">
+        <v>53245.43</v>
+      </c>
+      <c r="JM8" s="1" t="n">
+        <v>212113.29</v>
+      </c>
+      <c r="JN8" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="JO8" s="1" t="n">
+        <v>199.31</v>
+      </c>
+      <c r="JP8" s="1" t="n">
+        <v>50025.78</v>
+      </c>
+      <c r="JQ8" s="1" t="n">
+        <v>129979.29</v>
+      </c>
+      <c r="JR8" s="1" t="n">
+        <v>10569.6</v>
+      </c>
+      <c r="JS8" s="1" t="n">
+        <v>360075.19</v>
+      </c>
+      <c r="JT8" s="1" t="n">
+        <v>6130.69</v>
+      </c>
+      <c r="JU8" s="1" t="n">
+        <v>4123.45</v>
+      </c>
+      <c r="JV8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="JX8" s="1" t="n">
+        <v>15090.78</v>
+      </c>
+      <c r="JY8" s="1" t="n">
+        <v>29371.87</v>
+      </c>
+      <c r="JZ8" s="1" t="n">
+        <v>1454583.45</v>
+      </c>
+      <c r="KA8" s="1" t="n">
+        <v>12659.33</v>
+      </c>
+      <c r="KB8" s="1" t="n">
+        <v>22223.3</v>
+      </c>
+      <c r="KC8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD8" s="1" t="n">
+        <v>759.5</v>
+      </c>
+      <c r="KE8" s="1" t="n">
+        <v>822.45</v>
+      </c>
+      <c r="KF8" s="1" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="KG8" s="1" t="n">
+        <v>19550.82</v>
+      </c>
+      <c r="KH8" s="1" t="n">
+        <v>811.4299999999999</v>
+      </c>
+      <c r="KI8" s="1" t="n">
+        <v>4414.46</v>
+      </c>
+      <c r="KJ8" s="1" t="n">
+        <v>108307.57</v>
+      </c>
+      <c r="KK8" s="1" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="KM8" s="1" t="n">
+        <v>9423.01</v>
+      </c>
+      <c r="KN8" s="1" t="n">
+        <v>365174.5</v>
+      </c>
+      <c r="KO8" s="1" t="n">
+        <v>167078.17</v>
+      </c>
+      <c r="KP8" s="1" t="n">
+        <v>299.25</v>
+      </c>
+      <c r="KQ8" s="1" t="n">
+        <v>398.97</v>
+      </c>
+      <c r="KR8" s="1" t="n">
+        <v>183.68</v>
+      </c>
+      <c r="KS8" s="1" t="n">
+        <v>44054.89</v>
+      </c>
+      <c r="KT8" s="1" t="n">
+        <v>63179.25</v>
+      </c>
+      <c r="KU8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KV8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KW8" s="1" t="n">
+        <v>147031.18</v>
+      </c>
+      <c r="KX8" s="1" t="n">
+        <v>1189.13</v>
+      </c>
+      <c r="KY8" s="1" t="n">
+        <v>34121.31</v>
+      </c>
+      <c r="KZ8" s="1" t="n">
+        <v>180801.95</v>
+      </c>
+      <c r="LA8" s="1" t="n">
+        <v>75.64</v>
+      </c>
+      <c r="LB8" s="1" t="n">
+        <v>49675.65</v>
+      </c>
+      <c r="LC8" s="1" t="n">
+        <v>593.62</v>
+      </c>
+      <c r="LD8" s="1" t="n">
+        <v>321419.28</v>
+      </c>
+      <c r="LE8" s="1" t="n">
+        <v>470.36</v>
+      </c>
+      <c r="LF8" s="1" t="n">
+        <v>199.48</v>
+      </c>
+      <c r="LG8" s="1" t="n">
+        <v>68120.2</v>
+      </c>
+      <c r="LI8" s="1" t="n">
+        <v>350.7</v>
+      </c>
+      <c r="LJ8" s="1" t="n">
+        <v>28987.6</v>
+      </c>
+      <c r="LK8" s="1" t="n">
+        <v>9518.459999999999</v>
+      </c>
+      <c r="LL8" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LO8" s="1" t="n">
+        <v>1790.79</v>
+      </c>
+      <c r="LP8" s="1" t="n">
+        <v>379.64</v>
+      </c>
+      <c r="LQ8" s="1" t="n">
+        <v>699.48</v>
+      </c>
+      <c r="LR8" s="1" t="n">
+        <v>68063.86</v>
+      </c>
+      <c r="LS8" s="1" t="n">
+        <v>3061.04</v>
+      </c>
+      <c r="LT8" s="1" t="n">
+        <v>1011665.9</v>
+      </c>
+      <c r="LU8" s="1" t="n">
+        <v>4114.96</v>
+      </c>
+      <c r="LV8" s="1" t="n">
+        <v>13597.82</v>
+      </c>
+      <c r="LW8" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="LX8" s="1" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="LY8" s="1" t="n">
+        <v>2987.94</v>
+      </c>
+      <c r="LZ8" s="1" t="n">
+        <v>106919.74</v>
+      </c>
+      <c r="MA8" s="1" t="n">
+        <v>11305.32</v>
+      </c>
+      <c r="MB8" s="1" t="n">
+        <v>1485.94</v>
+      </c>
+      <c r="MC8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MD8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ME8" s="1" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="MF8" s="1" t="n">
+        <v>63391.26</v>
+      </c>
+      <c r="MG8" s="1" t="n">
+        <v>226.34</v>
+      </c>
+      <c r="MH8" s="1" t="n">
+        <v>493183.52</v>
+      </c>
+      <c r="MI8" s="1" t="n">
+        <v>2502.16</v>
+      </c>
+      <c r="MJ8" s="1" t="n">
+        <v>139.66</v>
+      </c>
+      <c r="MK8" s="1" t="n">
+        <v>122650.18</v>
+      </c>
+      <c r="ML8" s="1" t="n">
+        <v>16800.18</v>
+      </c>
+      <c r="MM8" s="1" t="n">
+        <v>17521.83</v>
+      </c>
+      <c r="MN8" s="1" t="n">
+        <v>67751.32000000001</v>
+      </c>
+      <c r="MO8" s="1" t="n">
+        <v>199.47</v>
+      </c>
+      <c r="MP8" s="1" t="n">
+        <v>4531.98</v>
+      </c>
+      <c r="MQ8" s="1" t="n">
+        <v>6583.5</v>
+      </c>
+      <c r="MR8" s="1" t="n">
+        <v>4334.14</v>
+      </c>
+      <c r="MS8" s="1" t="n">
+        <v>41785.01</v>
+      </c>
+      <c r="MT8" s="1" t="n">
+        <v>3695.06</v>
+      </c>
+      <c r="MU8" s="1" t="n">
+        <v>7261.73</v>
+      </c>
+      <c r="MV8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MW8" s="1" t="n">
+        <v>127.26</v>
+      </c>
+      <c r="MX8" s="1" t="n">
+        <v>982.66</v>
+      </c>
+      <c r="MY8" s="1" t="n">
+        <v>3667.99</v>
+      </c>
+      <c r="MZ8" s="1" t="n">
+        <v>1306.44</v>
+      </c>
+      <c r="NA8" s="1" t="n">
+        <v>3265.01</v>
+      </c>
+      <c r="NB8" s="1" t="n">
+        <v>634.34</v>
+      </c>
+      <c r="NC8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ND8" s="1" t="n">
+        <v>4073.08</v>
+      </c>
+      <c r="NE8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NF8" s="1" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="NG8" s="1" t="n">
+        <v>440.59</v>
+      </c>
+      <c r="NH8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PB8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PK8" s="1" t="n">
+        <v>1147.5</v>
+      </c>
+      <c r="PV8" s="1" t="n">
+        <v>19969.81</v>
       </c>
     </row>
   </sheetData>
@@ -10884,7 +11964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW7"/>
+  <dimension ref="A1:BXW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11180,6 +12260,48 @@
       </c>
       <c r="M7" s="1" t="n">
         <v>1307.177864</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>663898092.9</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>90768932.19856</v>
+      </c>
+      <c r="D8" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1738635.2757</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>5744680.597</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1828824.6069</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1815371.2121</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>6106177.1453</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>40820.3024</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>55472.3395</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>2406.2268</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>22926.407217</v>
       </c>
     </row>
   </sheetData>
@@ -11193,7 +12315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW7"/>
+  <dimension ref="A1:BXW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13627,6 +14749,327 @@
         <v>0</v>
       </c>
       <c r="DB7" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>2516027.21619388</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>5661176.57772499</v>
+      </c>
+      <c r="D8" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>5914672.159152444</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>11818.9752277754</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>144186.3810903071</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>91675.9649849743</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>93009.91077186359</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>27324.2535804961</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>19403.4210013262</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>24307.0432577603</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>2001.8987809882</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>998.32946853</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1522.3119939132</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="1" t="n">
+        <v>106.9002</v>
+      </c>
+      <c r="AM8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="1" t="n">
+        <v>1106.513006488</v>
+      </c>
+      <c r="AV8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="1" t="n">
+        <v>1.632</v>
+      </c>
+      <c r="BD8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" s="1" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="BS8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" s="1" t="n">
+        <v>1027.2521003893</v>
+      </c>
+      <c r="CK8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" s="1" t="n">
+        <v>2024.5842371046</v>
+      </c>
+      <c r="CN8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" s="1" t="n">
+        <v>2691.5021005955</v>
+      </c>
+      <c r="CY8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13641,7 +15084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW7"/>
+  <dimension ref="A1:BXW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14424,6 +15867,126 @@
       </c>
       <c r="AM7" s="1" t="n">
         <v>36091.97</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>43493302.82</v>
+      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(B2:B8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>2437495.28</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1880993.27</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>464468.85</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>2997.15</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>27684810.1</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>53482.21</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>6841.54</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>5100.92</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>44136.08</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>524553.84</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>177664.04</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>31313.46</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>91212.64999999999</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>984.98</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>63974.44</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>4622.17</v>
+      </c>
+      <c r="T8" s="1" t="n">
+        <v>1515.75</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>17173.49</v>
+      </c>
+      <c r="V8" s="1" t="n">
+        <v>884</v>
+      </c>
+      <c r="W8" s="1" t="n">
+        <v>125828.68</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>13104.99</v>
+      </c>
+      <c r="Z8" s="1" t="n">
+        <v>983889.95</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>501.84</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>550.8099999999999</v>
+      </c>
+      <c r="AD8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1" t="n">
+        <v>12725.25</v>
+      </c>
+      <c r="AF8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="1" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AH8" s="1" t="n">
+        <v>499.66</v>
+      </c>
+      <c r="AI8" s="1" t="n">
+        <v>185.94</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <v>304366.61</v>
+      </c>
+      <c r="AL8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>713693516.2</v>
+        <v>740341862.52</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>663898092.9</v>
+        <v>585624367.65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>5914672.159152444</v>
+        <v>5096088.505715098</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>43493302.82</v>
+        <v>15172757.32</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>211392989.47</v>
+        <v>195029157.19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>90768932.19856</v>
+        <v>90854782.42874999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>5661176.57772499</v>
+        <v>3150677.600265065</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>27684810.1</v>
+        <v>1871487.73</v>
       </c>
     </row>
     <row r="4">
@@ -547,15 +547,15 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>60369541.99</v>
+        <v>82741110.41</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VELOTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>6106177.1453</v>
+        <v>5716728.1795</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -563,15 +563,15 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>2516027.21619388</v>
+        <v>1322736.353759038</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>2437495.28</v>
+        <v>1008683.37</v>
       </c>
     </row>
     <row r="5">
@@ -584,15 +584,15 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>30768388.56</v>
+        <v>34553096.93</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>VELOTHB</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>5744680.597</v>
+        <v>3363091.5582</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,15 +600,15 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>144186.3810903071</v>
+        <v>304145.8795130064</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>1880993.27</v>
+        <v>650445.8</v>
       </c>
     </row>
     <row r="6">
@@ -617,35 +617,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_NEAR</t>
+          <t>THB_DOGE</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>27847477.2</v>
+        <v>13489238.17</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SOLTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1828824.6069</v>
+        <v>2040003.7908</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DOGE_THB</t>
+          <t>SOL_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>93009.91077186359</v>
+        <v>92494.5983818425</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>XAUTTHB</t>
+          <t>UNITHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>983889.95</v>
+        <v>477139.25</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW8"/>
+  <dimension ref="A1:BXW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11951,6 +11951,1086 @@
       </c>
       <c r="PV8" s="1" t="n">
         <v>19969.81</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>740341862.52</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>195029157.19</v>
+      </c>
+      <c r="D9" s="1">
+        <f>AVERAGE(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>82741110.41</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>34553096.93</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>13385654.5</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>13489238.17</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>5350630.22</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>6379739.17</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>6535080.47</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>10220725.69</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>2159355.84</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>9676432.449999999</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>11425277.31</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>2036059.11</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>3214333.73</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>4460976.6</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>2668208.65</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>3731721.29</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>9007151.949999999</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>175916.48</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>2957800.14</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>262701.79</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <v>235801.54</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>1634188.86</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>3305373.69</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>4053247.08</v>
+      </c>
+      <c r="AD9" s="1" t="n">
+        <v>2537960.88</v>
+      </c>
+      <c r="AE9" s="1" t="n">
+        <v>831124.1800000001</v>
+      </c>
+      <c r="AF9" s="1" t="n">
+        <v>1043320.47</v>
+      </c>
+      <c r="AG9" s="1" t="n">
+        <v>607885.03</v>
+      </c>
+      <c r="AH9" s="1" t="n">
+        <v>1429798.45</v>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>6737527.19</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>150511.58</v>
+      </c>
+      <c r="AK9" s="1" t="n">
+        <v>70523.53</v>
+      </c>
+      <c r="AL9" s="1" t="n">
+        <v>1901037.84</v>
+      </c>
+      <c r="AN9" s="1" t="n">
+        <v>20595.1</v>
+      </c>
+      <c r="AO9" s="1" t="n">
+        <v>242442.12</v>
+      </c>
+      <c r="AP9" s="1" t="n">
+        <v>294216.3</v>
+      </c>
+      <c r="AQ9" s="1" t="n">
+        <v>4711224.66</v>
+      </c>
+      <c r="AR9" s="1" t="n">
+        <v>6393125.47</v>
+      </c>
+      <c r="AS9" s="1" t="n">
+        <v>346587.63</v>
+      </c>
+      <c r="AT9" s="1" t="n">
+        <v>1581569.37</v>
+      </c>
+      <c r="AU9" s="1" t="n">
+        <v>4502283.45</v>
+      </c>
+      <c r="AV9" s="1" t="n">
+        <v>328655.62</v>
+      </c>
+      <c r="AW9" s="1" t="n">
+        <v>1087236.91</v>
+      </c>
+      <c r="AX9" s="1" t="n">
+        <v>986345.5600000001</v>
+      </c>
+      <c r="AY9" s="1" t="n">
+        <v>84797.22</v>
+      </c>
+      <c r="AZ9" s="1" t="n">
+        <v>347110.67</v>
+      </c>
+      <c r="BA9" s="1" t="n">
+        <v>62238.75</v>
+      </c>
+      <c r="BB9" s="1" t="n">
+        <v>115748.15</v>
+      </c>
+      <c r="BC9" s="1" t="n">
+        <v>970242.13</v>
+      </c>
+      <c r="BD9" s="1" t="n">
+        <v>521301.21</v>
+      </c>
+      <c r="BE9" s="1" t="n">
+        <v>270453.85</v>
+      </c>
+      <c r="BF9" s="1" t="n">
+        <v>776022.29</v>
+      </c>
+      <c r="BG9" s="1" t="n">
+        <v>8746.99</v>
+      </c>
+      <c r="BI9" s="1" t="n">
+        <v>94023.08</v>
+      </c>
+      <c r="BJ9" s="1" t="n">
+        <v>950814.85</v>
+      </c>
+      <c r="BK9" s="1" t="n">
+        <v>947325.61</v>
+      </c>
+      <c r="BL9" s="1" t="n">
+        <v>876.42</v>
+      </c>
+      <c r="BM9" s="1" t="n">
+        <v>259825.53</v>
+      </c>
+      <c r="BN9" s="1" t="n">
+        <v>281465.11</v>
+      </c>
+      <c r="BO9" s="1" t="n">
+        <v>58519.79</v>
+      </c>
+      <c r="BP9" s="1" t="n">
+        <v>332204.57</v>
+      </c>
+      <c r="BQ9" s="1" t="n">
+        <v>57930.23</v>
+      </c>
+      <c r="BS9" s="1" t="n">
+        <v>531078.74</v>
+      </c>
+      <c r="BT9" s="1" t="n">
+        <v>178162.24</v>
+      </c>
+      <c r="BU9" s="1" t="n">
+        <v>1659454.04</v>
+      </c>
+      <c r="BV9" s="1" t="n">
+        <v>486424.48</v>
+      </c>
+      <c r="BW9" s="1" t="n">
+        <v>383414.9</v>
+      </c>
+      <c r="BX9" s="1" t="n">
+        <v>737.97</v>
+      </c>
+      <c r="BY9" s="1" t="n">
+        <v>327082.08</v>
+      </c>
+      <c r="BZ9" s="1" t="n">
+        <v>849922.64</v>
+      </c>
+      <c r="CA9" s="1" t="n">
+        <v>169843.47</v>
+      </c>
+      <c r="CB9" s="1" t="n">
+        <v>60514.32</v>
+      </c>
+      <c r="CC9" s="1" t="n">
+        <v>36492.11</v>
+      </c>
+      <c r="CD9" s="1" t="n">
+        <v>25749.76</v>
+      </c>
+      <c r="CE9" s="1" t="n">
+        <v>17889.17</v>
+      </c>
+      <c r="CF9" s="1" t="n">
+        <v>30877.52</v>
+      </c>
+      <c r="CG9" s="1" t="n">
+        <v>1061668.1</v>
+      </c>
+      <c r="CH9" s="1" t="n">
+        <v>94807.81</v>
+      </c>
+      <c r="CI9" s="1" t="n">
+        <v>547.8099999999999</v>
+      </c>
+      <c r="CJ9" s="1" t="n">
+        <v>816869.76</v>
+      </c>
+      <c r="CK9" s="1" t="n">
+        <v>53582.06</v>
+      </c>
+      <c r="CL9" s="1" t="n">
+        <v>46787.67</v>
+      </c>
+      <c r="CM9" s="1" t="n">
+        <v>16498.29</v>
+      </c>
+      <c r="CN9" s="1" t="n">
+        <v>230046.96</v>
+      </c>
+      <c r="CO9" s="1" t="n">
+        <v>371640.44</v>
+      </c>
+      <c r="CP9" s="1" t="n">
+        <v>125336.77</v>
+      </c>
+      <c r="CQ9" s="1" t="n">
+        <v>117297.8</v>
+      </c>
+      <c r="CR9" s="1" t="n">
+        <v>965.92</v>
+      </c>
+      <c r="CS9" s="1" t="n">
+        <v>39749.75</v>
+      </c>
+      <c r="CT9" s="1" t="n">
+        <v>26043.19</v>
+      </c>
+      <c r="CV9" s="1" t="n">
+        <v>305774.99</v>
+      </c>
+      <c r="CW9" s="1" t="n">
+        <v>2061299.63</v>
+      </c>
+      <c r="CX9" s="1" t="n">
+        <v>592132.65</v>
+      </c>
+      <c r="CY9" s="1" t="n">
+        <v>3128.01</v>
+      </c>
+      <c r="CZ9" s="1" t="n">
+        <v>169802.78</v>
+      </c>
+      <c r="DA9" s="1" t="n">
+        <v>2202.77</v>
+      </c>
+      <c r="DB9" s="1" t="n">
+        <v>136087.63</v>
+      </c>
+      <c r="DC9" s="1" t="n">
+        <v>39606.44</v>
+      </c>
+      <c r="DD9" s="1" t="n">
+        <v>38180.75</v>
+      </c>
+      <c r="DE9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG9" s="1" t="n">
+        <v>896566.6</v>
+      </c>
+      <c r="DH9" s="1" t="n">
+        <v>521370.33</v>
+      </c>
+      <c r="DI9" s="1" t="n">
+        <v>68414.52</v>
+      </c>
+      <c r="DJ9" s="1" t="n">
+        <v>40665.66</v>
+      </c>
+      <c r="DK9" s="1" t="n">
+        <v>128829.89</v>
+      </c>
+      <c r="DL9" s="1" t="n">
+        <v>37150.39</v>
+      </c>
+      <c r="DM9" s="1" t="n">
+        <v>37202.85</v>
+      </c>
+      <c r="DN9" s="1" t="n">
+        <v>23583.76</v>
+      </c>
+      <c r="DO9" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="DP9" s="1" t="n">
+        <v>398.98</v>
+      </c>
+      <c r="DQ9" s="1" t="n">
+        <v>261173.8</v>
+      </c>
+      <c r="DR9" s="1" t="n">
+        <v>30736.73</v>
+      </c>
+      <c r="DS9" s="1" t="n">
+        <v>84712.66</v>
+      </c>
+      <c r="DT9" s="1" t="n">
+        <v>121507.76</v>
+      </c>
+      <c r="DV9" s="1" t="n">
+        <v>842251.23</v>
+      </c>
+      <c r="DW9" s="1" t="n">
+        <v>89898.81</v>
+      </c>
+      <c r="DX9" s="1" t="n">
+        <v>85117.66</v>
+      </c>
+      <c r="DY9" s="1" t="n">
+        <v>42945.96</v>
+      </c>
+      <c r="DZ9" s="1" t="n">
+        <v>43426.67</v>
+      </c>
+      <c r="EA9" s="1" t="n">
+        <v>55562.94</v>
+      </c>
+      <c r="EB9" s="1" t="n">
+        <v>7618.83</v>
+      </c>
+      <c r="EC9" s="1" t="n">
+        <v>46743.45</v>
+      </c>
+      <c r="ED9" s="1" t="n">
+        <v>7052.57</v>
+      </c>
+      <c r="EE9" s="1" t="n">
+        <v>50420.41</v>
+      </c>
+      <c r="EF9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG9" s="1" t="n">
+        <v>13215.93</v>
+      </c>
+      <c r="EH9" s="1" t="n">
+        <v>598.4400000000001</v>
+      </c>
+      <c r="EI9" s="1" t="n">
+        <v>50379.32</v>
+      </c>
+      <c r="EJ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK9" s="1" t="n">
+        <v>44261.09</v>
+      </c>
+      <c r="EL9" s="1" t="n">
+        <v>39088.77</v>
+      </c>
+      <c r="EM9" s="1" t="n">
+        <v>948.54</v>
+      </c>
+      <c r="EN9" s="1" t="n">
+        <v>10363.74</v>
+      </c>
+      <c r="EO9" s="1" t="n">
+        <v>4452959.04</v>
+      </c>
+      <c r="EP9" s="1" t="n">
+        <v>7703263.87</v>
+      </c>
+      <c r="EQ9" s="1" t="n">
+        <v>32176.37</v>
+      </c>
+      <c r="ER9" s="1" t="n">
+        <v>3641.22</v>
+      </c>
+      <c r="ES9" s="1" t="n">
+        <v>885.7</v>
+      </c>
+      <c r="ET9" s="1" t="n">
+        <v>513.52</v>
+      </c>
+      <c r="EU9" s="1" t="n">
+        <v>56603.23</v>
+      </c>
+      <c r="EV9" s="1" t="n">
+        <v>982.0599999999999</v>
+      </c>
+      <c r="EW9" s="1" t="n">
+        <v>108791.2</v>
+      </c>
+      <c r="EX9" s="1" t="n">
+        <v>152757.08</v>
+      </c>
+      <c r="EY9" s="1" t="n">
+        <v>2239.53</v>
+      </c>
+      <c r="EZ9" s="1" t="n">
+        <v>25854.3</v>
+      </c>
+      <c r="FB9" s="1" t="n">
+        <v>12107.04</v>
+      </c>
+      <c r="FC9" s="1" t="n">
+        <v>90820.23</v>
+      </c>
+      <c r="FD9" s="1" t="n">
+        <v>7667.83</v>
+      </c>
+      <c r="FE9" s="1" t="n">
+        <v>2328104.7</v>
+      </c>
+      <c r="FF9" s="1" t="n">
+        <v>8354.84</v>
+      </c>
+      <c r="FG9" s="1" t="n">
+        <v>49954.66</v>
+      </c>
+      <c r="FH9" s="1" t="n">
+        <v>36657.81</v>
+      </c>
+      <c r="FI9" s="1" t="n">
+        <v>305171.97</v>
+      </c>
+      <c r="FK9" s="1" t="n">
+        <v>144422.33</v>
+      </c>
+      <c r="FL9" s="1" t="n">
+        <v>23772.65</v>
+      </c>
+      <c r="FM9" s="1" t="n">
+        <v>58443.96</v>
+      </c>
+      <c r="FN9" s="1" t="n">
+        <v>20424.97</v>
+      </c>
+      <c r="FO9" s="1" t="n">
+        <v>4987.52</v>
+      </c>
+      <c r="FP9" s="1" t="n">
+        <v>40715.14</v>
+      </c>
+      <c r="FQ9" s="1" t="n">
+        <v>21993.3</v>
+      </c>
+      <c r="FR9" s="1" t="n">
+        <v>3530.15</v>
+      </c>
+      <c r="FS9" s="1" t="n">
+        <v>6825067.81</v>
+      </c>
+      <c r="FT9" s="1" t="n">
+        <v>2233.6</v>
+      </c>
+      <c r="FU9" s="1" t="n">
+        <v>40099.44</v>
+      </c>
+      <c r="FV9" s="1" t="n">
+        <v>49929.59</v>
+      </c>
+      <c r="FW9" s="1" t="n">
+        <v>77245.67</v>
+      </c>
+      <c r="FX9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" s="1" t="n">
+        <v>21594</v>
+      </c>
+      <c r="FZ9" s="1" t="n">
+        <v>677255.15</v>
+      </c>
+      <c r="GA9" s="1" t="n">
+        <v>3036.63</v>
+      </c>
+      <c r="GB9" s="1" t="n">
+        <v>1279.14</v>
+      </c>
+      <c r="GC9" s="1" t="n">
+        <v>106643.14</v>
+      </c>
+      <c r="GD9" s="1" t="n">
+        <v>2431.62</v>
+      </c>
+      <c r="GE9" s="1" t="n">
+        <v>102668.6</v>
+      </c>
+      <c r="GF9" s="1" t="n">
+        <v>60872.82</v>
+      </c>
+      <c r="GG9" s="1" t="n">
+        <v>397.92</v>
+      </c>
+      <c r="GH9" s="1" t="n">
+        <v>74876.31</v>
+      </c>
+      <c r="GI9" s="1" t="n">
+        <v>27816.72</v>
+      </c>
+      <c r="GJ9" s="1" t="n">
+        <v>22273.71</v>
+      </c>
+      <c r="GK9" s="1" t="n">
+        <v>591315.8100000001</v>
+      </c>
+      <c r="GL9" s="1" t="n">
+        <v>392.56</v>
+      </c>
+      <c r="GM9" s="1" t="n">
+        <v>4214.36</v>
+      </c>
+      <c r="GN9" s="1" t="n">
+        <v>15922.56</v>
+      </c>
+      <c r="GO9" s="1" t="n">
+        <v>76687.69</v>
+      </c>
+      <c r="GP9" s="1" t="n">
+        <v>7567.79</v>
+      </c>
+      <c r="GQ9" s="1" t="n">
+        <v>15197.23</v>
+      </c>
+      <c r="GR9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS9" s="1" t="n">
+        <v>4485.42</v>
+      </c>
+      <c r="GT9" s="1" t="n">
+        <v>453558.64</v>
+      </c>
+      <c r="GU9" s="1" t="n">
+        <v>1170.33</v>
+      </c>
+      <c r="GV9" s="1" t="n">
+        <v>38527.57</v>
+      </c>
+      <c r="GX9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY9" s="1" t="n">
+        <v>33094.47</v>
+      </c>
+      <c r="GZ9" s="1" t="n">
+        <v>540.77</v>
+      </c>
+      <c r="HA9" s="1" t="n">
+        <v>466.38</v>
+      </c>
+      <c r="HB9" s="1" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="HC9" s="1" t="n">
+        <v>1859.52</v>
+      </c>
+      <c r="HD9" s="1" t="n">
+        <v>5558.85</v>
+      </c>
+      <c r="HE9" s="1" t="n">
+        <v>40947.7</v>
+      </c>
+      <c r="HF9" s="1" t="n">
+        <v>1098.25</v>
+      </c>
+      <c r="HG9" s="1" t="n">
+        <v>121301.04</v>
+      </c>
+      <c r="HH9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI9" s="1" t="n">
+        <v>28093.23</v>
+      </c>
+      <c r="HJ9" s="1" t="n">
+        <v>9822.84</v>
+      </c>
+      <c r="HK9" s="1" t="n">
+        <v>277434.89</v>
+      </c>
+      <c r="HL9" s="1" t="n">
+        <v>154730.75</v>
+      </c>
+      <c r="HM9" s="1" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="HN9" s="1" t="n">
+        <v>67819.56</v>
+      </c>
+      <c r="HO9" s="1" t="n">
+        <v>11146.05</v>
+      </c>
+      <c r="HP9" s="1" t="n">
+        <v>12772.18</v>
+      </c>
+      <c r="HQ9" s="1" t="n">
+        <v>5702.48</v>
+      </c>
+      <c r="HR9" s="1" t="n">
+        <v>14830</v>
+      </c>
+      <c r="HS9" s="1" t="n">
+        <v>51060.83</v>
+      </c>
+      <c r="HT9" s="1" t="n">
+        <v>52767.51</v>
+      </c>
+      <c r="HU9" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="HV9" s="1" t="n">
+        <v>10477.56</v>
+      </c>
+      <c r="HW9" s="1" t="n">
+        <v>195797.76</v>
+      </c>
+      <c r="HX9" s="1" t="n">
+        <v>2636.41</v>
+      </c>
+      <c r="HY9" s="1" t="n">
+        <v>4708.65</v>
+      </c>
+      <c r="HZ9" s="1" t="n">
+        <v>2033.75</v>
+      </c>
+      <c r="IA9" s="1" t="n">
+        <v>24113.99</v>
+      </c>
+      <c r="IB9" s="1" t="n">
+        <v>25032.1</v>
+      </c>
+      <c r="IC9" s="1" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="ID9" s="1" t="n">
+        <v>21375.72</v>
+      </c>
+      <c r="IE9" s="1" t="n">
+        <v>133569.26</v>
+      </c>
+      <c r="IF9" s="1" t="n">
+        <v>7062.83</v>
+      </c>
+      <c r="IG9" s="1" t="n">
+        <v>811320.97</v>
+      </c>
+      <c r="IH9" s="1" t="n">
+        <v>328115.74</v>
+      </c>
+      <c r="II9" s="1" t="n">
+        <v>65292.18</v>
+      </c>
+      <c r="IJ9" s="1" t="n">
+        <v>258.61</v>
+      </c>
+      <c r="IK9" s="1" t="n">
+        <v>3144.15</v>
+      </c>
+      <c r="IL9" s="1" t="n">
+        <v>77929.00999999999</v>
+      </c>
+      <c r="IM9" s="1" t="n">
+        <v>1954.86</v>
+      </c>
+      <c r="IN9" s="1" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="IO9" s="1" t="n">
+        <v>2224.81</v>
+      </c>
+      <c r="IP9" s="1" t="n">
+        <v>698.25</v>
+      </c>
+      <c r="IQ9" s="1" t="n">
+        <v>14176.31</v>
+      </c>
+      <c r="IR9" s="1" t="n">
+        <v>1304.7</v>
+      </c>
+      <c r="IS9" s="1" t="n">
+        <v>982.76</v>
+      </c>
+      <c r="IT9" s="1" t="n">
+        <v>199319.88</v>
+      </c>
+      <c r="IU9" s="1" t="n">
+        <v>10084.75</v>
+      </c>
+      <c r="IV9" s="1" t="n">
+        <v>68.38</v>
+      </c>
+      <c r="IW9" s="1" t="n">
+        <v>11300.13</v>
+      </c>
+      <c r="IX9" s="1" t="n">
+        <v>49366.99</v>
+      </c>
+      <c r="IY9" s="1" t="n">
+        <v>9094.219999999999</v>
+      </c>
+      <c r="IZ9" s="1" t="n">
+        <v>1886.2</v>
+      </c>
+      <c r="JA9" s="1" t="n">
+        <v>21000.77</v>
+      </c>
+      <c r="JB9" s="1" t="n">
+        <v>788.4</v>
+      </c>
+      <c r="JC9" s="1" t="n">
+        <v>96079.14999999999</v>
+      </c>
+      <c r="JD9" s="1" t="n">
+        <v>10660.44</v>
+      </c>
+      <c r="JE9" s="1" t="n">
+        <v>512.2</v>
+      </c>
+      <c r="JF9" s="1" t="n">
+        <v>1264.96</v>
+      </c>
+      <c r="JG9" s="1" t="n">
+        <v>96129.35000000001</v>
+      </c>
+      <c r="JH9" s="1" t="n">
+        <v>74201.34</v>
+      </c>
+      <c r="JI9" s="1" t="n">
+        <v>60923.89</v>
+      </c>
+      <c r="JJ9" s="1" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="JK9" s="1" t="n">
+        <v>70020</v>
+      </c>
+      <c r="JM9" s="1" t="n">
+        <v>37760.83</v>
+      </c>
+      <c r="JN9" s="1" t="n">
+        <v>12451.02</v>
+      </c>
+      <c r="JO9" s="1" t="n">
+        <v>398.16</v>
+      </c>
+      <c r="JP9" s="1" t="n">
+        <v>1019.4</v>
+      </c>
+      <c r="JQ9" s="1" t="n">
+        <v>129979.29</v>
+      </c>
+      <c r="JR9" s="1" t="n">
+        <v>598.5</v>
+      </c>
+      <c r="JS9" s="1" t="n">
+        <v>209497.82</v>
+      </c>
+      <c r="JT9" s="1" t="n">
+        <v>6130.69</v>
+      </c>
+      <c r="JU9" s="1" t="n">
+        <v>33350.4</v>
+      </c>
+      <c r="JV9" s="1" t="n">
+        <v>2674.28</v>
+      </c>
+      <c r="JX9" s="1" t="n">
+        <v>42768.52</v>
+      </c>
+      <c r="JY9" s="1" t="n">
+        <v>83424.75999999999</v>
+      </c>
+      <c r="JZ9" s="1" t="n">
+        <v>705814.28</v>
+      </c>
+      <c r="KA9" s="1" t="n">
+        <v>200.75</v>
+      </c>
+      <c r="KB9" s="1" t="n">
+        <v>1446.11</v>
+      </c>
+      <c r="KC9" s="1" t="n">
+        <v>273519.01</v>
+      </c>
+      <c r="KD9" s="1" t="n">
+        <v>796.08</v>
+      </c>
+      <c r="KE9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="KF9" s="1" t="n">
+        <v>398.99</v>
+      </c>
+      <c r="KG9" s="1" t="n">
+        <v>19550.82</v>
+      </c>
+      <c r="KH9" s="1" t="n">
+        <v>14368.03</v>
+      </c>
+      <c r="KI9" s="1" t="n">
+        <v>11736.79</v>
+      </c>
+      <c r="KJ9" s="1" t="n">
+        <v>101876.27</v>
+      </c>
+      <c r="KK9" s="1" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="KM9" s="1" t="n">
+        <v>563.59</v>
+      </c>
+      <c r="KN9" s="1" t="n">
+        <v>334732.78</v>
+      </c>
+      <c r="KO9" s="1" t="n">
+        <v>150822.48</v>
+      </c>
+      <c r="KP9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KQ9" s="1" t="n">
+        <v>398.97</v>
+      </c>
+      <c r="KR9" s="1" t="n">
+        <v>642.73</v>
+      </c>
+      <c r="KS9" s="1" t="n">
+        <v>66677.64999999999</v>
+      </c>
+      <c r="KT9" s="1" t="n">
+        <v>909.28</v>
+      </c>
+      <c r="KU9" s="1" t="n">
+        <v>47741.27</v>
+      </c>
+      <c r="KV9" s="1" t="n">
+        <v>42805.58</v>
+      </c>
+      <c r="KW9" s="1" t="n">
+        <v>41654.61</v>
+      </c>
+      <c r="KX9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KY9" s="1" t="n">
+        <v>1426.74</v>
+      </c>
+      <c r="KZ9" s="1" t="n">
+        <v>244855.51</v>
+      </c>
+      <c r="LA9" s="1" t="n">
+        <v>148.84</v>
+      </c>
+      <c r="LB9" s="1" t="n">
+        <v>60724.21</v>
+      </c>
+      <c r="LC9" s="1" t="n">
+        <v>593.62</v>
+      </c>
+      <c r="LD9" s="1" t="n">
+        <v>321419.28</v>
+      </c>
+      <c r="LE9" s="1" t="n">
+        <v>1108.8</v>
+      </c>
+      <c r="LF9" s="1" t="n">
+        <v>398.98</v>
+      </c>
+      <c r="LG9" s="1" t="n">
+        <v>71201</v>
+      </c>
+      <c r="LI9" s="1" t="n">
+        <v>1462.72</v>
+      </c>
+      <c r="LJ9" s="1" t="n">
+        <v>29187.1</v>
+      </c>
+      <c r="LK9" s="1" t="n">
+        <v>1377.3</v>
+      </c>
+      <c r="LL9" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LO9" s="1" t="n">
+        <v>1790.79</v>
+      </c>
+      <c r="LP9" s="1" t="n">
+        <v>3858.96</v>
+      </c>
+      <c r="LQ9" s="1" t="n">
+        <v>610.86</v>
+      </c>
+      <c r="LR9" s="1" t="n">
+        <v>7553.14</v>
+      </c>
+      <c r="LS9" s="1" t="n">
+        <v>1661.84</v>
+      </c>
+      <c r="LT9" s="1" t="n">
+        <v>292973.63</v>
+      </c>
+      <c r="LU9" s="1" t="n">
+        <v>4114.96</v>
+      </c>
+      <c r="LV9" s="1" t="n">
+        <v>5704.55</v>
+      </c>
+      <c r="LW9" s="1" t="n">
+        <v>9336.200000000001</v>
+      </c>
+      <c r="LX9" s="1" t="n">
+        <v>8594.209999999999</v>
+      </c>
+      <c r="LY9" s="1" t="n">
+        <v>13097.57</v>
+      </c>
+      <c r="LZ9" s="1" t="n">
+        <v>140772.72</v>
+      </c>
+      <c r="MA9" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="MB9" s="1" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="MC9" s="1" t="n">
+        <v>221.42</v>
+      </c>
+      <c r="MD9" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="ME9" s="1" t="n">
+        <v>15024.59</v>
+      </c>
+      <c r="MF9" s="1" t="n">
+        <v>13974.49</v>
+      </c>
+      <c r="MG9" s="1" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="MH9" s="1" t="n">
+        <v>110605.15</v>
+      </c>
+      <c r="MI9" s="1" t="n">
+        <v>1229.78</v>
+      </c>
+      <c r="MJ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MK9" s="1" t="n">
+        <v>122650.18</v>
+      </c>
+      <c r="ML9" s="1" t="n">
+        <v>431.1</v>
+      </c>
+      <c r="MM9" s="1" t="n">
+        <v>1617.06</v>
+      </c>
+      <c r="MN9" s="1" t="n">
+        <v>10251.89</v>
+      </c>
+      <c r="MO9" s="1" t="n">
+        <v>598.4299999999999</v>
+      </c>
+      <c r="MP9" s="1" t="n">
+        <v>2992.38</v>
+      </c>
+      <c r="MQ9" s="1" t="n">
+        <v>6583.5</v>
+      </c>
+      <c r="MR9" s="1" t="n">
+        <v>1013.25</v>
+      </c>
+      <c r="MS9" s="1" t="n">
+        <v>1934.85</v>
+      </c>
+      <c r="MT9" s="1" t="n">
+        <v>12169.28</v>
+      </c>
+      <c r="MU9" s="1" t="n">
+        <v>7465.74</v>
+      </c>
+      <c r="MV9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MW9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MX9" s="1" t="n">
+        <v>1066.21</v>
+      </c>
+      <c r="MY9" s="1" t="n">
+        <v>19607.48</v>
+      </c>
+      <c r="MZ9" s="1" t="n">
+        <v>28689.27</v>
+      </c>
+      <c r="NA9" s="1" t="n">
+        <v>6772.63</v>
+      </c>
+      <c r="NB9" s="1" t="n">
+        <v>7627.76</v>
+      </c>
+      <c r="NC9" s="1" t="n">
+        <v>281.29</v>
+      </c>
+      <c r="ND9" s="1" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="NE9" s="1" t="n">
+        <v>1703.04</v>
+      </c>
+      <c r="NF9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NG9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NH9" s="1" t="n">
+        <v>25588.97</v>
+      </c>
+      <c r="PB9" s="1" t="n">
+        <v>5770.81</v>
+      </c>
+      <c r="PK9" s="1" t="n">
+        <v>536.9400000000001</v>
+      </c>
+      <c r="PV9" s="1" t="n">
+        <v>9976.110000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11964,7 +13044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW8"/>
+  <dimension ref="A1:BXW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12302,6 +13382,48 @@
       </c>
       <c r="M8" s="1" t="n">
         <v>22926.407217</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>585624367.65</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>90854782.42874999</v>
+      </c>
+      <c r="D9" s="1">
+        <f>AVERAGE(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>2040003.7908</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>5716728.1795</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>788791.9314</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1419182.8212</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>3363091.5582</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>112409.1611</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>11817.1122</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>2406.2268</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>1412.486274</v>
       </c>
     </row>
   </sheetData>
@@ -12315,7 +13437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW8"/>
+  <dimension ref="A1:BXW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15070,6 +16192,327 @@
         <v>0</v>
       </c>
       <c r="DB8" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>1322736.353759038</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>3150677.600265065</v>
+      </c>
+      <c r="D9" s="1">
+        <f>AVERAGE(C3:C9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>5096088.505715098</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>16105.7979364972</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>304145.8795130064</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>92494.5983818425</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>68704.33891542334</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>61212.248253846</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>5687.5048237182</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>91376.58485457049</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>3.753</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>99.94226</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>65.82769999999999</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>2207.6537468895</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>153.608</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="AE9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="1" t="n">
+        <v>76.58499999999999</v>
+      </c>
+      <c r="AM9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="1" t="n">
+        <v>615.59246138951</v>
+      </c>
+      <c r="BD9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="1" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="BJ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" s="1" t="n">
+        <v>31.3101198</v>
+      </c>
+      <c r="BN9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" s="1" t="n">
+        <v>19.9465900267</v>
+      </c>
+      <c r="CH9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" s="1" t="n">
+        <v>498.6660682342</v>
+      </c>
+      <c r="CN9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15084,7 +16527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW8"/>
+  <dimension ref="A1:BXW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15987,6 +17430,126 @@
       </c>
       <c r="AM8" s="1" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>15172757.32</v>
+      </c>
+      <c r="C9" s="1">
+        <f>AVERAGE(B3:B9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>650445.8</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1008683.37</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>87492.53</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1871487.73</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>156948.63</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>409374.4</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>77793.25</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>88210.81</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>108406.75</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>68086.77</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>24379.33</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>8228.08</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>1896.33</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>71971.36</v>
+      </c>
+      <c r="T9" s="1" t="n">
+        <v>4963.94</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>12183.68</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>3110.31</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>37102.74</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>16579.29</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>67337.59</v>
+      </c>
+      <c r="Z9" s="1" t="n">
+        <v>71892.07000000001</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>499.95</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>1340.89</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1" t="n">
+        <v>169770.7</v>
+      </c>
+      <c r="AE9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1" t="n">
+        <v>901.12</v>
+      </c>
+      <c r="AG9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="1" t="n">
+        <v>1417.14</v>
+      </c>
+      <c r="AI9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="1" t="n">
+        <v>477139.25</v>
+      </c>
+      <c r="AL9" s="1" t="n">
+        <v>56885.79</v>
+      </c>
+      <c r="AM9" s="1" t="n">
+        <v>1062.15</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>740341862.52</v>
+        <v>778022941.53</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,15 +481,15 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>585624367.65</v>
+        <v>588712981.67</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>USDT_THB</t>
+          <t>BTC_THB</t>
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>5096088.505715098</v>
+        <v>6665779.14768751</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>15172757.32</v>
+        <v>41785767.53</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>195029157.19</v>
+        <v>412272515.01</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,23 +518,23 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>90854782.42874999</v>
+        <v>114133133.64179</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BTC_THB</t>
+          <t>USDT_THB</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3150677.600265065</v>
+        <v>5253379.002108257</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>USDTTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>1871487.73</v>
+        <v>3090862.69</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>82741110.41</v>
+        <v>116329486.85</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>5716728.1795</v>
+        <v>14134587.1235</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1322736.353759038</v>
+        <v>1941521.276431996</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1008683.37</v>
+        <v>1182793.47</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>34553096.93</v>
+        <v>82022851.06999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VELOTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>3363091.5582</v>
+        <v>3692738.6925</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>XRP_THB</t>
+          <t>DOGE_THB</t>
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>304145.8795130064</v>
+        <v>744704.3419076545</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>BCHTHB</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>650445.8</v>
+        <v>698723.5600000001</v>
       </c>
     </row>
     <row r="6">
@@ -621,15 +621,15 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>13489238.17</v>
+        <v>52051403.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>VELOTHB</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>2040003.7908</v>
+        <v>2813582.4913</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -637,15 +637,15 @@
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>92494.5983818425</v>
+        <v>569677.9811667287</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>UNITHB</t>
+          <t>USDTTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>477139.25</v>
+        <v>662781.5</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW9"/>
+  <dimension ref="A1:BXW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13031,6 +13031,1086 @@
       </c>
       <c r="PV9" s="1" t="n">
         <v>9976.110000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>778022941.53</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>412272515.01</v>
+      </c>
+      <c r="D10" s="1">
+        <f>AVERAGE(C4:C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>116329486.85</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>82022851.06999999</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>27425398.96</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>52051403.15</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>12561598.79</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>11830135.2</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>18337424.89</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>16319729.43</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>7634114.07</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>17921270.85</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>30256411.23</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>794812.29</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>5691500.11</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>3015379.24</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>4188473.67</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>4482191.75</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>8252176.38</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>393006.2</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>13999284.43</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>560210.36</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>70798.11</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>1376061.56</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>6687434.37</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>4024602.31</v>
+      </c>
+      <c r="AD10" s="1" t="n">
+        <v>9307320.51</v>
+      </c>
+      <c r="AE10" s="1" t="n">
+        <v>1781131.34</v>
+      </c>
+      <c r="AF10" s="1" t="n">
+        <v>2421176.38</v>
+      </c>
+      <c r="AG10" s="1" t="n">
+        <v>622807.49</v>
+      </c>
+      <c r="AH10" s="1" t="n">
+        <v>5629380.67</v>
+      </c>
+      <c r="AI10" s="1" t="n">
+        <v>5303386.21</v>
+      </c>
+      <c r="AJ10" s="1" t="n">
+        <v>526633.0600000001</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>2477295.02</v>
+      </c>
+      <c r="AL10" s="1" t="n">
+        <v>2578321.98</v>
+      </c>
+      <c r="AN10" s="1" t="n">
+        <v>1364714.38</v>
+      </c>
+      <c r="AO10" s="1" t="n">
+        <v>454248.6</v>
+      </c>
+      <c r="AP10" s="1" t="n">
+        <v>992647.9399999999</v>
+      </c>
+      <c r="AQ10" s="1" t="n">
+        <v>2024172.29</v>
+      </c>
+      <c r="AR10" s="1" t="n">
+        <v>2090905.5</v>
+      </c>
+      <c r="AS10" s="1" t="n">
+        <v>339613.78</v>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>2443028.55</v>
+      </c>
+      <c r="AU10" s="1" t="n">
+        <v>1455164.18</v>
+      </c>
+      <c r="AV10" s="1" t="n">
+        <v>871350.4300000001</v>
+      </c>
+      <c r="AW10" s="1" t="n">
+        <v>1884560.01</v>
+      </c>
+      <c r="AX10" s="1" t="n">
+        <v>2592992.55</v>
+      </c>
+      <c r="AY10" s="1" t="n">
+        <v>324912.67</v>
+      </c>
+      <c r="AZ10" s="1" t="n">
+        <v>1959717.75</v>
+      </c>
+      <c r="BA10" s="1" t="n">
+        <v>549944.45</v>
+      </c>
+      <c r="BB10" s="1" t="n">
+        <v>170740.8</v>
+      </c>
+      <c r="BC10" s="1" t="n">
+        <v>1232642.77</v>
+      </c>
+      <c r="BD10" s="1" t="n">
+        <v>551091.28</v>
+      </c>
+      <c r="BE10" s="1" t="n">
+        <v>383826.74</v>
+      </c>
+      <c r="BF10" s="1" t="n">
+        <v>1348719.94</v>
+      </c>
+      <c r="BG10" s="1" t="n">
+        <v>48582.34</v>
+      </c>
+      <c r="BI10" s="1" t="n">
+        <v>13342.54</v>
+      </c>
+      <c r="BJ10" s="1" t="n">
+        <v>248882.2</v>
+      </c>
+      <c r="BK10" s="1" t="n">
+        <v>465182.66</v>
+      </c>
+      <c r="BL10" s="1" t="n">
+        <v>1929388.73</v>
+      </c>
+      <c r="BM10" s="1" t="n">
+        <v>302367.79</v>
+      </c>
+      <c r="BN10" s="1" t="n">
+        <v>739079.76</v>
+      </c>
+      <c r="BO10" s="1" t="n">
+        <v>232351.65</v>
+      </c>
+      <c r="BP10" s="1" t="n">
+        <v>574184.86</v>
+      </c>
+      <c r="BQ10" s="1" t="n">
+        <v>36447.18</v>
+      </c>
+      <c r="BS10" s="1" t="n">
+        <v>326531.37</v>
+      </c>
+      <c r="BT10" s="1" t="n">
+        <v>828933.7</v>
+      </c>
+      <c r="BU10" s="1" t="n">
+        <v>1889868.57</v>
+      </c>
+      <c r="BV10" s="1" t="n">
+        <v>1486264.98</v>
+      </c>
+      <c r="BW10" s="1" t="n">
+        <v>231778</v>
+      </c>
+      <c r="BX10" s="1" t="n">
+        <v>737.97</v>
+      </c>
+      <c r="BY10" s="1" t="n">
+        <v>547060.67</v>
+      </c>
+      <c r="BZ10" s="1" t="n">
+        <v>454534.59</v>
+      </c>
+      <c r="CA10" s="1" t="n">
+        <v>281873.07</v>
+      </c>
+      <c r="CB10" s="1" t="n">
+        <v>38972.21</v>
+      </c>
+      <c r="CC10" s="1" t="n">
+        <v>45077.46</v>
+      </c>
+      <c r="CD10" s="1" t="n">
+        <v>200192.23</v>
+      </c>
+      <c r="CE10" s="1" t="n">
+        <v>42065.08</v>
+      </c>
+      <c r="CF10" s="1" t="n">
+        <v>34915.91</v>
+      </c>
+      <c r="CG10" s="1" t="n">
+        <v>1422202.92</v>
+      </c>
+      <c r="CH10" s="1" t="n">
+        <v>55572.65</v>
+      </c>
+      <c r="CI10" s="1" t="n">
+        <v>43277.35</v>
+      </c>
+      <c r="CJ10" s="1" t="n">
+        <v>2115586.24</v>
+      </c>
+      <c r="CK10" s="1" t="n">
+        <v>14153.43</v>
+      </c>
+      <c r="CL10" s="1" t="n">
+        <v>166070.84</v>
+      </c>
+      <c r="CM10" s="1" t="n">
+        <v>8559.02</v>
+      </c>
+      <c r="CN10" s="1" t="n">
+        <v>28263.21</v>
+      </c>
+      <c r="CO10" s="1" t="n">
+        <v>118302.38</v>
+      </c>
+      <c r="CP10" s="1" t="n">
+        <v>4939981.63</v>
+      </c>
+      <c r="CQ10" s="1" t="n">
+        <v>8669.26</v>
+      </c>
+      <c r="CR10" s="1" t="n">
+        <v>36352.46</v>
+      </c>
+      <c r="CS10" s="1" t="n">
+        <v>141069.83</v>
+      </c>
+      <c r="CT10" s="1" t="n">
+        <v>29451.42</v>
+      </c>
+      <c r="CV10" s="1" t="n">
+        <v>230801.66</v>
+      </c>
+      <c r="CW10" s="1" t="n">
+        <v>10177223.85</v>
+      </c>
+      <c r="CX10" s="1" t="n">
+        <v>91158.25999999999</v>
+      </c>
+      <c r="CY10" s="1" t="n">
+        <v>3186.05</v>
+      </c>
+      <c r="CZ10" s="1" t="n">
+        <v>1725632.85</v>
+      </c>
+      <c r="DA10" s="1" t="n">
+        <v>11867.18</v>
+      </c>
+      <c r="DB10" s="1" t="n">
+        <v>77833.61</v>
+      </c>
+      <c r="DC10" s="1" t="n">
+        <v>56269.94</v>
+      </c>
+      <c r="DD10" s="1" t="n">
+        <v>77887.56</v>
+      </c>
+      <c r="DE10" s="1" t="n">
+        <v>4118.25</v>
+      </c>
+      <c r="DG10" s="1" t="n">
+        <v>4023606.92</v>
+      </c>
+      <c r="DH10" s="1" t="n">
+        <v>296244.51</v>
+      </c>
+      <c r="DI10" s="1" t="n">
+        <v>66524.41</v>
+      </c>
+      <c r="DJ10" s="1" t="n">
+        <v>168416.8</v>
+      </c>
+      <c r="DK10" s="1" t="n">
+        <v>50942.6</v>
+      </c>
+      <c r="DL10" s="1" t="n">
+        <v>37150.39</v>
+      </c>
+      <c r="DM10" s="1" t="n">
+        <v>120542.26</v>
+      </c>
+      <c r="DN10" s="1" t="n">
+        <v>40362.01</v>
+      </c>
+      <c r="DO10" s="1" t="n">
+        <v>49714.74</v>
+      </c>
+      <c r="DP10" s="1" t="n">
+        <v>51433.85</v>
+      </c>
+      <c r="DQ10" s="1" t="n">
+        <v>293880.44</v>
+      </c>
+      <c r="DR10" s="1" t="n">
+        <v>129841.59</v>
+      </c>
+      <c r="DS10" s="1" t="n">
+        <v>63776.48</v>
+      </c>
+      <c r="DT10" s="1" t="n">
+        <v>890353.5699999999</v>
+      </c>
+      <c r="DV10" s="1" t="n">
+        <v>86835.14</v>
+      </c>
+      <c r="DW10" s="1" t="n">
+        <v>251627.89</v>
+      </c>
+      <c r="DX10" s="1" t="n">
+        <v>263793.8</v>
+      </c>
+      <c r="DY10" s="1" t="n">
+        <v>171916.77</v>
+      </c>
+      <c r="DZ10" s="1" t="n">
+        <v>125724.6</v>
+      </c>
+      <c r="EA10" s="1" t="n">
+        <v>93101.94</v>
+      </c>
+      <c r="EB10" s="1" t="n">
+        <v>4166.58</v>
+      </c>
+      <c r="EC10" s="1" t="n">
+        <v>71728.00999999999</v>
+      </c>
+      <c r="ED10" s="1" t="n">
+        <v>23729.07</v>
+      </c>
+      <c r="EE10" s="1" t="n">
+        <v>24223.49</v>
+      </c>
+      <c r="EF10" s="1" t="n">
+        <v>1249.26</v>
+      </c>
+      <c r="EG10" s="1" t="n">
+        <v>43282.27</v>
+      </c>
+      <c r="EH10" s="1" t="n">
+        <v>5183.67</v>
+      </c>
+      <c r="EI10" s="1" t="n">
+        <v>25181.01</v>
+      </c>
+      <c r="EJ10" s="1" t="n">
+        <v>16658.15</v>
+      </c>
+      <c r="EK10" s="1" t="n">
+        <v>486208.65</v>
+      </c>
+      <c r="EL10" s="1" t="n">
+        <v>24056.76</v>
+      </c>
+      <c r="EM10" s="1" t="n">
+        <v>948.54</v>
+      </c>
+      <c r="EN10" s="1" t="n">
+        <v>18826.98</v>
+      </c>
+      <c r="EO10" s="1" t="n">
+        <v>1517698.62</v>
+      </c>
+      <c r="EP10" s="1" t="n">
+        <v>7661965.77</v>
+      </c>
+      <c r="EQ10" s="1" t="n">
+        <v>31760.73</v>
+      </c>
+      <c r="ER10" s="1" t="n">
+        <v>14908.82</v>
+      </c>
+      <c r="ES10" s="1" t="n">
+        <v>5690.06</v>
+      </c>
+      <c r="ET10" s="1" t="n">
+        <v>212.35</v>
+      </c>
+      <c r="EU10" s="1" t="n">
+        <v>77188.07000000001</v>
+      </c>
+      <c r="EV10" s="1" t="n">
+        <v>55688.38</v>
+      </c>
+      <c r="EW10" s="1" t="n">
+        <v>128358.17</v>
+      </c>
+      <c r="EX10" s="1" t="n">
+        <v>70097.86</v>
+      </c>
+      <c r="EY10" s="1" t="n">
+        <v>26472.65</v>
+      </c>
+      <c r="EZ10" s="1" t="n">
+        <v>1098.75</v>
+      </c>
+      <c r="FB10" s="1" t="n">
+        <v>12124.84</v>
+      </c>
+      <c r="FC10" s="1" t="n">
+        <v>199708.46</v>
+      </c>
+      <c r="FD10" s="1" t="n">
+        <v>149500.71</v>
+      </c>
+      <c r="FE10" s="1" t="n">
+        <v>1174014.69</v>
+      </c>
+      <c r="FF10" s="1" t="n">
+        <v>2627.58</v>
+      </c>
+      <c r="FG10" s="1" t="n">
+        <v>70174.82000000001</v>
+      </c>
+      <c r="FH10" s="1" t="n">
+        <v>15316.34</v>
+      </c>
+      <c r="FI10" s="1" t="n">
+        <v>71129.35000000001</v>
+      </c>
+      <c r="FK10" s="1" t="n">
+        <v>34374.26</v>
+      </c>
+      <c r="FL10" s="1" t="n">
+        <v>178609.18</v>
+      </c>
+      <c r="FM10" s="1" t="n">
+        <v>10918.17</v>
+      </c>
+      <c r="FN10" s="1" t="n">
+        <v>30755.42</v>
+      </c>
+      <c r="FO10" s="1" t="n">
+        <v>897.74</v>
+      </c>
+      <c r="FP10" s="1" t="n">
+        <v>464653.86</v>
+      </c>
+      <c r="FQ10" s="1" t="n">
+        <v>64156.16</v>
+      </c>
+      <c r="FR10" s="1" t="n">
+        <v>7824.94</v>
+      </c>
+      <c r="FS10" s="1" t="n">
+        <v>4211589.52</v>
+      </c>
+      <c r="FT10" s="1" t="n">
+        <v>2465.35</v>
+      </c>
+      <c r="FU10" s="1" t="n">
+        <v>94773.00999999999</v>
+      </c>
+      <c r="FV10" s="1" t="n">
+        <v>530629.38</v>
+      </c>
+      <c r="FW10" s="1" t="n">
+        <v>17648.13</v>
+      </c>
+      <c r="FX10" s="1" t="n">
+        <v>2695.77</v>
+      </c>
+      <c r="FY10" s="1" t="n">
+        <v>69611.41</v>
+      </c>
+      <c r="FZ10" s="1" t="n">
+        <v>240136.35</v>
+      </c>
+      <c r="GA10" s="1" t="n">
+        <v>87580.88</v>
+      </c>
+      <c r="GB10" s="1" t="n">
+        <v>38544.36</v>
+      </c>
+      <c r="GC10" s="1" t="n">
+        <v>74818.78</v>
+      </c>
+      <c r="GD10" s="1" t="n">
+        <v>26856.61</v>
+      </c>
+      <c r="GE10" s="1" t="n">
+        <v>165607.55</v>
+      </c>
+      <c r="GF10" s="1" t="n">
+        <v>24179.95</v>
+      </c>
+      <c r="GG10" s="1" t="n">
+        <v>3182.51</v>
+      </c>
+      <c r="GH10" s="1" t="n">
+        <v>140738.21</v>
+      </c>
+      <c r="GI10" s="1" t="n">
+        <v>60649.8</v>
+      </c>
+      <c r="GJ10" s="1" t="n">
+        <v>52745.05</v>
+      </c>
+      <c r="GK10" s="1" t="n">
+        <v>1732466.96</v>
+      </c>
+      <c r="GL10" s="1" t="n">
+        <v>171.14</v>
+      </c>
+      <c r="GM10" s="1" t="n">
+        <v>82104.28999999999</v>
+      </c>
+      <c r="GN10" s="1" t="n">
+        <v>2328.61</v>
+      </c>
+      <c r="GO10" s="1" t="n">
+        <v>247909.21</v>
+      </c>
+      <c r="GP10" s="1" t="n">
+        <v>22231.32</v>
+      </c>
+      <c r="GQ10" s="1" t="n">
+        <v>112304.64</v>
+      </c>
+      <c r="GR10" s="1" t="n">
+        <v>55536.83</v>
+      </c>
+      <c r="GS10" s="1" t="n">
+        <v>10157.27</v>
+      </c>
+      <c r="GT10" s="1" t="n">
+        <v>215685.81</v>
+      </c>
+      <c r="GU10" s="1" t="n">
+        <v>20747.33</v>
+      </c>
+      <c r="GV10" s="1" t="n">
+        <v>330771.1</v>
+      </c>
+      <c r="GX10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY10" s="1" t="n">
+        <v>125705.35</v>
+      </c>
+      <c r="GZ10" s="1" t="n">
+        <v>33297.77</v>
+      </c>
+      <c r="HA10" s="1" t="n">
+        <v>8673.379999999999</v>
+      </c>
+      <c r="HB10" s="1" t="n">
+        <v>129.34</v>
+      </c>
+      <c r="HC10" s="1" t="n">
+        <v>126002.38</v>
+      </c>
+      <c r="HD10" s="1" t="n">
+        <v>5351.08</v>
+      </c>
+      <c r="HE10" s="1" t="n">
+        <v>184455.37</v>
+      </c>
+      <c r="HF10" s="1" t="n">
+        <v>13375.37</v>
+      </c>
+      <c r="HG10" s="1" t="n">
+        <v>4007.42</v>
+      </c>
+      <c r="HH10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI10" s="1" t="n">
+        <v>3485.76</v>
+      </c>
+      <c r="HJ10" s="1" t="n">
+        <v>48642.46</v>
+      </c>
+      <c r="HK10" s="1" t="n">
+        <v>593799.98</v>
+      </c>
+      <c r="HL10" s="1" t="n">
+        <v>99003.85000000001</v>
+      </c>
+      <c r="HM10" s="1" t="n">
+        <v>67146.11</v>
+      </c>
+      <c r="HN10" s="1" t="n">
+        <v>16694.95</v>
+      </c>
+      <c r="HO10" s="1" t="n">
+        <v>50060.77</v>
+      </c>
+      <c r="HP10" s="1" t="n">
+        <v>9986.969999999999</v>
+      </c>
+      <c r="HQ10" s="1" t="n">
+        <v>274.45</v>
+      </c>
+      <c r="HR10" s="1" t="n">
+        <v>3307.38</v>
+      </c>
+      <c r="HS10" s="1" t="n">
+        <v>46192.52</v>
+      </c>
+      <c r="HT10" s="1" t="n">
+        <v>59654.86</v>
+      </c>
+      <c r="HU10" s="1" t="n">
+        <v>2035.27</v>
+      </c>
+      <c r="HV10" s="1" t="n">
+        <v>246830.03</v>
+      </c>
+      <c r="HW10" s="1" t="n">
+        <v>49499.51</v>
+      </c>
+      <c r="HX10" s="1" t="n">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="HY10" s="1" t="n">
+        <v>237626.6</v>
+      </c>
+      <c r="HZ10" s="1" t="n">
+        <v>185435.38</v>
+      </c>
+      <c r="IA10" s="1" t="n">
+        <v>29374.39</v>
+      </c>
+      <c r="IB10" s="1" t="n">
+        <v>46686.2</v>
+      </c>
+      <c r="IC10" s="1" t="n">
+        <v>1247.22</v>
+      </c>
+      <c r="ID10" s="1" t="n">
+        <v>28193.61</v>
+      </c>
+      <c r="IE10" s="1" t="n">
+        <v>4524.17</v>
+      </c>
+      <c r="IF10" s="1" t="n">
+        <v>68663.87</v>
+      </c>
+      <c r="IG10" s="1" t="n">
+        <v>601756.88</v>
+      </c>
+      <c r="IH10" s="1" t="n">
+        <v>140612.55</v>
+      </c>
+      <c r="II10" s="1" t="n">
+        <v>317688.1</v>
+      </c>
+      <c r="IJ10" s="1" t="n">
+        <v>24188.48</v>
+      </c>
+      <c r="IK10" s="1" t="n">
+        <v>44094.43</v>
+      </c>
+      <c r="IL10" s="1" t="n">
+        <v>126.69</v>
+      </c>
+      <c r="IM10" s="1" t="n">
+        <v>1954.86</v>
+      </c>
+      <c r="IN10" s="1" t="n">
+        <v>675.1799999999999</v>
+      </c>
+      <c r="IO10" s="1" t="n">
+        <v>2538.83</v>
+      </c>
+      <c r="IP10" s="1" t="n">
+        <v>794.6900000000001</v>
+      </c>
+      <c r="IQ10" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="IR10" s="1" t="n">
+        <v>878.34</v>
+      </c>
+      <c r="IS10" s="1" t="n">
+        <v>270.5</v>
+      </c>
+      <c r="IT10" s="1" t="n">
+        <v>93570.46000000001</v>
+      </c>
+      <c r="IU10" s="1" t="n">
+        <v>29406.73</v>
+      </c>
+      <c r="IV10" s="1" t="n">
+        <v>32344.35</v>
+      </c>
+      <c r="IW10" s="1" t="n">
+        <v>35579.85</v>
+      </c>
+      <c r="IX10" s="1" t="n">
+        <v>80979.95</v>
+      </c>
+      <c r="IY10" s="1" t="n">
+        <v>116051.07</v>
+      </c>
+      <c r="IZ10" s="1" t="n">
+        <v>529.24</v>
+      </c>
+      <c r="JA10" s="1" t="n">
+        <v>4987.49</v>
+      </c>
+      <c r="JB10" s="1" t="n">
+        <v>18446.3</v>
+      </c>
+      <c r="JC10" s="1" t="n">
+        <v>19272</v>
+      </c>
+      <c r="JD10" s="1" t="n">
+        <v>18871.69</v>
+      </c>
+      <c r="JE10" s="1" t="n">
+        <v>512.2</v>
+      </c>
+      <c r="JF10" s="1" t="n">
+        <v>18921.06</v>
+      </c>
+      <c r="JG10" s="1" t="n">
+        <v>30283.72</v>
+      </c>
+      <c r="JH10" s="1" t="n">
+        <v>801.1</v>
+      </c>
+      <c r="JI10" s="1" t="n">
+        <v>1368.13</v>
+      </c>
+      <c r="JJ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK10" s="1" t="n">
+        <v>16367.33</v>
+      </c>
+      <c r="JM10" s="1" t="n">
+        <v>37760.83</v>
+      </c>
+      <c r="JN10" s="1" t="n">
+        <v>9093.32</v>
+      </c>
+      <c r="JO10" s="1" t="n">
+        <v>398.16</v>
+      </c>
+      <c r="JP10" s="1" t="n">
+        <v>995.78</v>
+      </c>
+      <c r="JQ10" s="1" t="n">
+        <v>9934.549999999999</v>
+      </c>
+      <c r="JR10" s="1" t="n">
+        <v>121.63</v>
+      </c>
+      <c r="JS10" s="1" t="n">
+        <v>54679.55</v>
+      </c>
+      <c r="JT10" s="1" t="n">
+        <v>6130.69</v>
+      </c>
+      <c r="JU10" s="1" t="n">
+        <v>36747.81</v>
+      </c>
+      <c r="JV10" s="1" t="n">
+        <v>25036</v>
+      </c>
+      <c r="JX10" s="1" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="JY10" s="1" t="n">
+        <v>10651.58</v>
+      </c>
+      <c r="JZ10" s="1" t="n">
+        <v>1476204.72</v>
+      </c>
+      <c r="KA10" s="1" t="n">
+        <v>13585.48</v>
+      </c>
+      <c r="KB10" s="1" t="n">
+        <v>13543.23</v>
+      </c>
+      <c r="KC10" s="1" t="n">
+        <v>193143.68</v>
+      </c>
+      <c r="KD10" s="1" t="n">
+        <v>796.08</v>
+      </c>
+      <c r="KE10" s="1" t="n">
+        <v>325.69</v>
+      </c>
+      <c r="KF10" s="1" t="n">
+        <v>6194.83</v>
+      </c>
+      <c r="KG10" s="1" t="n">
+        <v>134374.23</v>
+      </c>
+      <c r="KH10" s="1" t="n">
+        <v>12192.29</v>
+      </c>
+      <c r="KI10" s="1" t="n">
+        <v>6051.38</v>
+      </c>
+      <c r="KJ10" s="1" t="n">
+        <v>25468.58</v>
+      </c>
+      <c r="KK10" s="1" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="KM10" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="KN10" s="1" t="n">
+        <v>52119.48</v>
+      </c>
+      <c r="KO10" s="1" t="n">
+        <v>591428.76</v>
+      </c>
+      <c r="KP10" s="1" t="n">
+        <v>47916.02</v>
+      </c>
+      <c r="KQ10" s="1" t="n">
+        <v>398.97</v>
+      </c>
+      <c r="KR10" s="1" t="n">
+        <v>85.26000000000001</v>
+      </c>
+      <c r="KS10" s="1" t="n">
+        <v>38247.34</v>
+      </c>
+      <c r="KT10" s="1" t="n">
+        <v>909.28</v>
+      </c>
+      <c r="KU10" s="1" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="KV10" s="1" t="n">
+        <v>153.88</v>
+      </c>
+      <c r="KW10" s="1" t="n">
+        <v>9755.049999999999</v>
+      </c>
+      <c r="KX10" s="1" t="n">
+        <v>1183.48</v>
+      </c>
+      <c r="KY10" s="1" t="n">
+        <v>3736.1</v>
+      </c>
+      <c r="KZ10" s="1" t="n">
+        <v>10854.17</v>
+      </c>
+      <c r="LA10" s="1" t="n">
+        <v>37788.26</v>
+      </c>
+      <c r="LB10" s="1" t="n">
+        <v>5159.37</v>
+      </c>
+      <c r="LC10" s="1" t="n">
+        <v>593.62</v>
+      </c>
+      <c r="LD10" s="1" t="n">
+        <v>10889.02</v>
+      </c>
+      <c r="LE10" s="1" t="n">
+        <v>2613.4</v>
+      </c>
+      <c r="LF10" s="1" t="n">
+        <v>4843.9</v>
+      </c>
+      <c r="LG10" s="1" t="n">
+        <v>16922.41</v>
+      </c>
+      <c r="LI10" s="1" t="n">
+        <v>43331.1</v>
+      </c>
+      <c r="LJ10" s="1" t="n">
+        <v>1188.69</v>
+      </c>
+      <c r="LK10" s="1" t="n">
+        <v>2624.36</v>
+      </c>
+      <c r="LL10" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LO10" s="1" t="n">
+        <v>1790.79</v>
+      </c>
+      <c r="LP10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LQ10" s="1" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="LR10" s="1" t="n">
+        <v>493.34</v>
+      </c>
+      <c r="LS10" s="1" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="LT10" s="1" t="n">
+        <v>207815.72</v>
+      </c>
+      <c r="LU10" s="1" t="n">
+        <v>4114.96</v>
+      </c>
+      <c r="LV10" s="1" t="n">
+        <v>118177.72</v>
+      </c>
+      <c r="LW10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LX10" s="1" t="n">
+        <v>10570.77</v>
+      </c>
+      <c r="LY10" s="1" t="n">
+        <v>24858.99</v>
+      </c>
+      <c r="LZ10" s="1" t="n">
+        <v>20994.8</v>
+      </c>
+      <c r="MA10" s="1" t="n">
+        <v>307.05</v>
+      </c>
+      <c r="MB10" s="1" t="n">
+        <v>274.79</v>
+      </c>
+      <c r="MC10" s="1" t="n">
+        <v>6029.91</v>
+      </c>
+      <c r="MD10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ME10" s="1" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="MF10" s="1" t="n">
+        <v>1697.47</v>
+      </c>
+      <c r="MG10" s="1" t="n">
+        <v>39900.24</v>
+      </c>
+      <c r="MH10" s="1" t="n">
+        <v>14805.17</v>
+      </c>
+      <c r="MI10" s="1" t="n">
+        <v>1551</v>
+      </c>
+      <c r="MJ10" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="MK10" s="1" t="n">
+        <v>122650.18</v>
+      </c>
+      <c r="ML10" s="1" t="n">
+        <v>5225.44</v>
+      </c>
+      <c r="MM10" s="1" t="n">
+        <v>3911.31</v>
+      </c>
+      <c r="MN10" s="1" t="n">
+        <v>10309.63</v>
+      </c>
+      <c r="MO10" s="1" t="n">
+        <v>598.4299999999999</v>
+      </c>
+      <c r="MP10" s="1" t="n">
+        <v>2992.38</v>
+      </c>
+      <c r="MQ10" s="1" t="n">
+        <v>225.71</v>
+      </c>
+      <c r="MR10" s="1" t="n">
+        <v>577.62</v>
+      </c>
+      <c r="MS10" s="1" t="n">
+        <v>5258.32</v>
+      </c>
+      <c r="MT10" s="1" t="n">
+        <v>6060.56</v>
+      </c>
+      <c r="MU10" s="1" t="n">
+        <v>10443.48</v>
+      </c>
+      <c r="MV10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MW10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MX10" s="1" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="MY10" s="1" t="n">
+        <v>11516.07</v>
+      </c>
+      <c r="MZ10" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="NA10" s="1" t="n">
+        <v>4036.24</v>
+      </c>
+      <c r="NB10" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="NC10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ND10" s="1" t="n">
+        <v>1633.71</v>
+      </c>
+      <c r="NE10" s="1" t="n">
+        <v>455.42</v>
+      </c>
+      <c r="NF10" s="1" t="n">
+        <v>34103.78</v>
+      </c>
+      <c r="NG10" s="1" t="n">
+        <v>735.2</v>
+      </c>
+      <c r="NH10" s="1" t="n">
+        <v>13056.48</v>
+      </c>
+      <c r="PB10" s="1" t="n">
+        <v>5539.52</v>
+      </c>
+      <c r="PK10" s="1" t="n">
+        <v>262.85</v>
+      </c>
+      <c r="PV10" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -13044,7 +14124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW9"/>
+  <dimension ref="A1:BXW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13424,6 +14504,48 @@
       </c>
       <c r="M9" s="1" t="n">
         <v>1412.486274</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>588712981.67</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>114133133.64179</v>
+      </c>
+      <c r="D10" s="1">
+        <f>AVERAGE(C4:C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>3692738.6925</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>14134587.1235</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>2605491.8937</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>1977974.6502</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>2813582.4913</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>121509.1449</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>14907.2051</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>2406.2268</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>11235.909921</v>
       </c>
     </row>
   </sheetData>
@@ -13437,7 +14559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW9"/>
+  <dimension ref="A1:BXW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16513,6 +17635,327 @@
         <v>0</v>
       </c>
       <c r="DB9" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>1941521.276431996</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>6665779.14768751</v>
+      </c>
+      <c r="D10" s="1">
+        <f>AVERAGE(C4:C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>5253379.002108257</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>4515.7040067605</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>292803.0591076134</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>569677.9811667287</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>744704.3419076545</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>67819.4837002422</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>1977.1985313597</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>15319.3304135816</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>3.37302</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>1027.1541365276</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>848.7284931237</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="1" t="n">
+        <v>58.842296</v>
+      </c>
+      <c r="AV10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="1" t="n">
+        <v>315.67734</v>
+      </c>
+      <c r="BD10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" s="1" t="n">
+        <v>174.33321365</v>
+      </c>
+      <c r="BS10" s="1" t="n">
+        <v>356.7492</v>
+      </c>
+      <c r="BT10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" s="1" t="n">
+        <v>19.296</v>
+      </c>
+      <c r="CA10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" s="1" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="CE10" s="1" t="n">
+        <v>149.8685938178</v>
+      </c>
+      <c r="CF10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" s="1" t="n">
+        <v>1009.5493619733</v>
+      </c>
+      <c r="CH10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16527,7 +17970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW9"/>
+  <dimension ref="A1:BXW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17550,6 +18993,126 @@
       </c>
       <c r="AM9" s="1" t="n">
         <v>1062.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>41785767.53</v>
+      </c>
+      <c r="C10" s="1">
+        <f>AVERAGE(B4:B10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>3090862.69</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1182793.47</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>239144.91</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>698723.5600000001</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>662781.5</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>81892.77</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>130081.91</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>47122.71</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>54092.71</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>73371.60000000001</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>44324.67</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>33957.13</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>42660.23</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>37184.1</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>53393.16</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>17485.89</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>2400.15</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>2794.91</v>
+      </c>
+      <c r="W10" s="1" t="n">
+        <v>36417.12</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>18650.13</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>47149.67</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>502.5</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD10" s="1" t="n">
+        <v>150752.35</v>
+      </c>
+      <c r="AE10" s="1" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="AF10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="1" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="AH10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="1" t="n">
+        <v>3044.71</v>
+      </c>
+      <c r="AJ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>94492.35000000001</v>
+      </c>
+      <c r="AL10" s="1" t="n">
+        <v>14899.69</v>
+      </c>
+      <c r="AM10" s="1" t="n">
+        <v>25625.6</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>778022941.53</v>
+        <v>577284182.33</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>588712981.67</v>
+        <v>481627457.82</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>6665779.14768751</v>
+        <v>8407675.470363926</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>41785767.53</v>
+        <v>17934575.5</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>412272515.01</v>
+        <v>264644621.31</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>114133133.64179</v>
+        <v>58735576.22076</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>5253379.002108257</v>
+        <v>4178427.654207562</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>3090862.69</v>
+        <v>2236963.79</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>116329486.85</v>
+        <v>98991058.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,15 +555,15 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>14134587.1235</v>
+        <v>5029439.4503</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ETH_THB</t>
+          <t>SOL_THB</t>
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1941521.276431996</v>
+        <v>4095795.982163961</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1182793.47</v>
+        <v>1022680.03</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>82022851.06999999</v>
+        <v>56976918.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>SOLTHB</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>3692738.6925</v>
+        <v>4682507.5249</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DOGE_THB</t>
+          <t>ETH_THB</t>
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>744704.3419076545</v>
+        <v>2236512.42196813</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>BCHTHB</t>
+          <t>USDTTHB</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>698723.5600000001</v>
+        <v>342634.47</v>
       </c>
     </row>
     <row r="6">
@@ -617,11 +617,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_DOGE</t>
+          <t>THB_NEAR</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>52051403.15</v>
+        <v>51248012.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,23 +629,23 @@
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>2813582.4913</v>
+        <v>2664755.3577</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SOL_THB</t>
+          <t>XRP_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>569677.9811667287</v>
+        <v>381427.4185812122</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>USDTTHB</t>
+          <t>XLMTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>662781.5</v>
+        <v>287134.3</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW10"/>
+  <dimension ref="A1:BXW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14111,6 +14111,1086 @@
       </c>
       <c r="PV10" s="1" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>577284182.33</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>264644621.31</v>
+      </c>
+      <c r="D11" s="1">
+        <f>AVERAGE(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>98991058.05</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>56976918.1</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>15880061.19</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>18611629.83</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>8520369.02</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>7925688.42</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>12208885.66</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>8615773.23</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>6250871.63</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>51248012.36</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>18396877.25</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>208254.22</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>3844939.56</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>2061204.11</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>2800039.79</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>5995566.85</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>7819580.48</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>348429.39</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>6190906.5</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>357105.7</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>244786.02</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>379088.6</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>3486419.03</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>1695241.09</v>
+      </c>
+      <c r="AD11" s="1" t="n">
+        <v>6163895.39</v>
+      </c>
+      <c r="AE11" s="1" t="n">
+        <v>1764387.41</v>
+      </c>
+      <c r="AF11" s="1" t="n">
+        <v>1733145.18</v>
+      </c>
+      <c r="AG11" s="1" t="n">
+        <v>1080432.28</v>
+      </c>
+      <c r="AH11" s="1" t="n">
+        <v>1842873.59</v>
+      </c>
+      <c r="AI11" s="1" t="n">
+        <v>3955576.38</v>
+      </c>
+      <c r="AJ11" s="1" t="n">
+        <v>554444.1899999999</v>
+      </c>
+      <c r="AK11" s="1" t="n">
+        <v>3414621.44</v>
+      </c>
+      <c r="AL11" s="1" t="n">
+        <v>3865973.28</v>
+      </c>
+      <c r="AN11" s="1" t="n">
+        <v>2457335.93</v>
+      </c>
+      <c r="AO11" s="1" t="n">
+        <v>277250.28</v>
+      </c>
+      <c r="AP11" s="1" t="n">
+        <v>421367.8</v>
+      </c>
+      <c r="AQ11" s="1" t="n">
+        <v>1981593.13</v>
+      </c>
+      <c r="AR11" s="1" t="n">
+        <v>2283577.08</v>
+      </c>
+      <c r="AS11" s="1" t="n">
+        <v>90752.57000000001</v>
+      </c>
+      <c r="AT11" s="1" t="n">
+        <v>1666416.82</v>
+      </c>
+      <c r="AU11" s="1" t="n">
+        <v>1280347.25</v>
+      </c>
+      <c r="AV11" s="1" t="n">
+        <v>3122799.27</v>
+      </c>
+      <c r="AW11" s="1" t="n">
+        <v>944216.5699999999</v>
+      </c>
+      <c r="AX11" s="1" t="n">
+        <v>759326.65</v>
+      </c>
+      <c r="AY11" s="1" t="n">
+        <v>352497.93</v>
+      </c>
+      <c r="AZ11" s="1" t="n">
+        <v>1234943.81</v>
+      </c>
+      <c r="BA11" s="1" t="n">
+        <v>659778.5699999999</v>
+      </c>
+      <c r="BB11" s="1" t="n">
+        <v>51660.41</v>
+      </c>
+      <c r="BC11" s="1" t="n">
+        <v>4671943.66</v>
+      </c>
+      <c r="BD11" s="1" t="n">
+        <v>309214.94</v>
+      </c>
+      <c r="BE11" s="1" t="n">
+        <v>314887.02</v>
+      </c>
+      <c r="BF11" s="1" t="n">
+        <v>2312800.69</v>
+      </c>
+      <c r="BG11" s="1" t="n">
+        <v>3336.09</v>
+      </c>
+      <c r="BI11" s="1" t="n">
+        <v>30539.87</v>
+      </c>
+      <c r="BJ11" s="1" t="n">
+        <v>96440.56</v>
+      </c>
+      <c r="BK11" s="1" t="n">
+        <v>306281.05</v>
+      </c>
+      <c r="BL11" s="1" t="n">
+        <v>40624.75</v>
+      </c>
+      <c r="BM11" s="1" t="n">
+        <v>361926.84</v>
+      </c>
+      <c r="BN11" s="1" t="n">
+        <v>1113151.76</v>
+      </c>
+      <c r="BO11" s="1" t="n">
+        <v>112175.1</v>
+      </c>
+      <c r="BP11" s="1" t="n">
+        <v>360959.47</v>
+      </c>
+      <c r="BQ11" s="1" t="n">
+        <v>1802.7</v>
+      </c>
+      <c r="BS11" s="1" t="n">
+        <v>283494.65</v>
+      </c>
+      <c r="BT11" s="1" t="n">
+        <v>295287.82</v>
+      </c>
+      <c r="BU11" s="1" t="n">
+        <v>554083.52</v>
+      </c>
+      <c r="BV11" s="1" t="n">
+        <v>1712972.34</v>
+      </c>
+      <c r="BW11" s="1" t="n">
+        <v>35852.33</v>
+      </c>
+      <c r="BX11" s="1" t="n">
+        <v>737.97</v>
+      </c>
+      <c r="BY11" s="1" t="n">
+        <v>716213.8100000001</v>
+      </c>
+      <c r="BZ11" s="1" t="n">
+        <v>46408.6</v>
+      </c>
+      <c r="CA11" s="1" t="n">
+        <v>295333.6</v>
+      </c>
+      <c r="CB11" s="1" t="n">
+        <v>5672.66</v>
+      </c>
+      <c r="CC11" s="1" t="n">
+        <v>70296.52</v>
+      </c>
+      <c r="CD11" s="1" t="n">
+        <v>630494.39</v>
+      </c>
+      <c r="CE11" s="1" t="n">
+        <v>1198778.47</v>
+      </c>
+      <c r="CF11" s="1" t="n">
+        <v>30457.83</v>
+      </c>
+      <c r="CG11" s="1" t="n">
+        <v>435250.7</v>
+      </c>
+      <c r="CH11" s="1" t="n">
+        <v>35912.73</v>
+      </c>
+      <c r="CI11" s="1" t="n">
+        <v>43277.35</v>
+      </c>
+      <c r="CJ11" s="1" t="n">
+        <v>10317073.41</v>
+      </c>
+      <c r="CK11" s="1" t="n">
+        <v>63244.83</v>
+      </c>
+      <c r="CL11" s="1" t="n">
+        <v>105406.84</v>
+      </c>
+      <c r="CM11" s="1" t="n">
+        <v>27622.75</v>
+      </c>
+      <c r="CN11" s="1" t="n">
+        <v>326017.47</v>
+      </c>
+      <c r="CO11" s="1" t="n">
+        <v>330644.04</v>
+      </c>
+      <c r="CP11" s="1" t="n">
+        <v>1909355.11</v>
+      </c>
+      <c r="CQ11" s="1" t="n">
+        <v>210789.71</v>
+      </c>
+      <c r="CR11" s="1" t="n">
+        <v>36219.64</v>
+      </c>
+      <c r="CS11" s="1" t="n">
+        <v>651837.95</v>
+      </c>
+      <c r="CT11" s="1" t="n">
+        <v>3001.54</v>
+      </c>
+      <c r="CV11" s="1" t="n">
+        <v>86176.19</v>
+      </c>
+      <c r="CW11" s="1" t="n">
+        <v>5187594.07</v>
+      </c>
+      <c r="CX11" s="1" t="n">
+        <v>143977.96</v>
+      </c>
+      <c r="CY11" s="1" t="n">
+        <v>5632.01</v>
+      </c>
+      <c r="CZ11" s="1" t="n">
+        <v>503803.15</v>
+      </c>
+      <c r="DA11" s="1" t="n">
+        <v>1515.15</v>
+      </c>
+      <c r="DB11" s="1" t="n">
+        <v>135108.43</v>
+      </c>
+      <c r="DC11" s="1" t="n">
+        <v>311958.96</v>
+      </c>
+      <c r="DD11" s="1" t="n">
+        <v>42195.08</v>
+      </c>
+      <c r="DE11" s="1" t="n">
+        <v>36684.53</v>
+      </c>
+      <c r="DG11" s="1" t="n">
+        <v>1432853.45</v>
+      </c>
+      <c r="DH11" s="1" t="n">
+        <v>374266.94</v>
+      </c>
+      <c r="DI11" s="1" t="n">
+        <v>56645.04</v>
+      </c>
+      <c r="DJ11" s="1" t="n">
+        <v>9722.07</v>
+      </c>
+      <c r="DK11" s="1" t="n">
+        <v>54146.59</v>
+      </c>
+      <c r="DL11" s="1" t="n">
+        <v>649.8200000000001</v>
+      </c>
+      <c r="DM11" s="1" t="n">
+        <v>120418.18</v>
+      </c>
+      <c r="DN11" s="1" t="n">
+        <v>104373.47</v>
+      </c>
+      <c r="DO11" s="1" t="n">
+        <v>554.17</v>
+      </c>
+      <c r="DP11" s="1" t="n">
+        <v>51433.85</v>
+      </c>
+      <c r="DQ11" s="1" t="n">
+        <v>264195.08</v>
+      </c>
+      <c r="DR11" s="1" t="n">
+        <v>397545.62</v>
+      </c>
+      <c r="DS11" s="1" t="n">
+        <v>411646.89</v>
+      </c>
+      <c r="DT11" s="1" t="n">
+        <v>17576.5</v>
+      </c>
+      <c r="DV11" s="1" t="n">
+        <v>319535.58</v>
+      </c>
+      <c r="DW11" s="1" t="n">
+        <v>10067.38</v>
+      </c>
+      <c r="DX11" s="1" t="n">
+        <v>454921.48</v>
+      </c>
+      <c r="DY11" s="1" t="n">
+        <v>11464.67</v>
+      </c>
+      <c r="DZ11" s="1" t="n">
+        <v>114380.63</v>
+      </c>
+      <c r="EA11" s="1" t="n">
+        <v>3365.48</v>
+      </c>
+      <c r="EB11" s="1" t="n">
+        <v>32336.86</v>
+      </c>
+      <c r="EC11" s="1" t="n">
+        <v>42601.52</v>
+      </c>
+      <c r="ED11" s="1" t="n">
+        <v>23685.21</v>
+      </c>
+      <c r="EE11" s="1" t="n">
+        <v>13229.48</v>
+      </c>
+      <c r="EF11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" s="1" t="n">
+        <v>1202.62</v>
+      </c>
+      <c r="EH11" s="1" t="n">
+        <v>1440111.56</v>
+      </c>
+      <c r="EI11" s="1" t="n">
+        <v>110626.32</v>
+      </c>
+      <c r="EJ11" s="1" t="n">
+        <v>13501.83</v>
+      </c>
+      <c r="EK11" s="1" t="n">
+        <v>176783.78</v>
+      </c>
+      <c r="EL11" s="1" t="n">
+        <v>24056.76</v>
+      </c>
+      <c r="EM11" s="1" t="n">
+        <v>948.54</v>
+      </c>
+      <c r="EN11" s="1" t="n">
+        <v>7815.71</v>
+      </c>
+      <c r="EO11" s="1" t="n">
+        <v>1254788.59</v>
+      </c>
+      <c r="EP11" s="1" t="n">
+        <v>1275201.94</v>
+      </c>
+      <c r="EQ11" s="1" t="n">
+        <v>133.15</v>
+      </c>
+      <c r="ER11" s="1" t="n">
+        <v>12944.13</v>
+      </c>
+      <c r="ES11" s="1" t="n">
+        <v>146035.31</v>
+      </c>
+      <c r="ET11" s="1" t="n">
+        <v>20560.59</v>
+      </c>
+      <c r="EU11" s="1" t="n">
+        <v>136017.7</v>
+      </c>
+      <c r="EV11" s="1" t="n">
+        <v>28496.09</v>
+      </c>
+      <c r="EW11" s="1" t="n">
+        <v>168512.1</v>
+      </c>
+      <c r="EX11" s="1" t="n">
+        <v>259773.88</v>
+      </c>
+      <c r="EY11" s="1" t="n">
+        <v>2407.49</v>
+      </c>
+      <c r="EZ11" s="1" t="n">
+        <v>46577.32</v>
+      </c>
+      <c r="FB11" s="1" t="n">
+        <v>150.59</v>
+      </c>
+      <c r="FC11" s="1" t="n">
+        <v>120018.89</v>
+      </c>
+      <c r="FD11" s="1" t="n">
+        <v>191940.29</v>
+      </c>
+      <c r="FE11" s="1" t="n">
+        <v>1475786.29</v>
+      </c>
+      <c r="FF11" s="1" t="n">
+        <v>12626.89</v>
+      </c>
+      <c r="FG11" s="1" t="n">
+        <v>252634.76</v>
+      </c>
+      <c r="FH11" s="1" t="n">
+        <v>5988.57</v>
+      </c>
+      <c r="FI11" s="1" t="n">
+        <v>88838.22</v>
+      </c>
+      <c r="FK11" s="1" t="n">
+        <v>66918.78999999999</v>
+      </c>
+      <c r="FL11" s="1" t="n">
+        <v>61521.51</v>
+      </c>
+      <c r="FM11" s="1" t="n">
+        <v>143557.2</v>
+      </c>
+      <c r="FN11" s="1" t="n">
+        <v>29374.07</v>
+      </c>
+      <c r="FO11" s="1" t="n">
+        <v>199.48</v>
+      </c>
+      <c r="FP11" s="1" t="n">
+        <v>965.67</v>
+      </c>
+      <c r="FQ11" s="1" t="n">
+        <v>21653.59</v>
+      </c>
+      <c r="FR11" s="1" t="n">
+        <v>30557.4</v>
+      </c>
+      <c r="FS11" s="1" t="n">
+        <v>7816972.79</v>
+      </c>
+      <c r="FT11" s="1" t="n">
+        <v>61868.84</v>
+      </c>
+      <c r="FU11" s="1" t="n">
+        <v>6580.85</v>
+      </c>
+      <c r="FV11" s="1" t="n">
+        <v>1076352.67</v>
+      </c>
+      <c r="FW11" s="1" t="n">
+        <v>16294.58</v>
+      </c>
+      <c r="FX11" s="1" t="n">
+        <v>69316.91</v>
+      </c>
+      <c r="FY11" s="1" t="n">
+        <v>30820.89</v>
+      </c>
+      <c r="FZ11" s="1" t="n">
+        <v>72895.63</v>
+      </c>
+      <c r="GA11" s="1" t="n">
+        <v>10636.71</v>
+      </c>
+      <c r="GB11" s="1" t="n">
+        <v>23608.3</v>
+      </c>
+      <c r="GC11" s="1" t="n">
+        <v>74660.21000000001</v>
+      </c>
+      <c r="GD11" s="1" t="n">
+        <v>32471.75</v>
+      </c>
+      <c r="GE11" s="1" t="n">
+        <v>64694.49</v>
+      </c>
+      <c r="GF11" s="1" t="n">
+        <v>20502.21</v>
+      </c>
+      <c r="GG11" s="1" t="n">
+        <v>530.25</v>
+      </c>
+      <c r="GH11" s="1" t="n">
+        <v>60032.46</v>
+      </c>
+      <c r="GI11" s="1" t="n">
+        <v>32568.61</v>
+      </c>
+      <c r="GJ11" s="1" t="n">
+        <v>1382.81</v>
+      </c>
+      <c r="GK11" s="1" t="n">
+        <v>431774.72</v>
+      </c>
+      <c r="GL11" s="1" t="n">
+        <v>3016.47</v>
+      </c>
+      <c r="GM11" s="1" t="n">
+        <v>75300.92</v>
+      </c>
+      <c r="GN11" s="1" t="n">
+        <v>1002.91</v>
+      </c>
+      <c r="GO11" s="1" t="n">
+        <v>74289.19</v>
+      </c>
+      <c r="GP11" s="1" t="n">
+        <v>7502.24</v>
+      </c>
+      <c r="GQ11" s="1" t="n">
+        <v>115342.34</v>
+      </c>
+      <c r="GR11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="GS11" s="1" t="n">
+        <v>1845.73</v>
+      </c>
+      <c r="GT11" s="1" t="n">
+        <v>206059.08</v>
+      </c>
+      <c r="GU11" s="1" t="n">
+        <v>7203.02</v>
+      </c>
+      <c r="GV11" s="1" t="n">
+        <v>157431.26</v>
+      </c>
+      <c r="GX11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY11" s="1" t="n">
+        <v>497.12</v>
+      </c>
+      <c r="GZ11" s="1" t="n">
+        <v>11330.98</v>
+      </c>
+      <c r="HA11" s="1" t="n">
+        <v>8673.379999999999</v>
+      </c>
+      <c r="HB11" s="1" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="HC11" s="1" t="n">
+        <v>43368.38</v>
+      </c>
+      <c r="HD11" s="1" t="n">
+        <v>41429.39</v>
+      </c>
+      <c r="HE11" s="1" t="n">
+        <v>56877.89</v>
+      </c>
+      <c r="HF11" s="1" t="n">
+        <v>4576.65</v>
+      </c>
+      <c r="HG11" s="1" t="n">
+        <v>66652.23</v>
+      </c>
+      <c r="HH11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI11" s="1" t="n">
+        <v>3564.39</v>
+      </c>
+      <c r="HJ11" s="1" t="n">
+        <v>22376.24</v>
+      </c>
+      <c r="HK11" s="1" t="n">
+        <v>31726.01</v>
+      </c>
+      <c r="HL11" s="1" t="n">
+        <v>872728.0699999999</v>
+      </c>
+      <c r="HM11" s="1" t="n">
+        <v>2746.76</v>
+      </c>
+      <c r="HN11" s="1" t="n">
+        <v>20460.38</v>
+      </c>
+      <c r="HO11" s="1" t="n">
+        <v>43522.69</v>
+      </c>
+      <c r="HP11" s="1" t="n">
+        <v>61605.06</v>
+      </c>
+      <c r="HQ11" s="1" t="n">
+        <v>274.45</v>
+      </c>
+      <c r="HR11" s="1" t="n">
+        <v>18055.67</v>
+      </c>
+      <c r="HS11" s="1" t="n">
+        <v>226593.79</v>
+      </c>
+      <c r="HT11" s="1" t="n">
+        <v>25423.72</v>
+      </c>
+      <c r="HU11" s="1" t="n">
+        <v>17576.74</v>
+      </c>
+      <c r="HV11" s="1" t="n">
+        <v>4190.75</v>
+      </c>
+      <c r="HW11" s="1" t="n">
+        <v>250958.45</v>
+      </c>
+      <c r="HX11" s="1" t="n">
+        <v>1133.7</v>
+      </c>
+      <c r="HY11" s="1" t="n">
+        <v>75613.31</v>
+      </c>
+      <c r="HZ11" s="1" t="n">
+        <v>308492.36</v>
+      </c>
+      <c r="IA11" s="1" t="n">
+        <v>14102.73</v>
+      </c>
+      <c r="IB11" s="1" t="n">
+        <v>3484.13</v>
+      </c>
+      <c r="IC11" s="1" t="n">
+        <v>69991.37</v>
+      </c>
+      <c r="ID11" s="1" t="n">
+        <v>45792.69</v>
+      </c>
+      <c r="IE11" s="1" t="n">
+        <v>135790.79</v>
+      </c>
+      <c r="IF11" s="1" t="n">
+        <v>20906.93</v>
+      </c>
+      <c r="IG11" s="1" t="n">
+        <v>1745642.1</v>
+      </c>
+      <c r="IH11" s="1" t="n">
+        <v>36055.26</v>
+      </c>
+      <c r="II11" s="1" t="n">
+        <v>107108.48</v>
+      </c>
+      <c r="IJ11" s="1" t="n">
+        <v>80657.78999999999</v>
+      </c>
+      <c r="IK11" s="1" t="n">
+        <v>17308.79</v>
+      </c>
+      <c r="IL11" s="1" t="n">
+        <v>1497.37</v>
+      </c>
+      <c r="IM11" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="IN11" s="1" t="n">
+        <v>10161.18</v>
+      </c>
+      <c r="IO11" s="1" t="n">
+        <v>13570.26</v>
+      </c>
+      <c r="IP11" s="1" t="n">
+        <v>45345.79</v>
+      </c>
+      <c r="IQ11" s="1" t="n">
+        <v>3161.74</v>
+      </c>
+      <c r="IR11" s="1" t="n">
+        <v>445298.72</v>
+      </c>
+      <c r="IS11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT11" s="1" t="n">
+        <v>11030.67</v>
+      </c>
+      <c r="IU11" s="1" t="n">
+        <v>2750.5</v>
+      </c>
+      <c r="IV11" s="1" t="n">
+        <v>23239.94</v>
+      </c>
+      <c r="IW11" s="1" t="n">
+        <v>79321.12</v>
+      </c>
+      <c r="IX11" s="1" t="n">
+        <v>20079.39</v>
+      </c>
+      <c r="IY11" s="1" t="n">
+        <v>130710.01</v>
+      </c>
+      <c r="IZ11" s="1" t="n">
+        <v>47005.16</v>
+      </c>
+      <c r="JA11" s="1" t="n">
+        <v>4987.49</v>
+      </c>
+      <c r="JB11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC11" s="1" t="n">
+        <v>64187.38</v>
+      </c>
+      <c r="JD11" s="1" t="n">
+        <v>11657.56</v>
+      </c>
+      <c r="JE11" s="1" t="n">
+        <v>512.2</v>
+      </c>
+      <c r="JF11" s="1" t="n">
+        <v>5002.98</v>
+      </c>
+      <c r="JG11" s="1" t="n">
+        <v>19912.47</v>
+      </c>
+      <c r="JH11" s="1" t="n">
+        <v>801.1</v>
+      </c>
+      <c r="JI11" s="1" t="n">
+        <v>399.13</v>
+      </c>
+      <c r="JJ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK11" s="1" t="n">
+        <v>144921.27</v>
+      </c>
+      <c r="JM11" s="1" t="n">
+        <v>6374.33</v>
+      </c>
+      <c r="JN11" s="1" t="n">
+        <v>878353.4399999999</v>
+      </c>
+      <c r="JO11" s="1" t="n">
+        <v>398.16</v>
+      </c>
+      <c r="JP11" s="1" t="n">
+        <v>6276.2</v>
+      </c>
+      <c r="JQ11" s="1" t="n">
+        <v>9934.549999999999</v>
+      </c>
+      <c r="JR11" s="1" t="n">
+        <v>47.56</v>
+      </c>
+      <c r="JS11" s="1" t="n">
+        <v>344291.8</v>
+      </c>
+      <c r="JT11" s="1" t="n">
+        <v>197.02</v>
+      </c>
+      <c r="JU11" s="1" t="n">
+        <v>96995.62</v>
+      </c>
+      <c r="JV11" s="1" t="n">
+        <v>6493.57</v>
+      </c>
+      <c r="JX11" s="1" t="n">
+        <v>10505.79</v>
+      </c>
+      <c r="JY11" s="1" t="n">
+        <v>29645.3</v>
+      </c>
+      <c r="JZ11" s="1" t="n">
+        <v>9131857.02</v>
+      </c>
+      <c r="KA11" s="1" t="n">
+        <v>1020.82</v>
+      </c>
+      <c r="KB11" s="1" t="n">
+        <v>698.37</v>
+      </c>
+      <c r="KC11" s="1" t="n">
+        <v>15148.3</v>
+      </c>
+      <c r="KD11" s="1" t="n">
+        <v>796.08</v>
+      </c>
+      <c r="KE11" s="1" t="n">
+        <v>965.52</v>
+      </c>
+      <c r="KF11" s="1" t="n">
+        <v>23063.27</v>
+      </c>
+      <c r="KG11" s="1" t="n">
+        <v>10607.69</v>
+      </c>
+      <c r="KH11" s="1" t="n">
+        <v>2859.66</v>
+      </c>
+      <c r="KI11" s="1" t="n">
+        <v>29604.32</v>
+      </c>
+      <c r="KJ11" s="1" t="n">
+        <v>10422.23</v>
+      </c>
+      <c r="KK11" s="1" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="KM11" s="1" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="KN11" s="1" t="n">
+        <v>266732.02</v>
+      </c>
+      <c r="KO11" s="1" t="n">
+        <v>581233.13</v>
+      </c>
+      <c r="KP11" s="1" t="n">
+        <v>14618.14</v>
+      </c>
+      <c r="KQ11" s="1" t="n">
+        <v>398.97</v>
+      </c>
+      <c r="KR11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KS11" s="1" t="n">
+        <v>282827.72</v>
+      </c>
+      <c r="KT11" s="1" t="n">
+        <v>12368.18</v>
+      </c>
+      <c r="KU11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KV11" s="1" t="n">
+        <v>147.48</v>
+      </c>
+      <c r="KW11" s="1" t="n">
+        <v>126118.66</v>
+      </c>
+      <c r="KX11" s="1" t="n">
+        <v>48.08</v>
+      </c>
+      <c r="KY11" s="1" t="n">
+        <v>14211.31</v>
+      </c>
+      <c r="KZ11" s="1" t="n">
+        <v>11456.19</v>
+      </c>
+      <c r="LA11" s="1" t="n">
+        <v>1695.75</v>
+      </c>
+      <c r="LB11" s="1" t="n">
+        <v>52294.85</v>
+      </c>
+      <c r="LC11" s="1" t="n">
+        <v>593.62</v>
+      </c>
+      <c r="LD11" s="1" t="n">
+        <v>10889.02</v>
+      </c>
+      <c r="LE11" s="1" t="n">
+        <v>2700.45</v>
+      </c>
+      <c r="LF11" s="1" t="n">
+        <v>201.67</v>
+      </c>
+      <c r="LG11" s="1" t="n">
+        <v>38738.71</v>
+      </c>
+      <c r="LI11" s="1" t="n">
+        <v>158182.32</v>
+      </c>
+      <c r="LJ11" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="LK11" s="1" t="n">
+        <v>2624.36</v>
+      </c>
+      <c r="LL11" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LO11" s="1" t="n">
+        <v>1790.79</v>
+      </c>
+      <c r="LP11" s="1" t="n">
+        <v>304770.38</v>
+      </c>
+      <c r="LQ11" s="1" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="LR11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LS11" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="LT11" s="1" t="n">
+        <v>120658.9</v>
+      </c>
+      <c r="LU11" s="1" t="n">
+        <v>4114.96</v>
+      </c>
+      <c r="LV11" s="1" t="n">
+        <v>135.99</v>
+      </c>
+      <c r="LW11" s="1" t="n">
+        <v>109.72</v>
+      </c>
+      <c r="LX11" s="1" t="n">
+        <v>18773.02</v>
+      </c>
+      <c r="LY11" s="1" t="n">
+        <v>65149.03</v>
+      </c>
+      <c r="LZ11" s="1" t="n">
+        <v>242331.6</v>
+      </c>
+      <c r="MA11" s="1" t="n">
+        <v>45232.41</v>
+      </c>
+      <c r="MB11" s="1" t="n">
+        <v>8623.76</v>
+      </c>
+      <c r="MC11" s="1" t="n">
+        <v>2278.64</v>
+      </c>
+      <c r="MD11" s="1" t="n">
+        <v>5147.12</v>
+      </c>
+      <c r="ME11" s="1" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="MF11" s="1" t="n">
+        <v>553.51</v>
+      </c>
+      <c r="MG11" s="1" t="n">
+        <v>2621.59</v>
+      </c>
+      <c r="MH11" s="1" t="n">
+        <v>139495.72</v>
+      </c>
+      <c r="MI11" s="1" t="n">
+        <v>361.83</v>
+      </c>
+      <c r="MJ11" s="1" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="MK11" s="1" t="n">
+        <v>116067.18</v>
+      </c>
+      <c r="ML11" s="1" t="n">
+        <v>52408.82</v>
+      </c>
+      <c r="MM11" s="1" t="n">
+        <v>3298.35</v>
+      </c>
+      <c r="MN11" s="1" t="n">
+        <v>10309.63</v>
+      </c>
+      <c r="MO11" s="1" t="n">
+        <v>89184.57000000001</v>
+      </c>
+      <c r="MP11" s="1" t="n">
+        <v>2992.38</v>
+      </c>
+      <c r="MQ11" s="1" t="n">
+        <v>30007.81</v>
+      </c>
+      <c r="MR11" s="1" t="n">
+        <v>153494.87</v>
+      </c>
+      <c r="MS11" s="1" t="n">
+        <v>10496.64</v>
+      </c>
+      <c r="MT11" s="1" t="n">
+        <v>4668.96</v>
+      </c>
+      <c r="MU11" s="1" t="n">
+        <v>5220.76</v>
+      </c>
+      <c r="MV11" s="1" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="MW11" s="1" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="MX11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MY11" s="1" t="n">
+        <v>302.71</v>
+      </c>
+      <c r="MZ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NA11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NB11" s="1" t="n">
+        <v>233.37</v>
+      </c>
+      <c r="NC11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ND11" s="1" t="n">
+        <v>531.38</v>
+      </c>
+      <c r="NE11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NF11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NG11" s="1" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="NH11" s="1" t="n">
+        <v>31672.68</v>
+      </c>
+      <c r="PB11" s="1" t="n">
+        <v>105.06</v>
+      </c>
+      <c r="PK11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PV11" s="1" t="n">
+        <v>13538.36</v>
       </c>
     </row>
   </sheetData>
@@ -14124,7 +15204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW10"/>
+  <dimension ref="A1:BXW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14546,6 +15626,48 @@
       </c>
       <c r="M10" s="1" t="n">
         <v>11235.909921</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>481627457.82</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>58735576.22076</v>
+      </c>
+      <c r="D11" s="1">
+        <f>AVERAGE(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>2031066.7022</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>5029439.4503</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>4682507.5249</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>1344000.1911</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>2664755.3577</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>68937.0717</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>12915.3158</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>2406.2268</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>22187.285284</v>
       </c>
     </row>
   </sheetData>
@@ -14559,7 +15681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW10"/>
+  <dimension ref="A1:BXW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17956,6 +19078,327 @@
         <v>0</v>
       </c>
       <c r="DB10" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>2236512.42196813</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>8407675.470363926</v>
+      </c>
+      <c r="D11" s="1">
+        <f>AVERAGE(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>4178427.654207562</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>40861.1842897686</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>381427.4185812122</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>4095795.982163961</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>139957.8676299141</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>3352.5508455742</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>995.6106698777</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>7939.9355601657</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>760</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>617.12014</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>285.924485</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>386.1688</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>154942.0703431663</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="1" t="n">
+        <v>20.372848</v>
+      </c>
+      <c r="AV11" s="1" t="n">
+        <v>24.544343675</v>
+      </c>
+      <c r="AW11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="1" t="n">
+        <v>99.73321361767999</v>
+      </c>
+      <c r="BD11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" s="1" t="n">
+        <v>99.73321365</v>
+      </c>
+      <c r="BS11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17970,7 +19413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW10"/>
+  <dimension ref="A1:BXW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19113,6 +20556,126 @@
       </c>
       <c r="AM10" s="1" t="n">
         <v>25625.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>17934575.5</v>
+      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(B5:B11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>2236963.79</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>1022680.03</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>110992.21</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>181486.06</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>342634.47</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>287134.3</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>152872.56</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>5432.66</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>16773.67</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>27346.12</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>164279.4</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>5331.2</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>16390.07</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>14761</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>12506.26</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>1566.68</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>3170</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1" t="n">
+        <v>138995.68</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>8604.15</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>77085.77</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>6727.68</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>1003</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>792.88</v>
+      </c>
+      <c r="AD11" s="1" t="n">
+        <v>2498.63</v>
+      </c>
+      <c r="AE11" s="1" t="n">
+        <v>12660.98</v>
+      </c>
+      <c r="AF11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="1" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AH11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="1" t="n">
+        <v>9562.26</v>
+      </c>
+      <c r="AL11" s="1" t="n">
+        <v>20817.99</v>
+      </c>
+      <c r="AM11" s="1" t="n">
+        <v>725.4400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>577284182.33</v>
+        <v>393359699.58</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,15 +481,15 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>481627457.82</v>
+        <v>276450784.18</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>BTC_THB</t>
+          <t>USDT_THB</t>
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>8407675.470363926</v>
+        <v>3252134.850426358</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>17934575.5</v>
+        <v>5436370.01</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>264644621.31</v>
+        <v>107008687.33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,23 +518,23 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>58735576.22076</v>
+        <v>58935210.07156</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>USDT_THB</t>
+          <t>ETH_THB</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>4178427.654207562</v>
+        <v>1463968.936541992</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>USDTTHB</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>2236963.79</v>
+        <v>2193869.3</v>
       </c>
     </row>
     <row r="4">
@@ -543,35 +543,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THB_ETH</t>
+          <t>THB_DOGE</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>98991058.05</v>
+        <v>39807681.59</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>BNBTHB</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>5029439.4503</v>
+        <v>2448321.8178</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SOL_THB</t>
+          <t>BTC_THB</t>
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>4095795.982163961</v>
+        <v>889794.6224998767</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1022680.03</v>
+        <v>800345.33</v>
       </c>
     </row>
     <row r="5">
@@ -580,11 +580,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THB_XRP</t>
+          <t>THB_ETH</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>56976918.1</v>
+        <v>39484578.03</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -592,23 +592,23 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>4682507.5249</v>
+        <v>1946164.4838</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ETH_THB</t>
+          <t>SOL_THB</t>
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>2236512.42196813</v>
+        <v>319755.4287445909</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>USDTTHB</t>
+          <t>ARBTHB</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>342634.47</v>
+        <v>270334.64</v>
       </c>
     </row>
     <row r="6">
@@ -617,19 +617,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_NEAR</t>
+          <t>THB_XRP</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>51248012.36</v>
+        <v>34006141.07</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VELOTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>2664755.3577</v>
+        <v>1691205.0614</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -637,15 +637,15 @@
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>381427.4185812122</v>
+        <v>113342.653096172</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>XLMTHB</t>
+          <t>BCHTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>287134.3</v>
+        <v>186490.86</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW11"/>
+  <dimension ref="A1:BXW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15191,6 +15191,1086 @@
       </c>
       <c r="PV11" s="1" t="n">
         <v>13538.36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>393359699.58</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>107008687.33</v>
+      </c>
+      <c r="D12" s="1">
+        <f>AVERAGE(C6:C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>39484578.03</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>34006141.07</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>13336996.41</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>39807681.59</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>5565247.46</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>15680598.93</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>2123958.28</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>12850431.82</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>5097293.77</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>31844613.63</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>6639624.62</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>421345.55</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>3173426.04</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>1155943.37</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>5385394.88</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>8162464.16</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>7942996.8</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>115667.39</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>11031557.74</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>137712.38</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <v>197665</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>3400736.08</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>9567255.1</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>3650277.85</v>
+      </c>
+      <c r="AD12" s="1" t="n">
+        <v>1559935.31</v>
+      </c>
+      <c r="AE12" s="1" t="n">
+        <v>2054180.73</v>
+      </c>
+      <c r="AF12" s="1" t="n">
+        <v>783504.4399999999</v>
+      </c>
+      <c r="AG12" s="1" t="n">
+        <v>811760.6899999999</v>
+      </c>
+      <c r="AH12" s="1" t="n">
+        <v>1887341.44</v>
+      </c>
+      <c r="AI12" s="1" t="n">
+        <v>7704517.19</v>
+      </c>
+      <c r="AJ12" s="1" t="n">
+        <v>354318.15</v>
+      </c>
+      <c r="AK12" s="1" t="n">
+        <v>1338664.09</v>
+      </c>
+      <c r="AL12" s="1" t="n">
+        <v>2258576.57</v>
+      </c>
+      <c r="AN12" s="1" t="n">
+        <v>4436423.35</v>
+      </c>
+      <c r="AO12" s="1" t="n">
+        <v>352013.55</v>
+      </c>
+      <c r="AP12" s="1" t="n">
+        <v>881594.21</v>
+      </c>
+      <c r="AQ12" s="1" t="n">
+        <v>1294682.03</v>
+      </c>
+      <c r="AR12" s="1" t="n">
+        <v>7757975</v>
+      </c>
+      <c r="AS12" s="1" t="n">
+        <v>501328.26</v>
+      </c>
+      <c r="AT12" s="1" t="n">
+        <v>3172024.83</v>
+      </c>
+      <c r="AU12" s="1" t="n">
+        <v>327870.89</v>
+      </c>
+      <c r="AV12" s="1" t="n">
+        <v>8842361.890000001</v>
+      </c>
+      <c r="AW12" s="1" t="n">
+        <v>1331280.58</v>
+      </c>
+      <c r="AX12" s="1" t="n">
+        <v>1369942.85</v>
+      </c>
+      <c r="AY12" s="1" t="n">
+        <v>729299.17</v>
+      </c>
+      <c r="AZ12" s="1" t="n">
+        <v>1209804.72</v>
+      </c>
+      <c r="BA12" s="1" t="n">
+        <v>251438.17</v>
+      </c>
+      <c r="BB12" s="1" t="n">
+        <v>17298.08</v>
+      </c>
+      <c r="BC12" s="1" t="n">
+        <v>1488165.57</v>
+      </c>
+      <c r="BD12" s="1" t="n">
+        <v>866636.47</v>
+      </c>
+      <c r="BE12" s="1" t="n">
+        <v>147351.34</v>
+      </c>
+      <c r="BF12" s="1" t="n">
+        <v>1591559.3</v>
+      </c>
+      <c r="BG12" s="1" t="n">
+        <v>2593.5</v>
+      </c>
+      <c r="BI12" s="1" t="n">
+        <v>2142.2</v>
+      </c>
+      <c r="BJ12" s="1" t="n">
+        <v>441488.33</v>
+      </c>
+      <c r="BK12" s="1" t="n">
+        <v>159155.43</v>
+      </c>
+      <c r="BL12" s="1" t="n">
+        <v>957024.91</v>
+      </c>
+      <c r="BM12" s="1" t="n">
+        <v>373560.86</v>
+      </c>
+      <c r="BN12" s="1" t="n">
+        <v>649528.5600000001</v>
+      </c>
+      <c r="BO12" s="1" t="n">
+        <v>55578.74</v>
+      </c>
+      <c r="BP12" s="1" t="n">
+        <v>3755491.4</v>
+      </c>
+      <c r="BQ12" s="1" t="n">
+        <v>242.26</v>
+      </c>
+      <c r="BS12" s="1" t="n">
+        <v>440023.01</v>
+      </c>
+      <c r="BT12" s="1" t="n">
+        <v>496474.21</v>
+      </c>
+      <c r="BU12" s="1" t="n">
+        <v>1272253.54</v>
+      </c>
+      <c r="BV12" s="1" t="n">
+        <v>768342.3199999999</v>
+      </c>
+      <c r="BW12" s="1" t="n">
+        <v>24858.75</v>
+      </c>
+      <c r="BX12" s="1" t="n">
+        <v>254.22</v>
+      </c>
+      <c r="BY12" s="1" t="n">
+        <v>177319.95</v>
+      </c>
+      <c r="BZ12" s="1" t="n">
+        <v>165367.76</v>
+      </c>
+      <c r="CA12" s="1" t="n">
+        <v>242936.19</v>
+      </c>
+      <c r="CB12" s="1" t="n">
+        <v>13920.95</v>
+      </c>
+      <c r="CC12" s="1" t="n">
+        <v>31253.16</v>
+      </c>
+      <c r="CD12" s="1" t="n">
+        <v>69735.74000000001</v>
+      </c>
+      <c r="CE12" s="1" t="n">
+        <v>1977493.01</v>
+      </c>
+      <c r="CF12" s="1" t="n">
+        <v>53869.99</v>
+      </c>
+      <c r="CG12" s="1" t="n">
+        <v>991636.16</v>
+      </c>
+      <c r="CH12" s="1" t="n">
+        <v>54381.94</v>
+      </c>
+      <c r="CI12" s="1" t="n">
+        <v>22602.76</v>
+      </c>
+      <c r="CJ12" s="1" t="n">
+        <v>5860422.58</v>
+      </c>
+      <c r="CK12" s="1" t="n">
+        <v>703072.34</v>
+      </c>
+      <c r="CL12" s="1" t="n">
+        <v>1292.26</v>
+      </c>
+      <c r="CM12" s="1" t="n">
+        <v>5792.92</v>
+      </c>
+      <c r="CN12" s="1" t="n">
+        <v>85016.00999999999</v>
+      </c>
+      <c r="CO12" s="1" t="n">
+        <v>354593.21</v>
+      </c>
+      <c r="CP12" s="1" t="n">
+        <v>283230.4</v>
+      </c>
+      <c r="CQ12" s="1" t="n">
+        <v>183144.55</v>
+      </c>
+      <c r="CR12" s="1" t="n">
+        <v>485.6</v>
+      </c>
+      <c r="CS12" s="1" t="n">
+        <v>77294.5</v>
+      </c>
+      <c r="CT12" s="1" t="n">
+        <v>28007.38</v>
+      </c>
+      <c r="CV12" s="1" t="n">
+        <v>665153.86</v>
+      </c>
+      <c r="CW12" s="1" t="n">
+        <v>1807133.49</v>
+      </c>
+      <c r="CX12" s="1" t="n">
+        <v>114977.94</v>
+      </c>
+      <c r="CY12" s="1" t="n">
+        <v>23056.48</v>
+      </c>
+      <c r="CZ12" s="1" t="n">
+        <v>331999.19</v>
+      </c>
+      <c r="DA12" s="1" t="n">
+        <v>719.8099999999999</v>
+      </c>
+      <c r="DB12" s="1" t="n">
+        <v>8520.6</v>
+      </c>
+      <c r="DC12" s="1" t="n">
+        <v>21555.63</v>
+      </c>
+      <c r="DD12" s="1" t="n">
+        <v>64597.48</v>
+      </c>
+      <c r="DE12" s="1" t="n">
+        <v>9629.049999999999</v>
+      </c>
+      <c r="DG12" s="1" t="n">
+        <v>987327.66</v>
+      </c>
+      <c r="DH12" s="1" t="n">
+        <v>239298.55</v>
+      </c>
+      <c r="DI12" s="1" t="n">
+        <v>81879.37</v>
+      </c>
+      <c r="DJ12" s="1" t="n">
+        <v>120740.36</v>
+      </c>
+      <c r="DK12" s="1" t="n">
+        <v>52124.22</v>
+      </c>
+      <c r="DL12" s="1" t="n">
+        <v>12241.86</v>
+      </c>
+      <c r="DM12" s="1" t="n">
+        <v>135523.08</v>
+      </c>
+      <c r="DN12" s="1" t="n">
+        <v>104373.47</v>
+      </c>
+      <c r="DO12" s="1" t="n">
+        <v>5323.33</v>
+      </c>
+      <c r="DP12" s="1" t="n">
+        <v>741929.23</v>
+      </c>
+      <c r="DQ12" s="1" t="n">
+        <v>110306.53</v>
+      </c>
+      <c r="DR12" s="1" t="n">
+        <v>310368.73</v>
+      </c>
+      <c r="DS12" s="1" t="n">
+        <v>336230.79</v>
+      </c>
+      <c r="DT12" s="1" t="n">
+        <v>47106.87</v>
+      </c>
+      <c r="DV12" s="1" t="n">
+        <v>193000.53</v>
+      </c>
+      <c r="DW12" s="1" t="n">
+        <v>200186.73</v>
+      </c>
+      <c r="DX12" s="1" t="n">
+        <v>314826.39</v>
+      </c>
+      <c r="DY12" s="1" t="n">
+        <v>101247.52</v>
+      </c>
+      <c r="DZ12" s="1" t="n">
+        <v>274790.03</v>
+      </c>
+      <c r="EA12" s="1" t="n">
+        <v>59997.52</v>
+      </c>
+      <c r="EB12" s="1" t="n">
+        <v>1109.69</v>
+      </c>
+      <c r="EC12" s="1" t="n">
+        <v>75054.71000000001</v>
+      </c>
+      <c r="ED12" s="1" t="n">
+        <v>18657.64</v>
+      </c>
+      <c r="EE12" s="1" t="n">
+        <v>58077.95</v>
+      </c>
+      <c r="EF12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG12" s="1" t="n">
+        <v>218144.42</v>
+      </c>
+      <c r="EH12" s="1" t="n">
+        <v>692829.16</v>
+      </c>
+      <c r="EI12" s="1" t="n">
+        <v>147178.77</v>
+      </c>
+      <c r="EJ12" s="1" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="EK12" s="1" t="n">
+        <v>683900.96</v>
+      </c>
+      <c r="EL12" s="1" t="n">
+        <v>24056.76</v>
+      </c>
+      <c r="EM12" s="1" t="n">
+        <v>948.54</v>
+      </c>
+      <c r="EN12" s="1" t="n">
+        <v>153472.95</v>
+      </c>
+      <c r="EO12" s="1" t="n">
+        <v>666717.48</v>
+      </c>
+      <c r="EP12" s="1" t="n">
+        <v>5967203.74</v>
+      </c>
+      <c r="EQ12" s="1" t="n">
+        <v>2375.53</v>
+      </c>
+      <c r="ER12" s="1" t="n">
+        <v>3128.88</v>
+      </c>
+      <c r="ES12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET12" s="1" t="n">
+        <v>16897.84</v>
+      </c>
+      <c r="EU12" s="1" t="n">
+        <v>74947.50999999999</v>
+      </c>
+      <c r="EV12" s="1" t="n">
+        <v>130749.75</v>
+      </c>
+      <c r="EW12" s="1" t="n">
+        <v>114965.45</v>
+      </c>
+      <c r="EX12" s="1" t="n">
+        <v>153864.17</v>
+      </c>
+      <c r="EY12" s="1" t="n">
+        <v>7832.48</v>
+      </c>
+      <c r="EZ12" s="1" t="n">
+        <v>1039.48</v>
+      </c>
+      <c r="FB12" s="1" t="n">
+        <v>5339.6</v>
+      </c>
+      <c r="FC12" s="1" t="n">
+        <v>37945.27</v>
+      </c>
+      <c r="FD12" s="1" t="n">
+        <v>136560.93</v>
+      </c>
+      <c r="FE12" s="1" t="n">
+        <v>841952.58</v>
+      </c>
+      <c r="FF12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG12" s="1" t="n">
+        <v>184787.97</v>
+      </c>
+      <c r="FH12" s="1" t="n">
+        <v>16787.7</v>
+      </c>
+      <c r="FI12" s="1" t="n">
+        <v>131426.63</v>
+      </c>
+      <c r="FK12" s="1" t="n">
+        <v>22006.77</v>
+      </c>
+      <c r="FL12" s="1" t="n">
+        <v>47242.1</v>
+      </c>
+      <c r="FM12" s="1" t="n">
+        <v>48102.72</v>
+      </c>
+      <c r="FN12" s="1" t="n">
+        <v>68619.85000000001</v>
+      </c>
+      <c r="FO12" s="1" t="n">
+        <v>8449.48</v>
+      </c>
+      <c r="FP12" s="1" t="n">
+        <v>326973.37</v>
+      </c>
+      <c r="FQ12" s="1" t="n">
+        <v>105371.13</v>
+      </c>
+      <c r="FR12" s="1" t="n">
+        <v>46180.76</v>
+      </c>
+      <c r="FS12" s="1" t="n">
+        <v>4238190.81</v>
+      </c>
+      <c r="FT12" s="1" t="n">
+        <v>5758.78</v>
+      </c>
+      <c r="FU12" s="1" t="n">
+        <v>2423.7</v>
+      </c>
+      <c r="FV12" s="1" t="n">
+        <v>711449.4300000001</v>
+      </c>
+      <c r="FW12" s="1" t="n">
+        <v>36164.11</v>
+      </c>
+      <c r="FX12" s="1" t="n">
+        <v>46171.22</v>
+      </c>
+      <c r="FY12" s="1" t="n">
+        <v>82287.77</v>
+      </c>
+      <c r="FZ12" s="1" t="n">
+        <v>95458.96000000001</v>
+      </c>
+      <c r="GA12" s="1" t="n">
+        <v>6744.23</v>
+      </c>
+      <c r="GB12" s="1" t="n">
+        <v>9373.92</v>
+      </c>
+      <c r="GC12" s="1" t="n">
+        <v>197631.57</v>
+      </c>
+      <c r="GD12" s="1" t="n">
+        <v>34573.45</v>
+      </c>
+      <c r="GE12" s="1" t="n">
+        <v>1259.76</v>
+      </c>
+      <c r="GF12" s="1" t="n">
+        <v>33833.75</v>
+      </c>
+      <c r="GG12" s="1" t="n">
+        <v>1021.71</v>
+      </c>
+      <c r="GH12" s="1" t="n">
+        <v>38240.62</v>
+      </c>
+      <c r="GI12" s="1" t="n">
+        <v>63566.5</v>
+      </c>
+      <c r="GJ12" s="1" t="n">
+        <v>6932.24</v>
+      </c>
+      <c r="GK12" s="1" t="n">
+        <v>664476.66</v>
+      </c>
+      <c r="GL12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM12" s="1" t="n">
+        <v>539631.63</v>
+      </c>
+      <c r="GN12" s="1" t="n">
+        <v>1900.09</v>
+      </c>
+      <c r="GO12" s="1" t="n">
+        <v>86954.45</v>
+      </c>
+      <c r="GP12" s="1" t="n">
+        <v>25201.46</v>
+      </c>
+      <c r="GQ12" s="1" t="n">
+        <v>27698.5</v>
+      </c>
+      <c r="GR12" s="1" t="n">
+        <v>4321.49</v>
+      </c>
+      <c r="GS12" s="1" t="n">
+        <v>4437.13</v>
+      </c>
+      <c r="GT12" s="1" t="n">
+        <v>35965.05</v>
+      </c>
+      <c r="GU12" s="1" t="n">
+        <v>5307.33</v>
+      </c>
+      <c r="GV12" s="1" t="n">
+        <v>86090.03</v>
+      </c>
+      <c r="GX12" s="1" t="n">
+        <v>61.33</v>
+      </c>
+      <c r="GY12" s="1" t="n">
+        <v>1496.93</v>
+      </c>
+      <c r="GZ12" s="1" t="n">
+        <v>88342.60000000001</v>
+      </c>
+      <c r="HA12" s="1" t="n">
+        <v>814.92</v>
+      </c>
+      <c r="HB12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC12" s="1" t="n">
+        <v>7449.32</v>
+      </c>
+      <c r="HD12" s="1" t="n">
+        <v>209.41</v>
+      </c>
+      <c r="HE12" s="1" t="n">
+        <v>166251.33</v>
+      </c>
+      <c r="HF12" s="1" t="n">
+        <v>10463.66</v>
+      </c>
+      <c r="HG12" s="1" t="n">
+        <v>67131.75999999999</v>
+      </c>
+      <c r="HH12" s="1" t="n">
+        <v>335.26</v>
+      </c>
+      <c r="HI12" s="1" t="n">
+        <v>3540.86</v>
+      </c>
+      <c r="HJ12" s="1" t="n">
+        <v>21004.49</v>
+      </c>
+      <c r="HK12" s="1" t="n">
+        <v>23876.72</v>
+      </c>
+      <c r="HL12" s="1" t="n">
+        <v>344634.13</v>
+      </c>
+      <c r="HM12" s="1" t="n">
+        <v>478.36</v>
+      </c>
+      <c r="HN12" s="1" t="n">
+        <v>249788.2</v>
+      </c>
+      <c r="HO12" s="1" t="n">
+        <v>64134.78</v>
+      </c>
+      <c r="HP12" s="1" t="n">
+        <v>59479.56</v>
+      </c>
+      <c r="HQ12" s="1" t="n">
+        <v>274.45</v>
+      </c>
+      <c r="HR12" s="1" t="n">
+        <v>5366.56</v>
+      </c>
+      <c r="HS12" s="1" t="n">
+        <v>13661.17</v>
+      </c>
+      <c r="HT12" s="1" t="n">
+        <v>278614.9</v>
+      </c>
+      <c r="HU12" s="1" t="n">
+        <v>28783.72</v>
+      </c>
+      <c r="HV12" s="1" t="n">
+        <v>463.22</v>
+      </c>
+      <c r="HW12" s="1" t="n">
+        <v>182660.73</v>
+      </c>
+      <c r="HX12" s="1" t="n">
+        <v>42934.59</v>
+      </c>
+      <c r="HY12" s="1" t="n">
+        <v>60705.33</v>
+      </c>
+      <c r="HZ12" s="1" t="n">
+        <v>164.52</v>
+      </c>
+      <c r="IA12" s="1" t="n">
+        <v>1224921.3</v>
+      </c>
+      <c r="IB12" s="1" t="n">
+        <v>28340.48</v>
+      </c>
+      <c r="IC12" s="1" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="ID12" s="1" t="n">
+        <v>22761.73</v>
+      </c>
+      <c r="IE12" s="1" t="n">
+        <v>90740.21000000001</v>
+      </c>
+      <c r="IF12" s="1" t="n">
+        <v>11877.53</v>
+      </c>
+      <c r="IG12" s="1" t="n">
+        <v>689502.13</v>
+      </c>
+      <c r="IH12" s="1" t="n">
+        <v>16617.68</v>
+      </c>
+      <c r="II12" s="1" t="n">
+        <v>619166.84</v>
+      </c>
+      <c r="IJ12" s="1" t="n">
+        <v>32892.25</v>
+      </c>
+      <c r="IK12" s="1" t="n">
+        <v>156708.02</v>
+      </c>
+      <c r="IL12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IM12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN12" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="IO12" s="1" t="n">
+        <v>17021.44</v>
+      </c>
+      <c r="IP12" s="1" t="n">
+        <v>14160.81</v>
+      </c>
+      <c r="IQ12" s="1" t="n">
+        <v>3308.04</v>
+      </c>
+      <c r="IR12" s="1" t="n">
+        <v>308478.79</v>
+      </c>
+      <c r="IS12" s="1" t="n">
+        <v>5506.16</v>
+      </c>
+      <c r="IT12" s="1" t="n">
+        <v>45868.73</v>
+      </c>
+      <c r="IU12" s="1" t="n">
+        <v>7329.81</v>
+      </c>
+      <c r="IV12" s="1" t="n">
+        <v>4289.41</v>
+      </c>
+      <c r="IW12" s="1" t="n">
+        <v>78732.77</v>
+      </c>
+      <c r="IX12" s="1" t="n">
+        <v>89933.45</v>
+      </c>
+      <c r="IY12" s="1" t="n">
+        <v>17348.19</v>
+      </c>
+      <c r="IZ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA12" s="1" t="n">
+        <v>7140.84</v>
+      </c>
+      <c r="JB12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC12" s="1" t="n">
+        <v>23373.75</v>
+      </c>
+      <c r="JD12" s="1" t="n">
+        <v>148.67</v>
+      </c>
+      <c r="JE12" s="1" t="n">
+        <v>205.3</v>
+      </c>
+      <c r="JF12" s="1" t="n">
+        <v>6629.93</v>
+      </c>
+      <c r="JG12" s="1" t="n">
+        <v>4394.36</v>
+      </c>
+      <c r="JH12" s="1" t="n">
+        <v>42305.7</v>
+      </c>
+      <c r="JI12" s="1" t="n">
+        <v>1001.33</v>
+      </c>
+      <c r="JJ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK12" s="1" t="n">
+        <v>100029.45</v>
+      </c>
+      <c r="JM12" s="1" t="n">
+        <v>6374.33</v>
+      </c>
+      <c r="JN12" s="1" t="n">
+        <v>91289.2</v>
+      </c>
+      <c r="JO12" s="1" t="n">
+        <v>398.16</v>
+      </c>
+      <c r="JP12" s="1" t="n">
+        <v>3238.76</v>
+      </c>
+      <c r="JQ12" s="1" t="n">
+        <v>14071.35</v>
+      </c>
+      <c r="JR12" s="1" t="n">
+        <v>4389.52</v>
+      </c>
+      <c r="JS12" s="1" t="n">
+        <v>218661.4</v>
+      </c>
+      <c r="JT12" s="1" t="n">
+        <v>197.02</v>
+      </c>
+      <c r="JU12" s="1" t="n">
+        <v>325893.35</v>
+      </c>
+      <c r="JV12" s="1" t="n">
+        <v>1369.48</v>
+      </c>
+      <c r="JX12" s="1" t="n">
+        <v>17320.03</v>
+      </c>
+      <c r="JY12" s="1" t="n">
+        <v>48293.14</v>
+      </c>
+      <c r="JZ12" s="1" t="n">
+        <v>8729572.16</v>
+      </c>
+      <c r="KA12" s="1" t="n">
+        <v>26479.42</v>
+      </c>
+      <c r="KB12" s="1" t="n">
+        <v>12426.03</v>
+      </c>
+      <c r="KC12" s="1" t="n">
+        <v>5078.53</v>
+      </c>
+      <c r="KD12" s="1" t="n">
+        <v>48446</v>
+      </c>
+      <c r="KE12" s="1" t="n">
+        <v>11071.99</v>
+      </c>
+      <c r="KF12" s="1" t="n">
+        <v>313601.25</v>
+      </c>
+      <c r="KG12" s="1" t="n">
+        <v>1010.37</v>
+      </c>
+      <c r="KH12" s="1" t="n">
+        <v>3071.11</v>
+      </c>
+      <c r="KI12" s="1" t="n">
+        <v>1790.96</v>
+      </c>
+      <c r="KJ12" s="1" t="n">
+        <v>34773.62</v>
+      </c>
+      <c r="KK12" s="1" t="n">
+        <v>5688.65</v>
+      </c>
+      <c r="KM12" s="1" t="n">
+        <v>1980.86</v>
+      </c>
+      <c r="KN12" s="1" t="n">
+        <v>3123848.49</v>
+      </c>
+      <c r="KO12" s="1" t="n">
+        <v>787572.78</v>
+      </c>
+      <c r="KP12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KQ12" s="1" t="n">
+        <v>398.97</v>
+      </c>
+      <c r="KR12" s="1" t="n">
+        <v>1581.9</v>
+      </c>
+      <c r="KS12" s="1" t="n">
+        <v>69361.62</v>
+      </c>
+      <c r="KT12" s="1" t="n">
+        <v>1292.74</v>
+      </c>
+      <c r="KU12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KV12" s="1" t="n">
+        <v>477.84</v>
+      </c>
+      <c r="KW12" s="1" t="n">
+        <v>93864.99000000001</v>
+      </c>
+      <c r="KX12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KY12" s="1" t="n">
+        <v>6005.03</v>
+      </c>
+      <c r="KZ12" s="1" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="LA12" s="1" t="n">
+        <v>38080.05</v>
+      </c>
+      <c r="LB12" s="1" t="n">
+        <v>60461.56</v>
+      </c>
+      <c r="LC12" s="1" t="n">
+        <v>593.62</v>
+      </c>
+      <c r="LD12" s="1" t="n">
+        <v>10889.02</v>
+      </c>
+      <c r="LE12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LF12" s="1" t="n">
+        <v>4933.1</v>
+      </c>
+      <c r="LG12" s="1" t="n">
+        <v>65826.39</v>
+      </c>
+      <c r="LI12" s="1" t="n">
+        <v>41523.27</v>
+      </c>
+      <c r="LJ12" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="LK12" s="1" t="n">
+        <v>9888.16</v>
+      </c>
+      <c r="LL12" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LO12" s="1" t="n">
+        <v>270.71</v>
+      </c>
+      <c r="LP12" s="1" t="n">
+        <v>3743.91</v>
+      </c>
+      <c r="LQ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LR12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LS12" s="1" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="LT12" s="1" t="n">
+        <v>61295.69</v>
+      </c>
+      <c r="LU12" s="1" t="n">
+        <v>4952.36</v>
+      </c>
+      <c r="LV12" s="1" t="n">
+        <v>53171.6</v>
+      </c>
+      <c r="LW12" s="1" t="n">
+        <v>1378.8</v>
+      </c>
+      <c r="LX12" s="1" t="n">
+        <v>8033.66</v>
+      </c>
+      <c r="LY12" s="1" t="n">
+        <v>77631.46000000001</v>
+      </c>
+      <c r="LZ12" s="1" t="n">
+        <v>319.24</v>
+      </c>
+      <c r="MA12" s="1" t="n">
+        <v>57472.91</v>
+      </c>
+      <c r="MB12" s="1" t="n">
+        <v>2122.17</v>
+      </c>
+      <c r="MC12" s="1" t="n">
+        <v>299492.78</v>
+      </c>
+      <c r="MD12" s="1" t="n">
+        <v>15691.52</v>
+      </c>
+      <c r="ME12" s="1" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="MF12" s="1" t="n">
+        <v>1216.1</v>
+      </c>
+      <c r="MG12" s="1" t="n">
+        <v>20142.24</v>
+      </c>
+      <c r="MH12" s="1" t="n">
+        <v>39976.18</v>
+      </c>
+      <c r="MI12" s="1" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="MJ12" s="1" t="n">
+        <v>482.28</v>
+      </c>
+      <c r="MK12" s="1" t="n">
+        <v>116067.18</v>
+      </c>
+      <c r="ML12" s="1" t="n">
+        <v>1304.74</v>
+      </c>
+      <c r="MM12" s="1" t="n">
+        <v>436.39</v>
+      </c>
+      <c r="MN12" s="1" t="n">
+        <v>10309.63</v>
+      </c>
+      <c r="MO12" s="1" t="n">
+        <v>43117.53</v>
+      </c>
+      <c r="MP12" s="1" t="n">
+        <v>2992.38</v>
+      </c>
+      <c r="MQ12" s="1" t="n">
+        <v>30007.81</v>
+      </c>
+      <c r="MR12" s="1" t="n">
+        <v>4364.79</v>
+      </c>
+      <c r="MS12" s="1" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="MT12" s="1" t="n">
+        <v>124.54</v>
+      </c>
+      <c r="MU12" s="1" t="n">
+        <v>524550.25</v>
+      </c>
+      <c r="MV12" s="1" t="n">
+        <v>186.28</v>
+      </c>
+      <c r="MW12" s="1" t="n">
+        <v>4842.83</v>
+      </c>
+      <c r="MX12" s="1" t="n">
+        <v>402.13</v>
+      </c>
+      <c r="MY12" s="1" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="MZ12" s="1" t="n">
+        <v>2668.45</v>
+      </c>
+      <c r="NA12" s="1" t="n">
+        <v>15574.34</v>
+      </c>
+      <c r="NB12" s="1" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="NC12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ND12" s="1" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="NE12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NF12" s="1" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="NG12" s="1" t="n">
+        <v>216302.9</v>
+      </c>
+      <c r="NH12" s="1" t="n">
+        <v>40598.16</v>
+      </c>
+      <c r="PB12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PK12" s="1" t="n">
+        <v>2018.6</v>
+      </c>
+      <c r="PV12" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15204,7 +16284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW11"/>
+  <dimension ref="A1:BXW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15668,6 +16748,48 @@
       </c>
       <c r="M11" s="1" t="n">
         <v>22187.285284</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>276450784.18</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>58935210.07156</v>
+      </c>
+      <c r="D12" s="1">
+        <f>AVERAGE(C6:C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>1691205.0614</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>1078914.0555</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>1946164.4838</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>2448321.8178</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>1235949.6428</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>474396.9642</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>17386.5324</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>2406.2268</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>25829.995365</v>
       </c>
     </row>
   </sheetData>
@@ -15681,7 +16803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW11"/>
+  <dimension ref="A1:BXW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19399,6 +20521,327 @@
         <v>0</v>
       </c>
       <c r="DB11" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>1463968.936541992</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>889794.6224998767</v>
+      </c>
+      <c r="D12" s="1">
+        <f>AVERAGE(C6:C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>3252134.850426358</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>87434.621</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>113342.653096172</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>319755.4287445909</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>79606.2163300582</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>17836.9457702259</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>30914.0609388435</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>21.744</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>336</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>894.6820039658</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>351.0594630216</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>11476.80074</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>539.4745675838</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="1" t="n">
+        <v>113.0675442684</v>
+      </c>
+      <c r="AV12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" s="1" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="BS12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" s="1" t="n">
+        <v>13.243233</v>
+      </c>
+      <c r="CF12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19413,7 +20856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW11"/>
+  <dimension ref="A1:BXW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20676,6 +22119,126 @@
       </c>
       <c r="AM11" s="1" t="n">
         <v>725.4400000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>5436370.01</v>
+      </c>
+      <c r="C12" s="1">
+        <f>AVERAGE(B6:B12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>800345.33</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>124520.13</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>71670.14999999999</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>186490.86</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>2193869.3</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>63778.68</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>156451.39</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>68762.39</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>270334.64</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>16519.8</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>7431.96</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>19508.87</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>6613.83</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>8978.23</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>21907.69</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>7488.33</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>71385.48</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1" t="n">
+        <v>79430.35000000001</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>12538.32</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>22660.42</v>
+      </c>
+      <c r="Z12" s="1" t="n">
+        <v>30448.36</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>999.46</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>1576.27</v>
+      </c>
+      <c r="AD12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1" t="n">
+        <v>9259.469999999999</v>
+      </c>
+      <c r="AF12" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" s="1" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="AH12" s="1" t="n">
+        <v>16558.85</v>
+      </c>
+      <c r="AI12" s="1" t="n">
+        <v>404.21</v>
+      </c>
+      <c r="AJ12" s="1" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AK12" s="1" t="n">
+        <v>26697.71</v>
+      </c>
+      <c r="AL12" s="1" t="n">
+        <v>1019.39</v>
+      </c>
+      <c r="AM12" s="1" t="n">
+        <v>500.28</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>393359699.58</v>
+        <v>499178452.43</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,15 +481,15 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>276450784.18</v>
+        <v>404960241.45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>USDT_THB</t>
+          <t>BTC_THB</t>
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>3252134.850426358</v>
+        <v>4864989.108762554</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>5436370.01</v>
+        <v>10239932.65</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>107008687.33</v>
+        <v>123495711.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,15 +518,15 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>58935210.07156</v>
+        <v>59970758.51794</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ETH_THB</t>
+          <t>USDT_THB</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1463968.936541992</v>
+        <v>1842293.82157506</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>2193869.3</v>
+        <v>7180224.32</v>
       </c>
     </row>
     <row r="4">
@@ -543,27 +543,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THB_DOGE</t>
+          <t>THB_ETH</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>39807681.59</v>
+        <v>70243697.03</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BNBTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>2448321.8178</v>
+        <v>3625962.366</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BTC_THB</t>
+          <t>ETH_THB</t>
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>889794.6224998767</v>
+        <v>562941.6559291828</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>800345.33</v>
+        <v>2113183.86</v>
       </c>
     </row>
     <row r="5">
@@ -580,11 +580,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THB_ETH</t>
+          <t>THB_NEAR</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>39484578.03</v>
+        <v>55080958.25</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>1946164.4838</v>
+        <v>2074765.3827</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,15 +600,15 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>319755.4287445909</v>
+        <v>396992.0773777857</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ARBTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>270334.64</v>
+        <v>301318.92</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>34006141.07</v>
+        <v>33840140.05</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1691205.0614</v>
+        <v>1276471.7137</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -637,15 +637,15 @@
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>113342.653096172</v>
+        <v>239710.4072852955</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>BCHTHB</t>
+          <t>XLMTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>186490.86</v>
+        <v>247005.45</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW12"/>
+  <dimension ref="A1:BXW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16270,6 +16270,1083 @@
         <v>2018.6</v>
       </c>
       <c r="PV12" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>499178452.43</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>123495711.99</v>
+      </c>
+      <c r="D13" s="1">
+        <f>AVERAGE(C7:C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>70243697.03</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>33840140.05</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>17885411.51</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>30726464.62</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>11260596.85</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>6575480.35</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>2498428.36</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>6730579.94</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>2915139.93</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>55080958.25</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>11258138.46</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>214802.48</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>2413358.48</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>2904016.32</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>4506467.47</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>4761764.09</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>10762266.27</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>146616.53</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>7810413.97</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>94271.92</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <v>80458.12</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>1904846.93</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>4191860.1</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <v>1232989.04</v>
+      </c>
+      <c r="AD13" s="1" t="n">
+        <v>2808688.1</v>
+      </c>
+      <c r="AE13" s="1" t="n">
+        <v>1030078.26</v>
+      </c>
+      <c r="AF13" s="1" t="n">
+        <v>2073694.16</v>
+      </c>
+      <c r="AG13" s="1" t="n">
+        <v>1982504.2</v>
+      </c>
+      <c r="AH13" s="1" t="n">
+        <v>597831.11</v>
+      </c>
+      <c r="AI13" s="1" t="n">
+        <v>3706561.63</v>
+      </c>
+      <c r="AJ13" s="1" t="n">
+        <v>435473.89</v>
+      </c>
+      <c r="AK13" s="1" t="n">
+        <v>935043.39</v>
+      </c>
+      <c r="AL13" s="1" t="n">
+        <v>2206058.1</v>
+      </c>
+      <c r="AN13" s="1" t="n">
+        <v>1861735.7</v>
+      </c>
+      <c r="AO13" s="1" t="n">
+        <v>811753.5</v>
+      </c>
+      <c r="AP13" s="1" t="n">
+        <v>190228.95</v>
+      </c>
+      <c r="AQ13" s="1" t="n">
+        <v>1715792.87</v>
+      </c>
+      <c r="AR13" s="1" t="n">
+        <v>6407713.89</v>
+      </c>
+      <c r="AS13" s="1" t="n">
+        <v>1032512.77</v>
+      </c>
+      <c r="AT13" s="1" t="n">
+        <v>3512715.18</v>
+      </c>
+      <c r="AU13" s="1" t="n">
+        <v>487393.98</v>
+      </c>
+      <c r="AV13" s="1" t="n">
+        <v>17112878.52</v>
+      </c>
+      <c r="AW13" s="1" t="n">
+        <v>1212558.11</v>
+      </c>
+      <c r="AX13" s="1" t="n">
+        <v>343416.88</v>
+      </c>
+      <c r="AY13" s="1" t="n">
+        <v>364141.59</v>
+      </c>
+      <c r="AZ13" s="1" t="n">
+        <v>1823304</v>
+      </c>
+      <c r="BA13" s="1" t="n">
+        <v>243510.19</v>
+      </c>
+      <c r="BB13" s="1" t="n">
+        <v>24213.66</v>
+      </c>
+      <c r="BC13" s="1" t="n">
+        <v>2345844.12</v>
+      </c>
+      <c r="BD13" s="1" t="n">
+        <v>561574.08</v>
+      </c>
+      <c r="BE13" s="1" t="n">
+        <v>482245.51</v>
+      </c>
+      <c r="BF13" s="1" t="n">
+        <v>1580023.15</v>
+      </c>
+      <c r="BG13" s="1" t="n">
+        <v>806.89</v>
+      </c>
+      <c r="BI13" s="1" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="BJ13" s="1" t="n">
+        <v>889813.39</v>
+      </c>
+      <c r="BK13" s="1" t="n">
+        <v>175888.78</v>
+      </c>
+      <c r="BL13" s="1" t="n">
+        <v>1717500.46</v>
+      </c>
+      <c r="BM13" s="1" t="n">
+        <v>1080589.74</v>
+      </c>
+      <c r="BN13" s="1" t="n">
+        <v>237618.45</v>
+      </c>
+      <c r="BO13" s="1" t="n">
+        <v>191786.7</v>
+      </c>
+      <c r="BP13" s="1" t="n">
+        <v>2696646.01</v>
+      </c>
+      <c r="BQ13" s="1" t="n">
+        <v>8122.12</v>
+      </c>
+      <c r="BS13" s="1" t="n">
+        <v>114814.12</v>
+      </c>
+      <c r="BT13" s="1" t="n">
+        <v>496408.93</v>
+      </c>
+      <c r="BU13" s="1" t="n">
+        <v>1025672.77</v>
+      </c>
+      <c r="BV13" s="1" t="n">
+        <v>2992602.88</v>
+      </c>
+      <c r="BW13" s="1" t="n">
+        <v>14563.42</v>
+      </c>
+      <c r="BX13" s="1" t="n">
+        <v>254.22</v>
+      </c>
+      <c r="BY13" s="1" t="n">
+        <v>1438913.48</v>
+      </c>
+      <c r="BZ13" s="1" t="n">
+        <v>30635.32</v>
+      </c>
+      <c r="CA13" s="1" t="n">
+        <v>243961.73</v>
+      </c>
+      <c r="CB13" s="1" t="n">
+        <v>8533.610000000001</v>
+      </c>
+      <c r="CC13" s="1" t="n">
+        <v>58778.26</v>
+      </c>
+      <c r="CD13" s="1" t="n">
+        <v>380662.68</v>
+      </c>
+      <c r="CE13" s="1" t="n">
+        <v>242005.29</v>
+      </c>
+      <c r="CF13" s="1" t="n">
+        <v>40451.27</v>
+      </c>
+      <c r="CG13" s="1" t="n">
+        <v>548635.4</v>
+      </c>
+      <c r="CH13" s="1" t="n">
+        <v>49527.84</v>
+      </c>
+      <c r="CI13" s="1" t="n">
+        <v>10410.87</v>
+      </c>
+      <c r="CJ13" s="1" t="n">
+        <v>3010059.98</v>
+      </c>
+      <c r="CK13" s="1" t="n">
+        <v>161321.02</v>
+      </c>
+      <c r="CL13" s="1" t="n">
+        <v>125144.53</v>
+      </c>
+      <c r="CM13" s="1" t="n">
+        <v>4362.89</v>
+      </c>
+      <c r="CN13" s="1" t="n">
+        <v>168438.53</v>
+      </c>
+      <c r="CO13" s="1" t="n">
+        <v>582025.8199999999</v>
+      </c>
+      <c r="CP13" s="1" t="n">
+        <v>594449.22</v>
+      </c>
+      <c r="CQ13" s="1" t="n">
+        <v>74994.28</v>
+      </c>
+      <c r="CR13" s="1" t="n">
+        <v>4785.69</v>
+      </c>
+      <c r="CS13" s="1" t="n">
+        <v>13901.93</v>
+      </c>
+      <c r="CT13" s="1" t="n">
+        <v>10984.81</v>
+      </c>
+      <c r="CV13" s="1" t="n">
+        <v>547249.58</v>
+      </c>
+      <c r="CW13" s="1" t="n">
+        <v>1004801.91</v>
+      </c>
+      <c r="CX13" s="1" t="n">
+        <v>159106.3</v>
+      </c>
+      <c r="CY13" s="1" t="n">
+        <v>23056.48</v>
+      </c>
+      <c r="CZ13" s="1" t="n">
+        <v>636134.71</v>
+      </c>
+      <c r="DA13" s="1" t="n">
+        <v>1105.48</v>
+      </c>
+      <c r="DB13" s="1" t="n">
+        <v>76380.69</v>
+      </c>
+      <c r="DC13" s="1" t="n">
+        <v>22158.2</v>
+      </c>
+      <c r="DD13" s="1" t="n">
+        <v>35528.07</v>
+      </c>
+      <c r="DE13" s="1" t="n">
+        <v>72792.03999999999</v>
+      </c>
+      <c r="DG13" s="1" t="n">
+        <v>342563.42</v>
+      </c>
+      <c r="DH13" s="1" t="n">
+        <v>201964.79</v>
+      </c>
+      <c r="DI13" s="1" t="n">
+        <v>234841.85</v>
+      </c>
+      <c r="DJ13" s="1" t="n">
+        <v>33236.59</v>
+      </c>
+      <c r="DK13" s="1" t="n">
+        <v>37024.1</v>
+      </c>
+      <c r="DL13" s="1" t="n">
+        <v>74027.25999999999</v>
+      </c>
+      <c r="DM13" s="1" t="n">
+        <v>101084.17</v>
+      </c>
+      <c r="DN13" s="1" t="n">
+        <v>49149.09</v>
+      </c>
+      <c r="DO13" s="1" t="n">
+        <v>2376.62</v>
+      </c>
+      <c r="DP13" s="1" t="n">
+        <v>741929.23</v>
+      </c>
+      <c r="DQ13" s="1" t="n">
+        <v>43653.4</v>
+      </c>
+      <c r="DR13" s="1" t="n">
+        <v>545299.15</v>
+      </c>
+      <c r="DS13" s="1" t="n">
+        <v>251748.53</v>
+      </c>
+      <c r="DT13" s="1" t="n">
+        <v>56610.83</v>
+      </c>
+      <c r="DV13" s="1" t="n">
+        <v>296711.44</v>
+      </c>
+      <c r="DW13" s="1" t="n">
+        <v>308424.38</v>
+      </c>
+      <c r="DX13" s="1" t="n">
+        <v>827721.33</v>
+      </c>
+      <c r="DY13" s="1" t="n">
+        <v>68647.7</v>
+      </c>
+      <c r="DZ13" s="1" t="n">
+        <v>217990.35</v>
+      </c>
+      <c r="EA13" s="1" t="n">
+        <v>24882.44</v>
+      </c>
+      <c r="EB13" s="1" t="n">
+        <v>1109.69</v>
+      </c>
+      <c r="EC13" s="1" t="n">
+        <v>175048.64</v>
+      </c>
+      <c r="ED13" s="1" t="n">
+        <v>1574520.68</v>
+      </c>
+      <c r="EE13" s="1" t="n">
+        <v>29157.47</v>
+      </c>
+      <c r="EF13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG13" s="1" t="n">
+        <v>424942.56</v>
+      </c>
+      <c r="EH13" s="1" t="n">
+        <v>118913.39</v>
+      </c>
+      <c r="EI13" s="1" t="n">
+        <v>67006.61</v>
+      </c>
+      <c r="EJ13" s="1" t="n">
+        <v>1798.26</v>
+      </c>
+      <c r="EK13" s="1" t="n">
+        <v>82643.92</v>
+      </c>
+      <c r="EL13" s="1" t="n">
+        <v>9990.98</v>
+      </c>
+      <c r="EM13" s="1" t="n">
+        <v>948.54</v>
+      </c>
+      <c r="EN13" s="1" t="n">
+        <v>5521.25</v>
+      </c>
+      <c r="EO13" s="1" t="n">
+        <v>392309.43</v>
+      </c>
+      <c r="EP13" s="1" t="n">
+        <v>5637713.1</v>
+      </c>
+      <c r="EQ13" s="1" t="n">
+        <v>13818.93</v>
+      </c>
+      <c r="ER13" s="1" t="n">
+        <v>78302.64</v>
+      </c>
+      <c r="ES13" s="1" t="n">
+        <v>10109.82</v>
+      </c>
+      <c r="ET13" s="1" t="n">
+        <v>4419.11</v>
+      </c>
+      <c r="EU13" s="1" t="n">
+        <v>62016.31</v>
+      </c>
+      <c r="EV13" s="1" t="n">
+        <v>242018.31</v>
+      </c>
+      <c r="EX13" s="1" t="n">
+        <v>411518.77</v>
+      </c>
+      <c r="EY13" s="1" t="n">
+        <v>13776.33</v>
+      </c>
+      <c r="EZ13" s="1" t="n">
+        <v>31881.72</v>
+      </c>
+      <c r="FB13" s="1" t="n">
+        <v>5147.39</v>
+      </c>
+      <c r="FC13" s="1" t="n">
+        <v>524889.1</v>
+      </c>
+      <c r="FD13" s="1" t="n">
+        <v>103304.15</v>
+      </c>
+      <c r="FE13" s="1" t="n">
+        <v>313638.81</v>
+      </c>
+      <c r="FF13" s="1" t="n">
+        <v>675.5599999999999</v>
+      </c>
+      <c r="FG13" s="1" t="n">
+        <v>319735.65</v>
+      </c>
+      <c r="FH13" s="1" t="n">
+        <v>21010.13</v>
+      </c>
+      <c r="FI13" s="1" t="n">
+        <v>56186.97</v>
+      </c>
+      <c r="FK13" s="1" t="n">
+        <v>122089.42</v>
+      </c>
+      <c r="FL13" s="1" t="n">
+        <v>397516.71</v>
+      </c>
+      <c r="FM13" s="1" t="n">
+        <v>127115.39</v>
+      </c>
+      <c r="FN13" s="1" t="n">
+        <v>15521.73</v>
+      </c>
+      <c r="FO13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" s="1" t="n">
+        <v>588.14</v>
+      </c>
+      <c r="FQ13" s="1" t="n">
+        <v>14058.61</v>
+      </c>
+      <c r="FR13" s="1" t="n">
+        <v>317209.7</v>
+      </c>
+      <c r="FS13" s="1" t="n">
+        <v>3136842.75</v>
+      </c>
+      <c r="FT13" s="1" t="n">
+        <v>46508.85</v>
+      </c>
+      <c r="FU13" s="1" t="n">
+        <v>12858.33</v>
+      </c>
+      <c r="FV13" s="1" t="n">
+        <v>234111.5</v>
+      </c>
+      <c r="FW13" s="1" t="n">
+        <v>24186.82</v>
+      </c>
+      <c r="FX13" s="1" t="n">
+        <v>3675.54</v>
+      </c>
+      <c r="FY13" s="1" t="n">
+        <v>21300.43</v>
+      </c>
+      <c r="FZ13" s="1" t="n">
+        <v>12494.97</v>
+      </c>
+      <c r="GA13" s="1" t="n">
+        <v>7004.57</v>
+      </c>
+      <c r="GB13" s="1" t="n">
+        <v>12379.18</v>
+      </c>
+      <c r="GC13" s="1" t="n">
+        <v>48814.57</v>
+      </c>
+      <c r="GD13" s="1" t="n">
+        <v>11891.38</v>
+      </c>
+      <c r="GE13" s="1" t="n">
+        <v>6280.86</v>
+      </c>
+      <c r="GF13" s="1" t="n">
+        <v>14538.23</v>
+      </c>
+      <c r="GG13" s="1" t="n">
+        <v>1220.5</v>
+      </c>
+      <c r="GH13" s="1" t="n">
+        <v>183838.79</v>
+      </c>
+      <c r="GI13" s="1" t="n">
+        <v>87603.56</v>
+      </c>
+      <c r="GJ13" s="1" t="n">
+        <v>37499.37</v>
+      </c>
+      <c r="GK13" s="1" t="n">
+        <v>614381.25</v>
+      </c>
+      <c r="GL13" s="1" t="n">
+        <v>84673.5</v>
+      </c>
+      <c r="GM13" s="1" t="n">
+        <v>108535.34</v>
+      </c>
+      <c r="GN13" s="1" t="n">
+        <v>3678.3</v>
+      </c>
+      <c r="GO13" s="1" t="n">
+        <v>164352.06</v>
+      </c>
+      <c r="GP13" s="1" t="n">
+        <v>71088.81</v>
+      </c>
+      <c r="GQ13" s="1" t="n">
+        <v>28119.18</v>
+      </c>
+      <c r="GR13" s="1" t="n">
+        <v>1726.88</v>
+      </c>
+      <c r="GS13" s="1" t="n">
+        <v>34402.91</v>
+      </c>
+      <c r="GT13" s="1" t="n">
+        <v>1072036.99</v>
+      </c>
+      <c r="GU13" s="1" t="n">
+        <v>8207.16</v>
+      </c>
+      <c r="GV13" s="1" t="n">
+        <v>68079.95</v>
+      </c>
+      <c r="GX13" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="GY13" s="1" t="n">
+        <v>10648.62</v>
+      </c>
+      <c r="GZ13" s="1" t="n">
+        <v>1468098.01</v>
+      </c>
+      <c r="HA13" s="1" t="n">
+        <v>2310.59</v>
+      </c>
+      <c r="HB13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC13" s="1" t="n">
+        <v>86679.59</v>
+      </c>
+      <c r="HD13" s="1" t="n">
+        <v>19057.41</v>
+      </c>
+      <c r="HE13" s="1" t="n">
+        <v>15490.09</v>
+      </c>
+      <c r="HF13" s="1" t="n">
+        <v>26507.1</v>
+      </c>
+      <c r="HG13" s="1" t="n">
+        <v>93468.14999999999</v>
+      </c>
+      <c r="HH13" s="1" t="n">
+        <v>1561.14</v>
+      </c>
+      <c r="HI13" s="1" t="n">
+        <v>262.41</v>
+      </c>
+      <c r="HJ13" s="1" t="n">
+        <v>30093.38</v>
+      </c>
+      <c r="HK13" s="1" t="n">
+        <v>78854.09</v>
+      </c>
+      <c r="HL13" s="1" t="n">
+        <v>40749.71</v>
+      </c>
+      <c r="HM13" s="1" t="n">
+        <v>41716.62</v>
+      </c>
+      <c r="HN13" s="1" t="n">
+        <v>77802.03</v>
+      </c>
+      <c r="HO13" s="1" t="n">
+        <v>12841.11</v>
+      </c>
+      <c r="HP13" s="1" t="n">
+        <v>57915.13</v>
+      </c>
+      <c r="HQ13" s="1" t="n">
+        <v>11847.94</v>
+      </c>
+      <c r="HR13" s="1" t="n">
+        <v>7569.6</v>
+      </c>
+      <c r="HS13" s="1" t="n">
+        <v>1074291.03</v>
+      </c>
+      <c r="HT13" s="1" t="n">
+        <v>582276.51</v>
+      </c>
+      <c r="HU13" s="1" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="HV13" s="1" t="n">
+        <v>5775.39</v>
+      </c>
+      <c r="HW13" s="1" t="n">
+        <v>54362.34</v>
+      </c>
+      <c r="HX13" s="1" t="n">
+        <v>36866.12</v>
+      </c>
+      <c r="HY13" s="1" t="n">
+        <v>17983.5</v>
+      </c>
+      <c r="HZ13" s="1" t="n">
+        <v>51928.46</v>
+      </c>
+      <c r="IA13" s="1" t="n">
+        <v>187460.71</v>
+      </c>
+      <c r="IB13" s="1" t="n">
+        <v>5068.02</v>
+      </c>
+      <c r="IC13" s="1" t="n">
+        <v>47135.78</v>
+      </c>
+      <c r="ID13" s="1" t="n">
+        <v>23033.11</v>
+      </c>
+      <c r="IE13" s="1" t="n">
+        <v>5428.89</v>
+      </c>
+      <c r="IF13" s="1" t="n">
+        <v>32335.95</v>
+      </c>
+      <c r="IG13" s="1" t="n">
+        <v>763560.14</v>
+      </c>
+      <c r="IH13" s="1" t="n">
+        <v>141772.31</v>
+      </c>
+      <c r="II13" s="1" t="n">
+        <v>1272717.72</v>
+      </c>
+      <c r="IJ13" s="1" t="n">
+        <v>32892.25</v>
+      </c>
+      <c r="IK13" s="1" t="n">
+        <v>1016276.87</v>
+      </c>
+      <c r="IL13" s="1" t="n">
+        <v>534.72</v>
+      </c>
+      <c r="IM13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IO13" s="1" t="n">
+        <v>10462.64</v>
+      </c>
+      <c r="IP13" s="1" t="n">
+        <v>11390.27</v>
+      </c>
+      <c r="IQ13" s="1" t="n">
+        <v>18116.25</v>
+      </c>
+      <c r="IR13" s="1" t="n">
+        <v>50079.02</v>
+      </c>
+      <c r="IS13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT13" s="1" t="n">
+        <v>83216.14</v>
+      </c>
+      <c r="IU13" s="1" t="n">
+        <v>142.81</v>
+      </c>
+      <c r="IV13" s="1" t="n">
+        <v>44853.32</v>
+      </c>
+      <c r="IW13" s="1" t="n">
+        <v>155687.58</v>
+      </c>
+      <c r="IX13" s="1" t="n">
+        <v>75277.47</v>
+      </c>
+      <c r="IY13" s="1" t="n">
+        <v>2323205.43</v>
+      </c>
+      <c r="IZ13" s="1" t="n">
+        <v>236.7</v>
+      </c>
+      <c r="JA13" s="1" t="n">
+        <v>7140.84</v>
+      </c>
+      <c r="JB13" s="1" t="n">
+        <v>1148.86</v>
+      </c>
+      <c r="JC13" s="1" t="n">
+        <v>678807.8</v>
+      </c>
+      <c r="JD13" s="1" t="n">
+        <v>42318.62</v>
+      </c>
+      <c r="JE13" s="1" t="n">
+        <v>205.3</v>
+      </c>
+      <c r="JF13" s="1" t="n">
+        <v>29233.16</v>
+      </c>
+      <c r="JG13" s="1" t="n">
+        <v>685588.99</v>
+      </c>
+      <c r="JH13" s="1" t="n">
+        <v>71746.00999999999</v>
+      </c>
+      <c r="JI13" s="1" t="n">
+        <v>13401.82</v>
+      </c>
+      <c r="JJ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK13" s="1" t="n">
+        <v>218321.5</v>
+      </c>
+      <c r="JM13" s="1" t="n">
+        <v>212.47</v>
+      </c>
+      <c r="JN13" s="1" t="n">
+        <v>13039.16</v>
+      </c>
+      <c r="JO13" s="1" t="n">
+        <v>3568.55</v>
+      </c>
+      <c r="JP13" s="1" t="n">
+        <v>224.87</v>
+      </c>
+      <c r="JQ13" s="1" t="n">
+        <v>148155.17</v>
+      </c>
+      <c r="JR13" s="1" t="n">
+        <v>28086.59</v>
+      </c>
+      <c r="JS13" s="1" t="n">
+        <v>371418.03</v>
+      </c>
+      <c r="JT13" s="1" t="n">
+        <v>197.02</v>
+      </c>
+      <c r="JU13" s="1" t="n">
+        <v>3772.53</v>
+      </c>
+      <c r="JV13" s="1" t="n">
+        <v>193.48</v>
+      </c>
+      <c r="JX13" s="1" t="n">
+        <v>14426.39</v>
+      </c>
+      <c r="JY13" s="1" t="n">
+        <v>31102.19</v>
+      </c>
+      <c r="JZ13" s="1" t="n">
+        <v>8359525.28</v>
+      </c>
+      <c r="KA13" s="1" t="n">
+        <v>1038.18</v>
+      </c>
+      <c r="KB13" s="1" t="n">
+        <v>38846.47</v>
+      </c>
+      <c r="KC13" s="1" t="n">
+        <v>22756.87</v>
+      </c>
+      <c r="KD13" s="1" t="n">
+        <v>59519.2</v>
+      </c>
+      <c r="KE13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KF13" s="1" t="n">
+        <v>105982</v>
+      </c>
+      <c r="KG13" s="1" t="n">
+        <v>5394.18</v>
+      </c>
+      <c r="KH13" s="1" t="n">
+        <v>18422.97</v>
+      </c>
+      <c r="KI13" s="1" t="n">
+        <v>2429.32</v>
+      </c>
+      <c r="KJ13" s="1" t="n">
+        <v>15354.81</v>
+      </c>
+      <c r="KK13" s="1" t="n">
+        <v>5688.65</v>
+      </c>
+      <c r="KM13" s="1" t="n">
+        <v>3393.33</v>
+      </c>
+      <c r="KN13" s="1" t="n">
+        <v>1358500.04</v>
+      </c>
+      <c r="KO13" s="1" t="n">
+        <v>1100079.41</v>
+      </c>
+      <c r="KP13" s="1" t="n">
+        <v>16248.68</v>
+      </c>
+      <c r="KQ13" s="1" t="n">
+        <v>398.97</v>
+      </c>
+      <c r="KR13" s="1" t="n">
+        <v>14298.65</v>
+      </c>
+      <c r="KS13" s="1" t="n">
+        <v>633660.29</v>
+      </c>
+      <c r="KT13" s="1" t="n">
+        <v>1292.74</v>
+      </c>
+      <c r="KU13" s="1" t="n">
+        <v>713.5700000000001</v>
+      </c>
+      <c r="KV13" s="1" t="n">
+        <v>129.71</v>
+      </c>
+      <c r="KW13" s="1" t="n">
+        <v>111470.76</v>
+      </c>
+      <c r="KX13" s="1" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="KY13" s="1" t="n">
+        <v>22675.27</v>
+      </c>
+      <c r="KZ13" s="1" t="n">
+        <v>519.79</v>
+      </c>
+      <c r="LA13" s="1" t="n">
+        <v>8383.27</v>
+      </c>
+      <c r="LB13" s="1" t="n">
+        <v>4987.53</v>
+      </c>
+      <c r="LC13" s="1" t="n">
+        <v>593.62</v>
+      </c>
+      <c r="LD13" s="1" t="n">
+        <v>10889.02</v>
+      </c>
+      <c r="LE13" s="1" t="n">
+        <v>2330.01</v>
+      </c>
+      <c r="LF13" s="1" t="n">
+        <v>4933.1</v>
+      </c>
+      <c r="LG13" s="1" t="n">
+        <v>41913.45</v>
+      </c>
+      <c r="LI13" s="1" t="n">
+        <v>2337.5</v>
+      </c>
+      <c r="LJ13" s="1" t="n">
+        <v>128770.53</v>
+      </c>
+      <c r="LK13" s="1" t="n">
+        <v>8950.610000000001</v>
+      </c>
+      <c r="LL13" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LO13" s="1" t="n">
+        <v>1015.81</v>
+      </c>
+      <c r="LP13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LQ13" s="1" t="n">
+        <v>565.96</v>
+      </c>
+      <c r="LR13" s="1" t="n">
+        <v>908.98</v>
+      </c>
+      <c r="LS13" s="1" t="n">
+        <v>286.6</v>
+      </c>
+      <c r="LT13" s="1" t="n">
+        <v>133038.75</v>
+      </c>
+      <c r="LU13" s="1" t="n">
+        <v>4952.36</v>
+      </c>
+      <c r="LV13" s="1" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="LW13" s="1" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="LX13" s="1" t="n">
+        <v>290.25</v>
+      </c>
+      <c r="LY13" s="1" t="n">
+        <v>14212.82</v>
+      </c>
+      <c r="LZ13" s="1" t="n">
+        <v>1155.62</v>
+      </c>
+      <c r="MA13" s="1" t="n">
+        <v>27662.28</v>
+      </c>
+      <c r="MB13" s="1" t="n">
+        <v>25337.01</v>
+      </c>
+      <c r="MC13" s="1" t="n">
+        <v>1038.08</v>
+      </c>
+      <c r="MD13" s="1" t="n">
+        <v>645.91</v>
+      </c>
+      <c r="ME13" s="1" t="n">
+        <v>131956.39</v>
+      </c>
+      <c r="MF13" s="1" t="n">
+        <v>2048.19</v>
+      </c>
+      <c r="MG13" s="1" t="n">
+        <v>111428.12</v>
+      </c>
+      <c r="MH13" s="1" t="n">
+        <v>705.42</v>
+      </c>
+      <c r="MI13" s="1" t="n">
+        <v>1001.12</v>
+      </c>
+      <c r="MJ13" s="1" t="n">
+        <v>17510.13</v>
+      </c>
+      <c r="MK13" s="1" t="n">
+        <v>115607.81</v>
+      </c>
+      <c r="ML13" s="1" t="n">
+        <v>3243.48</v>
+      </c>
+      <c r="MM13" s="1" t="n">
+        <v>1613.79</v>
+      </c>
+      <c r="MN13" s="1" t="n">
+        <v>10309.63</v>
+      </c>
+      <c r="MO13" s="1" t="n">
+        <v>11054.78</v>
+      </c>
+      <c r="MP13" s="1" t="n">
+        <v>2992.38</v>
+      </c>
+      <c r="MQ13" s="1" t="n">
+        <v>30007.81</v>
+      </c>
+      <c r="MR13" s="1" t="n">
+        <v>2802.98</v>
+      </c>
+      <c r="MS13" s="1" t="n">
+        <v>747.59</v>
+      </c>
+      <c r="MT13" s="1" t="n">
+        <v>616.14</v>
+      </c>
+      <c r="MU13" s="1" t="n">
+        <v>153553.45</v>
+      </c>
+      <c r="MV13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MW13" s="1" t="n">
+        <v>2671.32</v>
+      </c>
+      <c r="MX13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MY13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MZ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NA13" s="1" t="n">
+        <v>1022.3</v>
+      </c>
+      <c r="NB13" s="1" t="n">
+        <v>223.02</v>
+      </c>
+      <c r="NC13" s="1" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="ND13" s="1" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="NE13" s="1" t="n">
+        <v>27269.6</v>
+      </c>
+      <c r="NF13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NG13" s="1" t="n">
+        <v>3719.97</v>
+      </c>
+      <c r="NH13" s="1" t="n">
+        <v>2413.68</v>
+      </c>
+      <c r="PB13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="PK13" s="1" t="n">
+        <v>23408.07</v>
+      </c>
+      <c r="PV13" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16284,7 +17361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW12"/>
+  <dimension ref="A1:BXW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16790,6 +17867,48 @@
       </c>
       <c r="M12" s="1" t="n">
         <v>25829.995365</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>404960241.45</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>59970758.51794</v>
+      </c>
+      <c r="D13" s="1">
+        <f>AVERAGE(C7:C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>1276471.7137</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>3625962.366</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>2074765.3827</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>677779.1715000001</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>1037896.2954</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>386344.2856</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>5970.231</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>4620</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>11833.742037</v>
       </c>
     </row>
   </sheetData>
@@ -16803,7 +17922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW12"/>
+  <dimension ref="A1:BXW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20842,6 +21961,327 @@
         <v>0</v>
       </c>
       <c r="DB12" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>562941.6559291828</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>4864989.108762554</v>
+      </c>
+      <c r="D13" s="1">
+        <f>AVERAGE(C7:C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>1842293.82157506</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>51416.9830219183</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>239710.4072852955</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>396992.0773777857</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>28510.38586044365</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>25657.682</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>111922.416484136</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>26986.617</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>109.61132</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>3499.238183</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>498.6660682584</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>1463.327668704</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>98.88548046299999</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="1" t="n">
+        <v>191.3571</v>
+      </c>
+      <c r="AM13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="1" t="n">
+        <v>1029.365442416</v>
+      </c>
+      <c r="AV13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" s="1" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="BS13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB13" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20856,7 +22296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW12"/>
+  <dimension ref="A1:BXW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22239,6 +23679,126 @@
       </c>
       <c r="AM12" s="1" t="n">
         <v>500.28</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>10239932.65</v>
+      </c>
+      <c r="C13" s="1">
+        <f>AVERAGE(B7:B13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>2113183.86</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>301318.92</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>155661.14</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>22242.47</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>7180224.32</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>247005.45</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>13376.94</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>638</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>221211.55</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>5778.1</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>17273.62</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>33682.71</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>5779.1</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>13500.08</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>55485.27</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>102673.69</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>87312.21000000001</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>26195.35</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1" t="n">
+        <v>36478.24</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>531.88</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>499.95</v>
+      </c>
+      <c r="Z13" s="1" t="n">
+        <v>69907.34</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>999.92</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AD13" s="1" t="n">
+        <v>30018.89</v>
+      </c>
+      <c r="AE13" s="1" t="n">
+        <v>13052.61</v>
+      </c>
+      <c r="AF13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="1" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="AH13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="1" t="n">
+        <v>212.48</v>
+      </c>
+      <c r="AJ13" s="1" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="AK13" s="1" t="n">
+        <v>16909.63</v>
+      </c>
+      <c r="AL13" s="1" t="n">
+        <v>2783.66</v>
+      </c>
+      <c r="AM13" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>499178452.43</v>
+        <v>743734563.38</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,15 +481,15 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>404960241.45</v>
+        <v>567046652.4299999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>BTC_THB</t>
+          <t>USDT_THB</t>
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>4864989.108762554</v>
+        <v>4521657.551256294</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>10239932.65</v>
+        <v>10275044.05</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>123495711.99</v>
+        <v>141091422.78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,15 +518,15 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>59970758.51794</v>
+        <v>61491945.55025</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>USDT_THB</t>
+          <t>BTC_THB</t>
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1842293.82157506</v>
+        <v>1940421.921864982</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>7180224.32</v>
+        <v>1714556.11</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>70243697.03</v>
+        <v>49779909.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>3625962.366</v>
+        <v>2956148.8185</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>562941.6559291828</v>
+        <v>561859.33143742</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>2113183.86</v>
+        <v>1486384.69</v>
       </c>
     </row>
     <row r="5">
@@ -584,15 +584,15 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>55080958.25</v>
+        <v>30202409.61</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SOLTHB</t>
+          <t>VELOTHB</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2074765.3827</v>
+        <v>1681160.9633</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>396992.0773777857</v>
+        <v>226202.6784594208</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>301318.92</v>
+        <v>607709.98</v>
       </c>
     </row>
     <row r="6">
@@ -617,35 +617,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_XRP</t>
+          <t>THB_LUNA</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>33840140.05</v>
+        <v>28408123.99</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>BNBTHB</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1276471.7137</v>
+        <v>1413009.6093</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>XRP_THB</t>
+          <t>ADA_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>239710.4072852955</v>
+        <v>171054.4362521691</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>XLMTHB</t>
+          <t>ARBTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>247005.45</v>
+        <v>250509.59</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW13"/>
+  <dimension ref="A1:BXW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17347,6 +17347,1083 @@
         <v>23408.07</v>
       </c>
       <c r="PV13" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>743734563.38</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>141091422.78</v>
+      </c>
+      <c r="D14" s="1">
+        <f>AVERAGE(C8:C14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>49779909.55</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>23245394.65</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>12830226.86</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>23447425.4</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>10475748.64</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>28408123.99</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>3028451.51</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>9123654.619999999</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>2109544.57</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>30202409.61</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>9142376.51</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>175058.28</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>3269430.39</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>2029503.73</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>17506175.52</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>5421359.24</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>6150753.62</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>10450.56</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>4637671.49</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>151883.92</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>241323.31</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>3906042.36</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>5594724.93</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>1217338.87</v>
+      </c>
+      <c r="AD14" s="1" t="n">
+        <v>1592980.75</v>
+      </c>
+      <c r="AE14" s="1" t="n">
+        <v>560284.34</v>
+      </c>
+      <c r="AF14" s="1" t="n">
+        <v>1706861.82</v>
+      </c>
+      <c r="AG14" s="1" t="n">
+        <v>1235114.94</v>
+      </c>
+      <c r="AH14" s="1" t="n">
+        <v>535708.53</v>
+      </c>
+      <c r="AI14" s="1" t="n">
+        <v>1933035.51</v>
+      </c>
+      <c r="AJ14" s="1" t="n">
+        <v>1735537.58</v>
+      </c>
+      <c r="AK14" s="1" t="n">
+        <v>294668.45</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>3592773.61</v>
+      </c>
+      <c r="AN14" s="1" t="n">
+        <v>3628629.24</v>
+      </c>
+      <c r="AO14" s="1" t="n">
+        <v>399639.29</v>
+      </c>
+      <c r="AP14" s="1" t="n">
+        <v>1856694.29</v>
+      </c>
+      <c r="AQ14" s="1" t="n">
+        <v>679255.24</v>
+      </c>
+      <c r="AR14" s="1" t="n">
+        <v>5331420.17</v>
+      </c>
+      <c r="AS14" s="1" t="n">
+        <v>239520.4</v>
+      </c>
+      <c r="AT14" s="1" t="n">
+        <v>7732315.63</v>
+      </c>
+      <c r="AU14" s="1" t="n">
+        <v>811336.05</v>
+      </c>
+      <c r="AV14" s="1" t="n">
+        <v>4684022.81</v>
+      </c>
+      <c r="AW14" s="1" t="n">
+        <v>2220091.48</v>
+      </c>
+      <c r="AX14" s="1" t="n">
+        <v>474180.41</v>
+      </c>
+      <c r="AY14" s="1" t="n">
+        <v>256935.16</v>
+      </c>
+      <c r="AZ14" s="1" t="n">
+        <v>2268373.01</v>
+      </c>
+      <c r="BA14" s="1" t="n">
+        <v>177139.33</v>
+      </c>
+      <c r="BB14" s="1" t="n">
+        <v>56289.77</v>
+      </c>
+      <c r="BC14" s="1" t="n">
+        <v>1772211.83</v>
+      </c>
+      <c r="BD14" s="1" t="n">
+        <v>1866966.14</v>
+      </c>
+      <c r="BE14" s="1" t="n">
+        <v>188297.37</v>
+      </c>
+      <c r="BF14" s="1" t="n">
+        <v>3048169.87</v>
+      </c>
+      <c r="BG14" s="1" t="n">
+        <v>806.89</v>
+      </c>
+      <c r="BI14" s="1" t="n">
+        <v>9815.860000000001</v>
+      </c>
+      <c r="BJ14" s="1" t="n">
+        <v>1231404.43</v>
+      </c>
+      <c r="BK14" s="1" t="n">
+        <v>266385.01</v>
+      </c>
+      <c r="BL14" s="1" t="n">
+        <v>1657252.24</v>
+      </c>
+      <c r="BM14" s="1" t="n">
+        <v>2914605.35</v>
+      </c>
+      <c r="BN14" s="1" t="n">
+        <v>918835.29</v>
+      </c>
+      <c r="BO14" s="1" t="n">
+        <v>110989.81</v>
+      </c>
+      <c r="BP14" s="1" t="n">
+        <v>11839169.1</v>
+      </c>
+      <c r="BQ14" s="1" t="n">
+        <v>1679.93</v>
+      </c>
+      <c r="BS14" s="1" t="n">
+        <v>292754.94</v>
+      </c>
+      <c r="BT14" s="1" t="n">
+        <v>166015.59</v>
+      </c>
+      <c r="BU14" s="1" t="n">
+        <v>1255086.15</v>
+      </c>
+      <c r="BV14" s="1" t="n">
+        <v>2478065.75</v>
+      </c>
+      <c r="BW14" s="1" t="n">
+        <v>20981.06</v>
+      </c>
+      <c r="BX14" s="1" t="n">
+        <v>4104.3</v>
+      </c>
+      <c r="BY14" s="1" t="n">
+        <v>432572.75</v>
+      </c>
+      <c r="BZ14" s="1" t="n">
+        <v>31074.91</v>
+      </c>
+      <c r="CA14" s="1" t="n">
+        <v>91080.2</v>
+      </c>
+      <c r="CB14" s="1" t="n">
+        <v>192.47</v>
+      </c>
+      <c r="CC14" s="1" t="n">
+        <v>46510.6</v>
+      </c>
+      <c r="CD14" s="1" t="n">
+        <v>747468.03</v>
+      </c>
+      <c r="CE14" s="1" t="n">
+        <v>178572.54</v>
+      </c>
+      <c r="CF14" s="1" t="n">
+        <v>33004.96</v>
+      </c>
+      <c r="CG14" s="1" t="n">
+        <v>624613.6</v>
+      </c>
+      <c r="CH14" s="1" t="n">
+        <v>64230.44</v>
+      </c>
+      <c r="CI14" s="1" t="n">
+        <v>15023.24</v>
+      </c>
+      <c r="CJ14" s="1" t="n">
+        <v>894087.1800000001</v>
+      </c>
+      <c r="CK14" s="1" t="n">
+        <v>50094.44</v>
+      </c>
+      <c r="CL14" s="1" t="n">
+        <v>193940.44</v>
+      </c>
+      <c r="CM14" s="1" t="n">
+        <v>13911.31</v>
+      </c>
+      <c r="CN14" s="1" t="n">
+        <v>57831.75</v>
+      </c>
+      <c r="CO14" s="1" t="n">
+        <v>105501.45</v>
+      </c>
+      <c r="CP14" s="1" t="n">
+        <v>952205.58</v>
+      </c>
+      <c r="CQ14" s="1" t="n">
+        <v>113639.12</v>
+      </c>
+      <c r="CR14" s="1" t="n">
+        <v>3750</v>
+      </c>
+      <c r="CS14" s="1" t="n">
+        <v>3847.14</v>
+      </c>
+      <c r="CT14" s="1" t="n">
+        <v>31125.34</v>
+      </c>
+      <c r="CV14" s="1" t="n">
+        <v>346431.21</v>
+      </c>
+      <c r="CW14" s="1" t="n">
+        <v>670602.88</v>
+      </c>
+      <c r="CX14" s="1" t="n">
+        <v>219023.11</v>
+      </c>
+      <c r="CY14" s="1" t="n">
+        <v>26393.78</v>
+      </c>
+      <c r="CZ14" s="1" t="n">
+        <v>1391635.05</v>
+      </c>
+      <c r="DA14" s="1" t="n">
+        <v>22016.09</v>
+      </c>
+      <c r="DB14" s="1" t="n">
+        <v>253326.48</v>
+      </c>
+      <c r="DC14" s="1" t="n">
+        <v>190235.01</v>
+      </c>
+      <c r="DD14" s="1" t="n">
+        <v>124040.36</v>
+      </c>
+      <c r="DE14" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="DG14" s="1" t="n">
+        <v>246973.1</v>
+      </c>
+      <c r="DH14" s="1" t="n">
+        <v>119621.75</v>
+      </c>
+      <c r="DI14" s="1" t="n">
+        <v>122412.05</v>
+      </c>
+      <c r="DJ14" s="1" t="n">
+        <v>755158.29</v>
+      </c>
+      <c r="DK14" s="1" t="n">
+        <v>33455.8</v>
+      </c>
+      <c r="DL14" s="1" t="n">
+        <v>92538.2</v>
+      </c>
+      <c r="DM14" s="1" t="n">
+        <v>304719.26</v>
+      </c>
+      <c r="DN14" s="1" t="n">
+        <v>55619.75</v>
+      </c>
+      <c r="DO14" s="1" t="n">
+        <v>6245.66</v>
+      </c>
+      <c r="DP14" s="1" t="n">
+        <v>40861.16</v>
+      </c>
+      <c r="DQ14" s="1" t="n">
+        <v>97794.49000000001</v>
+      </c>
+      <c r="DR14" s="1" t="n">
+        <v>715958.13</v>
+      </c>
+      <c r="DS14" s="1" t="n">
+        <v>270018.19</v>
+      </c>
+      <c r="DT14" s="1" t="n">
+        <v>38980.67</v>
+      </c>
+      <c r="DV14" s="1" t="n">
+        <v>364602.03</v>
+      </c>
+      <c r="DW14" s="1" t="n">
+        <v>111504.52</v>
+      </c>
+      <c r="DX14" s="1" t="n">
+        <v>1150656.49</v>
+      </c>
+      <c r="DY14" s="1" t="n">
+        <v>46956.66</v>
+      </c>
+      <c r="DZ14" s="1" t="n">
+        <v>124562.46</v>
+      </c>
+      <c r="EA14" s="1" t="n">
+        <v>16041.74</v>
+      </c>
+      <c r="EB14" s="1" t="n">
+        <v>1115.67</v>
+      </c>
+      <c r="EC14" s="1" t="n">
+        <v>49419.86</v>
+      </c>
+      <c r="ED14" s="1" t="n">
+        <v>387324.38</v>
+      </c>
+      <c r="EE14" s="1" t="n">
+        <v>79991.25999999999</v>
+      </c>
+      <c r="EF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG14" s="1" t="n">
+        <v>36697.46</v>
+      </c>
+      <c r="EH14" s="1" t="n">
+        <v>95781.02</v>
+      </c>
+      <c r="EI14" s="1" t="n">
+        <v>75407.05</v>
+      </c>
+      <c r="EJ14" s="1" t="n">
+        <v>5781.17</v>
+      </c>
+      <c r="EK14" s="1" t="n">
+        <v>120242.17</v>
+      </c>
+      <c r="EL14" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="EM14" s="1" t="n">
+        <v>948.54</v>
+      </c>
+      <c r="EN14" s="1" t="n">
+        <v>60046.32</v>
+      </c>
+      <c r="EO14" s="1" t="n">
+        <v>280567.88</v>
+      </c>
+      <c r="EP14" s="1" t="n">
+        <v>2528560.37</v>
+      </c>
+      <c r="EQ14" s="1" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="ER14" s="1" t="n">
+        <v>80294.74000000001</v>
+      </c>
+      <c r="ES14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET14" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="EU14" s="1" t="n">
+        <v>92756.67</v>
+      </c>
+      <c r="EV14" s="1" t="n">
+        <v>198766.3</v>
+      </c>
+      <c r="EX14" s="1" t="n">
+        <v>916651.59</v>
+      </c>
+      <c r="EY14" s="1" t="n">
+        <v>14228.7</v>
+      </c>
+      <c r="EZ14" s="1" t="n">
+        <v>29792.26</v>
+      </c>
+      <c r="FB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC14" s="1" t="n">
+        <v>23361.46</v>
+      </c>
+      <c r="FD14" s="1" t="n">
+        <v>83817.64</v>
+      </c>
+      <c r="FE14" s="1" t="n">
+        <v>73476.64999999999</v>
+      </c>
+      <c r="FF14" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="FG14" s="1" t="n">
+        <v>599699.37</v>
+      </c>
+      <c r="FH14" s="1" t="n">
+        <v>75221.03999999999</v>
+      </c>
+      <c r="FI14" s="1" t="n">
+        <v>49872.16</v>
+      </c>
+      <c r="FK14" s="1" t="n">
+        <v>40002.43</v>
+      </c>
+      <c r="FL14" s="1" t="n">
+        <v>2284979.4</v>
+      </c>
+      <c r="FM14" s="1" t="n">
+        <v>275951.52</v>
+      </c>
+      <c r="FN14" s="1" t="n">
+        <v>2684.12</v>
+      </c>
+      <c r="FO14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" s="1" t="n">
+        <v>2080.18</v>
+      </c>
+      <c r="FQ14" s="1" t="n">
+        <v>2365.54</v>
+      </c>
+      <c r="FR14" s="1" t="n">
+        <v>372323.47</v>
+      </c>
+      <c r="FS14" s="1" t="n">
+        <v>2944638.21</v>
+      </c>
+      <c r="FT14" s="1" t="n">
+        <v>4227.8</v>
+      </c>
+      <c r="FU14" s="1" t="n">
+        <v>20442.92</v>
+      </c>
+      <c r="FV14" s="1" t="n">
+        <v>422928.78</v>
+      </c>
+      <c r="FW14" s="1" t="n">
+        <v>9663.57</v>
+      </c>
+      <c r="FX14" s="1" t="n">
+        <v>58127.58</v>
+      </c>
+      <c r="FY14" s="1" t="n">
+        <v>35919.03</v>
+      </c>
+      <c r="FZ14" s="1" t="n">
+        <v>424.27</v>
+      </c>
+      <c r="GA14" s="1" t="n">
+        <v>1598.97</v>
+      </c>
+      <c r="GB14" s="1" t="n">
+        <v>30589.59</v>
+      </c>
+      <c r="GC14" s="1" t="n">
+        <v>10242.5</v>
+      </c>
+      <c r="GD14" s="1" t="n">
+        <v>248.35</v>
+      </c>
+      <c r="GE14" s="1" t="n">
+        <v>4905.96</v>
+      </c>
+      <c r="GF14" s="1" t="n">
+        <v>53758.55</v>
+      </c>
+      <c r="GG14" s="1" t="n">
+        <v>498.18</v>
+      </c>
+      <c r="GH14" s="1" t="n">
+        <v>96493.33</v>
+      </c>
+      <c r="GI14" s="1" t="n">
+        <v>186618.32</v>
+      </c>
+      <c r="GJ14" s="1" t="n">
+        <v>6115.57</v>
+      </c>
+      <c r="GK14" s="1" t="n">
+        <v>267944.11</v>
+      </c>
+      <c r="GL14" s="1" t="n">
+        <v>1132.3</v>
+      </c>
+      <c r="GM14" s="1" t="n">
+        <v>1117983.81</v>
+      </c>
+      <c r="GN14" s="1" t="n">
+        <v>1319.23</v>
+      </c>
+      <c r="GO14" s="1" t="n">
+        <v>55883.89</v>
+      </c>
+      <c r="GP14" s="1" t="n">
+        <v>18165.52</v>
+      </c>
+      <c r="GQ14" s="1" t="n">
+        <v>86563.31</v>
+      </c>
+      <c r="GR14" s="1" t="n">
+        <v>76467.94</v>
+      </c>
+      <c r="GS14" s="1" t="n">
+        <v>34402.91</v>
+      </c>
+      <c r="GT14" s="1" t="n">
+        <v>562435.73</v>
+      </c>
+      <c r="GU14" s="1" t="n">
+        <v>3561.51</v>
+      </c>
+      <c r="GV14" s="1" t="n">
+        <v>723681.9</v>
+      </c>
+      <c r="GX14" s="1" t="n">
+        <v>428.11</v>
+      </c>
+      <c r="GY14" s="1" t="n">
+        <v>295515.97</v>
+      </c>
+      <c r="GZ14" s="1" t="n">
+        <v>109022.86</v>
+      </c>
+      <c r="HA14" s="1" t="n">
+        <v>2310.59</v>
+      </c>
+      <c r="HB14" s="1" t="n">
+        <v>263.69</v>
+      </c>
+      <c r="HC14" s="1" t="n">
+        <v>5578.96</v>
+      </c>
+      <c r="HD14" s="1" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="HE14" s="1" t="n">
+        <v>17096.11</v>
+      </c>
+      <c r="HF14" s="1" t="n">
+        <v>16774.58</v>
+      </c>
+      <c r="HG14" s="1" t="n">
+        <v>14319.37</v>
+      </c>
+      <c r="HH14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HI14" s="1" t="n">
+        <v>69328.42</v>
+      </c>
+      <c r="HJ14" s="1" t="n">
+        <v>38154.24</v>
+      </c>
+      <c r="HK14" s="1" t="n">
+        <v>107563.9</v>
+      </c>
+      <c r="HL14" s="1" t="n">
+        <v>9436.549999999999</v>
+      </c>
+      <c r="HM14" s="1" t="n">
+        <v>5528.46</v>
+      </c>
+      <c r="HN14" s="1" t="n">
+        <v>34781.87</v>
+      </c>
+      <c r="HO14" s="1" t="n">
+        <v>10172.78</v>
+      </c>
+      <c r="HP14" s="1" t="n">
+        <v>20673.8</v>
+      </c>
+      <c r="HQ14" s="1" t="n">
+        <v>39134.84</v>
+      </c>
+      <c r="HR14" s="1" t="n">
+        <v>198504.48</v>
+      </c>
+      <c r="HS14" s="1" t="n">
+        <v>8340.48</v>
+      </c>
+      <c r="HT14" s="1" t="n">
+        <v>73517.99000000001</v>
+      </c>
+      <c r="HU14" s="1" t="n">
+        <v>2149.96</v>
+      </c>
+      <c r="HV14" s="1" t="n">
+        <v>13778.45</v>
+      </c>
+      <c r="HW14" s="1" t="n">
+        <v>46120.29</v>
+      </c>
+      <c r="HX14" s="1" t="n">
+        <v>108896.92</v>
+      </c>
+      <c r="HY14" s="1" t="n">
+        <v>28611.13</v>
+      </c>
+      <c r="HZ14" s="1" t="n">
+        <v>76464.69</v>
+      </c>
+      <c r="IA14" s="1" t="n">
+        <v>24143.57</v>
+      </c>
+      <c r="IB14" s="1" t="n">
+        <v>38204.32</v>
+      </c>
+      <c r="IC14" s="1" t="n">
+        <v>976.92</v>
+      </c>
+      <c r="ID14" s="1" t="n">
+        <v>31660.13</v>
+      </c>
+      <c r="IE14" s="1" t="n">
+        <v>32341.75</v>
+      </c>
+      <c r="IF14" s="1" t="n">
+        <v>79879.98</v>
+      </c>
+      <c r="IG14" s="1" t="n">
+        <v>408614.23</v>
+      </c>
+      <c r="IH14" s="1" t="n">
+        <v>110611.46</v>
+      </c>
+      <c r="II14" s="1" t="n">
+        <v>74169.36</v>
+      </c>
+      <c r="IJ14" s="1" t="n">
+        <v>192834.34</v>
+      </c>
+      <c r="IK14" s="1" t="n">
+        <v>256394.79</v>
+      </c>
+      <c r="IL14" s="1" t="n">
+        <v>9894.389999999999</v>
+      </c>
+      <c r="IM14" s="1" t="n">
+        <v>171.05</v>
+      </c>
+      <c r="IN14" s="1" t="n">
+        <v>1082.68</v>
+      </c>
+      <c r="IO14" s="1" t="n">
+        <v>310262.85</v>
+      </c>
+      <c r="IP14" s="1" t="n">
+        <v>12417.41</v>
+      </c>
+      <c r="IQ14" s="1" t="n">
+        <v>31722.18</v>
+      </c>
+      <c r="IR14" s="1" t="n">
+        <v>100975.71</v>
+      </c>
+      <c r="IS14" s="1" t="n">
+        <v>659.52</v>
+      </c>
+      <c r="IT14" s="1" t="n">
+        <v>19477.39</v>
+      </c>
+      <c r="IU14" s="1" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="IV14" s="1" t="n">
+        <v>39171.65</v>
+      </c>
+      <c r="IW14" s="1" t="n">
+        <v>225316.64</v>
+      </c>
+      <c r="IX14" s="1" t="n">
+        <v>402751.52</v>
+      </c>
+      <c r="IY14" s="1" t="n">
+        <v>3656129.52</v>
+      </c>
+      <c r="IZ14" s="1" t="n">
+        <v>15665.76</v>
+      </c>
+      <c r="JA14" s="1" t="n">
+        <v>1982.59</v>
+      </c>
+      <c r="JB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JC14" s="1" t="n">
+        <v>59151.97</v>
+      </c>
+      <c r="JD14" s="1" t="n">
+        <v>4923.34</v>
+      </c>
+      <c r="JE14" s="1" t="n">
+        <v>205.3</v>
+      </c>
+      <c r="JF14" s="1" t="n">
+        <v>52522.73</v>
+      </c>
+      <c r="JG14" s="1" t="n">
+        <v>2472193.37</v>
+      </c>
+      <c r="JH14" s="1" t="n">
+        <v>31423.78</v>
+      </c>
+      <c r="JI14" s="1" t="n">
+        <v>10698.95</v>
+      </c>
+      <c r="JJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK14" s="1" t="n">
+        <v>170678.11</v>
+      </c>
+      <c r="JM14" s="1" t="n">
+        <v>277.76</v>
+      </c>
+      <c r="JN14" s="1" t="n">
+        <v>10880.88</v>
+      </c>
+      <c r="JO14" s="1" t="n">
+        <v>3568.55</v>
+      </c>
+      <c r="JP14" s="1" t="n">
+        <v>103.93</v>
+      </c>
+      <c r="JQ14" s="1" t="n">
+        <v>3114.62</v>
+      </c>
+      <c r="JR14" s="1" t="n">
+        <v>1499.07</v>
+      </c>
+      <c r="JS14" s="1" t="n">
+        <v>110763.33</v>
+      </c>
+      <c r="JT14" s="1" t="n">
+        <v>11526.46</v>
+      </c>
+      <c r="JU14" s="1" t="n">
+        <v>73821.32000000001</v>
+      </c>
+      <c r="JV14" s="1" t="n">
+        <v>24770.86</v>
+      </c>
+      <c r="JX14" s="1" t="n">
+        <v>20090.08</v>
+      </c>
+      <c r="JY14" s="1" t="n">
+        <v>21010.78</v>
+      </c>
+      <c r="JZ14" s="1" t="n">
+        <v>3616119.7</v>
+      </c>
+      <c r="KA14" s="1" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="KB14" s="1" t="n">
+        <v>105384.32</v>
+      </c>
+      <c r="KC14" s="1" t="n">
+        <v>9216.370000000001</v>
+      </c>
+      <c r="KD14" s="1" t="n">
+        <v>59519.2</v>
+      </c>
+      <c r="KE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KF14" s="1" t="n">
+        <v>130140.85</v>
+      </c>
+      <c r="KG14" s="1" t="n">
+        <v>8751.540000000001</v>
+      </c>
+      <c r="KH14" s="1" t="n">
+        <v>12898.42</v>
+      </c>
+      <c r="KI14" s="1" t="n">
+        <v>897.6</v>
+      </c>
+      <c r="KJ14" s="1" t="n">
+        <v>33279.97</v>
+      </c>
+      <c r="KK14" s="1" t="n">
+        <v>5688.65</v>
+      </c>
+      <c r="KM14" s="1" t="n">
+        <v>2051.22</v>
+      </c>
+      <c r="KN14" s="1" t="n">
+        <v>304945.55</v>
+      </c>
+      <c r="KO14" s="1" t="n">
+        <v>68415.42</v>
+      </c>
+      <c r="KP14" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="KQ14" s="1" t="n">
+        <v>984.08</v>
+      </c>
+      <c r="KR14" s="1" t="n">
+        <v>4485.73</v>
+      </c>
+      <c r="KS14" s="1" t="n">
+        <v>159684.51</v>
+      </c>
+      <c r="KT14" s="1" t="n">
+        <v>9749.99</v>
+      </c>
+      <c r="KU14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KV14" s="1" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="KW14" s="1" t="n">
+        <v>30783.6</v>
+      </c>
+      <c r="KX14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KY14" s="1" t="n">
+        <v>16111.94</v>
+      </c>
+      <c r="KZ14" s="1" t="n">
+        <v>20165</v>
+      </c>
+      <c r="LA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LB14" s="1" t="n">
+        <v>3495.22</v>
+      </c>
+      <c r="LC14" s="1" t="n">
+        <v>593.62</v>
+      </c>
+      <c r="LD14" s="1" t="n">
+        <v>170479.62</v>
+      </c>
+      <c r="LE14" s="1" t="n">
+        <v>716.8200000000001</v>
+      </c>
+      <c r="LF14" s="1" t="n">
+        <v>4933.1</v>
+      </c>
+      <c r="LG14" s="1" t="n">
+        <v>2740.44</v>
+      </c>
+      <c r="LI14" s="1" t="n">
+        <v>20063.04</v>
+      </c>
+      <c r="LJ14" s="1" t="n">
+        <v>198836.6</v>
+      </c>
+      <c r="LK14" s="1" t="n">
+        <v>20861.28</v>
+      </c>
+      <c r="LL14" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LO14" s="1" t="n">
+        <v>1015.81</v>
+      </c>
+      <c r="LP14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LQ14" s="1" t="n">
+        <v>661.5700000000001</v>
+      </c>
+      <c r="LR14" s="1" t="n">
+        <v>6186.33</v>
+      </c>
+      <c r="LS14" s="1" t="n">
+        <v>887.28</v>
+      </c>
+      <c r="LT14" s="1" t="n">
+        <v>133038.75</v>
+      </c>
+      <c r="LU14" s="1" t="n">
+        <v>4952.36</v>
+      </c>
+      <c r="LV14" s="1" t="n">
+        <v>1347.36</v>
+      </c>
+      <c r="LW14" s="1" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="LX14" s="1" t="n">
+        <v>641.11</v>
+      </c>
+      <c r="LY14" s="1" t="n">
+        <v>876.99</v>
+      </c>
+      <c r="LZ14" s="1" t="n">
+        <v>8598.370000000001</v>
+      </c>
+      <c r="MA14" s="1" t="n">
+        <v>36557.43</v>
+      </c>
+      <c r="MB14" s="1" t="n">
+        <v>13260.51</v>
+      </c>
+      <c r="MC14" s="1" t="n">
+        <v>1947.13</v>
+      </c>
+      <c r="MD14" s="1" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="ME14" s="1" t="n">
+        <v>30210.65</v>
+      </c>
+      <c r="MF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MG14" s="1" t="n">
+        <v>2268.89</v>
+      </c>
+      <c r="MH14" s="1" t="n">
+        <v>4726.01</v>
+      </c>
+      <c r="MI14" s="1" t="n">
+        <v>337.15</v>
+      </c>
+      <c r="MJ14" s="1" t="n">
+        <v>6345.41</v>
+      </c>
+      <c r="MK14" s="1" t="n">
+        <v>115647.71</v>
+      </c>
+      <c r="ML14" s="1" t="n">
+        <v>6020.01</v>
+      </c>
+      <c r="MM14" s="1" t="n">
+        <v>3171.14</v>
+      </c>
+      <c r="MN14" s="1" t="n">
+        <v>209.02</v>
+      </c>
+      <c r="MO14" s="1" t="n">
+        <v>11909.36</v>
+      </c>
+      <c r="MP14" s="1" t="n">
+        <v>434.75</v>
+      </c>
+      <c r="MQ14" s="1" t="n">
+        <v>199.33</v>
+      </c>
+      <c r="MR14" s="1" t="n">
+        <v>672.11</v>
+      </c>
+      <c r="MS14" s="1" t="n">
+        <v>1373.68</v>
+      </c>
+      <c r="MT14" s="1" t="n">
+        <v>58079.56</v>
+      </c>
+      <c r="MU14" s="1" t="n">
+        <v>1913.56</v>
+      </c>
+      <c r="MV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MW14" s="1" t="n">
+        <v>11341.91</v>
+      </c>
+      <c r="MX14" s="1" t="n">
+        <v>160.27</v>
+      </c>
+      <c r="MY14" s="1" t="n">
+        <v>253.02</v>
+      </c>
+      <c r="MZ14" s="1" t="n">
+        <v>81490.64999999999</v>
+      </c>
+      <c r="NA14" s="1" t="n">
+        <v>898.28</v>
+      </c>
+      <c r="NB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NC14" s="1" t="n">
+        <v>3968.7</v>
+      </c>
+      <c r="ND14" s="1" t="n">
+        <v>6229.45</v>
+      </c>
+      <c r="NE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NF14" s="1" t="n">
+        <v>3491.09</v>
+      </c>
+      <c r="NG14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NH14" s="1" t="n">
+        <v>368270.34</v>
+      </c>
+      <c r="PB14" s="1" t="n">
+        <v>2125.42</v>
+      </c>
+      <c r="PK14" s="1" t="n">
+        <v>7867.37</v>
+      </c>
+      <c r="PV14" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17361,7 +18438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW13"/>
+  <dimension ref="A1:BXW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17909,6 +18986,48 @@
       </c>
       <c r="M13" s="1" t="n">
         <v>11833.742037</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>567046652.4299999</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>61491945.55025</v>
+      </c>
+      <c r="D14" s="1">
+        <f>AVERAGE(C8:C14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>927634.8152</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>2956148.8185</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>1030913.53</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>1413009.6093</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>1681160.9633</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>249796.64</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>9350.1844</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>5323.8676</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>29176.45017</v>
       </c>
     </row>
   </sheetData>
@@ -17922,7 +19041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW13"/>
+  <dimension ref="A1:BXW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22282,6 +23401,327 @@
         <v>0</v>
       </c>
       <c r="DB13" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>561859.33143742</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>1940421.921864982</v>
+      </c>
+      <c r="D14" s="1">
+        <f>AVERAGE(C8:C14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>4521657.551256294</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>171054.4362521691</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>147181.4121479465</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>226202.6784594208</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>11698.72682095696</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>4900.74</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>53366.9738733569</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>100344.628</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>416.15361</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>11207.9487521898</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>5.870559</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>383.0636490117</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>249.946640648</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>1484.8580039532</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="1" t="n">
+        <v>13.892836</v>
+      </c>
+      <c r="AG14" s="1" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>51.77985624</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="1" t="n">
+        <v>10.474068</v>
+      </c>
+      <c r="AV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" s="1" t="n">
+        <v>17.723</v>
+      </c>
+      <c r="BS14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" s="1" t="n">
+        <v>997.5342000000001</v>
+      </c>
+      <c r="CE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" s="1" t="n">
+        <v>498.6659506669</v>
+      </c>
+      <c r="CH14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ14" s="1" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CK14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="CM14" s="1" t="n">
+        <v>27.533</v>
+      </c>
+      <c r="CN14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO14" s="1" t="n">
+        <v>24.93330315</v>
+      </c>
+      <c r="CP14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX14" s="1" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="CY14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22296,7 +23736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW13"/>
+  <dimension ref="A1:BXW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23799,6 +25239,126 @@
       </c>
       <c r="AM13" s="1" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>10275044.05</v>
+      </c>
+      <c r="C14" s="1">
+        <f>AVERAGE(B8:B14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>1486384.69</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>607709.98</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>240583.83</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>1714556.11</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>187425.18</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>153373.5</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>3162.54</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>250509.59</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>115715.7</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>29607.54</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>20000.24</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>51584.75</v>
+      </c>
+      <c r="S14" s="1" t="n">
+        <v>66250.66</v>
+      </c>
+      <c r="T14" s="1" t="n">
+        <v>78745.89</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>74712.8</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>855.75</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>168284.75</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>13576.94</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>3040.36</v>
+      </c>
+      <c r="Z14" s="1" t="n">
+        <v>493.9</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>7711.76</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="1" t="n">
+        <v>10230.5</v>
+      </c>
+      <c r="AH14" s="1" t="n">
+        <v>10095.15</v>
+      </c>
+      <c r="AI14" s="1" t="n">
+        <v>2940.4</v>
+      </c>
+      <c r="AJ14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="1" t="n">
+        <v>32563.71</v>
+      </c>
+      <c r="AL14" s="1" t="n">
+        <v>1757.86</v>
+      </c>
+      <c r="AM14" s="1" t="n">
+        <v>32518.21</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>743734563.38</v>
+        <v>696817045.27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>567046652.4299999</v>
+        <v>454310270.59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>4521657.551256294</v>
+        <v>4789464.493483041</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>10275044.05</v>
+        <v>7135431.82</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>141091422.78</v>
+        <v>134616439.06</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>61491945.55025</v>
+        <v>47308048.32616</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -526,15 +526,15 @@
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1940421.921864982</v>
+        <v>2752780.079370858</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>USDTTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>1714556.11</v>
+        <v>4943095.09</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>49779909.55</v>
+        <v>66085036.51</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>2956148.8185</v>
+        <v>4086130.9988</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -563,15 +563,15 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>561859.33143742</v>
+        <v>620506.5203042141</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1486384.69</v>
+        <v>1349106.95</v>
       </c>
     </row>
     <row r="5">
@@ -580,19 +580,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THB_NEAR</t>
+          <t>THB_XRP</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>30202409.61</v>
+        <v>50239067.23</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VELOTHB</t>
+          <t>BNBTHB</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>1681160.9633</v>
+        <v>2362150.2131</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,15 +600,15 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>226202.6784594208</v>
+        <v>259237.248161976</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>USDTTHB</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>607709.98</v>
+        <v>1305603.13</v>
       </c>
     </row>
     <row r="6">
@@ -617,35 +617,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_LUNA</t>
+          <t>THB_NEAR</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>28408123.99</v>
+        <v>30809792.71</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BNBTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1413009.6093</v>
+        <v>2067904.4892</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ADA_THB</t>
+          <t>XRP_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>171054.4362521691</v>
+        <v>168508.4952940393</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ARBTHB</t>
+          <t>ADATHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>250509.59</v>
+        <v>911852.8</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW14"/>
+  <dimension ref="A1:BXW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18425,6 +18425,1083 @@
       </c>
       <c r="PV14" s="1" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>696817045.27</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>134616439.06</v>
+      </c>
+      <c r="D15" s="1">
+        <f>AVERAGE(C9:C15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>66085036.51</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>50239067.23</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>8247786.9</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>21098847.54</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>13417033.39</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>8359743.86</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>4351868.64</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>7780527.04</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>2556620.57</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>30809792.71</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>18346004.86</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>655088.6</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>3035392.9</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>2204030.09</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>6933078.27</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>5453279.35</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>5418222.67</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>31782.06</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>8554439.42</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>408794.73</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>220327.36</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>1525949.29</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>7806698.72</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>2732105.34</v>
+      </c>
+      <c r="AD15" s="1" t="n">
+        <v>2345309.55</v>
+      </c>
+      <c r="AE15" s="1" t="n">
+        <v>610144.04</v>
+      </c>
+      <c r="AF15" s="1" t="n">
+        <v>1229914.58</v>
+      </c>
+      <c r="AG15" s="1" t="n">
+        <v>515096.05</v>
+      </c>
+      <c r="AH15" s="1" t="n">
+        <v>242505.3</v>
+      </c>
+      <c r="AI15" s="1" t="n">
+        <v>2038241.33</v>
+      </c>
+      <c r="AJ15" s="1" t="n">
+        <v>276168.7</v>
+      </c>
+      <c r="AK15" s="1" t="n">
+        <v>1377213.91</v>
+      </c>
+      <c r="AL15" s="1" t="n">
+        <v>2726356.72</v>
+      </c>
+      <c r="AN15" s="1" t="n">
+        <v>4639940.2</v>
+      </c>
+      <c r="AO15" s="1" t="n">
+        <v>349390.46</v>
+      </c>
+      <c r="AP15" s="1" t="n">
+        <v>1141262.08</v>
+      </c>
+      <c r="AQ15" s="1" t="n">
+        <v>655193.14</v>
+      </c>
+      <c r="AR15" s="1" t="n">
+        <v>2639370.92</v>
+      </c>
+      <c r="AS15" s="1" t="n">
+        <v>159170.28</v>
+      </c>
+      <c r="AT15" s="1" t="n">
+        <v>8314547.26</v>
+      </c>
+      <c r="AU15" s="1" t="n">
+        <v>2796446.77</v>
+      </c>
+      <c r="AV15" s="1" t="n">
+        <v>5356198.57</v>
+      </c>
+      <c r="AW15" s="1" t="n">
+        <v>2413874.5</v>
+      </c>
+      <c r="AX15" s="1" t="n">
+        <v>637744.58</v>
+      </c>
+      <c r="AY15" s="1" t="n">
+        <v>395466.62</v>
+      </c>
+      <c r="AZ15" s="1" t="n">
+        <v>1244794.52</v>
+      </c>
+      <c r="BA15" s="1" t="n">
+        <v>400968.31</v>
+      </c>
+      <c r="BB15" s="1" t="n">
+        <v>68112.41</v>
+      </c>
+      <c r="BC15" s="1" t="n">
+        <v>1778144.75</v>
+      </c>
+      <c r="BD15" s="1" t="n">
+        <v>955319.9</v>
+      </c>
+      <c r="BE15" s="1" t="n">
+        <v>481768.4</v>
+      </c>
+      <c r="BF15" s="1" t="n">
+        <v>962092.29</v>
+      </c>
+      <c r="BG15" s="1" t="n">
+        <v>414.22</v>
+      </c>
+      <c r="BI15" s="1" t="n">
+        <v>13289.83</v>
+      </c>
+      <c r="BJ15" s="1" t="n">
+        <v>4511153.25</v>
+      </c>
+      <c r="BK15" s="1" t="n">
+        <v>265752.69</v>
+      </c>
+      <c r="BL15" s="1" t="n">
+        <v>1657697.6</v>
+      </c>
+      <c r="BM15" s="1" t="n">
+        <v>4538563.52</v>
+      </c>
+      <c r="BN15" s="1" t="n">
+        <v>950917.45</v>
+      </c>
+      <c r="BO15" s="1" t="n">
+        <v>114458.62</v>
+      </c>
+      <c r="BP15" s="1" t="n">
+        <v>12150915.79</v>
+      </c>
+      <c r="BQ15" s="1" t="n">
+        <v>4157.65</v>
+      </c>
+      <c r="BS15" s="1" t="n">
+        <v>1220219.44</v>
+      </c>
+      <c r="BT15" s="1" t="n">
+        <v>208627.21</v>
+      </c>
+      <c r="BU15" s="1" t="n">
+        <v>1255450.39</v>
+      </c>
+      <c r="BV15" s="1" t="n">
+        <v>931584.23</v>
+      </c>
+      <c r="BW15" s="1" t="n">
+        <v>34878.4</v>
+      </c>
+      <c r="BX15" s="1" t="n">
+        <v>5359.98</v>
+      </c>
+      <c r="BY15" s="1" t="n">
+        <v>601640.67</v>
+      </c>
+      <c r="BZ15" s="1" t="n">
+        <v>95246.47</v>
+      </c>
+      <c r="CA15" s="1" t="n">
+        <v>423265.26</v>
+      </c>
+      <c r="CB15" s="1" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="CC15" s="1" t="n">
+        <v>71097.23</v>
+      </c>
+      <c r="CD15" s="1" t="n">
+        <v>5940096.84</v>
+      </c>
+      <c r="CE15" s="1" t="n">
+        <v>358431.31</v>
+      </c>
+      <c r="CF15" s="1" t="n">
+        <v>75146.33</v>
+      </c>
+      <c r="CG15" s="1" t="n">
+        <v>613422.51</v>
+      </c>
+      <c r="CH15" s="1" t="n">
+        <v>20392.77</v>
+      </c>
+      <c r="CI15" s="1" t="n">
+        <v>4612.37</v>
+      </c>
+      <c r="CJ15" s="1" t="n">
+        <v>1016832.45</v>
+      </c>
+      <c r="CK15" s="1" t="n">
+        <v>27059.64</v>
+      </c>
+      <c r="CL15" s="1" t="n">
+        <v>121038.45</v>
+      </c>
+      <c r="CM15" s="1" t="n">
+        <v>2473.82</v>
+      </c>
+      <c r="CN15" s="1" t="n">
+        <v>80415.58</v>
+      </c>
+      <c r="CO15" s="1" t="n">
+        <v>594386.5600000001</v>
+      </c>
+      <c r="CP15" s="1" t="n">
+        <v>371652.16</v>
+      </c>
+      <c r="CQ15" s="1" t="n">
+        <v>1029211.97</v>
+      </c>
+      <c r="CR15" s="1" t="n">
+        <v>8140.96</v>
+      </c>
+      <c r="CS15" s="1" t="n">
+        <v>86723.82000000001</v>
+      </c>
+      <c r="CT15" s="1" t="n">
+        <v>111225.34</v>
+      </c>
+      <c r="CV15" s="1" t="n">
+        <v>322061.53</v>
+      </c>
+      <c r="CW15" s="1" t="n">
+        <v>913882.8100000001</v>
+      </c>
+      <c r="CX15" s="1" t="n">
+        <v>88075.00999999999</v>
+      </c>
+      <c r="CY15" s="1" t="n">
+        <v>408.93</v>
+      </c>
+      <c r="CZ15" s="1" t="n">
+        <v>545207.12</v>
+      </c>
+      <c r="DA15" s="1" t="n">
+        <v>189384.82</v>
+      </c>
+      <c r="DB15" s="1" t="n">
+        <v>424862.03</v>
+      </c>
+      <c r="DC15" s="1" t="n">
+        <v>56750.02</v>
+      </c>
+      <c r="DD15" s="1" t="n">
+        <v>98627.67999999999</v>
+      </c>
+      <c r="DE15" s="1" t="n">
+        <v>224550.46</v>
+      </c>
+      <c r="DG15" s="1" t="n">
+        <v>755754.59</v>
+      </c>
+      <c r="DH15" s="1" t="n">
+        <v>43015.74</v>
+      </c>
+      <c r="DI15" s="1" t="n">
+        <v>23363.98</v>
+      </c>
+      <c r="DJ15" s="1" t="n">
+        <v>286249.49</v>
+      </c>
+      <c r="DK15" s="1" t="n">
+        <v>450771.8</v>
+      </c>
+      <c r="DL15" s="1" t="n">
+        <v>631.35</v>
+      </c>
+      <c r="DM15" s="1" t="n">
+        <v>82413.41</v>
+      </c>
+      <c r="DN15" s="1" t="n">
+        <v>3102.73</v>
+      </c>
+      <c r="DO15" s="1" t="n">
+        <v>1938.24</v>
+      </c>
+      <c r="DP15" s="1" t="n">
+        <v>3485.25</v>
+      </c>
+      <c r="DQ15" s="1" t="n">
+        <v>399123.17</v>
+      </c>
+      <c r="DR15" s="1" t="n">
+        <v>116561.52</v>
+      </c>
+      <c r="DS15" s="1" t="n">
+        <v>304594.55</v>
+      </c>
+      <c r="DT15" s="1" t="n">
+        <v>24057.49</v>
+      </c>
+      <c r="DV15" s="1" t="n">
+        <v>210622.65</v>
+      </c>
+      <c r="DW15" s="1" t="n">
+        <v>99806.69</v>
+      </c>
+      <c r="DX15" s="1" t="n">
+        <v>680552.05</v>
+      </c>
+      <c r="DY15" s="1" t="n">
+        <v>127363.94</v>
+      </c>
+      <c r="DZ15" s="1" t="n">
+        <v>269451.55</v>
+      </c>
+      <c r="EA15" s="1" t="n">
+        <v>40634.98</v>
+      </c>
+      <c r="EB15" s="1" t="n">
+        <v>1115.67</v>
+      </c>
+      <c r="EC15" s="1" t="n">
+        <v>65196.34</v>
+      </c>
+      <c r="ED15" s="1" t="n">
+        <v>380190.58</v>
+      </c>
+      <c r="EE15" s="1" t="n">
+        <v>518653.81</v>
+      </c>
+      <c r="EF15" s="1" t="n">
+        <v>149.31</v>
+      </c>
+      <c r="EG15" s="1" t="n">
+        <v>673090.01</v>
+      </c>
+      <c r="EH15" s="1" t="n">
+        <v>230101.52</v>
+      </c>
+      <c r="EI15" s="1" t="n">
+        <v>117363.69</v>
+      </c>
+      <c r="EJ15" s="1" t="n">
+        <v>49633.53</v>
+      </c>
+      <c r="EK15" s="1" t="n">
+        <v>104540.37</v>
+      </c>
+      <c r="EL15" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="EM15" s="1" t="n">
+        <v>948.54</v>
+      </c>
+      <c r="EN15" s="1" t="n">
+        <v>596.86</v>
+      </c>
+      <c r="EO15" s="1" t="n">
+        <v>613385.92</v>
+      </c>
+      <c r="EP15" s="1" t="n">
+        <v>2281088.02</v>
+      </c>
+      <c r="EQ15" s="1" t="n">
+        <v>9019.780000000001</v>
+      </c>
+      <c r="ER15" s="1" t="n">
+        <v>5957.45</v>
+      </c>
+      <c r="ES15" s="1" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="ET15" s="1" t="n">
+        <v>1485.65</v>
+      </c>
+      <c r="EU15" s="1" t="n">
+        <v>68801.00999999999</v>
+      </c>
+      <c r="EV15" s="1" t="n">
+        <v>117843.81</v>
+      </c>
+      <c r="EX15" s="1" t="n">
+        <v>897495.16</v>
+      </c>
+      <c r="EY15" s="1" t="n">
+        <v>15457.9</v>
+      </c>
+      <c r="EZ15" s="1" t="n">
+        <v>31444.63</v>
+      </c>
+      <c r="FB15" s="1" t="n">
+        <v>10054.01</v>
+      </c>
+      <c r="FC15" s="1" t="n">
+        <v>231151.82</v>
+      </c>
+      <c r="FD15" s="1" t="n">
+        <v>36821.96</v>
+      </c>
+      <c r="FE15" s="1" t="n">
+        <v>1332983.24</v>
+      </c>
+      <c r="FF15" s="1" t="n">
+        <v>1974.34</v>
+      </c>
+      <c r="FG15" s="1" t="n">
+        <v>113182.47</v>
+      </c>
+      <c r="FH15" s="1" t="n">
+        <v>44370.51</v>
+      </c>
+      <c r="FI15" s="1" t="n">
+        <v>154075.43</v>
+      </c>
+      <c r="FK15" s="1" t="n">
+        <v>35571.13</v>
+      </c>
+      <c r="FL15" s="1" t="n">
+        <v>1545614.02</v>
+      </c>
+      <c r="FM15" s="1" t="n">
+        <v>378181.23</v>
+      </c>
+      <c r="FN15" s="1" t="n">
+        <v>110809.31</v>
+      </c>
+      <c r="FO15" s="1" t="n">
+        <v>109592.38</v>
+      </c>
+      <c r="FP15" s="1" t="n">
+        <v>305376.97</v>
+      </c>
+      <c r="FQ15" s="1" t="n">
+        <v>106370.57</v>
+      </c>
+      <c r="FR15" s="1" t="n">
+        <v>344616.7</v>
+      </c>
+      <c r="FS15" s="1" t="n">
+        <v>4580401.47</v>
+      </c>
+      <c r="FT15" s="1" t="n">
+        <v>18760.09</v>
+      </c>
+      <c r="FU15" s="1" t="n">
+        <v>20442.92</v>
+      </c>
+      <c r="FV15" s="1" t="n">
+        <v>851450.03</v>
+      </c>
+      <c r="FW15" s="1" t="n">
+        <v>19670.26</v>
+      </c>
+      <c r="FX15" s="1" t="n">
+        <v>63628.56</v>
+      </c>
+      <c r="FY15" s="1" t="n">
+        <v>76058.44</v>
+      </c>
+      <c r="FZ15" s="1" t="n">
+        <v>210079.92</v>
+      </c>
+      <c r="GA15" s="1" t="n">
+        <v>7443.96</v>
+      </c>
+      <c r="GB15" s="1" t="n">
+        <v>294.83</v>
+      </c>
+      <c r="GC15" s="1" t="n">
+        <v>133211.86</v>
+      </c>
+      <c r="GD15" s="1" t="n">
+        <v>99598.38</v>
+      </c>
+      <c r="GE15" s="1" t="n">
+        <v>10068.36</v>
+      </c>
+      <c r="GF15" s="1" t="n">
+        <v>593350.47</v>
+      </c>
+      <c r="GG15" s="1" t="n">
+        <v>498.18</v>
+      </c>
+      <c r="GH15" s="1" t="n">
+        <v>225031.81</v>
+      </c>
+      <c r="GI15" s="1" t="n">
+        <v>103062.07</v>
+      </c>
+      <c r="GJ15" s="1" t="n">
+        <v>13717.56</v>
+      </c>
+      <c r="GK15" s="1" t="n">
+        <v>476899.47</v>
+      </c>
+      <c r="GL15" s="1" t="n">
+        <v>1453.08</v>
+      </c>
+      <c r="GM15" s="1" t="n">
+        <v>221770.16</v>
+      </c>
+      <c r="GN15" s="1" t="n">
+        <v>115861.82</v>
+      </c>
+      <c r="GO15" s="1" t="n">
+        <v>52092.47</v>
+      </c>
+      <c r="GP15" s="1" t="n">
+        <v>48328.96</v>
+      </c>
+      <c r="GQ15" s="1" t="n">
+        <v>142199.15</v>
+      </c>
+      <c r="GR15" s="1" t="n">
+        <v>280.83</v>
+      </c>
+      <c r="GS15" s="1" t="n">
+        <v>1033.93</v>
+      </c>
+      <c r="GT15" s="1" t="n">
+        <v>529238.16</v>
+      </c>
+      <c r="GU15" s="1" t="n">
+        <v>53625.05</v>
+      </c>
+      <c r="GV15" s="1" t="n">
+        <v>701291.34</v>
+      </c>
+      <c r="GX15" s="1" t="n">
+        <v>53041.17</v>
+      </c>
+      <c r="GY15" s="1" t="n">
+        <v>114753.2</v>
+      </c>
+      <c r="GZ15" s="1" t="n">
+        <v>80172.82000000001</v>
+      </c>
+      <c r="HA15" s="1" t="n">
+        <v>2310.59</v>
+      </c>
+      <c r="HB15" s="1" t="n">
+        <v>54667.31</v>
+      </c>
+      <c r="HC15" s="1" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="HD15" s="1" t="n">
+        <v>13413.71</v>
+      </c>
+      <c r="HE15" s="1" t="n">
+        <v>36953.22</v>
+      </c>
+      <c r="HF15" s="1" t="n">
+        <v>13527.41</v>
+      </c>
+      <c r="HG15" s="1" t="n">
+        <v>250.14</v>
+      </c>
+      <c r="HH15" s="1" t="n">
+        <v>227.45</v>
+      </c>
+      <c r="HI15" s="1" t="n">
+        <v>6269.47</v>
+      </c>
+      <c r="HJ15" s="1" t="n">
+        <v>43335.48</v>
+      </c>
+      <c r="HK15" s="1" t="n">
+        <v>88579.25999999999</v>
+      </c>
+      <c r="HL15" s="1" t="n">
+        <v>140496.06</v>
+      </c>
+      <c r="HM15" s="1" t="n">
+        <v>6946.04</v>
+      </c>
+      <c r="HN15" s="1" t="n">
+        <v>51731.29</v>
+      </c>
+      <c r="HO15" s="1" t="n">
+        <v>108835.68</v>
+      </c>
+      <c r="HP15" s="1" t="n">
+        <v>20518.61</v>
+      </c>
+      <c r="HQ15" s="1" t="n">
+        <v>28881</v>
+      </c>
+      <c r="HR15" s="1" t="n">
+        <v>5510.2</v>
+      </c>
+      <c r="HS15" s="1" t="n">
+        <v>3309.83</v>
+      </c>
+      <c r="HT15" s="1" t="n">
+        <v>401227.85</v>
+      </c>
+      <c r="HU15" s="1" t="n">
+        <v>638873.1</v>
+      </c>
+      <c r="HV15" s="1" t="n">
+        <v>5796.16</v>
+      </c>
+      <c r="HW15" s="1" t="n">
+        <v>14602.23</v>
+      </c>
+      <c r="HX15" s="1" t="n">
+        <v>713.45</v>
+      </c>
+      <c r="HY15" s="1" t="n">
+        <v>13648.07</v>
+      </c>
+      <c r="HZ15" s="1" t="n">
+        <v>286445.29</v>
+      </c>
+      <c r="IA15" s="1" t="n">
+        <v>45514.39</v>
+      </c>
+      <c r="IB15" s="1" t="n">
+        <v>4740.99</v>
+      </c>
+      <c r="IC15" s="1" t="n">
+        <v>57745.1</v>
+      </c>
+      <c r="ID15" s="1" t="n">
+        <v>35967.2</v>
+      </c>
+      <c r="IE15" s="1" t="n">
+        <v>53049.87</v>
+      </c>
+      <c r="IF15" s="1" t="n">
+        <v>26074.65</v>
+      </c>
+      <c r="IG15" s="1" t="n">
+        <v>576666.47</v>
+      </c>
+      <c r="IH15" s="1" t="n">
+        <v>15486.6</v>
+      </c>
+      <c r="II15" s="1" t="n">
+        <v>129937.51</v>
+      </c>
+      <c r="IJ15" s="1" t="n">
+        <v>181489.79</v>
+      </c>
+      <c r="IK15" s="1" t="n">
+        <v>438356.37</v>
+      </c>
+      <c r="IL15" s="1" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="IM15" s="1" t="n">
+        <v>2540.96</v>
+      </c>
+      <c r="IN15" s="1" t="n">
+        <v>10214.52</v>
+      </c>
+      <c r="IO15" s="1" t="n">
+        <v>59093.66</v>
+      </c>
+      <c r="IP15" s="1" t="n">
+        <v>20809.73</v>
+      </c>
+      <c r="IQ15" s="1" t="n">
+        <v>7359</v>
+      </c>
+      <c r="IR15" s="1" t="n">
+        <v>43792.39</v>
+      </c>
+      <c r="IS15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT15" s="1" t="n">
+        <v>39381.83</v>
+      </c>
+      <c r="IU15" s="1" t="n">
+        <v>3938.61</v>
+      </c>
+      <c r="IV15" s="1" t="n">
+        <v>29225.01</v>
+      </c>
+      <c r="IW15" s="1" t="n">
+        <v>106795.49</v>
+      </c>
+      <c r="IX15" s="1" t="n">
+        <v>286908.58</v>
+      </c>
+      <c r="IY15" s="1" t="n">
+        <v>1429895.28</v>
+      </c>
+      <c r="IZ15" s="1" t="n">
+        <v>2388.24</v>
+      </c>
+      <c r="JA15" s="1" t="n">
+        <v>3987.85</v>
+      </c>
+      <c r="JB15" s="1" t="n">
+        <v>13136.99</v>
+      </c>
+      <c r="JC15" s="1" t="n">
+        <v>156804.9</v>
+      </c>
+      <c r="JD15" s="1" t="n">
+        <v>1147562.78</v>
+      </c>
+      <c r="JE15" s="1" t="n">
+        <v>423.45</v>
+      </c>
+      <c r="JF15" s="1" t="n">
+        <v>3497.08</v>
+      </c>
+      <c r="JG15" s="1" t="n">
+        <v>322765.56</v>
+      </c>
+      <c r="JH15" s="1" t="n">
+        <v>215.34</v>
+      </c>
+      <c r="JI15" s="1" t="n">
+        <v>14506.3</v>
+      </c>
+      <c r="JJ15" s="1" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="JK15" s="1" t="n">
+        <v>41915.94</v>
+      </c>
+      <c r="JM15" s="1" t="n">
+        <v>674.6900000000001</v>
+      </c>
+      <c r="JN15" s="1" t="n">
+        <v>133088.14</v>
+      </c>
+      <c r="JO15" s="1" t="n">
+        <v>3568.55</v>
+      </c>
+      <c r="JP15" s="1" t="n">
+        <v>3106.26</v>
+      </c>
+      <c r="JQ15" s="1" t="n">
+        <v>517.29</v>
+      </c>
+      <c r="JR15" s="1" t="n">
+        <v>11577.29</v>
+      </c>
+      <c r="JS15" s="1" t="n">
+        <v>322214.22</v>
+      </c>
+      <c r="JT15" s="1" t="n">
+        <v>11526.46</v>
+      </c>
+      <c r="JU15" s="1" t="n">
+        <v>4770.19</v>
+      </c>
+      <c r="JV15" s="1" t="n">
+        <v>5145.63</v>
+      </c>
+      <c r="JX15" s="1" t="n">
+        <v>51184.34</v>
+      </c>
+      <c r="JY15" s="1" t="n">
+        <v>455.62</v>
+      </c>
+      <c r="JZ15" s="1" t="n">
+        <v>4557634.78</v>
+      </c>
+      <c r="KA15" s="1" t="n">
+        <v>4909.69</v>
+      </c>
+      <c r="KB15" s="1" t="n">
+        <v>3395.59</v>
+      </c>
+      <c r="KC15" s="1" t="n">
+        <v>1324.53</v>
+      </c>
+      <c r="KD15" s="1" t="n">
+        <v>19936.74</v>
+      </c>
+      <c r="KE15" s="1" t="n">
+        <v>157.36</v>
+      </c>
+      <c r="KF15" s="1" t="n">
+        <v>11894.11</v>
+      </c>
+      <c r="KG15" s="1" t="n">
+        <v>5781</v>
+      </c>
+      <c r="KH15" s="1" t="n">
+        <v>69921.45</v>
+      </c>
+      <c r="KI15" s="1" t="n">
+        <v>12687.71</v>
+      </c>
+      <c r="KJ15" s="1" t="n">
+        <v>1253.99</v>
+      </c>
+      <c r="KK15" s="1" t="n">
+        <v>5688.65</v>
+      </c>
+      <c r="KM15" s="1" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="KN15" s="1" t="n">
+        <v>145174.69</v>
+      </c>
+      <c r="KO15" s="1" t="n">
+        <v>434355.65</v>
+      </c>
+      <c r="KP15" s="1" t="n">
+        <v>5090.5</v>
+      </c>
+      <c r="KQ15" s="1" t="n">
+        <v>849.5599999999999</v>
+      </c>
+      <c r="KR15" s="1" t="n">
+        <v>4113.65</v>
+      </c>
+      <c r="KS15" s="1" t="n">
+        <v>135248.77</v>
+      </c>
+      <c r="KT15" s="1" t="n">
+        <v>9948.99</v>
+      </c>
+      <c r="KU15" s="1" t="n">
+        <v>1085.32</v>
+      </c>
+      <c r="KV15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KW15" s="1" t="n">
+        <v>414185.35</v>
+      </c>
+      <c r="KX15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KY15" s="1" t="n">
+        <v>109.71</v>
+      </c>
+      <c r="KZ15" s="1" t="n">
+        <v>475.76</v>
+      </c>
+      <c r="LA15" s="1" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="LB15" s="1" t="n">
+        <v>38132.24</v>
+      </c>
+      <c r="LC15" s="1" t="n">
+        <v>199.18</v>
+      </c>
+      <c r="LD15" s="1" t="n">
+        <v>120328.43</v>
+      </c>
+      <c r="LE15" s="1" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="LF15" s="1" t="n">
+        <v>1028.83</v>
+      </c>
+      <c r="LG15" s="1" t="n">
+        <v>52672.06</v>
+      </c>
+      <c r="LI15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LJ15" s="1" t="n">
+        <v>1280.37</v>
+      </c>
+      <c r="LK15" s="1" t="n">
+        <v>20861.28</v>
+      </c>
+      <c r="LL15" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LO15" s="1" t="n">
+        <v>215.02</v>
+      </c>
+      <c r="LP15" s="1" t="n">
+        <v>9233.33</v>
+      </c>
+      <c r="LQ15" s="1" t="n">
+        <v>2249.96</v>
+      </c>
+      <c r="LR15" s="1" t="n">
+        <v>842.86</v>
+      </c>
+      <c r="LS15" s="1" t="n">
+        <v>127.24</v>
+      </c>
+      <c r="LT15" s="1" t="n">
+        <v>35311.54</v>
+      </c>
+      <c r="LU15" s="1" t="n">
+        <v>429.63</v>
+      </c>
+      <c r="LV15" s="1" t="n">
+        <v>244.85</v>
+      </c>
+      <c r="LW15" s="1" t="n">
+        <v>18411.39</v>
+      </c>
+      <c r="LX15" s="1" t="n">
+        <v>262.51</v>
+      </c>
+      <c r="LY15" s="1" t="n">
+        <v>11673.5</v>
+      </c>
+      <c r="LZ15" s="1" t="n">
+        <v>29342.64</v>
+      </c>
+      <c r="MA15" s="1" t="n">
+        <v>154256.87</v>
+      </c>
+      <c r="MB15" s="1" t="n">
+        <v>42094.91</v>
+      </c>
+      <c r="MC15" s="1" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="MD15" s="1" t="n">
+        <v>10773.92</v>
+      </c>
+      <c r="ME15" s="1" t="n">
+        <v>36890.15</v>
+      </c>
+      <c r="MF15" s="1" t="n">
+        <v>168.38</v>
+      </c>
+      <c r="MG15" s="1" t="n">
+        <v>22472.55</v>
+      </c>
+      <c r="MH15" s="1" t="n">
+        <v>57072.64</v>
+      </c>
+      <c r="MI15" s="1" t="n">
+        <v>131293.6</v>
+      </c>
+      <c r="MJ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MK15" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="ML15" s="1" t="n">
+        <v>31509.36</v>
+      </c>
+      <c r="MM15" s="1" t="n">
+        <v>2226.5</v>
+      </c>
+      <c r="MN15" s="1" t="n">
+        <v>614.0599999999999</v>
+      </c>
+      <c r="MO15" s="1" t="n">
+        <v>123209.15</v>
+      </c>
+      <c r="MP15" s="1" t="n">
+        <v>434.75</v>
+      </c>
+      <c r="MQ15" s="1" t="n">
+        <v>199.33</v>
+      </c>
+      <c r="MR15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MS15" s="1" t="n">
+        <v>429.66</v>
+      </c>
+      <c r="MT15" s="1" t="n">
+        <v>6197.83</v>
+      </c>
+      <c r="MU15" s="1" t="n">
+        <v>78947.99000000001</v>
+      </c>
+      <c r="MV15" s="1" t="n">
+        <v>65.41</v>
+      </c>
+      <c r="MW15" s="1" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="MX15" s="1" t="n">
+        <v>135.37</v>
+      </c>
+      <c r="MY15" s="1" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="MZ15" s="1" t="n">
+        <v>13916.95</v>
+      </c>
+      <c r="NA15" s="1" t="n">
+        <v>816.62</v>
+      </c>
+      <c r="NB15" s="1" t="n">
+        <v>4194.06</v>
+      </c>
+      <c r="NC15" s="1" t="n">
+        <v>19999.77</v>
+      </c>
+      <c r="ND15" s="1" t="n">
+        <v>1758.03</v>
+      </c>
+      <c r="NE15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NF15" s="1" t="n">
+        <v>178.83</v>
+      </c>
+      <c r="NG15" s="1" t="n">
+        <v>20634.39</v>
+      </c>
+      <c r="NH15" s="1" t="n">
+        <v>29990304.45</v>
+      </c>
+      <c r="PB15" s="1" t="n">
+        <v>47365.6</v>
+      </c>
+      <c r="PK15" s="1" t="n">
+        <v>273829.07</v>
+      </c>
+      <c r="PV15" s="1" t="n">
+        <v>97.06999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -18438,7 +19515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW14"/>
+  <dimension ref="A1:BXW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19028,6 +20105,48 @@
       </c>
       <c r="M14" s="1" t="n">
         <v>29176.45017</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>454310270.59</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>47308048.32616</v>
+      </c>
+      <c r="D15" s="1">
+        <f>AVERAGE(C9:C15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>2067904.4892</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>4086130.9988</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1369791.3768</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>2362150.2131</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>1859367.8711</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>70602.1646</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>8145.8835</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>5323.8676</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>5638.406701</v>
       </c>
     </row>
   </sheetData>
@@ -19041,7 +20160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW14"/>
+  <dimension ref="A1:BXW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23722,6 +24841,327 @@
         <v>0</v>
       </c>
       <c r="DB14" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>620506.5203042141</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>2752780.079370858</v>
+      </c>
+      <c r="D15" s="1">
+        <f>AVERAGE(C9:C15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>4789464.493483041</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>97785.3632891442</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>168508.4952940393</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>259237.248161976</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>58804.61762055446</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>4652.279088196</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>89501.1247272753</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>1766.643745048</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>3470.2523609016</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>115.70921</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>65.82391200000001</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>17343.539379304</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>43830.8017196342</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>3169.849994926</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" s="1" t="n">
+        <v>43.38394793</v>
+      </c>
+      <c r="BS15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" s="1" t="n">
+        <v>1014.506535</v>
+      </c>
+      <c r="CH15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" s="1" t="n">
+        <v>7.130123</v>
+      </c>
+      <c r="CP15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23736,7 +25176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW14"/>
+  <dimension ref="A1:BXW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25359,6 +26799,126 @@
       </c>
       <c r="AM14" s="1" t="n">
         <v>32518.21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>7135431.82</v>
+      </c>
+      <c r="C15" s="1">
+        <f>AVERAGE(B9:B15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>4943095.09</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1349106.95</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>240955.7</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>3393.25</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>1305603.13</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>74200.75999999999</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>911852.8</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>10699.21</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>67156.10000000001</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>93021.22</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>85875.69</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>5006.76</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>8980.219999999999</v>
+      </c>
+      <c r="S15" s="1" t="n">
+        <v>17702.45</v>
+      </c>
+      <c r="T15" s="1" t="n">
+        <v>24749.18</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>14058.3</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>1039.34</v>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>53515.71</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>18961.5</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>13332.59</v>
+      </c>
+      <c r="Z15" s="1" t="n">
+        <v>88128.82000000001</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>1411.62</v>
+      </c>
+      <c r="AD15" s="1" t="n">
+        <v>39570.94</v>
+      </c>
+      <c r="AE15" s="1" t="n">
+        <v>12018.34</v>
+      </c>
+      <c r="AF15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="1" t="n">
+        <v>40152.98</v>
+      </c>
+      <c r="AI15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="1" t="n">
+        <v>2998.5</v>
+      </c>
+      <c r="AL15" s="1" t="n">
+        <v>1851.26</v>
+      </c>
+      <c r="AM15" s="1" t="n">
+        <v>111070.5</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>696817045.27</v>
+        <v>675084403.76</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>454310270.59</v>
+        <v>456968641.17</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>4789464.493483041</v>
+        <v>5710780.509850427</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>7135431.82</v>
+        <v>8571887.83</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>134616439.06</v>
+        <v>178999769.47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>47308048.32616</v>
+        <v>42783905.15514</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2752780.079370858</v>
+        <v>1736044.0320233</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>4943095.09</v>
+        <v>4100378.12</v>
       </c>
     </row>
     <row r="4">
@@ -543,11 +543,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THB_ETH</t>
+          <t>THB_IOST</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>66085036.51</v>
+        <v>72802998.89</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>4086130.9988</v>
+        <v>7195853.7616</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>620506.5203042141</v>
+        <v>1729809.904360272</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1349106.95</v>
+        <v>1031618.33</v>
       </c>
     </row>
     <row r="5">
@@ -580,27 +580,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THB_XRP</t>
+          <t>THB_ETH</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>50239067.23</v>
+        <v>72658387.89</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BNBTHB</t>
+          <t>VELOTHB</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2362150.2131</v>
+        <v>2204854.5166</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SOL_THB</t>
+          <t>DOGE_THB</t>
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>259237.248161976</v>
+        <v>208173.8068224366</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>1305603.13</v>
+        <v>937039.65</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>30809792.71</v>
+        <v>71444446.20999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,23 +629,23 @@
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>2067904.4892</v>
+        <v>1639842.8656</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>XRP_THB</t>
+          <t>ADA_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>168508.4952940393</v>
+        <v>174075.0077624685</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ADATHB</t>
+          <t>ASTERTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>911852.8</v>
+        <v>854223.66</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW15"/>
+  <dimension ref="A1:BXW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19502,6 +19502,1083 @@
       </c>
       <c r="PV15" s="1" t="n">
         <v>97.06999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>675084403.76</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>178999769.47</v>
+      </c>
+      <c r="D16" s="1">
+        <f>AVERAGE(C10:C16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>72658387.89</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>35427465.68</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>16145198.67</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>40239003.65</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>9459688.76</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>12452690.15</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>5396220.81</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>7109452.15</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>3627700.89</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>71444446.20999999</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>12114564.71</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>193715.82</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>2769115.67</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>2624841.21</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>7512364.43</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>8135534.77</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>6547964.92</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>228423.16</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>3526181.37</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>68261.89</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>196904.26</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>5299915.44</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>6154603.08</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>3516040.41</v>
+      </c>
+      <c r="AD16" s="1" t="n">
+        <v>3076762.75</v>
+      </c>
+      <c r="AE16" s="1" t="n">
+        <v>851682.24</v>
+      </c>
+      <c r="AF16" s="1" t="n">
+        <v>2674485.24</v>
+      </c>
+      <c r="AG16" s="1" t="n">
+        <v>1033163.84</v>
+      </c>
+      <c r="AH16" s="1" t="n">
+        <v>511326.59</v>
+      </c>
+      <c r="AI16" s="1" t="n">
+        <v>3722409.62</v>
+      </c>
+      <c r="AJ16" s="1" t="n">
+        <v>345771.09</v>
+      </c>
+      <c r="AK16" s="1" t="n">
+        <v>2062885.14</v>
+      </c>
+      <c r="AL16" s="1" t="n">
+        <v>3176750.41</v>
+      </c>
+      <c r="AN16" s="1" t="n">
+        <v>392064.3</v>
+      </c>
+      <c r="AO16" s="1" t="n">
+        <v>560663</v>
+      </c>
+      <c r="AP16" s="1" t="n">
+        <v>1227469.76</v>
+      </c>
+      <c r="AQ16" s="1" t="n">
+        <v>2264703.51</v>
+      </c>
+      <c r="AR16" s="1" t="n">
+        <v>2692900.08</v>
+      </c>
+      <c r="AS16" s="1" t="n">
+        <v>437277.03</v>
+      </c>
+      <c r="AT16" s="1" t="n">
+        <v>9086130.859999999</v>
+      </c>
+      <c r="AU16" s="1" t="n">
+        <v>1998243.99</v>
+      </c>
+      <c r="AV16" s="1" t="n">
+        <v>2979260.74</v>
+      </c>
+      <c r="AW16" s="1" t="n">
+        <v>1424903.82</v>
+      </c>
+      <c r="AX16" s="1" t="n">
+        <v>583932.26</v>
+      </c>
+      <c r="AY16" s="1" t="n">
+        <v>374911.4</v>
+      </c>
+      <c r="AZ16" s="1" t="n">
+        <v>12838.99</v>
+      </c>
+      <c r="BA16" s="1" t="n">
+        <v>403394.05</v>
+      </c>
+      <c r="BB16" s="1" t="n">
+        <v>630557.63</v>
+      </c>
+      <c r="BC16" s="1" t="n">
+        <v>2812901.77</v>
+      </c>
+      <c r="BD16" s="1" t="n">
+        <v>451021.94</v>
+      </c>
+      <c r="BE16" s="1" t="n">
+        <v>289705.18</v>
+      </c>
+      <c r="BF16" s="1" t="n">
+        <v>677279.4</v>
+      </c>
+      <c r="BG16" s="1" t="n">
+        <v>2403.84</v>
+      </c>
+      <c r="BI16" s="1" t="n">
+        <v>30831.98</v>
+      </c>
+      <c r="BJ16" s="1" t="n">
+        <v>2208060.43</v>
+      </c>
+      <c r="BK16" s="1" t="n">
+        <v>142439.15</v>
+      </c>
+      <c r="BL16" s="1" t="n">
+        <v>466777.01</v>
+      </c>
+      <c r="BM16" s="1" t="n">
+        <v>2639231.13</v>
+      </c>
+      <c r="BN16" s="1" t="n">
+        <v>402366.74</v>
+      </c>
+      <c r="BO16" s="1" t="n">
+        <v>128477.93</v>
+      </c>
+      <c r="BP16" s="1" t="n">
+        <v>72802998.89</v>
+      </c>
+      <c r="BQ16" s="1" t="n">
+        <v>5216.98</v>
+      </c>
+      <c r="BS16" s="1" t="n">
+        <v>1068431.84</v>
+      </c>
+      <c r="BT16" s="1" t="n">
+        <v>330769.46</v>
+      </c>
+      <c r="BU16" s="1" t="n">
+        <v>514660.47</v>
+      </c>
+      <c r="BV16" s="1" t="n">
+        <v>1500051.32</v>
+      </c>
+      <c r="BW16" s="1" t="n">
+        <v>17677.74</v>
+      </c>
+      <c r="BX16" s="1" t="n">
+        <v>5962.92</v>
+      </c>
+      <c r="BY16" s="1" t="n">
+        <v>616459.96</v>
+      </c>
+      <c r="BZ16" s="1" t="n">
+        <v>106691.89</v>
+      </c>
+      <c r="CA16" s="1" t="n">
+        <v>159206.08</v>
+      </c>
+      <c r="CB16" s="1" t="n">
+        <v>1488.65</v>
+      </c>
+      <c r="CC16" s="1" t="n">
+        <v>48906.48</v>
+      </c>
+      <c r="CD16" s="1" t="n">
+        <v>7434017.32</v>
+      </c>
+      <c r="CE16" s="1" t="n">
+        <v>876919.88</v>
+      </c>
+      <c r="CF16" s="1" t="n">
+        <v>15903.34</v>
+      </c>
+      <c r="CG16" s="1" t="n">
+        <v>707342.13</v>
+      </c>
+      <c r="CH16" s="1" t="n">
+        <v>752788.64</v>
+      </c>
+      <c r="CI16" s="1" t="n">
+        <v>75922.95</v>
+      </c>
+      <c r="CJ16" s="1" t="n">
+        <v>1450532.57</v>
+      </c>
+      <c r="CK16" s="1" t="n">
+        <v>25553.18</v>
+      </c>
+      <c r="CL16" s="1" t="n">
+        <v>205876.24</v>
+      </c>
+      <c r="CM16" s="1" t="n">
+        <v>68627.49000000001</v>
+      </c>
+      <c r="CN16" s="1" t="n">
+        <v>14528.51</v>
+      </c>
+      <c r="CO16" s="1" t="n">
+        <v>241248.13</v>
+      </c>
+      <c r="CP16" s="1" t="n">
+        <v>1043028.24</v>
+      </c>
+      <c r="CQ16" s="1" t="n">
+        <v>1681487.93</v>
+      </c>
+      <c r="CR16" s="1" t="n">
+        <v>71020.60000000001</v>
+      </c>
+      <c r="CS16" s="1" t="n">
+        <v>630902.03</v>
+      </c>
+      <c r="CT16" s="1" t="n">
+        <v>74384.31</v>
+      </c>
+      <c r="CV16" s="1" t="n">
+        <v>1291558.69</v>
+      </c>
+      <c r="CW16" s="1" t="n">
+        <v>124310.45</v>
+      </c>
+      <c r="CX16" s="1" t="n">
+        <v>271601.47</v>
+      </c>
+      <c r="CY16" s="1" t="n">
+        <v>407.49</v>
+      </c>
+      <c r="CZ16" s="1" t="n">
+        <v>514897.72</v>
+      </c>
+      <c r="DA16" s="1" t="n">
+        <v>185940.51</v>
+      </c>
+      <c r="DB16" s="1" t="n">
+        <v>201085.31</v>
+      </c>
+      <c r="DC16" s="1" t="n">
+        <v>248748.71</v>
+      </c>
+      <c r="DD16" s="1" t="n">
+        <v>14460.27</v>
+      </c>
+      <c r="DE16" s="1" t="n">
+        <v>132913.9</v>
+      </c>
+      <c r="DG16" s="1" t="n">
+        <v>214077.98</v>
+      </c>
+      <c r="DH16" s="1" t="n">
+        <v>62354.05</v>
+      </c>
+      <c r="DI16" s="1" t="n">
+        <v>21585.25</v>
+      </c>
+      <c r="DJ16" s="1" t="n">
+        <v>254626.04</v>
+      </c>
+      <c r="DK16" s="1" t="n">
+        <v>37846.63</v>
+      </c>
+      <c r="DL16" s="1" t="n">
+        <v>13850.74</v>
+      </c>
+      <c r="DM16" s="1" t="n">
+        <v>340211.6</v>
+      </c>
+      <c r="DN16" s="1" t="n">
+        <v>26827.37</v>
+      </c>
+      <c r="DO16" s="1" t="n">
+        <v>1582.3</v>
+      </c>
+      <c r="DP16" s="1" t="n">
+        <v>6894.25</v>
+      </c>
+      <c r="DQ16" s="1" t="n">
+        <v>289006.53</v>
+      </c>
+      <c r="DR16" s="1" t="n">
+        <v>209963.52</v>
+      </c>
+      <c r="DS16" s="1" t="n">
+        <v>84113.87</v>
+      </c>
+      <c r="DT16" s="1" t="n">
+        <v>101498.72</v>
+      </c>
+      <c r="DV16" s="1" t="n">
+        <v>2110718.8</v>
+      </c>
+      <c r="DW16" s="1" t="n">
+        <v>30023.83</v>
+      </c>
+      <c r="DX16" s="1" t="n">
+        <v>218432.05</v>
+      </c>
+      <c r="DY16" s="1" t="n">
+        <v>479501.94</v>
+      </c>
+      <c r="DZ16" s="1" t="n">
+        <v>131918.96</v>
+      </c>
+      <c r="EA16" s="1" t="n">
+        <v>55996.8</v>
+      </c>
+      <c r="EB16" s="1" t="n">
+        <v>508.86</v>
+      </c>
+      <c r="EC16" s="1" t="n">
+        <v>254373.37</v>
+      </c>
+      <c r="ED16" s="1" t="n">
+        <v>13263.16</v>
+      </c>
+      <c r="EE16" s="1" t="n">
+        <v>59303.66</v>
+      </c>
+      <c r="EF16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" s="1" t="n">
+        <v>514972.14</v>
+      </c>
+      <c r="EH16" s="1" t="n">
+        <v>12601.89</v>
+      </c>
+      <c r="EI16" s="1" t="n">
+        <v>24734.59</v>
+      </c>
+      <c r="EJ16" s="1" t="n">
+        <v>124.33</v>
+      </c>
+      <c r="EK16" s="1" t="n">
+        <v>32217.59</v>
+      </c>
+      <c r="EL16" s="1" t="n">
+        <v>1201.42</v>
+      </c>
+      <c r="EM16" s="1" t="n">
+        <v>1141.61</v>
+      </c>
+      <c r="EN16" s="1" t="n">
+        <v>6730.67</v>
+      </c>
+      <c r="EO16" s="1" t="n">
+        <v>356369.17</v>
+      </c>
+      <c r="EP16" s="1" t="n">
+        <v>1877514.1</v>
+      </c>
+      <c r="EQ16" s="1" t="n">
+        <v>44262.53</v>
+      </c>
+      <c r="ER16" s="1" t="n">
+        <v>71243.83</v>
+      </c>
+      <c r="ES16" s="1" t="n">
+        <v>454.77</v>
+      </c>
+      <c r="ET16" s="1" t="n">
+        <v>22343.01</v>
+      </c>
+      <c r="EU16" s="1" t="n">
+        <v>52682.72</v>
+      </c>
+      <c r="EV16" s="1" t="n">
+        <v>31256.38</v>
+      </c>
+      <c r="EX16" s="1" t="n">
+        <v>51914.96</v>
+      </c>
+      <c r="EY16" s="1" t="n">
+        <v>30611.09</v>
+      </c>
+      <c r="EZ16" s="1" t="n">
+        <v>8431.209999999999</v>
+      </c>
+      <c r="FB16" s="1" t="n">
+        <v>20424.05</v>
+      </c>
+      <c r="FC16" s="1" t="n">
+        <v>33031.85</v>
+      </c>
+      <c r="FD16" s="1" t="n">
+        <v>2029502.03</v>
+      </c>
+      <c r="FE16" s="1" t="n">
+        <v>776716.9300000001</v>
+      </c>
+      <c r="FF16" s="1" t="n">
+        <v>37728.82</v>
+      </c>
+      <c r="FG16" s="1" t="n">
+        <v>104767.71</v>
+      </c>
+      <c r="FH16" s="1" t="n">
+        <v>30309.46</v>
+      </c>
+      <c r="FI16" s="1" t="n">
+        <v>175828.92</v>
+      </c>
+      <c r="FK16" s="1" t="n">
+        <v>16150.11</v>
+      </c>
+      <c r="FL16" s="1" t="n">
+        <v>198245.98</v>
+      </c>
+      <c r="FM16" s="1" t="n">
+        <v>183811.02</v>
+      </c>
+      <c r="FN16" s="1" t="n">
+        <v>22347.95</v>
+      </c>
+      <c r="FO16" s="1" t="n">
+        <v>61683.42</v>
+      </c>
+      <c r="FP16" s="1" t="n">
+        <v>417262.28</v>
+      </c>
+      <c r="FQ16" s="1" t="n">
+        <v>86260.95</v>
+      </c>
+      <c r="FR16" s="1" t="n">
+        <v>264694.89</v>
+      </c>
+      <c r="FS16" s="1" t="n">
+        <v>3378156.98</v>
+      </c>
+      <c r="FT16" s="1" t="n">
+        <v>51565.05</v>
+      </c>
+      <c r="FU16" s="1" t="n">
+        <v>4369.24</v>
+      </c>
+      <c r="FV16" s="1" t="n">
+        <v>1742820.95</v>
+      </c>
+      <c r="FW16" s="1" t="n">
+        <v>71936.81</v>
+      </c>
+      <c r="FX16" s="1" t="n">
+        <v>21244.21</v>
+      </c>
+      <c r="FY16" s="1" t="n">
+        <v>1606107.24</v>
+      </c>
+      <c r="FZ16" s="1" t="n">
+        <v>15805.35</v>
+      </c>
+      <c r="GA16" s="1" t="n">
+        <v>5038.96</v>
+      </c>
+      <c r="GB16" s="1" t="n">
+        <v>4871.14</v>
+      </c>
+      <c r="GC16" s="1" t="n">
+        <v>226424.54</v>
+      </c>
+      <c r="GD16" s="1" t="n">
+        <v>99598.38</v>
+      </c>
+      <c r="GE16" s="1" t="n">
+        <v>364599.52</v>
+      </c>
+      <c r="GF16" s="1" t="n">
+        <v>71259.02</v>
+      </c>
+      <c r="GG16" s="1" t="n">
+        <v>1752.5</v>
+      </c>
+      <c r="GH16" s="1" t="n">
+        <v>62652.17</v>
+      </c>
+      <c r="GI16" s="1" t="n">
+        <v>313348.01</v>
+      </c>
+      <c r="GJ16" s="1" t="n">
+        <v>34925</v>
+      </c>
+      <c r="GK16" s="1" t="n">
+        <v>205357.88</v>
+      </c>
+      <c r="GL16" s="1" t="n">
+        <v>1496.47</v>
+      </c>
+      <c r="GM16" s="1" t="n">
+        <v>1572415.45</v>
+      </c>
+      <c r="GN16" s="1" t="n">
+        <v>499.24</v>
+      </c>
+      <c r="GO16" s="1" t="n">
+        <v>92395.49000000001</v>
+      </c>
+      <c r="GP16" s="1" t="n">
+        <v>8616.299999999999</v>
+      </c>
+      <c r="GQ16" s="1" t="n">
+        <v>196966.31</v>
+      </c>
+      <c r="GR16" s="1" t="n">
+        <v>3871.04</v>
+      </c>
+      <c r="GS16" s="1" t="n">
+        <v>45284.84</v>
+      </c>
+      <c r="GT16" s="1" t="n">
+        <v>353508.34</v>
+      </c>
+      <c r="GU16" s="1" t="n">
+        <v>53671.95</v>
+      </c>
+      <c r="GV16" s="1" t="n">
+        <v>154633.08</v>
+      </c>
+      <c r="GX16" s="1" t="n">
+        <v>337.37</v>
+      </c>
+      <c r="GY16" s="1" t="n">
+        <v>88737.64</v>
+      </c>
+      <c r="GZ16" s="1" t="n">
+        <v>73540.85000000001</v>
+      </c>
+      <c r="HA16" s="1" t="n">
+        <v>1950.83</v>
+      </c>
+      <c r="HB16" s="1" t="n">
+        <v>337.64</v>
+      </c>
+      <c r="HC16" s="1" t="n">
+        <v>25125.21</v>
+      </c>
+      <c r="HD16" s="1" t="n">
+        <v>3705.01</v>
+      </c>
+      <c r="HE16" s="1" t="n">
+        <v>105777.63</v>
+      </c>
+      <c r="HF16" s="1" t="n">
+        <v>12136.14</v>
+      </c>
+      <c r="HG16" s="1" t="n">
+        <v>52896.83</v>
+      </c>
+      <c r="HH16" s="1" t="n">
+        <v>1181.74</v>
+      </c>
+      <c r="HI16" s="1" t="n">
+        <v>30939.86</v>
+      </c>
+      <c r="HJ16" s="1" t="n">
+        <v>100424.4</v>
+      </c>
+      <c r="HK16" s="1" t="n">
+        <v>73751</v>
+      </c>
+      <c r="HL16" s="1" t="n">
+        <v>238692.48</v>
+      </c>
+      <c r="HM16" s="1" t="n">
+        <v>9160.51</v>
+      </c>
+      <c r="HN16" s="1" t="n">
+        <v>45107.41</v>
+      </c>
+      <c r="HO16" s="1" t="n">
+        <v>52918.61</v>
+      </c>
+      <c r="HP16" s="1" t="n">
+        <v>41915.13</v>
+      </c>
+      <c r="HQ16" s="1" t="n">
+        <v>19346.03</v>
+      </c>
+      <c r="HR16" s="1" t="n">
+        <v>6381.41</v>
+      </c>
+      <c r="HS16" s="1" t="n">
+        <v>81090.95</v>
+      </c>
+      <c r="HT16" s="1" t="n">
+        <v>142170.93</v>
+      </c>
+      <c r="HU16" s="1" t="n">
+        <v>110289.01</v>
+      </c>
+      <c r="HV16" s="1" t="n">
+        <v>25079.73</v>
+      </c>
+      <c r="HW16" s="1" t="n">
+        <v>14602.23</v>
+      </c>
+      <c r="HX16" s="1" t="n">
+        <v>599.6799999999999</v>
+      </c>
+      <c r="HY16" s="1" t="n">
+        <v>44878.17</v>
+      </c>
+      <c r="HZ16" s="1" t="n">
+        <v>59674.2</v>
+      </c>
+      <c r="IA16" s="1" t="n">
+        <v>168647.59</v>
+      </c>
+      <c r="IB16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IC16" s="1" t="n">
+        <v>561052.02</v>
+      </c>
+      <c r="ID16" s="1" t="n">
+        <v>69702.75</v>
+      </c>
+      <c r="IE16" s="1" t="n">
+        <v>133009.77</v>
+      </c>
+      <c r="IF16" s="1" t="n">
+        <v>105290.77</v>
+      </c>
+      <c r="IG16" s="1" t="n">
+        <v>121107.55</v>
+      </c>
+      <c r="IH16" s="1" t="n">
+        <v>19970.77</v>
+      </c>
+      <c r="II16" s="1" t="n">
+        <v>242107.68</v>
+      </c>
+      <c r="IJ16" s="1" t="n">
+        <v>41731.58</v>
+      </c>
+      <c r="IK16" s="1" t="n">
+        <v>905591.51</v>
+      </c>
+      <c r="IL16" s="1" t="n">
+        <v>1055718.7</v>
+      </c>
+      <c r="IM16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN16" s="1" t="n">
+        <v>1170.05</v>
+      </c>
+      <c r="IO16" s="1" t="n">
+        <v>37028.39</v>
+      </c>
+      <c r="IP16" s="1" t="n">
+        <v>6734.47</v>
+      </c>
+      <c r="IQ16" s="1" t="n">
+        <v>111443.81</v>
+      </c>
+      <c r="IR16" s="1" t="n">
+        <v>43792.39</v>
+      </c>
+      <c r="IS16" s="1" t="n">
+        <v>395.24</v>
+      </c>
+      <c r="IT16" s="1" t="n">
+        <v>43924.87</v>
+      </c>
+      <c r="IU16" s="1" t="n">
+        <v>41309</v>
+      </c>
+      <c r="IV16" s="1" t="n">
+        <v>215621.82</v>
+      </c>
+      <c r="IW16" s="1" t="n">
+        <v>150679.38</v>
+      </c>
+      <c r="IX16" s="1" t="n">
+        <v>548312.75</v>
+      </c>
+      <c r="IY16" s="1" t="n">
+        <v>379049.77</v>
+      </c>
+      <c r="IZ16" s="1" t="n">
+        <v>13288.4</v>
+      </c>
+      <c r="JA16" s="1" t="n">
+        <v>589.46</v>
+      </c>
+      <c r="JB16" s="1" t="n">
+        <v>17699.43</v>
+      </c>
+      <c r="JC16" s="1" t="n">
+        <v>443944.59</v>
+      </c>
+      <c r="JD16" s="1" t="n">
+        <v>763266.84</v>
+      </c>
+      <c r="JE16" s="1" t="n">
+        <v>423.45</v>
+      </c>
+      <c r="JF16" s="1" t="n">
+        <v>13361.17</v>
+      </c>
+      <c r="JG16" s="1" t="n">
+        <v>41608.38</v>
+      </c>
+      <c r="JH16" s="1" t="n">
+        <v>12096.6</v>
+      </c>
+      <c r="JI16" s="1" t="n">
+        <v>7273.38</v>
+      </c>
+      <c r="JJ16" s="1" t="n">
+        <v>204.15</v>
+      </c>
+      <c r="JK16" s="1" t="n">
+        <v>72055.72</v>
+      </c>
+      <c r="JM16" s="1" t="n">
+        <v>2124.37</v>
+      </c>
+      <c r="JN16" s="1" t="n">
+        <v>59216.52</v>
+      </c>
+      <c r="JO16" s="1" t="n">
+        <v>618.34</v>
+      </c>
+      <c r="JP16" s="1" t="n">
+        <v>2326.88</v>
+      </c>
+      <c r="JQ16" s="1" t="n">
+        <v>21614.08</v>
+      </c>
+      <c r="JR16" s="1" t="n">
+        <v>9412.59</v>
+      </c>
+      <c r="JS16" s="1" t="n">
+        <v>4590.65</v>
+      </c>
+      <c r="JT16" s="1" t="n">
+        <v>599.85</v>
+      </c>
+      <c r="JU16" s="1" t="n">
+        <v>182220.97</v>
+      </c>
+      <c r="JV16" s="1" t="n">
+        <v>18122.13</v>
+      </c>
+      <c r="JX16" s="1" t="n">
+        <v>6466.02</v>
+      </c>
+      <c r="JY16" s="1" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="JZ16" s="1" t="n">
+        <v>4275798.57</v>
+      </c>
+      <c r="KA16" s="1" t="n">
+        <v>1238.49</v>
+      </c>
+      <c r="KB16" s="1" t="n">
+        <v>82514.78</v>
+      </c>
+      <c r="KC16" s="1" t="n">
+        <v>10861.7</v>
+      </c>
+      <c r="KD16" s="1" t="n">
+        <v>3583.38</v>
+      </c>
+      <c r="KE16" s="1" t="n">
+        <v>2776</v>
+      </c>
+      <c r="KF16" s="1" t="n">
+        <v>11555.67</v>
+      </c>
+      <c r="KG16" s="1" t="n">
+        <v>10017.7</v>
+      </c>
+      <c r="KH16" s="1" t="n">
+        <v>1337.02</v>
+      </c>
+      <c r="KI16" s="1" t="n">
+        <v>961.6</v>
+      </c>
+      <c r="KJ16" s="1" t="n">
+        <v>11740.52</v>
+      </c>
+      <c r="KK16" s="1" t="n">
+        <v>1984.16</v>
+      </c>
+      <c r="KM16" s="1" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="KN16" s="1" t="n">
+        <v>159124.06</v>
+      </c>
+      <c r="KO16" s="1" t="n">
+        <v>907428.47</v>
+      </c>
+      <c r="KP16" s="1" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="KQ16" s="1" t="n">
+        <v>1441.92</v>
+      </c>
+      <c r="KR16" s="1" t="n">
+        <v>86612.49000000001</v>
+      </c>
+      <c r="KS16" s="1" t="n">
+        <v>47814.3</v>
+      </c>
+      <c r="KT16" s="1" t="n">
+        <v>1193.14</v>
+      </c>
+      <c r="KU16" s="1" t="n">
+        <v>90164.41</v>
+      </c>
+      <c r="KV16" s="1" t="n">
+        <v>1257.02</v>
+      </c>
+      <c r="KW16" s="1" t="n">
+        <v>114724.09</v>
+      </c>
+      <c r="KX16" s="1" t="n">
+        <v>582.8200000000001</v>
+      </c>
+      <c r="KY16" s="1" t="n">
+        <v>14647.44</v>
+      </c>
+      <c r="KZ16" s="1" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="LA16" s="1" t="n">
+        <v>796.3</v>
+      </c>
+      <c r="LB16" s="1" t="n">
+        <v>760.0599999999999</v>
+      </c>
+      <c r="LC16" s="1" t="n">
+        <v>218.86</v>
+      </c>
+      <c r="LD16" s="1" t="n">
+        <v>125734.32</v>
+      </c>
+      <c r="LE16" s="1" t="n">
+        <v>1269.86</v>
+      </c>
+      <c r="LF16" s="1" t="n">
+        <v>1239.78</v>
+      </c>
+      <c r="LG16" s="1" t="n">
+        <v>9471.34</v>
+      </c>
+      <c r="LI16" s="1" t="n">
+        <v>1486.8</v>
+      </c>
+      <c r="LJ16" s="1" t="n">
+        <v>2120.65</v>
+      </c>
+      <c r="LK16" s="1" t="n">
+        <v>23499.54</v>
+      </c>
+      <c r="LL16" s="1" t="n">
+        <v>152675.46</v>
+      </c>
+      <c r="LO16" s="1" t="n">
+        <v>489.33</v>
+      </c>
+      <c r="LP16" s="1" t="n">
+        <v>1278.07</v>
+      </c>
+      <c r="LQ16" s="1" t="n">
+        <v>515.03</v>
+      </c>
+      <c r="LR16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LS16" s="1" t="n">
+        <v>15433.08</v>
+      </c>
+      <c r="LT16" s="1" t="n">
+        <v>10182.38</v>
+      </c>
+      <c r="LU16" s="1" t="n">
+        <v>19164.35</v>
+      </c>
+      <c r="LV16" s="1" t="n">
+        <v>17976.33</v>
+      </c>
+      <c r="LW16" s="1" t="n">
+        <v>48223.88</v>
+      </c>
+      <c r="LX16" s="1" t="n">
+        <v>265.27</v>
+      </c>
+      <c r="LY16" s="1" t="n">
+        <v>213832.59</v>
+      </c>
+      <c r="LZ16" s="1" t="n">
+        <v>73777.60000000001</v>
+      </c>
+      <c r="MA16" s="1" t="n">
+        <v>69957.03</v>
+      </c>
+      <c r="MB16" s="1" t="n">
+        <v>5279.35</v>
+      </c>
+      <c r="MC16" s="1" t="n">
+        <v>851.27</v>
+      </c>
+      <c r="MD16" s="1" t="n">
+        <v>7721.19</v>
+      </c>
+      <c r="ME16" s="1" t="n">
+        <v>16217.62</v>
+      </c>
+      <c r="MF16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MG16" s="1" t="n">
+        <v>52779.07</v>
+      </c>
+      <c r="MH16" s="1" t="n">
+        <v>9668.889999999999</v>
+      </c>
+      <c r="MI16" s="1" t="n">
+        <v>99947.06</v>
+      </c>
+      <c r="MJ16" s="1" t="n">
+        <v>16174.47</v>
+      </c>
+      <c r="MK16" s="1" t="n">
+        <v>1028.23</v>
+      </c>
+      <c r="ML16" s="1" t="n">
+        <v>407.48</v>
+      </c>
+      <c r="MM16" s="1" t="n">
+        <v>1023.01</v>
+      </c>
+      <c r="MN16" s="1" t="n">
+        <v>813.09</v>
+      </c>
+      <c r="MO16" s="1" t="n">
+        <v>4449.1</v>
+      </c>
+      <c r="MP16" s="1" t="n">
+        <v>208.75</v>
+      </c>
+      <c r="MQ16" s="1" t="n">
+        <v>1167.29</v>
+      </c>
+      <c r="MR16" s="1" t="n">
+        <v>429.75</v>
+      </c>
+      <c r="MS16" s="1" t="n">
+        <v>267.59</v>
+      </c>
+      <c r="MT16" s="1" t="n">
+        <v>37621.06</v>
+      </c>
+      <c r="MU16" s="1" t="n">
+        <v>3374.83</v>
+      </c>
+      <c r="MV16" s="1" t="n">
+        <v>216.48</v>
+      </c>
+      <c r="MW16" s="1" t="n">
+        <v>2812.79</v>
+      </c>
+      <c r="MX16" s="1" t="n">
+        <v>4742.74</v>
+      </c>
+      <c r="MY16" s="1" t="n">
+        <v>3537.29</v>
+      </c>
+      <c r="MZ16" s="1" t="n">
+        <v>4081</v>
+      </c>
+      <c r="NA16" s="1" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="NB16" s="1" t="n">
+        <v>25616.25</v>
+      </c>
+      <c r="NC16" s="1" t="n">
+        <v>43711.76</v>
+      </c>
+      <c r="ND16" s="1" t="n">
+        <v>1663.99</v>
+      </c>
+      <c r="NE16" s="1" t="n">
+        <v>846.4299999999999</v>
+      </c>
+      <c r="NF16" s="1" t="n">
+        <v>491.51</v>
+      </c>
+      <c r="NG16" s="1" t="n">
+        <v>483.9</v>
+      </c>
+      <c r="NH16" s="1" t="n">
+        <v>5996882.25</v>
+      </c>
+      <c r="PB16" s="1" t="n">
+        <v>2925.04</v>
+      </c>
+      <c r="PK16" s="1" t="n">
+        <v>29471.16</v>
+      </c>
+      <c r="PV16" s="1" t="n">
+        <v>272.31</v>
       </c>
     </row>
   </sheetData>
@@ -19515,7 +20592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW15"/>
+  <dimension ref="A1:BXW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20147,6 +21224,48 @@
       </c>
       <c r="M15" s="1" t="n">
         <v>5638.406701</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>456968641.17</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>42783905.15514</v>
+      </c>
+      <c r="D16" s="1">
+        <f>AVERAGE(C10:C16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>1639842.8656</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>7195853.7616</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>1460389.4557</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>365907.2392</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>2204854.5166</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>107759.377</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>14969.1858</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>8177.79537</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>40373.877824</v>
       </c>
     </row>
   </sheetData>
@@ -20160,7 +21279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW15"/>
+  <dimension ref="A1:BXW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25162,6 +26281,327 @@
         <v>0</v>
       </c>
       <c r="DB15" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1729809.904360272</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>1736044.0320233</v>
+      </c>
+      <c r="D16" s="1">
+        <f>AVERAGE(C10:C16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>5710780.509850427</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>174075.0077624685</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>55576.3657928776</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>128955.7693009538</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>208173.8068224366</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>2237.602068184</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>76545.5394537242</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>505.305</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>2095.99181</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>5486.0056682584</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>2568.2484343937</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>19.9466425365</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>400.2056417</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="1" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" s="1" t="n">
+        <v>41.09008402</v>
+      </c>
+      <c r="BS16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" s="1" t="n">
+        <v>605.69364455</v>
+      </c>
+      <c r="CP16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25176,7 +26616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW15"/>
+  <dimension ref="A1:BXW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26919,6 +28359,126 @@
       </c>
       <c r="AM15" s="1" t="n">
         <v>111070.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>8571887.83</v>
+      </c>
+      <c r="C16" s="1">
+        <f>AVERAGE(B10:B16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>4100378.12</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>1031618.33</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>849153.75</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>10146.75</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>937039.65</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>105606.78</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>209412.05</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>15047.03</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>164589.1</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>34494.45</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>71584.64</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>6266.23</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>3102.8</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>39343.27</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>28997.25</v>
+      </c>
+      <c r="T16" s="1" t="n">
+        <v>16522.2</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>59582.33</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>46982.69</v>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>10252</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>50801.3</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>8704.33</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>11930.54</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="1" t="n">
+        <v>854223.66</v>
+      </c>
+      <c r="AE16" s="1" t="n">
+        <v>2004.67</v>
+      </c>
+      <c r="AF16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="1" t="n">
+        <v>10138.58</v>
+      </c>
+      <c r="AH16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="1" t="n">
+        <v>174523.54</v>
+      </c>
+      <c r="AL16" s="1" t="n">
+        <v>929.64</v>
+      </c>
+      <c r="AM16" s="1" t="n">
+        <v>77867.71000000001</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>675084403.76</v>
+        <v>802674486.76</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>456968641.17</v>
+        <v>610679011.09</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>5710780.509850427</v>
+        <v>6917001.92561134</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>8571887.83</v>
+        <v>8928029.439999999</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>178999769.47</v>
+        <v>186364910.69</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>42783905.15514</v>
+        <v>57378075.01877</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1736044.0320233</v>
+        <v>3653557.394302025</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>4100378.12</v>
+        <v>2231042.97</v>
       </c>
     </row>
     <row r="4">
@@ -543,11 +543,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THB_IOST</t>
+          <t>THB_ETH</t>
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>72802998.89</v>
+        <v>63297985.81</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>7195853.7616</v>
+        <v>5471211.234</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1729809.904360272</v>
+        <v>1243351.248979664</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1031618.33</v>
+        <v>1080786.09</v>
       </c>
     </row>
     <row r="5">
@@ -580,11 +580,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THB_ETH</t>
+          <t>THB_XRP</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>72658387.89</v>
+        <v>43829639.71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2204854.5166</v>
+        <v>2222899.8177</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>208173.8068224366</v>
+        <v>166734.4356868842</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>937039.65</v>
+        <v>981498.0699999999</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>71444446.20999999</v>
+        <v>27800182.15</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,23 +629,23 @@
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1639842.8656</v>
+        <v>1822550.4695</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ADA_THB</t>
+          <t>XRP_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>174075.0077624685</v>
+        <v>150463.1496818284</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ASTERTHB</t>
+          <t>SOLTHB</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>854223.66</v>
+        <v>344387.69</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW16"/>
+  <dimension ref="A1:BXW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20579,6 +20579,1083 @@
       </c>
       <c r="PV16" s="1" t="n">
         <v>272.31</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>802674486.76</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>186364910.69</v>
+      </c>
+      <c r="D17" s="1">
+        <f>AVERAGE(C11:C17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>63297985.81</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>43829639.71</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>9475581.289999999</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>18155232.18</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>4574073.89</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>7583658.78</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>5756476.38</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>11265763.9</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>2517675.06</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>27800182.15</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>10251918.96</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>73676.95</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>3189770.88</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>2128122.33</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>4824869.28</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>3564706.37</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>3494117.8</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>59231.1</v>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>2626435.36</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>21997.02</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>95470.35000000001</v>
+      </c>
+      <c r="AA17" s="1" t="n">
+        <v>1952028.29</v>
+      </c>
+      <c r="AB17" s="1" t="n">
+        <v>5333751.22</v>
+      </c>
+      <c r="AC17" s="1" t="n">
+        <v>1265947.86</v>
+      </c>
+      <c r="AD17" s="1" t="n">
+        <v>2067937.76</v>
+      </c>
+      <c r="AE17" s="1" t="n">
+        <v>1945979.61</v>
+      </c>
+      <c r="AF17" s="1" t="n">
+        <v>1235679.54</v>
+      </c>
+      <c r="AG17" s="1" t="n">
+        <v>2826513.32</v>
+      </c>
+      <c r="AH17" s="1" t="n">
+        <v>281694.93</v>
+      </c>
+      <c r="AI17" s="1" t="n">
+        <v>2572680.01</v>
+      </c>
+      <c r="AJ17" s="1" t="n">
+        <v>388332.1</v>
+      </c>
+      <c r="AK17" s="1" t="n">
+        <v>639703.79</v>
+      </c>
+      <c r="AL17" s="1" t="n">
+        <v>1443541.66</v>
+      </c>
+      <c r="AN17" s="1" t="n">
+        <v>255359.07</v>
+      </c>
+      <c r="AO17" s="1" t="n">
+        <v>368067.62</v>
+      </c>
+      <c r="AP17" s="1" t="n">
+        <v>460937.23</v>
+      </c>
+      <c r="AQ17" s="1" t="n">
+        <v>1792424.4</v>
+      </c>
+      <c r="AR17" s="1" t="n">
+        <v>2728250.21</v>
+      </c>
+      <c r="AS17" s="1" t="n">
+        <v>401569.41</v>
+      </c>
+      <c r="AT17" s="1" t="n">
+        <v>2548225.67</v>
+      </c>
+      <c r="AU17" s="1" t="n">
+        <v>498668.44</v>
+      </c>
+      <c r="AV17" s="1" t="n">
+        <v>1256510.32</v>
+      </c>
+      <c r="AW17" s="1" t="n">
+        <v>2159114.37</v>
+      </c>
+      <c r="AX17" s="1" t="n">
+        <v>245823.32</v>
+      </c>
+      <c r="AY17" s="1" t="n">
+        <v>84137.33</v>
+      </c>
+      <c r="AZ17" s="1" t="n">
+        <v>10731.96</v>
+      </c>
+      <c r="BA17" s="1" t="n">
+        <v>20429.02</v>
+      </c>
+      <c r="BB17" s="1" t="n">
+        <v>70060.41</v>
+      </c>
+      <c r="BC17" s="1" t="n">
+        <v>998866</v>
+      </c>
+      <c r="BD17" s="1" t="n">
+        <v>346738.66</v>
+      </c>
+      <c r="BE17" s="1" t="n">
+        <v>182091.62</v>
+      </c>
+      <c r="BF17" s="1" t="n">
+        <v>1842717.13</v>
+      </c>
+      <c r="BG17" s="1" t="n">
+        <v>2595.91</v>
+      </c>
+      <c r="BI17" s="1" t="n">
+        <v>10461.52</v>
+      </c>
+      <c r="BJ17" s="1" t="n">
+        <v>298930.58</v>
+      </c>
+      <c r="BK17" s="1" t="n">
+        <v>70124.10000000001</v>
+      </c>
+      <c r="BL17" s="1" t="n">
+        <v>1701983.39</v>
+      </c>
+      <c r="BM17" s="1" t="n">
+        <v>354647.15</v>
+      </c>
+      <c r="BN17" s="1" t="n">
+        <v>461608.47</v>
+      </c>
+      <c r="BO17" s="1" t="n">
+        <v>157028.95</v>
+      </c>
+      <c r="BP17" s="1" t="n">
+        <v>9013216.34</v>
+      </c>
+      <c r="BQ17" s="1" t="n">
+        <v>5545.04</v>
+      </c>
+      <c r="BS17" s="1" t="n">
+        <v>515831.95</v>
+      </c>
+      <c r="BT17" s="1" t="n">
+        <v>525492.9</v>
+      </c>
+      <c r="BU17" s="1" t="n">
+        <v>362532.9</v>
+      </c>
+      <c r="BV17" s="1" t="n">
+        <v>1258868.11</v>
+      </c>
+      <c r="BW17" s="1" t="n">
+        <v>17412.63</v>
+      </c>
+      <c r="BX17" s="1" t="n">
+        <v>1210.01</v>
+      </c>
+      <c r="BY17" s="1" t="n">
+        <v>192625.93</v>
+      </c>
+      <c r="BZ17" s="1" t="n">
+        <v>1433704.6</v>
+      </c>
+      <c r="CA17" s="1" t="n">
+        <v>332965.08</v>
+      </c>
+      <c r="CB17" s="1" t="n">
+        <v>4776.61</v>
+      </c>
+      <c r="CC17" s="1" t="n">
+        <v>16077.89</v>
+      </c>
+      <c r="CD17" s="1" t="n">
+        <v>1956848.8</v>
+      </c>
+      <c r="CE17" s="1" t="n">
+        <v>136939.71</v>
+      </c>
+      <c r="CF17" s="1" t="n">
+        <v>170837.65</v>
+      </c>
+      <c r="CG17" s="1" t="n">
+        <v>418701.44</v>
+      </c>
+      <c r="CH17" s="1" t="n">
+        <v>193328.01</v>
+      </c>
+      <c r="CI17" s="1" t="n">
+        <v>50879.66</v>
+      </c>
+      <c r="CJ17" s="1" t="n">
+        <v>844453.1899999999</v>
+      </c>
+      <c r="CK17" s="1" t="n">
+        <v>91074.19</v>
+      </c>
+      <c r="CL17" s="1" t="n">
+        <v>78277.92</v>
+      </c>
+      <c r="CM17" s="1" t="n">
+        <v>234687.94</v>
+      </c>
+      <c r="CN17" s="1" t="n">
+        <v>123441.29</v>
+      </c>
+      <c r="CO17" s="1" t="n">
+        <v>884256.76</v>
+      </c>
+      <c r="CP17" s="1" t="n">
+        <v>261286.06</v>
+      </c>
+      <c r="CQ17" s="1" t="n">
+        <v>485360.47</v>
+      </c>
+      <c r="CR17" s="1" t="n">
+        <v>1235.83</v>
+      </c>
+      <c r="CS17" s="1" t="n">
+        <v>290116.51</v>
+      </c>
+      <c r="CT17" s="1" t="n">
+        <v>442569.6</v>
+      </c>
+      <c r="CV17" s="1" t="n">
+        <v>856696.99</v>
+      </c>
+      <c r="CW17" s="1" t="n">
+        <v>77026.57000000001</v>
+      </c>
+      <c r="CX17" s="1" t="n">
+        <v>173284.49</v>
+      </c>
+      <c r="CY17" s="1" t="n">
+        <v>23079.78</v>
+      </c>
+      <c r="CZ17" s="1" t="n">
+        <v>304323.61</v>
+      </c>
+      <c r="DA17" s="1" t="n">
+        <v>515550.64</v>
+      </c>
+      <c r="DB17" s="1" t="n">
+        <v>311134.68</v>
+      </c>
+      <c r="DC17" s="1" t="n">
+        <v>52876.97</v>
+      </c>
+      <c r="DD17" s="1" t="n">
+        <v>19406.12</v>
+      </c>
+      <c r="DE17" s="1" t="n">
+        <v>70592.42</v>
+      </c>
+      <c r="DG17" s="1" t="n">
+        <v>100276.25</v>
+      </c>
+      <c r="DH17" s="1" t="n">
+        <v>98887.97</v>
+      </c>
+      <c r="DI17" s="1" t="n">
+        <v>78470.63</v>
+      </c>
+      <c r="DJ17" s="1" t="n">
+        <v>85138.59</v>
+      </c>
+      <c r="DK17" s="1" t="n">
+        <v>745610.63</v>
+      </c>
+      <c r="DL17" s="1" t="n">
+        <v>399.52</v>
+      </c>
+      <c r="DM17" s="1" t="n">
+        <v>85382.08</v>
+      </c>
+      <c r="DN17" s="1" t="n">
+        <v>26732.19</v>
+      </c>
+      <c r="DO17" s="1" t="n">
+        <v>891.41</v>
+      </c>
+      <c r="DP17" s="1" t="n">
+        <v>598.49</v>
+      </c>
+      <c r="DQ17" s="1" t="n">
+        <v>66686.17</v>
+      </c>
+      <c r="DR17" s="1" t="n">
+        <v>4904.12</v>
+      </c>
+      <c r="DS17" s="1" t="n">
+        <v>138852.18</v>
+      </c>
+      <c r="DT17" s="1" t="n">
+        <v>57410.37</v>
+      </c>
+      <c r="DV17" s="1" t="n">
+        <v>2551060.71</v>
+      </c>
+      <c r="DW17" s="1" t="n">
+        <v>210620.71</v>
+      </c>
+      <c r="DX17" s="1" t="n">
+        <v>350618.88</v>
+      </c>
+      <c r="DY17" s="1" t="n">
+        <v>63965.55</v>
+      </c>
+      <c r="DZ17" s="1" t="n">
+        <v>96077.78</v>
+      </c>
+      <c r="EA17" s="1" t="n">
+        <v>280404.25</v>
+      </c>
+      <c r="EB17" s="1" t="n">
+        <v>199.14</v>
+      </c>
+      <c r="EC17" s="1" t="n">
+        <v>126405.76</v>
+      </c>
+      <c r="ED17" s="1" t="n">
+        <v>423586.42</v>
+      </c>
+      <c r="EE17" s="1" t="n">
+        <v>40221.22</v>
+      </c>
+      <c r="EF17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG17" s="1" t="n">
+        <v>938353.85</v>
+      </c>
+      <c r="EH17" s="1" t="n">
+        <v>107413</v>
+      </c>
+      <c r="EI17" s="1" t="n">
+        <v>2114.74</v>
+      </c>
+      <c r="EJ17" s="1" t="n">
+        <v>4569.33</v>
+      </c>
+      <c r="EK17" s="1" t="n">
+        <v>101271.47</v>
+      </c>
+      <c r="EL17" s="1" t="n">
+        <v>1281.92</v>
+      </c>
+      <c r="EM17" s="1" t="n">
+        <v>399</v>
+      </c>
+      <c r="EN17" s="1" t="n">
+        <v>772.5700000000001</v>
+      </c>
+      <c r="EO17" s="1" t="n">
+        <v>211865.36</v>
+      </c>
+      <c r="EP17" s="1" t="n">
+        <v>1498452.82</v>
+      </c>
+      <c r="EQ17" s="1" t="n">
+        <v>165.03</v>
+      </c>
+      <c r="ER17" s="1" t="n">
+        <v>90740.24000000001</v>
+      </c>
+      <c r="ES17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET17" s="1" t="n">
+        <v>508.58</v>
+      </c>
+      <c r="EU17" s="1" t="n">
+        <v>19004.07</v>
+      </c>
+      <c r="EV17" s="1" t="n">
+        <v>51482.91</v>
+      </c>
+      <c r="EX17" s="1" t="n">
+        <v>43745.59</v>
+      </c>
+      <c r="EY17" s="1" t="n">
+        <v>26675.69</v>
+      </c>
+      <c r="EZ17" s="1" t="n">
+        <v>9592.82</v>
+      </c>
+      <c r="FB17" s="1" t="n">
+        <v>245.87</v>
+      </c>
+      <c r="FC17" s="1" t="n">
+        <v>40368.33</v>
+      </c>
+      <c r="FD17" s="1" t="n">
+        <v>35658.04</v>
+      </c>
+      <c r="FE17" s="1" t="n">
+        <v>264006.45</v>
+      </c>
+      <c r="FF17" s="1" t="n">
+        <v>3680.05</v>
+      </c>
+      <c r="FG17" s="1" t="n">
+        <v>95157.69</v>
+      </c>
+      <c r="FH17" s="1" t="n">
+        <v>71341.12</v>
+      </c>
+      <c r="FI17" s="1" t="n">
+        <v>48423.96</v>
+      </c>
+      <c r="FK17" s="1" t="n">
+        <v>122764.73</v>
+      </c>
+      <c r="FL17" s="1" t="n">
+        <v>28367.73</v>
+      </c>
+      <c r="FM17" s="1" t="n">
+        <v>181188.61</v>
+      </c>
+      <c r="FN17" s="1" t="n">
+        <v>57816.28</v>
+      </c>
+      <c r="FO17" s="1" t="n">
+        <v>294.27</v>
+      </c>
+      <c r="FP17" s="1" t="n">
+        <v>77178.99000000001</v>
+      </c>
+      <c r="FQ17" s="1" t="n">
+        <v>16376.18</v>
+      </c>
+      <c r="FR17" s="1" t="n">
+        <v>153260.79</v>
+      </c>
+      <c r="FS17" s="1" t="n">
+        <v>735446.9300000001</v>
+      </c>
+      <c r="FT17" s="1" t="n">
+        <v>11474.29</v>
+      </c>
+      <c r="FU17" s="1" t="n">
+        <v>51152.03</v>
+      </c>
+      <c r="FV17" s="1" t="n">
+        <v>241183.19</v>
+      </c>
+      <c r="FW17" s="1" t="n">
+        <v>47217.61</v>
+      </c>
+      <c r="FX17" s="1" t="n">
+        <v>31934.45</v>
+      </c>
+      <c r="FY17" s="1" t="n">
+        <v>775930.1</v>
+      </c>
+      <c r="FZ17" s="1" t="n">
+        <v>825389.99</v>
+      </c>
+      <c r="GA17" s="1" t="n">
+        <v>487.35</v>
+      </c>
+      <c r="GB17" s="1" t="n">
+        <v>1487.81</v>
+      </c>
+      <c r="GC17" s="1" t="n">
+        <v>97344.35000000001</v>
+      </c>
+      <c r="GD17" s="1" t="n">
+        <v>14496.96</v>
+      </c>
+      <c r="GE17" s="1" t="n">
+        <v>530291.98</v>
+      </c>
+      <c r="GF17" s="1" t="n">
+        <v>45094.27</v>
+      </c>
+      <c r="GG17" s="1" t="n">
+        <v>1183.27</v>
+      </c>
+      <c r="GH17" s="1" t="n">
+        <v>9975.27</v>
+      </c>
+      <c r="GI17" s="1" t="n">
+        <v>301729.58</v>
+      </c>
+      <c r="GJ17" s="1" t="n">
+        <v>21940.78</v>
+      </c>
+      <c r="GK17" s="1" t="n">
+        <v>381384.49</v>
+      </c>
+      <c r="GL17" s="1" t="n">
+        <v>8627.129999999999</v>
+      </c>
+      <c r="GM17" s="1" t="n">
+        <v>2442310.65</v>
+      </c>
+      <c r="GN17" s="1" t="n">
+        <v>149818.5</v>
+      </c>
+      <c r="GO17" s="1" t="n">
+        <v>72145.32000000001</v>
+      </c>
+      <c r="GP17" s="1" t="n">
+        <v>8890.620000000001</v>
+      </c>
+      <c r="GQ17" s="1" t="n">
+        <v>104086.85</v>
+      </c>
+      <c r="GR17" s="1" t="n">
+        <v>14622.7</v>
+      </c>
+      <c r="GS17" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="GT17" s="1" t="n">
+        <v>146210.42</v>
+      </c>
+      <c r="GU17" s="1" t="n">
+        <v>4847.69</v>
+      </c>
+      <c r="GV17" s="1" t="n">
+        <v>26281.1</v>
+      </c>
+      <c r="GX17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="GY17" s="1" t="n">
+        <v>13486.37</v>
+      </c>
+      <c r="GZ17" s="1" t="n">
+        <v>241703.6</v>
+      </c>
+      <c r="HA17" s="1" t="n">
+        <v>398.65</v>
+      </c>
+      <c r="HB17" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="HC17" s="1" t="n">
+        <v>44448.08</v>
+      </c>
+      <c r="HD17" s="1" t="n">
+        <v>240.94</v>
+      </c>
+      <c r="HE17" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="HF17" s="1" t="n">
+        <v>27447.41</v>
+      </c>
+      <c r="HG17" s="1" t="n">
+        <v>7884.58</v>
+      </c>
+      <c r="HH17" s="1" t="n">
+        <v>1121</v>
+      </c>
+      <c r="HI17" s="1" t="n">
+        <v>44653.16</v>
+      </c>
+      <c r="HJ17" s="1" t="n">
+        <v>8695.84</v>
+      </c>
+      <c r="HK17" s="1" t="n">
+        <v>38127.14</v>
+      </c>
+      <c r="HL17" s="1" t="n">
+        <v>6926.41</v>
+      </c>
+      <c r="HM17" s="1" t="n">
+        <v>3269.11</v>
+      </c>
+      <c r="HN17" s="1" t="n">
+        <v>69353.35000000001</v>
+      </c>
+      <c r="HO17" s="1" t="n">
+        <v>147790.62</v>
+      </c>
+      <c r="HP17" s="1" t="n">
+        <v>44811.34</v>
+      </c>
+      <c r="HQ17" s="1" t="n">
+        <v>40548.98</v>
+      </c>
+      <c r="HR17" s="1" t="n">
+        <v>4106.48</v>
+      </c>
+      <c r="HS17" s="1" t="n">
+        <v>40586.75</v>
+      </c>
+      <c r="HT17" s="1" t="n">
+        <v>2194.52</v>
+      </c>
+      <c r="HU17" s="1" t="n">
+        <v>20387.48</v>
+      </c>
+      <c r="HV17" s="1" t="n">
+        <v>3314.29</v>
+      </c>
+      <c r="HW17" s="1" t="n">
+        <v>58928.17</v>
+      </c>
+      <c r="HX17" s="1" t="n">
+        <v>72351.75</v>
+      </c>
+      <c r="HY17" s="1" t="n">
+        <v>59091.42</v>
+      </c>
+      <c r="HZ17" s="1" t="n">
+        <v>27187.06</v>
+      </c>
+      <c r="IA17" s="1" t="n">
+        <v>16165.7</v>
+      </c>
+      <c r="IB17" s="1" t="n">
+        <v>241.43</v>
+      </c>
+      <c r="IC17" s="1" t="n">
+        <v>4263.2</v>
+      </c>
+      <c r="ID17" s="1" t="n">
+        <v>49207.59</v>
+      </c>
+      <c r="IE17" s="1" t="n">
+        <v>15678.05</v>
+      </c>
+      <c r="IF17" s="1" t="n">
+        <v>11095.91</v>
+      </c>
+      <c r="IG17" s="1" t="n">
+        <v>102090.16</v>
+      </c>
+      <c r="IH17" s="1" t="n">
+        <v>94527</v>
+      </c>
+      <c r="II17" s="1" t="n">
+        <v>112996.19</v>
+      </c>
+      <c r="IJ17" s="1" t="n">
+        <v>541568.76</v>
+      </c>
+      <c r="IK17" s="1" t="n">
+        <v>810642.39</v>
+      </c>
+      <c r="IL17" s="1" t="n">
+        <v>213703.16</v>
+      </c>
+      <c r="IM17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN17" s="1" t="n">
+        <v>99.73999999999999</v>
+      </c>
+      <c r="IO17" s="1" t="n">
+        <v>74604.60000000001</v>
+      </c>
+      <c r="IP17" s="1" t="n">
+        <v>7855.52</v>
+      </c>
+      <c r="IQ17" s="1" t="n">
+        <v>29892.23</v>
+      </c>
+      <c r="IR17" s="1" t="n">
+        <v>199.34</v>
+      </c>
+      <c r="IS17" s="1" t="n">
+        <v>283.35</v>
+      </c>
+      <c r="IT17" s="1" t="n">
+        <v>54165.38</v>
+      </c>
+      <c r="IU17" s="1" t="n">
+        <v>1170.69</v>
+      </c>
+      <c r="IV17" s="1" t="n">
+        <v>21811.37</v>
+      </c>
+      <c r="IW17" s="1" t="n">
+        <v>5979.98</v>
+      </c>
+      <c r="IX17" s="1" t="n">
+        <v>185298.26</v>
+      </c>
+      <c r="IY17" s="1" t="n">
+        <v>97614.67999999999</v>
+      </c>
+      <c r="IZ17" s="1" t="n">
+        <v>7556.68</v>
+      </c>
+      <c r="JA17" s="1" t="n">
+        <v>11538.3</v>
+      </c>
+      <c r="JB17" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="JC17" s="1" t="n">
+        <v>186277.78</v>
+      </c>
+      <c r="JD17" s="1" t="n">
+        <v>271326.43</v>
+      </c>
+      <c r="JE17" s="1" t="n">
+        <v>199.41</v>
+      </c>
+      <c r="JF17" s="1" t="n">
+        <v>1030.9</v>
+      </c>
+      <c r="JG17" s="1" t="n">
+        <v>22550.88</v>
+      </c>
+      <c r="JH17" s="1" t="n">
+        <v>27867.38</v>
+      </c>
+      <c r="JI17" s="1" t="n">
+        <v>3723.22</v>
+      </c>
+      <c r="JJ17" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="JK17" s="1" t="n">
+        <v>116381.82</v>
+      </c>
+      <c r="JM17" s="1" t="n">
+        <v>2941.76</v>
+      </c>
+      <c r="JN17" s="1" t="n">
+        <v>1356.91</v>
+      </c>
+      <c r="JO17" s="1" t="n">
+        <v>4568.79</v>
+      </c>
+      <c r="JP17" s="1" t="n">
+        <v>25836.2</v>
+      </c>
+      <c r="JQ17" s="1" t="n">
+        <v>398.47</v>
+      </c>
+      <c r="JR17" s="1" t="n">
+        <v>75786.92999999999</v>
+      </c>
+      <c r="JS17" s="1" t="n">
+        <v>243.42</v>
+      </c>
+      <c r="JT17" s="1" t="n">
+        <v>199.44</v>
+      </c>
+      <c r="JU17" s="1" t="n">
+        <v>10902.16</v>
+      </c>
+      <c r="JV17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JX17" s="1" t="n">
+        <v>6206.63</v>
+      </c>
+      <c r="JY17" s="1" t="n">
+        <v>2916.1</v>
+      </c>
+      <c r="JZ17" s="1" t="n">
+        <v>1492264.74</v>
+      </c>
+      <c r="KA17" s="1" t="n">
+        <v>1123.47</v>
+      </c>
+      <c r="KB17" s="1" t="n">
+        <v>1584.64</v>
+      </c>
+      <c r="KC17" s="1" t="n">
+        <v>72167.44</v>
+      </c>
+      <c r="KD17" s="1" t="n">
+        <v>2565.09</v>
+      </c>
+      <c r="KE17" s="1" t="n">
+        <v>274.63</v>
+      </c>
+      <c r="KF17" s="1" t="n">
+        <v>703.1900000000001</v>
+      </c>
+      <c r="KG17" s="1" t="n">
+        <v>6117.71</v>
+      </c>
+      <c r="KH17" s="1" t="n">
+        <v>10114.37</v>
+      </c>
+      <c r="KI17" s="1" t="n">
+        <v>4846.04</v>
+      </c>
+      <c r="KJ17" s="1" t="n">
+        <v>1499899.21</v>
+      </c>
+      <c r="KK17" s="1" t="n">
+        <v>1984.16</v>
+      </c>
+      <c r="KM17" s="1" t="n">
+        <v>172.62</v>
+      </c>
+      <c r="KN17" s="1" t="n">
+        <v>147941.47</v>
+      </c>
+      <c r="KO17" s="1" t="n">
+        <v>386878.41</v>
+      </c>
+      <c r="KP17" s="1" t="n">
+        <v>231.29</v>
+      </c>
+      <c r="KQ17" s="1" t="n">
+        <v>1441.92</v>
+      </c>
+      <c r="KR17" s="1" t="n">
+        <v>5608.33</v>
+      </c>
+      <c r="KS17" s="1" t="n">
+        <v>14233.08</v>
+      </c>
+      <c r="KT17" s="1" t="n">
+        <v>1040.29</v>
+      </c>
+      <c r="KU17" s="1" t="n">
+        <v>33070.94</v>
+      </c>
+      <c r="KV17" s="1" t="n">
+        <v>147.78</v>
+      </c>
+      <c r="KW17" s="1" t="n">
+        <v>69498.12</v>
+      </c>
+      <c r="KX17" s="1" t="n">
+        <v>998.77</v>
+      </c>
+      <c r="KY17" s="1" t="n">
+        <v>739.5</v>
+      </c>
+      <c r="KZ17" s="1" t="n">
+        <v>1309.97</v>
+      </c>
+      <c r="LA17" s="1" t="n">
+        <v>348.05</v>
+      </c>
+      <c r="LB17" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="LC17" s="1" t="n">
+        <v>418.12</v>
+      </c>
+      <c r="LD17" s="1" t="n">
+        <v>129913.2</v>
+      </c>
+      <c r="LE17" s="1" t="n">
+        <v>266.07</v>
+      </c>
+      <c r="LF17" s="1" t="n">
+        <v>1239.78</v>
+      </c>
+      <c r="LG17" s="1" t="n">
+        <v>14477.85</v>
+      </c>
+      <c r="LI17" s="1" t="n">
+        <v>3665.99</v>
+      </c>
+      <c r="LJ17" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="LK17" s="1" t="n">
+        <v>870.84</v>
+      </c>
+      <c r="LL17" s="1" t="n">
+        <v>199.2</v>
+      </c>
+      <c r="LO17" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="LP17" s="1" t="n">
+        <v>285.59</v>
+      </c>
+      <c r="LQ17" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="LR17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LS17" s="1" t="n">
+        <v>40164.99</v>
+      </c>
+      <c r="LT17" s="1" t="n">
+        <v>50896.48</v>
+      </c>
+      <c r="LU17" s="1" t="n">
+        <v>19164.35</v>
+      </c>
+      <c r="LV17" s="1" t="n">
+        <v>74248</v>
+      </c>
+      <c r="LW17" s="1" t="n">
+        <v>59277.46</v>
+      </c>
+      <c r="LX17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LY17" s="1" t="n">
+        <v>28099.22</v>
+      </c>
+      <c r="LZ17" s="1" t="n">
+        <v>34946.92</v>
+      </c>
+      <c r="MA17" s="1" t="n">
+        <v>166062.8</v>
+      </c>
+      <c r="MB17" s="1" t="n">
+        <v>47752.12</v>
+      </c>
+      <c r="MC17" s="1" t="n">
+        <v>63036.5</v>
+      </c>
+      <c r="MD17" s="1" t="n">
+        <v>1344.62</v>
+      </c>
+      <c r="ME17" s="1" t="n">
+        <v>875.95</v>
+      </c>
+      <c r="MF17" s="1" t="n">
+        <v>32765.64</v>
+      </c>
+      <c r="MG17" s="1" t="n">
+        <v>9490.01</v>
+      </c>
+      <c r="MH17" s="1" t="n">
+        <v>3143.51</v>
+      </c>
+      <c r="MI17" s="1" t="n">
+        <v>27982.39</v>
+      </c>
+      <c r="MJ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MK17" s="1" t="n">
+        <v>399</v>
+      </c>
+      <c r="ML17" s="1" t="n">
+        <v>2233.1</v>
+      </c>
+      <c r="MM17" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="MN17" s="1" t="n">
+        <v>398.99</v>
+      </c>
+      <c r="MO17" s="1" t="n">
+        <v>47145.28</v>
+      </c>
+      <c r="MP17" s="1" t="n">
+        <v>10402.07</v>
+      </c>
+      <c r="MQ17" s="1" t="n">
+        <v>1167.29</v>
+      </c>
+      <c r="MR17" s="1" t="n">
+        <v>17850</v>
+      </c>
+      <c r="MS17" s="1" t="n">
+        <v>2742.71</v>
+      </c>
+      <c r="MT17" s="1" t="n">
+        <v>6282.75</v>
+      </c>
+      <c r="MU17" s="1" t="n">
+        <v>26318.05</v>
+      </c>
+      <c r="MV17" s="1" t="n">
+        <v>5676.25</v>
+      </c>
+      <c r="MW17" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="MX17" s="1" t="n">
+        <v>11057.16</v>
+      </c>
+      <c r="MY17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MZ17" s="1" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="NA17" s="1" t="n">
+        <v>572.41</v>
+      </c>
+      <c r="NB17" s="1" t="n">
+        <v>42154.73</v>
+      </c>
+      <c r="NC17" s="1" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="ND17" s="1" t="n">
+        <v>5771.53</v>
+      </c>
+      <c r="NE17" s="1" t="n">
+        <v>4471.21</v>
+      </c>
+      <c r="NF17" s="1" t="n">
+        <v>11595.28</v>
+      </c>
+      <c r="NG17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NH17" s="1" t="n">
+        <v>3554603.43</v>
+      </c>
+      <c r="PB17" s="1" t="n">
+        <v>15445.97</v>
+      </c>
+      <c r="PK17" s="1" t="n">
+        <v>34635.61</v>
+      </c>
+      <c r="PV17" s="1" t="n">
+        <v>2996.67</v>
       </c>
     </row>
   </sheetData>
@@ -20592,7 +21669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW16"/>
+  <dimension ref="A1:BXW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21266,6 +22343,48 @@
       </c>
       <c r="M16" s="1" t="n">
         <v>40373.877824</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>610679011.09</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>57378075.01877</v>
+      </c>
+      <c r="D17" s="1">
+        <f>AVERAGE(C11:C17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>1822550.4695</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>5471211.234</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>1472708.5332</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>761442.0077</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>2222899.8177</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>195184.8717</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>18217.6991</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>38195.439974</v>
       </c>
     </row>
   </sheetData>
@@ -21279,7 +22398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW16"/>
+  <dimension ref="A1:BXW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26602,6 +27721,327 @@
         <v>0</v>
       </c>
       <c r="DB16" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>1243351.248979664</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>3653557.394302025</v>
+      </c>
+      <c r="D17" s="1">
+        <f>AVERAGE(C11:C17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>6917001.92561134</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>25370.01501091</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>150463.1496818284</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>57083.969190482</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>166734.4356868842</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>2533.53</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>12644.1469099597</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>14616.2121364692</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>351.33571</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>1955.7673378047</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>3186</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>5519.2182613057</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="1" t="n">
+        <v>11.016006</v>
+      </c>
+      <c r="AV17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" s="1" t="n">
+        <v>1815.9520657</v>
+      </c>
+      <c r="BJ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" s="1" t="n">
+        <v>456.34021844</v>
+      </c>
+      <c r="CP17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26616,7 +28056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW16"/>
+  <dimension ref="A1:BXW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28479,6 +29919,126 @@
       </c>
       <c r="AM16" s="1" t="n">
         <v>77867.71000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>8928029.439999999</v>
+      </c>
+      <c r="C17" s="1">
+        <f>AVERAGE(B11:B17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>2231042.97</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>1080786.09</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>344387.69</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>2463.73</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>981498.0699999999</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>95492.00999999999</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>147483.89</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>3938.19</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>50839.33</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>48587.86</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>35972.33</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>20104.37</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>5999.68</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>26489.44</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>145513.95</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>4856.24</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>36889.27</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>570</v>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>35095.65</v>
+      </c>
+      <c r="X17" s="1" t="n">
+        <v>17345.3</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>33628</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>10747.01</v>
+      </c>
+      <c r="AA17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="1" t="n">
+        <v>160424.34</v>
+      </c>
+      <c r="AE17" s="1" t="n">
+        <v>1487.3</v>
+      </c>
+      <c r="AF17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="1" t="n">
+        <v>5083.37</v>
+      </c>
+      <c r="AH17" s="1" t="n">
+        <v>4254.64</v>
+      </c>
+      <c r="AI17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="1" t="n">
+        <v>585.85</v>
+      </c>
+      <c r="AK17" s="1" t="n">
+        <v>129508.72</v>
+      </c>
+      <c r="AL17" s="1" t="n">
+        <v>941.36</v>
+      </c>
+      <c r="AM17" s="1" t="n">
+        <v>9998.5</v>
       </c>
     </row>
   </sheetData>

--- a/crypto_volume.xlsx
+++ b/crypto_volume.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>802674486.76</v>
+        <v>593659004.78</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>610679011.09</v>
+        <v>509018831.46</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="I2" s="1" t="n">
-        <v>6917001.92561134</v>
+        <v>6172839.619255594</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="L2" s="1" t="n">
-        <v>8928029.439999999</v>
+        <v>8172085.73</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>186364910.69</v>
+        <v>251396735.47</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>57378075.01877</v>
+        <v>60735421.09402</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -526,15 +526,15 @@
         </is>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3653557.394302025</v>
+        <v>4940024.275329733</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>ETHTHB</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
-        <v>2231042.97</v>
+        <v>3797181.24</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>63297985.81</v>
+        <v>229420778.12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>5471211.234</v>
+        <v>19520106.3651</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -563,15 +563,15 @@
         </is>
       </c>
       <c r="I4" s="1" t="n">
-        <v>1243351.248979664</v>
+        <v>4891661.252085375</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ETHTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1080786.09</v>
+        <v>2599120.01</v>
       </c>
     </row>
     <row r="5">
@@ -580,27 +580,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THB_XRP</t>
+          <t>THB_NEAR</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>43829639.71</v>
+        <v>68941260.34</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VELOTHB</t>
+          <t>XRPTHB</t>
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2222899.8177</v>
+        <v>3545289.5395</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DOGE_THB</t>
+          <t>XRP_THB</t>
         </is>
       </c>
       <c r="I5" s="1" t="n">
-        <v>166734.4356868842</v>
+        <v>352505.4884084313</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="L5" s="1" t="n">
-        <v>981498.0699999999</v>
+        <v>1231200.46</v>
       </c>
     </row>
     <row r="6">
@@ -617,27 +617,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>THB_NEAR</t>
+          <t>THB_XRP</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>27800182.15</v>
+        <v>60364643.44</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>XRPTHB</t>
+          <t>VELOTHB</t>
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1822550.4695</v>
+        <v>2413397.7377</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>XRP_THB</t>
+          <t>XAUT_THB</t>
         </is>
       </c>
       <c r="I6" s="1" t="n">
-        <v>150463.1496818284</v>
+        <v>169942.899</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="L6" s="1" t="n">
-        <v>344387.69</v>
+        <v>797466.3199999999</v>
       </c>
     </row>
     <row r="7"/>
@@ -662,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW17"/>
+  <dimension ref="A1:BXW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21656,6 +21656,1083 @@
       </c>
       <c r="PV17" s="1" t="n">
         <v>2996.67</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>593659004.78</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>251396735.47</v>
+      </c>
+      <c r="D18" s="1">
+        <f>AVERAGE(C12:C18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>229420778.12</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>60364643.44</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>20018807.28</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>27670887.05</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>14892846.21</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>6818331.02</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>4123518.83</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>9692842.02</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>3167493.52</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>68941260.34</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>10512882.62</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>45348.89</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>2525568.34</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>2008747.9</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>4643455.53</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>4576726.15</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>4671439.33</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>88224.92</v>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>3242436.05</v>
+      </c>
+      <c r="Y18" s="1" t="n">
+        <v>79430.13</v>
+      </c>
+      <c r="Z18" s="1" t="n">
+        <v>42772.46</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <v>1189477.57</v>
+      </c>
+      <c r="AB18" s="1" t="n">
+        <v>4193675.59</v>
+      </c>
+      <c r="AC18" s="1" t="n">
+        <v>1005658.07</v>
+      </c>
+      <c r="AD18" s="1" t="n">
+        <v>1855359.93</v>
+      </c>
+      <c r="AE18" s="1" t="n">
+        <v>893576.74</v>
+      </c>
+      <c r="AF18" s="1" t="n">
+        <v>2495921.43</v>
+      </c>
+      <c r="AG18" s="1" t="n">
+        <v>3697326.85</v>
+      </c>
+      <c r="AH18" s="1" t="n">
+        <v>517451.29</v>
+      </c>
+      <c r="AI18" s="1" t="n">
+        <v>2768422.19</v>
+      </c>
+      <c r="AJ18" s="1" t="n">
+        <v>909196.4</v>
+      </c>
+      <c r="AK18" s="1" t="n">
+        <v>301754.17</v>
+      </c>
+      <c r="AL18" s="1" t="n">
+        <v>4031545.24</v>
+      </c>
+      <c r="AN18" s="1" t="n">
+        <v>647089.46</v>
+      </c>
+      <c r="AO18" s="1" t="n">
+        <v>285469.91</v>
+      </c>
+      <c r="AP18" s="1" t="n">
+        <v>774181.45</v>
+      </c>
+      <c r="AQ18" s="1" t="n">
+        <v>1007419.94</v>
+      </c>
+      <c r="AR18" s="1" t="n">
+        <v>2095747.85</v>
+      </c>
+      <c r="AS18" s="1" t="n">
+        <v>132374.17</v>
+      </c>
+      <c r="AT18" s="1" t="n">
+        <v>2823747.69</v>
+      </c>
+      <c r="AU18" s="1" t="n">
+        <v>179370.97</v>
+      </c>
+      <c r="AV18" s="1" t="n">
+        <v>1036335.98</v>
+      </c>
+      <c r="AW18" s="1" t="n">
+        <v>2442794.96</v>
+      </c>
+      <c r="AX18" s="1" t="n">
+        <v>735264.12</v>
+      </c>
+      <c r="AY18" s="1" t="n">
+        <v>199313.06</v>
+      </c>
+      <c r="AZ18" s="1" t="n">
+        <v>312650.35</v>
+      </c>
+      <c r="BA18" s="1" t="n">
+        <v>147083.05</v>
+      </c>
+      <c r="BB18" s="1" t="n">
+        <v>159708.45</v>
+      </c>
+      <c r="BC18" s="1" t="n">
+        <v>792158.24</v>
+      </c>
+      <c r="BD18" s="1" t="n">
+        <v>851083.99</v>
+      </c>
+      <c r="BE18" s="1" t="n">
+        <v>205482.42</v>
+      </c>
+      <c r="BF18" s="1" t="n">
+        <v>1704060.6</v>
+      </c>
+      <c r="BG18" s="1" t="n">
+        <v>55745.18</v>
+      </c>
+      <c r="BI18" s="1" t="n">
+        <v>64270.66</v>
+      </c>
+      <c r="BJ18" s="1" t="n">
+        <v>118577.17</v>
+      </c>
+      <c r="BK18" s="1" t="n">
+        <v>28131.56</v>
+      </c>
+      <c r="BL18" s="1" t="n">
+        <v>8374371.46</v>
+      </c>
+      <c r="BM18" s="1" t="n">
+        <v>558242.87</v>
+      </c>
+      <c r="BN18" s="1" t="n">
+        <v>449178.55</v>
+      </c>
+      <c r="BO18" s="1" t="n">
+        <v>52280.32</v>
+      </c>
+      <c r="BP18" s="1" t="n">
+        <v>6806577.8</v>
+      </c>
+      <c r="BQ18" s="1" t="n">
+        <v>650571.6</v>
+      </c>
+      <c r="BS18" s="1" t="n">
+        <v>455294.08</v>
+      </c>
+      <c r="BT18" s="1" t="n">
+        <v>76345.34</v>
+      </c>
+      <c r="BU18" s="1" t="n">
+        <v>311633.07</v>
+      </c>
+      <c r="BV18" s="1" t="n">
+        <v>2111711.32</v>
+      </c>
+      <c r="BW18" s="1" t="n">
+        <v>167866.82</v>
+      </c>
+      <c r="BX18" s="1" t="n">
+        <v>1210.01</v>
+      </c>
+      <c r="BY18" s="1" t="n">
+        <v>418560.44</v>
+      </c>
+      <c r="BZ18" s="1" t="n">
+        <v>1368382.03</v>
+      </c>
+      <c r="CA18" s="1" t="n">
+        <v>344152.79</v>
+      </c>
+      <c r="CB18" s="1" t="n">
+        <v>17837.57</v>
+      </c>
+      <c r="CC18" s="1" t="n">
+        <v>49176.37</v>
+      </c>
+      <c r="CD18" s="1" t="n">
+        <v>3179368.6</v>
+      </c>
+      <c r="CE18" s="1" t="n">
+        <v>42499.59</v>
+      </c>
+      <c r="CF18" s="1" t="n">
+        <v>894578.3100000001</v>
+      </c>
+      <c r="CG18" s="1" t="n">
+        <v>299853.94</v>
+      </c>
+      <c r="CH18" s="1" t="n">
+        <v>27504.3</v>
+      </c>
+      <c r="CI18" s="1" t="n">
+        <v>54601.47</v>
+      </c>
+      <c r="CJ18" s="1" t="n">
+        <v>586364.1</v>
+      </c>
+      <c r="CK18" s="1" t="n">
+        <v>40370.86</v>
+      </c>
+      <c r="CL18" s="1" t="n">
+        <v>115826.76</v>
+      </c>
+      <c r="CM18" s="1" t="n">
+        <v>36946.12</v>
+      </c>
+      <c r="CN18" s="1" t="n">
+        <v>23992.02</v>
+      </c>
+      <c r="CO18" s="1" t="n">
+        <v>436353.71</v>
+      </c>
+      <c r="CP18" s="1" t="n">
+        <v>44120</v>
+      </c>
+      <c r="CQ18" s="1" t="n">
+        <v>82923.11</v>
+      </c>
+      <c r="CR18" s="1" t="n">
+        <v>5498.68</v>
+      </c>
+      <c r="CS18" s="1" t="n">
+        <v>221995.65</v>
+      </c>
+      <c r="CT18" s="1" t="n">
+        <v>41336.03</v>
+      </c>
+      <c r="CV18" s="1" t="n">
+        <v>653190.66</v>
+      </c>
+      <c r="CW18" s="1" t="n">
+        <v>339073.99</v>
+      </c>
+      <c r="CX18" s="1" t="n">
+        <v>33689.47</v>
+      </c>
+      <c r="CY18" s="1" t="n">
+        <v>147721.15</v>
+      </c>
+      <c r="CZ18" s="1" t="n">
+        <v>246818.42</v>
+      </c>
+      <c r="DA18" s="1" t="n">
+        <v>146516.18</v>
+      </c>
+      <c r="DB18" s="1" t="n">
+        <v>716408.36</v>
+      </c>
+      <c r="DC18" s="1" t="n">
+        <v>17736.23</v>
+      </c>
+      <c r="DD18" s="1" t="n">
+        <v>14487.56</v>
+      </c>
+      <c r="DE18" s="1" t="n">
+        <v>94369.97</v>
+      </c>
+      <c r="DG18" s="1" t="n">
+        <v>29681.34</v>
+      </c>
+      <c r="DH18" s="1" t="n">
+        <v>76780.10000000001</v>
+      </c>
+      <c r="DI18" s="1" t="n">
+        <v>27326.46</v>
+      </c>
+      <c r="DJ18" s="1" t="n">
+        <v>23919.85</v>
+      </c>
+      <c r="DK18" s="1" t="n">
+        <v>147679.3</v>
+      </c>
+      <c r="DL18" s="1" t="n">
+        <v>607.54</v>
+      </c>
+      <c r="DM18" s="1" t="n">
+        <v>107758.77</v>
+      </c>
+      <c r="DN18" s="1" t="n">
+        <v>74412.5</v>
+      </c>
+      <c r="DO18" s="1" t="n">
+        <v>292.98</v>
+      </c>
+      <c r="DP18" s="1" t="n">
+        <v>1354.71</v>
+      </c>
+      <c r="DQ18" s="1" t="n">
+        <v>405514.87</v>
+      </c>
+      <c r="DR18" s="1" t="n">
+        <v>27952.73</v>
+      </c>
+      <c r="DS18" s="1" t="n">
+        <v>71684.67999999999</v>
+      </c>
+      <c r="DT18" s="1" t="n">
+        <v>195854.79</v>
+      </c>
+      <c r="DV18" s="1" t="n">
+        <v>1666550.32</v>
+      </c>
+      <c r="DW18" s="1" t="n">
+        <v>16442.21</v>
+      </c>
+      <c r="DX18" s="1" t="n">
+        <v>450070.39</v>
+      </c>
+      <c r="DY18" s="1" t="n">
+        <v>261.85</v>
+      </c>
+      <c r="DZ18" s="1" t="n">
+        <v>162531.97</v>
+      </c>
+      <c r="EA18" s="1" t="n">
+        <v>127688.84</v>
+      </c>
+      <c r="EB18" s="1" t="n">
+        <v>1293.19</v>
+      </c>
+      <c r="EC18" s="1" t="n">
+        <v>47196.97</v>
+      </c>
+      <c r="ED18" s="1" t="n">
+        <v>189571.55</v>
+      </c>
+      <c r="EE18" s="1" t="n">
+        <v>101613.47</v>
+      </c>
+      <c r="EF18" s="1" t="n">
+        <v>415.93</v>
+      </c>
+      <c r="EG18" s="1" t="n">
+        <v>137203.97</v>
+      </c>
+      <c r="EH18" s="1" t="n">
+        <v>6872.52</v>
+      </c>
+      <c r="EI18" s="1" t="n">
+        <v>50608.74</v>
+      </c>
+      <c r="EJ18" s="1" t="n">
+        <v>1043.36</v>
+      </c>
+      <c r="EK18" s="1" t="n">
+        <v>124700.88</v>
+      </c>
+      <c r="EL18" s="1" t="n">
+        <v>492.25</v>
+      </c>
+      <c r="EM18" s="1" t="n">
+        <v>596.2</v>
+      </c>
+      <c r="EN18" s="1" t="n">
+        <v>499.27</v>
+      </c>
+      <c r="EO18" s="1" t="n">
+        <v>172796.83</v>
+      </c>
+      <c r="EP18" s="1" t="n">
+        <v>1554981.64</v>
+      </c>
+      <c r="EQ18" s="1" t="n">
+        <v>206.47</v>
+      </c>
+      <c r="ER18" s="1" t="n">
+        <v>146361.18</v>
+      </c>
+      <c r="ES18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU18" s="1" t="n">
+        <v>107098.18</v>
+      </c>
+      <c r="EV18" s="1" t="n">
+        <v>20133.34</v>
+      </c>
+      <c r="EX18" s="1" t="n">
+        <v>644153.98</v>
+      </c>
+      <c r="EY18" s="1" t="n">
+        <v>25018.69</v>
+      </c>
+      <c r="EZ18" s="1" t="n">
+        <v>9450.209999999999</v>
+      </c>
+      <c r="FB18" s="1" t="n">
+        <v>3530.68</v>
+      </c>
+      <c r="FC18" s="1" t="n">
+        <v>14667.01</v>
+      </c>
+      <c r="FD18" s="1" t="n">
+        <v>69806.22</v>
+      </c>
+      <c r="FE18" s="1" t="n">
+        <v>241252.47</v>
+      </c>
+      <c r="FF18" s="1" t="n">
+        <v>1140.29</v>
+      </c>
+      <c r="FG18" s="1" t="n">
+        <v>56286.83</v>
+      </c>
+      <c r="FH18" s="1" t="n">
+        <v>63984.06</v>
+      </c>
+      <c r="FI18" s="1" t="n">
+        <v>46400.98</v>
+      </c>
+      <c r="FK18" s="1" t="n">
+        <v>13953.02</v>
+      </c>
+      <c r="FL18" s="1" t="n">
+        <v>13315.62</v>
+      </c>
+      <c r="FM18" s="1" t="n">
+        <v>51414.73</v>
+      </c>
+      <c r="FN18" s="1" t="n">
+        <v>54228.74</v>
+      </c>
+      <c r="FO18" s="1" t="n">
+        <v>797.67</v>
+      </c>
+      <c r="FP18" s="1" t="n">
+        <v>388359.74</v>
+      </c>
+      <c r="FQ18" s="1" t="n">
+        <v>58034.77</v>
+      </c>
+      <c r="FR18" s="1" t="n">
+        <v>121204.35</v>
+      </c>
+      <c r="FS18" s="1" t="n">
+        <v>909113.03</v>
+      </c>
+      <c r="FT18" s="1" t="n">
+        <v>34223.61</v>
+      </c>
+      <c r="FU18" s="1" t="n">
+        <v>9292.290000000001</v>
+      </c>
+      <c r="FV18" s="1" t="n">
+        <v>62555.2</v>
+      </c>
+      <c r="FW18" s="1" t="n">
+        <v>705.8200000000001</v>
+      </c>
+      <c r="FX18" s="1" t="n">
+        <v>39014.76</v>
+      </c>
+      <c r="FY18" s="1" t="n">
+        <v>272774.18</v>
+      </c>
+      <c r="FZ18" s="1" t="n">
+        <v>133626.66</v>
+      </c>
+      <c r="GA18" s="1" t="n">
+        <v>15937.76</v>
+      </c>
+      <c r="GB18" s="1" t="n">
+        <v>146159.89</v>
+      </c>
+      <c r="GC18" s="1" t="n">
+        <v>119071.74</v>
+      </c>
+      <c r="GD18" s="1" t="n">
+        <v>1035.74</v>
+      </c>
+      <c r="GE18" s="1" t="n">
+        <v>292013.66</v>
+      </c>
+      <c r="GF18" s="1" t="n">
+        <v>5045.09</v>
+      </c>
+      <c r="GG18" s="1" t="n">
+        <v>1399.76</v>
+      </c>
+      <c r="GH18" s="1" t="n">
+        <v>403828.85</v>
+      </c>
+      <c r="GI18" s="1" t="n">
+        <v>82012.23</v>
+      </c>
+      <c r="GJ18" s="1" t="n">
+        <v>43291.35</v>
+      </c>
+      <c r="GK18" s="1" t="n">
+        <v>324870.24</v>
+      </c>
+      <c r="GL18" s="1" t="n">
+        <v>6924.01</v>
+      </c>
+      <c r="GM18" s="1" t="n">
+        <v>752066.58</v>
+      </c>
+      <c r="GN18" s="1" t="n">
+        <v>129953.44</v>
+      </c>
+      <c r="GO18" s="1" t="n">
+        <v>20971.27</v>
+      </c>
+      <c r="GP18" s="1" t="n">
+        <v>21560.06</v>
+      </c>
+      <c r="GQ18" s="1" t="n">
+        <v>36007.59</v>
+      </c>
+      <c r="GR18" s="1" t="n">
+        <v>3361.33</v>
+      </c>
+      <c r="GS18" s="1" t="n">
+        <v>3214.68</v>
+      </c>
+      <c r="GT18" s="1" t="n">
+        <v>1083165.49</v>
+      </c>
+      <c r="GU18" s="1" t="n">
+        <v>17034.65</v>
+      </c>
+      <c r="GV18" s="1" t="n">
+        <v>81413.25999999999</v>
+      </c>
+      <c r="GX18" s="1" t="n">
+        <v>177.01</v>
+      </c>
+      <c r="GY18" s="1" t="n">
+        <v>394752.66</v>
+      </c>
+      <c r="GZ18" s="1" t="n">
+        <v>21846.14</v>
+      </c>
+      <c r="HA18" s="1" t="n">
+        <v>2667.67</v>
+      </c>
+      <c r="HB18" s="1" t="n">
+        <v>244.57</v>
+      </c>
+      <c r="HC18" s="1" t="n">
+        <v>1865.82</v>
+      </c>
+      <c r="HD18" s="1" t="n">
+        <v>1834.39</v>
+      </c>
+      <c r="HE18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF18" s="1" t="n">
+        <v>7191.59</v>
+      </c>
+      <c r="HG18" s="1" t="n">
+        <v>10066.8</v>
+      </c>
+      <c r="HH18" s="1" t="n">
+        <v>182064.56</v>
+      </c>
+      <c r="HI18" s="1" t="n">
+        <v>25195.93</v>
+      </c>
+      <c r="HJ18" s="1" t="n">
+        <v>1194.75</v>
+      </c>
+      <c r="HK18" s="1" t="n">
+        <v>30833.93</v>
+      </c>
+      <c r="HL18" s="1" t="n">
+        <v>29324.65</v>
+      </c>
+      <c r="HM18" s="1" t="n">
+        <v>213.42</v>
+      </c>
+      <c r="HN18" s="1" t="n">
+        <v>86164.64999999999</v>
+      </c>
+      <c r="HO18" s="1" t="n">
+        <v>40337.13</v>
+      </c>
+      <c r="HP18" s="1" t="n">
+        <v>94388.50999999999</v>
+      </c>
+      <c r="HQ18" s="1" t="n">
+        <v>41297.24</v>
+      </c>
+      <c r="HR18" s="1" t="n">
+        <v>801.4</v>
+      </c>
+      <c r="HS18" s="1" t="n">
+        <v>43873.44</v>
+      </c>
+      <c r="HT18" s="1" t="n">
+        <v>2573.69</v>
+      </c>
+      <c r="HU18" s="1" t="n">
+        <v>4272.29</v>
+      </c>
+      <c r="HV18" s="1" t="n">
+        <v>9612.940000000001</v>
+      </c>
+      <c r="HW18" s="1" t="n">
+        <v>45550.6</v>
+      </c>
+      <c r="HX18" s="1" t="n">
+        <v>48363.75</v>
+      </c>
+      <c r="HY18" s="1" t="n">
+        <v>125593.62</v>
+      </c>
+      <c r="HZ18" s="1" t="n">
+        <v>4477.23</v>
+      </c>
+      <c r="IA18" s="1" t="n">
+        <v>116816.06</v>
+      </c>
+      <c r="IB18" s="1" t="n">
+        <v>7385.08</v>
+      </c>
+      <c r="IC18" s="1" t="n">
+        <v>23218.85</v>
+      </c>
+      <c r="ID18" s="1" t="n">
+        <v>594.11</v>
+      </c>
+      <c r="IE18" s="1" t="n">
+        <v>12965.48</v>
+      </c>
+      <c r="IF18" s="1" t="n">
+        <v>925.89</v>
+      </c>
+      <c r="IG18" s="1" t="n">
+        <v>93145.35000000001</v>
+      </c>
+      <c r="IH18" s="1" t="n">
+        <v>11258.83</v>
+      </c>
+      <c r="II18" s="1" t="n">
+        <v>89112.78</v>
+      </c>
+      <c r="IJ18" s="1" t="n">
+        <v>661400.6</v>
+      </c>
+      <c r="IK18" s="1" t="n">
+        <v>904154.85</v>
+      </c>
+      <c r="IL18" s="1" t="n">
+        <v>65635.05</v>
+      </c>
+      <c r="IM18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="IN18" s="1" t="n">
+        <v>3003.39</v>
+      </c>
+      <c r="IO18" s="1" t="n">
+        <v>14373.62</v>
+      </c>
+      <c r="IP18" s="1" t="n">
+        <v>35391.94</v>
+      </c>
+      <c r="IQ18" s="1" t="n">
+        <v>10869.95</v>
+      </c>
+      <c r="IR18" s="1" t="n">
+        <v>206.65</v>
+      </c>
+      <c r="IS18" s="1" t="n">
+        <v>92.28</v>
+      </c>
+      <c r="IT18" s="1" t="n">
+        <v>62704.45</v>
+      </c>
+      <c r="IU18" s="1" t="n">
+        <v>51812.45</v>
+      </c>
+      <c r="IV18" s="1" t="n">
+        <v>44319.42</v>
+      </c>
+      <c r="IW18" s="1" t="n">
+        <v>19426.06</v>
+      </c>
+      <c r="IX18" s="1" t="n">
+        <v>175704.06</v>
+      </c>
+      <c r="IY18" s="1" t="n">
+        <v>40391.64</v>
+      </c>
+      <c r="IZ18" s="1" t="n">
+        <v>638.1799999999999</v>
+      </c>
+      <c r="JA18" s="1" t="n">
+        <v>12123.91</v>
+      </c>
+      <c r="JB18" s="1" t="n">
+        <v>299.33</v>
+      </c>
+      <c r="JC18" s="1" t="n">
+        <v>38436.13</v>
+      </c>
+      <c r="JD18" s="1" t="n">
+        <v>286853.97</v>
+      </c>
+      <c r="JE18" s="1" t="n">
+        <v>405.08</v>
+      </c>
+      <c r="JF18" s="1" t="n">
+        <v>12085.74</v>
+      </c>
+      <c r="JG18" s="1" t="n">
+        <v>188402.45</v>
+      </c>
+      <c r="JH18" s="1" t="n">
+        <v>999.3200000000001</v>
+      </c>
+      <c r="JI18" s="1" t="n">
+        <v>1217.2</v>
+      </c>
+      <c r="JJ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="JK18" s="1" t="n">
+        <v>75610.61</v>
+      </c>
+      <c r="JM18" s="1" t="n">
+        <v>2746.92</v>
+      </c>
+      <c r="JN18" s="1" t="n">
+        <v>2923.46</v>
+      </c>
+      <c r="JO18" s="1" t="n">
+        <v>62577.61</v>
+      </c>
+      <c r="JP18" s="1" t="n">
+        <v>6278.28</v>
+      </c>
+      <c r="JQ18" s="1" t="n">
+        <v>2877.92</v>
+      </c>
+      <c r="JR18" s="1" t="n">
+        <v>75301.77</v>
+      </c>
+      <c r="JS18" s="1" t="n">
+        <v>27771.98</v>
+      </c>
+      <c r="JT18" s="1" t="n">
+        <v>593.53</v>
+      </c>
+      <c r="JU18" s="1" t="n">
+        <v>76713.5</v>
+      </c>
+      <c r="JV18" s="1" t="n">
+        <v>7344.81</v>
+      </c>
+      <c r="JX18" s="1" t="n">
+        <v>5012.41</v>
+      </c>
+      <c r="JY18" s="1" t="n">
+        <v>13761.25</v>
+      </c>
+      <c r="JZ18" s="1" t="n">
+        <v>1811621.2</v>
+      </c>
+      <c r="KA18" s="1" t="n">
+        <v>31303.86</v>
+      </c>
+      <c r="KB18" s="1" t="n">
+        <v>28807</v>
+      </c>
+      <c r="KC18" s="1" t="n">
+        <v>15978.59</v>
+      </c>
+      <c r="KD18" s="1" t="n">
+        <v>405.22</v>
+      </c>
+      <c r="KE18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="KF18" s="1" t="n">
+        <v>6306.58</v>
+      </c>
+      <c r="KG18" s="1" t="n">
+        <v>2262.05</v>
+      </c>
+      <c r="KH18" s="1" t="n">
+        <v>5350.44</v>
+      </c>
+      <c r="KI18" s="1" t="n">
+        <v>4770.69</v>
+      </c>
+      <c r="KJ18" s="1" t="n">
+        <v>92676.36</v>
+      </c>
+      <c r="KK18" s="1" t="n">
+        <v>1984.16</v>
+      </c>
+      <c r="KM18" s="1" t="n">
+        <v>13415.01</v>
+      </c>
+      <c r="KN18" s="1" t="n">
+        <v>462321.33</v>
+      </c>
+      <c r="KO18" s="1" t="n">
+        <v>2387.27</v>
+      </c>
+      <c r="KP18" s="1" t="n">
+        <v>10670.45</v>
+      </c>
+      <c r="KQ18" s="1" t="n">
+        <v>518.54</v>
+      </c>
+      <c r="KR18" s="1" t="n">
+        <v>193574.8</v>
+      </c>
+      <c r="KS18" s="1" t="n">
+        <v>40802.46</v>
+      </c>
+      <c r="KT18" s="1" t="n">
+        <v>1006.27</v>
+      </c>
+      <c r="KU18" s="1" t="n">
+        <v>18783.11</v>
+      </c>
+      <c r="KV18" s="1" t="n">
+        <v>907.16</v>
+      </c>
+      <c r="KW18" s="1" t="n">
+        <v>17754.64</v>
+      </c>
+      <c r="KX18" s="1" t="n">
+        <v>12614.46</v>
+      </c>
+      <c r="KY18" s="1" t="n">
+        <v>2765.15</v>
+      </c>
+      <c r="KZ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="LA18" s="1" t="n">
+        <v>189.61</v>
+      </c>
+      <c r="LB18" s="1" t="n">
+        <v>398.51</v>
+      </c>
+      <c r="LC18" s="1" t="n">
+        <v>1153.06</v>
+      </c>
+      <c r="LD18" s="1" t="n">
+        <v>4586.78</v>
+      </c>
+      <c r="LE18" s="1" t="n">
+        <v>11076.12</v>
+      </c>
+      <c r="LF18" s="1" t="n">
+        <v>795.8</v>
+      </c>
+      <c r="LG18" s="1" t="n">
+        <v>1059.99</v>
+      </c>
+      <c r="LI18" s="1" t="n">
+        <v>3115.35</v>
+      </c>
+      <c r="LJ18" s="1" t="n">
+        <v>5378.78</v>
+      </c>
+      <c r="LK18" s="1" t="n">
+        <v>1681.67</v>
+      </c>
+      <c r="LL18" s="1" t="n">
+        <v>594.77</v>
+      </c>
+      <c r="LO18" s="1" t="n">
+        <v>401.77</v>
+      </c>
+      <c r="LP18" s="1" t="n">
+        <v>410.97</v>
+      </c>
+      <c r="LQ18" s="1" t="n">
+        <v>12125.8</v>
+      </c>
+      <c r="LR18" s="1" t="n">
+        <v>1412.89</v>
+      </c>
+      <c r="LS18" s="1" t="n">
+        <v>38842.39</v>
+      </c>
+      <c r="LT18" s="1" t="n">
+        <v>7853.8</v>
+      </c>
+      <c r="LU18" s="1" t="n">
+        <v>401.31</v>
+      </c>
+      <c r="LV18" s="1" t="n">
+        <v>98770.56</v>
+      </c>
+      <c r="LW18" s="1" t="n">
+        <v>38556.81</v>
+      </c>
+      <c r="LX18" s="1" t="n">
+        <v>147.85</v>
+      </c>
+      <c r="LY18" s="1" t="n">
+        <v>49458.65</v>
+      </c>
+      <c r="LZ18" s="1" t="n">
+        <v>179836.14</v>
+      </c>
+      <c r="MA18" s="1" t="n">
+        <v>81798.61</v>
+      </c>
+      <c r="MB18" s="1" t="n">
+        <v>199.49</v>
+      </c>
+      <c r="MC18" s="1" t="n">
+        <v>3824.19</v>
+      </c>
+      <c r="MD18" s="1" t="n">
+        <v>770.47</v>
+      </c>
+      <c r="ME18" s="1" t="n">
+        <v>1992.94</v>
+      </c>
+      <c r="MF18" s="1" t="n">
+        <v>31231.62</v>
+      </c>
+      <c r="MG18" s="1" t="n">
+        <v>10906.98</v>
+      </c>
+      <c r="MH18" s="1" t="n">
+        <v>1815</v>
+      </c>
+      <c r="MI18" s="1" t="n">
+        <v>45192.35</v>
+      </c>
+      <c r="MJ18" s="1" t="n">
+        <v>2794.31</v>
+      </c>
+      <c r="MK18" s="1" t="n">
+        <v>1224.55</v>
+      </c>
+      <c r="ML18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="MM18" s="1" t="n">
+        <v>1195.04</v>
+      </c>
+      <c r="MN18" s="1" t="n">
+        <v>1189.38</v>
+      </c>
+      <c r="MO18" s="1" t="n">
+        <v>1183.02</v>
+      </c>
+      <c r="MP18" s="1" t="n">
+        <v>14003.8</v>
+      </c>
+      <c r="MQ18" s="1" t="n">
+        <v>792.98</v>
+      </c>
+      <c r="MR18" s="1" t="n">
+        <v>8646.360000000001</v>
+      </c>
+      <c r="MS18" s="1" t="n">
+        <v>836.64</v>
+      </c>
+      <c r="MT18" s="1" t="n">
+        <v>2570.04</v>
+      </c>
+      <c r="MU18" s="1" t="n">
+        <v>67070.17</v>
+      </c>
+      <c r="MV18" s="1" t="n">
+        <v>161.44</v>
+      </c>
+      <c r="MW18" s="1" t="n">
+        <v>1299.25</v>
+      </c>
+      <c r="MX18" s="1" t="n">
+        <v>783.8</v>
+      </c>
+      <c r="MY18" s="1" t="n">
+        <v>247.45</v>
+      </c>
+      <c r="MZ18" s="1" t="n">
+        <v>4656.19</v>
+      </c>
+      <c r="NA18" s="1" t="n">
+        <v>4139.33</v>
+      </c>
+      <c r="NB18" s="1" t="n">
+        <v>296.09</v>
+      </c>
+      <c r="NC18" s="1" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="ND18" s="1" t="n">
+        <v>5666.34</v>
+      </c>
+      <c r="NE18" s="1" t="n">
+        <v>95.93000000000001</v>
+      </c>
+      <c r="NF18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="NG18" s="1" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="NH18" s="1" t="n">
+        <v>4149061.58</v>
+      </c>
+      <c r="PB18" s="1" t="n">
+        <v>227.75</v>
+      </c>
+      <c r="PK18" s="1" t="n">
+        <v>103.08</v>
+      </c>
+      <c r="PV18" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21669,7 +22746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW17"/>
+  <dimension ref="A1:BXW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22385,6 +23462,48 @@
       </c>
       <c r="M17" s="1" t="n">
         <v>38195.439974</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>509018831.46</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>60735421.09402</v>
+      </c>
+      <c r="D18" s="1">
+        <f>AVERAGE(C12:C18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>3545289.5395</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>19520106.3651</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>1756296.1492</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>385442.7953</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>2413397.7377</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>160367.715</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>6564.9655</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>1730.63616</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>228841.241468</v>
       </c>
     </row>
   </sheetData>
@@ -22398,7 +23517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW17"/>
+  <dimension ref="A1:BXW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28042,6 +29161,327 @@
         <v>0</v>
       </c>
       <c r="DB17" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>4891661.252085375</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>4940024.275329733</v>
+      </c>
+      <c r="D18" s="1">
+        <f>AVERAGE(C12:C18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>6172839.619255594</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>21400.3735676792</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>352505.4884084313</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>128518.3294745238</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>142264.9065473579</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>3989.328546021</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>41406.3011756105</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>265.146</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>2043.8102241583</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>48.0438</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>8613.9882</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>169942.899</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>3032.1885413079</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="1" t="n">
+        <v>2293.8639139926</v>
+      </c>
+      <c r="AV18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" s="1" t="n">
+        <v>1004.83145645</v>
+      </c>
+      <c r="BJ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" s="1" t="n">
+        <v>10764.73598721</v>
+      </c>
+      <c r="CP18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB18" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28056,7 +29496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BXW17"/>
+  <dimension ref="A1:BXW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30039,6 +31479,126 @@
       </c>
       <c r="AM17" s="1" t="n">
         <v>9998.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>8172085.73</v>
+      </c>
+      <c r="C18" s="1">
+        <f>AVERAGE(B12:B18)</f>
+        <v/>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>2599120.01</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>3797181.24</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>797466.3199999999</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>4019.77</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>1231200.46</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>123068.91</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>152064.4</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>78520.27</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>116046.53</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>8467.49</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>20606.9</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>16790.24</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>1534.02</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>37746.75</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>20664.61</v>
+      </c>
+      <c r="T18" s="1" t="n">
+        <v>25471.98</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>7995.24</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>680073.28</v>
+      </c>
+      <c r="X18" s="1" t="n">
+        <v>20511.74</v>
+      </c>
+      <c r="Y18" s="1" t="n">
+        <v>14834.77</v>
+      </c>
+      <c r="Z18" s="1" t="n">
+        <v>2968.95</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="1" t="n">
+        <v>849.77</v>
+      </c>
+      <c r="AD18" s="1" t="n">
+        <v>46344.11</v>
+      </c>
+      <c r="AE18" s="1" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AF18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="1" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="AH18" s="1" t="n">
+        <v>504.85</v>
+      </c>
+      <c r="AI18" s="1" t="n">
+        <v>864.34</v>
+      </c>
+      <c r="AJ18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="1" t="n">
+        <v>62404.85</v>
+      </c>
+      <c r="AL18" s="1" t="n">
+        <v>1503.83</v>
+      </c>
+      <c r="AM18" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
